--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -35200,35 +35200,35 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C669" t="n">
-        <v>323.5</v>
+        <v>489.8</v>
       </c>
       <c r="D669" t="n">
-        <v>361.43</v>
+        <v>471.66</v>
       </c>
       <c r="E669" t="n">
-        <v>-37.93</v>
+        <v>18.14</v>
       </c>
       <c r="F669" t="n">
-        <v>324.8</v>
+        <v>511.95</v>
       </c>
       <c r="G669" t="n">
-        <v>361.43</v>
+        <v>501.29</v>
       </c>
       <c r="H669" t="n">
-        <v>-36.63</v>
+        <v>10.66</v>
       </c>
       <c r="I669" t="n">
-        <v>316.05</v>
+        <v>485.4</v>
       </c>
       <c r="J669" t="n">
-        <v>318.96</v>
+        <v>480.38</v>
       </c>
       <c r="K669" t="n">
-        <v>-2.91</v>
+        <v>5.02</v>
       </c>
       <c r="L669" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         </is>
       </c>
       <c r="N669" t="n">
-        <v>10.49</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="670">
@@ -35252,35 +35252,35 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C670" t="n">
-        <v>489.8</v>
+        <v>323.5</v>
       </c>
       <c r="D670" t="n">
-        <v>512.71</v>
+        <v>291.87</v>
       </c>
       <c r="E670" t="n">
-        <v>-22.91</v>
+        <v>31.63</v>
       </c>
       <c r="F670" t="n">
-        <v>511.95</v>
+        <v>324.8</v>
       </c>
       <c r="G670" t="n">
-        <v>512.71</v>
+        <v>327.66</v>
       </c>
       <c r="H670" t="n">
-        <v>-0.76</v>
+        <v>-2.86</v>
       </c>
       <c r="I670" t="n">
-        <v>485.4</v>
+        <v>316.05</v>
       </c>
       <c r="J670" t="n">
-        <v>483.68</v>
+        <v>313.87</v>
       </c>
       <c r="K670" t="n">
-        <v>1.72</v>
+        <v>2.18</v>
       </c>
       <c r="L670" t="inlineStr">
         <is>
@@ -35293,7 +35293,7 @@
         </is>
       </c>
       <c r="N670" t="n">
-        <v>4.47</v>
+        <v>10.84</v>
       </c>
     </row>
     <row r="671">
@@ -35311,28 +35311,28 @@
         <v>3276</v>
       </c>
       <c r="D671" t="n">
-        <v>2650.75</v>
+        <v>4081.14</v>
       </c>
       <c r="E671" t="n">
-        <v>625.25</v>
+        <v>-805.14</v>
       </c>
       <c r="F671" t="n">
         <v>3389</v>
       </c>
       <c r="G671" t="n">
-        <v>3293.11</v>
+        <v>4081.14</v>
       </c>
       <c r="H671" t="n">
-        <v>95.89</v>
+        <v>-692.14</v>
       </c>
       <c r="I671" t="n">
         <v>3247.2</v>
       </c>
       <c r="J671" t="n">
-        <v>3254.88</v>
+        <v>3222.36</v>
       </c>
       <c r="K671" t="n">
-        <v>-7.68</v>
+        <v>24.84</v>
       </c>
       <c r="L671" t="inlineStr">
         <is>
@@ -35341,11 +35341,11 @@
       </c>
       <c r="M671" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N671" t="n">
-        <v>23.59</v>
+        <v>19.73</v>
       </c>
     </row>
     <row r="672">
@@ -35356,48 +35356,48 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C672" t="n">
-        <v>1026.5</v>
+        <v>431</v>
       </c>
       <c r="D672" t="n">
-        <v>957.6</v>
+        <v>433.19</v>
       </c>
       <c r="E672" t="n">
-        <v>68.90000000000001</v>
+        <v>-2.19</v>
       </c>
       <c r="F672" t="n">
-        <v>1030.7</v>
+        <v>433</v>
       </c>
       <c r="G672" t="n">
-        <v>1021.74</v>
+        <v>443.36</v>
       </c>
       <c r="H672" t="n">
-        <v>8.960000000000001</v>
+        <v>-10.36</v>
       </c>
       <c r="I672" t="n">
-        <v>988</v>
+        <v>418.2</v>
       </c>
       <c r="J672" t="n">
-        <v>1009.53</v>
+        <v>424.93</v>
       </c>
       <c r="K672" t="n">
-        <v>-21.53</v>
+        <v>-6.73</v>
       </c>
       <c r="L672" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="M672" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N672" t="n">
-        <v>7.2</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="673">
@@ -35415,28 +35415,28 @@
         <v>2153.5</v>
       </c>
       <c r="D673" t="n">
-        <v>2159.29</v>
+        <v>2164.91</v>
       </c>
       <c r="E673" t="n">
-        <v>-5.79</v>
+        <v>-11.41</v>
       </c>
       <c r="F673" t="n">
         <v>2176.2</v>
       </c>
       <c r="G673" t="n">
-        <v>2162.34</v>
+        <v>2209.5</v>
       </c>
       <c r="H673" t="n">
-        <v>13.86</v>
+        <v>-33.3</v>
       </c>
       <c r="I673" t="n">
         <v>2109.8</v>
       </c>
       <c r="J673" t="n">
-        <v>2137.15</v>
+        <v>2117.49</v>
       </c>
       <c r="K673" t="n">
-        <v>-27.35</v>
+        <v>-7.69</v>
       </c>
       <c r="L673" t="inlineStr">
         <is>
@@ -35449,7 +35449,7 @@
         </is>
       </c>
       <c r="N673" t="n">
-        <v>0.27</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="674">
@@ -35460,35 +35460,35 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C674" t="n">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="D674" t="n">
-        <v>432.25</v>
+        <v>413.48</v>
       </c>
       <c r="E674" t="n">
-        <v>-1.25</v>
+        <v>5.52</v>
       </c>
       <c r="F674" t="n">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="G674" t="n">
-        <v>434.29</v>
+        <v>427.84</v>
       </c>
       <c r="H674" t="n">
-        <v>-1.29</v>
+        <v>-7.84</v>
       </c>
       <c r="I674" t="n">
-        <v>418.2</v>
+        <v>409.25</v>
       </c>
       <c r="J674" t="n">
-        <v>429.28</v>
+        <v>409.96</v>
       </c>
       <c r="K674" t="n">
-        <v>-11.08</v>
+        <v>-0.71</v>
       </c>
       <c r="L674" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         </is>
       </c>
       <c r="N674" t="n">
-        <v>0.29</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="675">
@@ -35512,35 +35512,35 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C675" t="n">
-        <v>116.75</v>
+        <v>562.9</v>
       </c>
       <c r="D675" t="n">
-        <v>118.63</v>
+        <v>572.1900000000001</v>
       </c>
       <c r="E675" t="n">
-        <v>-1.88</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="F675" t="n">
-        <v>117.79</v>
+        <v>572.35</v>
       </c>
       <c r="G675" t="n">
-        <v>118.63</v>
+        <v>572.1900000000001</v>
       </c>
       <c r="H675" t="n">
-        <v>-0.84</v>
+        <v>0.16</v>
       </c>
       <c r="I675" t="n">
-        <v>114.52</v>
+        <v>546</v>
       </c>
       <c r="J675" t="n">
-        <v>115.96</v>
+        <v>542.64</v>
       </c>
       <c r="K675" t="n">
-        <v>-1.44</v>
+        <v>3.36</v>
       </c>
       <c r="L675" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         </is>
       </c>
       <c r="N675" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="676">
@@ -35564,35 +35564,35 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C676" t="n">
-        <v>419</v>
+        <v>287.2</v>
       </c>
       <c r="D676" t="n">
-        <v>427.99</v>
+        <v>296.54</v>
       </c>
       <c r="E676" t="n">
-        <v>-8.99</v>
+        <v>-9.34</v>
       </c>
       <c r="F676" t="n">
-        <v>420</v>
+        <v>287.2</v>
       </c>
       <c r="G676" t="n">
-        <v>427.99</v>
+        <v>296.54</v>
       </c>
       <c r="H676" t="n">
-        <v>-7.99</v>
+        <v>-9.34</v>
       </c>
       <c r="I676" t="n">
-        <v>409.25</v>
+        <v>283.85</v>
       </c>
       <c r="J676" t="n">
-        <v>413.81</v>
+        <v>280.56</v>
       </c>
       <c r="K676" t="n">
-        <v>-4.56</v>
+        <v>3.29</v>
       </c>
       <c r="L676" t="inlineStr">
         <is>
@@ -35605,7 +35605,7 @@
         </is>
       </c>
       <c r="N676" t="n">
-        <v>2.1</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="677">
@@ -35616,35 +35616,35 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C677" t="n">
-        <v>287.2</v>
+        <v>116.75</v>
       </c>
       <c r="D677" t="n">
-        <v>280.38</v>
+        <v>115.81</v>
       </c>
       <c r="E677" t="n">
-        <v>6.82</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F677" t="n">
-        <v>287.2</v>
+        <v>117.79</v>
       </c>
       <c r="G677" t="n">
-        <v>286.38</v>
+        <v>120.07</v>
       </c>
       <c r="H677" t="n">
-        <v>0.82</v>
+        <v>-2.28</v>
       </c>
       <c r="I677" t="n">
-        <v>283.85</v>
+        <v>114.52</v>
       </c>
       <c r="J677" t="n">
-        <v>282.97</v>
+        <v>115.23</v>
       </c>
       <c r="K677" t="n">
-        <v>0.88</v>
+        <v>-0.71</v>
       </c>
       <c r="L677" t="inlineStr">
         <is>
@@ -35657,7 +35657,7 @@
         </is>
       </c>
       <c r="N677" t="n">
-        <v>2.43</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="678">
@@ -35668,35 +35668,35 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C678" t="n">
-        <v>1797.3</v>
+        <v>1026.5</v>
       </c>
       <c r="D678" t="n">
-        <v>1820.18</v>
+        <v>1109.16</v>
       </c>
       <c r="E678" t="n">
-        <v>-22.88</v>
+        <v>-82.66</v>
       </c>
       <c r="F678" t="n">
-        <v>1813.3</v>
+        <v>1030.7</v>
       </c>
       <c r="G678" t="n">
-        <v>1820.18</v>
+        <v>1109.16</v>
       </c>
       <c r="H678" t="n">
-        <v>-6.88</v>
+        <v>-78.45999999999999</v>
       </c>
       <c r="I678" t="n">
-        <v>1757.3</v>
+        <v>988</v>
       </c>
       <c r="J678" t="n">
-        <v>1783.33</v>
+        <v>1002.1</v>
       </c>
       <c r="K678" t="n">
-        <v>-26.03</v>
+        <v>-14.1</v>
       </c>
       <c r="L678" t="inlineStr">
         <is>
@@ -35709,7 +35709,7 @@
         </is>
       </c>
       <c r="N678" t="n">
-        <v>1.26</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="679">
@@ -35720,35 +35720,35 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C679" t="n">
-        <v>562.9</v>
+        <v>1797.3</v>
       </c>
       <c r="D679" t="n">
-        <v>558.1900000000001</v>
+        <v>1788.91</v>
       </c>
       <c r="E679" t="n">
-        <v>4.71</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="F679" t="n">
-        <v>572.35</v>
+        <v>1813.3</v>
       </c>
       <c r="G679" t="n">
-        <v>558.1900000000001</v>
+        <v>1845.46</v>
       </c>
       <c r="H679" t="n">
-        <v>14.16</v>
+        <v>-32.16</v>
       </c>
       <c r="I679" t="n">
-        <v>546</v>
+        <v>1757.3</v>
       </c>
       <c r="J679" t="n">
-        <v>547.52</v>
+        <v>1768.66</v>
       </c>
       <c r="K679" t="n">
-        <v>-1.52</v>
+        <v>-11.36</v>
       </c>
       <c r="L679" t="inlineStr">
         <is>
@@ -35761,7 +35761,7 @@
         </is>
       </c>
       <c r="N679" t="n">
-        <v>0.84</v>
+        <v>0.47</v>
       </c>
     </row>
   </sheetData>
@@ -41009,28 +41009,28 @@
         <v>323.5</v>
       </c>
       <c r="D29" t="n">
-        <v>361.43</v>
+        <v>291.87</v>
       </c>
       <c r="E29" t="n">
-        <v>-37.93</v>
+        <v>31.63</v>
       </c>
       <c r="F29" t="n">
         <v>324.8</v>
       </c>
       <c r="G29" t="n">
-        <v>361.43</v>
+        <v>327.66</v>
       </c>
       <c r="H29" t="n">
-        <v>-36.63</v>
+        <v>-2.86</v>
       </c>
       <c r="I29" t="n">
         <v>316.05</v>
       </c>
       <c r="J29" t="n">
-        <v>318.96</v>
+        <v>313.87</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.91</v>
+        <v>2.18</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -41043,7 +41043,7 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>10.49</v>
+        <v>10.84</v>
       </c>
     </row>
   </sheetData>
@@ -45877,28 +45877,28 @@
         <v>116.75</v>
       </c>
       <c r="D28" t="n">
-        <v>118.63</v>
+        <v>115.81</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F28" t="n">
         <v>117.79</v>
       </c>
       <c r="G28" t="n">
-        <v>118.63</v>
+        <v>120.07</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.84</v>
+        <v>-2.28</v>
       </c>
       <c r="I28" t="n">
         <v>114.52</v>
       </c>
       <c r="J28" t="n">
-        <v>115.96</v>
+        <v>115.23</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.44</v>
+        <v>-0.71</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -45911,7 +45911,7 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.58</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N679"/>
+  <dimension ref="A1:N685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35762,6 +35762,318 @@
       </c>
       <c r="N679" t="n">
         <v>0.47</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C680" t="n">
+        <v>485.6</v>
+      </c>
+      <c r="D680" t="n">
+        <v>508.32</v>
+      </c>
+      <c r="E680" t="n">
+        <v>-22.72</v>
+      </c>
+      <c r="F680" t="n">
+        <v>494.4</v>
+      </c>
+      <c r="G680" t="n">
+        <v>508.32</v>
+      </c>
+      <c r="H680" t="n">
+        <v>-13.92</v>
+      </c>
+      <c r="I680" t="n">
+        <v>483</v>
+      </c>
+      <c r="J680" t="n">
+        <v>484.69</v>
+      </c>
+      <c r="K680" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="L680" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M680" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N680" t="n">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C681" t="n">
+        <v>2119.3</v>
+      </c>
+      <c r="D681" t="n">
+        <v>2124.99</v>
+      </c>
+      <c r="E681" t="n">
+        <v>-5.69</v>
+      </c>
+      <c r="F681" t="n">
+        <v>2160</v>
+      </c>
+      <c r="G681" t="n">
+        <v>2124.99</v>
+      </c>
+      <c r="H681" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="I681" t="n">
+        <v>2107.7</v>
+      </c>
+      <c r="J681" t="n">
+        <v>2071.16</v>
+      </c>
+      <c r="K681" t="n">
+        <v>36.54</v>
+      </c>
+      <c r="L681" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M681" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N681" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C682" t="n">
+        <v>409.8</v>
+      </c>
+      <c r="D682" t="n">
+        <v>418.59</v>
+      </c>
+      <c r="E682" t="n">
+        <v>-8.789999999999999</v>
+      </c>
+      <c r="F682" t="n">
+        <v>420.5</v>
+      </c>
+      <c r="G682" t="n">
+        <v>418.59</v>
+      </c>
+      <c r="H682" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="I682" t="n">
+        <v>409.8</v>
+      </c>
+      <c r="J682" t="n">
+        <v>403.32</v>
+      </c>
+      <c r="K682" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="L682" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M682" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N682" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C683" t="n">
+        <v>3173.5</v>
+      </c>
+      <c r="D683" t="n">
+        <v>2567.81</v>
+      </c>
+      <c r="E683" t="n">
+        <v>605.6900000000001</v>
+      </c>
+      <c r="F683" t="n">
+        <v>3267.6</v>
+      </c>
+      <c r="G683" t="n">
+        <v>3170.33</v>
+      </c>
+      <c r="H683" t="n">
+        <v>97.27</v>
+      </c>
+      <c r="I683" t="n">
+        <v>3156.4</v>
+      </c>
+      <c r="J683" t="n">
+        <v>3153.81</v>
+      </c>
+      <c r="K683" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M683" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N683" t="n">
+        <v>23.59</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C684" t="n">
+        <v>990.8</v>
+      </c>
+      <c r="D684" t="n">
+        <v>924.3</v>
+      </c>
+      <c r="E684" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="F684" t="n">
+        <v>1030</v>
+      </c>
+      <c r="G684" t="n">
+        <v>975.54</v>
+      </c>
+      <c r="H684" t="n">
+        <v>54.46</v>
+      </c>
+      <c r="I684" t="n">
+        <v>985.1</v>
+      </c>
+      <c r="J684" t="n">
+        <v>969.96</v>
+      </c>
+      <c r="K684" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M684" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N684" t="n">
+        <v>7.19</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C685" t="n">
+        <v>542</v>
+      </c>
+      <c r="D685" t="n">
+        <v>537.47</v>
+      </c>
+      <c r="E685" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="F685" t="n">
+        <v>565.25</v>
+      </c>
+      <c r="G685" t="n">
+        <v>537.47</v>
+      </c>
+      <c r="H685" t="n">
+        <v>27.78</v>
+      </c>
+      <c r="I685" t="n">
+        <v>538.5</v>
+      </c>
+      <c r="J685" t="n">
+        <v>526.5599999999999</v>
+      </c>
+      <c r="K685" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="L685" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M685" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N685" t="n">
+        <v>0.84</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -35776,31 +35776,31 @@
         </is>
       </c>
       <c r="C680" t="n">
-        <v>485.6</v>
+        <v>489.8</v>
       </c>
       <c r="D680" t="n">
         <v>508.32</v>
       </c>
       <c r="E680" t="n">
-        <v>-22.72</v>
+        <v>-18.52</v>
       </c>
       <c r="F680" t="n">
-        <v>494.4</v>
+        <v>511.95</v>
       </c>
       <c r="G680" t="n">
         <v>508.32</v>
       </c>
       <c r="H680" t="n">
-        <v>-13.92</v>
+        <v>3.63</v>
       </c>
       <c r="I680" t="n">
-        <v>483</v>
+        <v>485.4</v>
       </c>
       <c r="J680" t="n">
         <v>484.69</v>
       </c>
       <c r="K680" t="n">
-        <v>-1.69</v>
+        <v>0.71</v>
       </c>
       <c r="L680" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         </is>
       </c>
       <c r="N680" t="n">
-        <v>4.47</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="681">
@@ -35828,31 +35828,31 @@
         </is>
       </c>
       <c r="C681" t="n">
-        <v>2119.3</v>
+        <v>2153.5</v>
       </c>
       <c r="D681" t="n">
         <v>2124.99</v>
       </c>
       <c r="E681" t="n">
-        <v>-5.69</v>
+        <v>28.51</v>
       </c>
       <c r="F681" t="n">
-        <v>2160</v>
+        <v>2176.2</v>
       </c>
       <c r="G681" t="n">
         <v>2124.99</v>
       </c>
       <c r="H681" t="n">
-        <v>35.01</v>
+        <v>51.21</v>
       </c>
       <c r="I681" t="n">
-        <v>2107.7</v>
+        <v>2109.8</v>
       </c>
       <c r="J681" t="n">
         <v>2071.16</v>
       </c>
       <c r="K681" t="n">
-        <v>36.54</v>
+        <v>38.64</v>
       </c>
       <c r="L681" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         </is>
       </c>
       <c r="N681" t="n">
-        <v>0.27</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="682">
@@ -35880,31 +35880,31 @@
         </is>
       </c>
       <c r="C682" t="n">
-        <v>409.8</v>
+        <v>419</v>
       </c>
       <c r="D682" t="n">
         <v>418.59</v>
       </c>
       <c r="E682" t="n">
-        <v>-8.789999999999999</v>
+        <v>0.41</v>
       </c>
       <c r="F682" t="n">
-        <v>420.5</v>
+        <v>420</v>
       </c>
       <c r="G682" t="n">
         <v>418.59</v>
       </c>
       <c r="H682" t="n">
-        <v>1.91</v>
+        <v>1.41</v>
       </c>
       <c r="I682" t="n">
-        <v>409.8</v>
+        <v>409.25</v>
       </c>
       <c r="J682" t="n">
         <v>403.32</v>
       </c>
       <c r="K682" t="n">
-        <v>6.48</v>
+        <v>5.93</v>
       </c>
       <c r="L682" t="inlineStr">
         <is>
@@ -35917,7 +35917,7 @@
         </is>
       </c>
       <c r="N682" t="n">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="683">
@@ -35932,31 +35932,31 @@
         </is>
       </c>
       <c r="C683" t="n">
-        <v>3173.5</v>
+        <v>3276</v>
       </c>
       <c r="D683" t="n">
         <v>2567.81</v>
       </c>
       <c r="E683" t="n">
-        <v>605.6900000000001</v>
+        <v>708.1900000000001</v>
       </c>
       <c r="F683" t="n">
-        <v>3267.6</v>
+        <v>3389</v>
       </c>
       <c r="G683" t="n">
         <v>3170.33</v>
       </c>
       <c r="H683" t="n">
-        <v>97.27</v>
+        <v>218.67</v>
       </c>
       <c r="I683" t="n">
-        <v>3156.4</v>
+        <v>3247.2</v>
       </c>
       <c r="J683" t="n">
         <v>3153.81</v>
       </c>
       <c r="K683" t="n">
-        <v>2.59</v>
+        <v>93.39</v>
       </c>
       <c r="L683" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         </is>
       </c>
       <c r="N683" t="n">
-        <v>23.59</v>
+        <v>27.58</v>
       </c>
     </row>
     <row r="684">
@@ -35984,31 +35984,31 @@
         </is>
       </c>
       <c r="C684" t="n">
-        <v>990.8</v>
+        <v>1026.5</v>
       </c>
       <c r="D684" t="n">
         <v>924.3</v>
       </c>
       <c r="E684" t="n">
-        <v>66.5</v>
+        <v>102.2</v>
       </c>
       <c r="F684" t="n">
-        <v>1030</v>
+        <v>1030.7</v>
       </c>
       <c r="G684" t="n">
         <v>975.54</v>
       </c>
       <c r="H684" t="n">
-        <v>54.46</v>
+        <v>55.16</v>
       </c>
       <c r="I684" t="n">
-        <v>985.1</v>
+        <v>988</v>
       </c>
       <c r="J684" t="n">
         <v>969.96</v>
       </c>
       <c r="K684" t="n">
-        <v>15.14</v>
+        <v>18.04</v>
       </c>
       <c r="L684" t="inlineStr">
         <is>
@@ -36021,7 +36021,7 @@
         </is>
       </c>
       <c r="N684" t="n">
-        <v>7.19</v>
+        <v>11.06</v>
       </c>
     </row>
     <row r="685">
@@ -36036,31 +36036,31 @@
         </is>
       </c>
       <c r="C685" t="n">
-        <v>542</v>
+        <v>562.9</v>
       </c>
       <c r="D685" t="n">
         <v>537.47</v>
       </c>
       <c r="E685" t="n">
-        <v>4.53</v>
+        <v>25.43</v>
       </c>
       <c r="F685" t="n">
-        <v>565.25</v>
+        <v>572.35</v>
       </c>
       <c r="G685" t="n">
         <v>537.47</v>
       </c>
       <c r="H685" t="n">
-        <v>27.78</v>
+        <v>34.88</v>
       </c>
       <c r="I685" t="n">
-        <v>538.5</v>
+        <v>546</v>
       </c>
       <c r="J685" t="n">
         <v>526.5599999999999</v>
       </c>
       <c r="K685" t="n">
-        <v>11.94</v>
+        <v>19.44</v>
       </c>
       <c r="L685" t="inlineStr">
         <is>
@@ -36069,11 +36069,11 @@
       </c>
       <c r="M685" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N685" t="n">
-        <v>0.84</v>
+        <v>4.73</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N685"/>
+  <dimension ref="A1:N692"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36074,6 +36074,370 @@
       </c>
       <c r="N685" t="n">
         <v>4.73</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C686" t="n">
+        <v>487.6</v>
+      </c>
+      <c r="D686" t="n">
+        <v>473.59</v>
+      </c>
+      <c r="E686" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="F686" t="n">
+        <v>489.5</v>
+      </c>
+      <c r="G686" t="n">
+        <v>507.49</v>
+      </c>
+      <c r="H686" t="n">
+        <v>-17.99</v>
+      </c>
+      <c r="I686" t="n">
+        <v>481.4</v>
+      </c>
+      <c r="J686" t="n">
+        <v>487.1</v>
+      </c>
+      <c r="K686" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="L686" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M686" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N686" t="n">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C687" t="n">
+        <v>415</v>
+      </c>
+      <c r="D687" t="n">
+        <v>418.73</v>
+      </c>
+      <c r="E687" t="n">
+        <v>-3.73</v>
+      </c>
+      <c r="F687" t="n">
+        <v>417.05</v>
+      </c>
+      <c r="G687" t="n">
+        <v>434.81</v>
+      </c>
+      <c r="H687" t="n">
+        <v>-17.76</v>
+      </c>
+      <c r="I687" t="n">
+        <v>409.35</v>
+      </c>
+      <c r="J687" t="n">
+        <v>415</v>
+      </c>
+      <c r="K687" t="n">
+        <v>-5.65</v>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M687" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N687" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C688" t="n">
+        <v>1827.1</v>
+      </c>
+      <c r="D688" t="n">
+        <v>1932.24</v>
+      </c>
+      <c r="E688" t="n">
+        <v>-105.14</v>
+      </c>
+      <c r="F688" t="n">
+        <v>1847</v>
+      </c>
+      <c r="G688" t="n">
+        <v>1947.92</v>
+      </c>
+      <c r="H688" t="n">
+        <v>-100.92</v>
+      </c>
+      <c r="I688" t="n">
+        <v>1710.1</v>
+      </c>
+      <c r="J688" t="n">
+        <v>1827.1</v>
+      </c>
+      <c r="K688" t="n">
+        <v>-117</v>
+      </c>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M688" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N688" t="n">
+        <v>5.44</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C689" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="D689" t="n">
+        <v>121.96</v>
+      </c>
+      <c r="E689" t="n">
+        <v>-5.16</v>
+      </c>
+      <c r="F689" t="n">
+        <v>117.48</v>
+      </c>
+      <c r="G689" t="n">
+        <v>122.72</v>
+      </c>
+      <c r="H689" t="n">
+        <v>-5.24</v>
+      </c>
+      <c r="I689" t="n">
+        <v>114.63</v>
+      </c>
+      <c r="J689" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="K689" t="n">
+        <v>-2.17</v>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M689" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N689" t="n">
+        <v>4.23</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C690" t="n">
+        <v>3211.2</v>
+      </c>
+      <c r="D690" t="n">
+        <v>4129.62</v>
+      </c>
+      <c r="E690" t="n">
+        <v>-918.42</v>
+      </c>
+      <c r="F690" t="n">
+        <v>3224.5</v>
+      </c>
+      <c r="G690" t="n">
+        <v>4129.62</v>
+      </c>
+      <c r="H690" t="n">
+        <v>-905.12</v>
+      </c>
+      <c r="I690" t="n">
+        <v>3056.6</v>
+      </c>
+      <c r="J690" t="n">
+        <v>3181.06</v>
+      </c>
+      <c r="K690" t="n">
+        <v>-124.46</v>
+      </c>
+      <c r="L690" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M690" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N690" t="n">
+        <v>22.24</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C691" t="n">
+        <v>543</v>
+      </c>
+      <c r="D691" t="n">
+        <v>573.23</v>
+      </c>
+      <c r="E691" t="n">
+        <v>-30.23</v>
+      </c>
+      <c r="F691" t="n">
+        <v>551.45</v>
+      </c>
+      <c r="G691" t="n">
+        <v>573.23</v>
+      </c>
+      <c r="H691" t="n">
+        <v>-21.78</v>
+      </c>
+      <c r="I691" t="n">
+        <v>529.6</v>
+      </c>
+      <c r="J691" t="n">
+        <v>542.7</v>
+      </c>
+      <c r="K691" t="n">
+        <v>-13.1</v>
+      </c>
+      <c r="L691" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M691" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N691" t="n">
+        <v>5.27</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C692" t="n">
+        <v>976.5</v>
+      </c>
+      <c r="D692" t="n">
+        <v>1093.15</v>
+      </c>
+      <c r="E692" t="n">
+        <v>-116.65</v>
+      </c>
+      <c r="F692" t="n">
+        <v>989.9</v>
+      </c>
+      <c r="G692" t="n">
+        <v>1093.15</v>
+      </c>
+      <c r="H692" t="n">
+        <v>-103.25</v>
+      </c>
+      <c r="I692" t="n">
+        <v>963.8</v>
+      </c>
+      <c r="J692" t="n">
+        <v>974.96</v>
+      </c>
+      <c r="K692" t="n">
+        <v>-11.16</v>
+      </c>
+      <c r="L692" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M692" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N692" t="n">
+        <v>10.67</v>
       </c>
     </row>
   </sheetData>
@@ -44747,7 +45111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46224,6 +46588,58 @@
       </c>
       <c r="N28" t="n">
         <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="D29" t="n">
+        <v>121.96</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-5.16</v>
+      </c>
+      <c r="F29" t="n">
+        <v>117.48</v>
+      </c>
+      <c r="G29" t="n">
+        <v>122.72</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-5.24</v>
+      </c>
+      <c r="I29" t="n">
+        <v>114.63</v>
+      </c>
+      <c r="J29" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-2.17</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>4.23</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -36088,31 +36088,31 @@
         </is>
       </c>
       <c r="C686" t="n">
-        <v>487.6</v>
+        <v>485.6</v>
       </c>
       <c r="D686" t="n">
         <v>473.59</v>
       </c>
       <c r="E686" t="n">
-        <v>14.01</v>
+        <v>12.01</v>
       </c>
       <c r="F686" t="n">
-        <v>489.5</v>
+        <v>494.4</v>
       </c>
       <c r="G686" t="n">
         <v>507.49</v>
       </c>
       <c r="H686" t="n">
-        <v>-17.99</v>
+        <v>-13.09</v>
       </c>
       <c r="I686" t="n">
-        <v>481.4</v>
+        <v>483</v>
       </c>
       <c r="J686" t="n">
         <v>487.1</v>
       </c>
       <c r="K686" t="n">
-        <v>-5.7</v>
+        <v>-4.1</v>
       </c>
       <c r="L686" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         </is>
       </c>
       <c r="N686" t="n">
-        <v>2.96</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="687">
@@ -36140,31 +36140,31 @@
         </is>
       </c>
       <c r="C687" t="n">
-        <v>415</v>
+        <v>409.8</v>
       </c>
       <c r="D687" t="n">
         <v>418.73</v>
       </c>
       <c r="E687" t="n">
-        <v>-3.73</v>
+        <v>-8.93</v>
       </c>
       <c r="F687" t="n">
-        <v>417.05</v>
+        <v>420.5</v>
       </c>
       <c r="G687" t="n">
         <v>434.81</v>
       </c>
       <c r="H687" t="n">
-        <v>-17.76</v>
+        <v>-14.31</v>
       </c>
       <c r="I687" t="n">
-        <v>409.35</v>
+        <v>409.8</v>
       </c>
       <c r="J687" t="n">
         <v>415</v>
       </c>
       <c r="K687" t="n">
-        <v>-5.65</v>
+        <v>-5.2</v>
       </c>
       <c r="L687" t="inlineStr">
         <is>
@@ -36177,7 +36177,7 @@
         </is>
       </c>
       <c r="N687" t="n">
-        <v>0.89</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="688">
@@ -36192,31 +36192,31 @@
         </is>
       </c>
       <c r="C688" t="n">
-        <v>1827.1</v>
+        <v>1736</v>
       </c>
       <c r="D688" t="n">
         <v>1932.24</v>
       </c>
       <c r="E688" t="n">
-        <v>-105.14</v>
+        <v>-196.24</v>
       </c>
       <c r="F688" t="n">
-        <v>1847</v>
+        <v>1804.3</v>
       </c>
       <c r="G688" t="n">
         <v>1947.92</v>
       </c>
       <c r="H688" t="n">
-        <v>-100.92</v>
+        <v>-143.62</v>
       </c>
       <c r="I688" t="n">
-        <v>1710.1</v>
+        <v>1736</v>
       </c>
       <c r="J688" t="n">
         <v>1827.1</v>
       </c>
       <c r="K688" t="n">
-        <v>-117</v>
+        <v>-91.09999999999999</v>
       </c>
       <c r="L688" t="inlineStr">
         <is>
@@ -36229,7 +36229,7 @@
         </is>
       </c>
       <c r="N688" t="n">
-        <v>5.44</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="689">
@@ -36244,31 +36244,31 @@
         </is>
       </c>
       <c r="C689" t="n">
-        <v>116.8</v>
+        <v>114.7</v>
       </c>
       <c r="D689" t="n">
         <v>121.96</v>
       </c>
       <c r="E689" t="n">
-        <v>-5.16</v>
+        <v>-7.26</v>
       </c>
       <c r="F689" t="n">
-        <v>117.48</v>
+        <v>117.23</v>
       </c>
       <c r="G689" t="n">
         <v>122.72</v>
       </c>
       <c r="H689" t="n">
-        <v>-5.24</v>
+        <v>-5.49</v>
       </c>
       <c r="I689" t="n">
-        <v>114.63</v>
+        <v>114.7</v>
       </c>
       <c r="J689" t="n">
         <v>116.8</v>
       </c>
       <c r="K689" t="n">
-        <v>-2.17</v>
+        <v>-2.1</v>
       </c>
       <c r="L689" t="inlineStr">
         <is>
@@ -36281,7 +36281,7 @@
         </is>
       </c>
       <c r="N689" t="n">
-        <v>4.23</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="690">
@@ -36296,31 +36296,31 @@
         </is>
       </c>
       <c r="C690" t="n">
-        <v>3211.2</v>
+        <v>3173.5</v>
       </c>
       <c r="D690" t="n">
         <v>4129.62</v>
       </c>
       <c r="E690" t="n">
-        <v>-918.42</v>
+        <v>-956.12</v>
       </c>
       <c r="F690" t="n">
-        <v>3224.5</v>
+        <v>3267.6</v>
       </c>
       <c r="G690" t="n">
         <v>4129.62</v>
       </c>
       <c r="H690" t="n">
-        <v>-905.12</v>
+        <v>-862.02</v>
       </c>
       <c r="I690" t="n">
-        <v>3056.6</v>
+        <v>3156.4</v>
       </c>
       <c r="J690" t="n">
         <v>3181.06</v>
       </c>
       <c r="K690" t="n">
-        <v>-124.46</v>
+        <v>-24.66</v>
       </c>
       <c r="L690" t="inlineStr">
         <is>
@@ -36329,11 +36329,11 @@
       </c>
       <c r="M690" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N690" t="n">
-        <v>22.24</v>
+        <v>23.15</v>
       </c>
     </row>
     <row r="691">
@@ -36348,31 +36348,31 @@
         </is>
       </c>
       <c r="C691" t="n">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D691" t="n">
         <v>573.23</v>
       </c>
       <c r="E691" t="n">
-        <v>-30.23</v>
+        <v>-31.23</v>
       </c>
       <c r="F691" t="n">
-        <v>551.45</v>
+        <v>565.25</v>
       </c>
       <c r="G691" t="n">
         <v>573.23</v>
       </c>
       <c r="H691" t="n">
-        <v>-21.78</v>
+        <v>-7.98</v>
       </c>
       <c r="I691" t="n">
-        <v>529.6</v>
+        <v>538.5</v>
       </c>
       <c r="J691" t="n">
         <v>542.7</v>
       </c>
       <c r="K691" t="n">
-        <v>-13.1</v>
+        <v>-4.2</v>
       </c>
       <c r="L691" t="inlineStr">
         <is>
@@ -36381,11 +36381,11 @@
       </c>
       <c r="M691" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N691" t="n">
-        <v>5.27</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="692">
@@ -36400,31 +36400,31 @@
         </is>
       </c>
       <c r="C692" t="n">
-        <v>976.5</v>
+        <v>990.8</v>
       </c>
       <c r="D692" t="n">
         <v>1093.15</v>
       </c>
       <c r="E692" t="n">
-        <v>-116.65</v>
+        <v>-102.35</v>
       </c>
       <c r="F692" t="n">
-        <v>989.9</v>
+        <v>1030</v>
       </c>
       <c r="G692" t="n">
         <v>1093.15</v>
       </c>
       <c r="H692" t="n">
-        <v>-103.25</v>
+        <v>-63.15</v>
       </c>
       <c r="I692" t="n">
-        <v>963.8</v>
+        <v>985.1</v>
       </c>
       <c r="J692" t="n">
         <v>974.96</v>
       </c>
       <c r="K692" t="n">
-        <v>-11.16</v>
+        <v>10.14</v>
       </c>
       <c r="L692" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         </is>
       </c>
       <c r="N692" t="n">
-        <v>10.67</v>
+        <v>9.359999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -46602,31 +46602,31 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>116.8</v>
+        <v>114.7</v>
       </c>
       <c r="D29" t="n">
         <v>121.96</v>
       </c>
       <c r="E29" t="n">
-        <v>-5.16</v>
+        <v>-7.26</v>
       </c>
       <c r="F29" t="n">
-        <v>117.48</v>
+        <v>117.23</v>
       </c>
       <c r="G29" t="n">
         <v>122.72</v>
       </c>
       <c r="H29" t="n">
-        <v>-5.24</v>
+        <v>-5.49</v>
       </c>
       <c r="I29" t="n">
-        <v>114.63</v>
+        <v>114.7</v>
       </c>
       <c r="J29" t="n">
         <v>116.8</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.17</v>
+        <v>-2.1</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -46639,7 +46639,7 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>4.23</v>
+        <v>5.95</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N692"/>
+  <dimension ref="A1:N699"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36438,6 +36438,370 @@
       </c>
       <c r="N692" t="n">
         <v>9.359999999999999</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C693" t="n">
+        <v>3265.2</v>
+      </c>
+      <c r="D693" t="n">
+        <v>2542.81</v>
+      </c>
+      <c r="E693" t="n">
+        <v>722.39</v>
+      </c>
+      <c r="F693" t="n">
+        <v>3304</v>
+      </c>
+      <c r="G693" t="n">
+        <v>3212.2</v>
+      </c>
+      <c r="H693" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="I693" t="n">
+        <v>3180.1</v>
+      </c>
+      <c r="J693" t="n">
+        <v>3215.78</v>
+      </c>
+      <c r="K693" t="n">
+        <v>-35.68</v>
+      </c>
+      <c r="L693" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M693" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N693" t="n">
+        <v>28.41</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C694" t="n">
+        <v>322.35</v>
+      </c>
+      <c r="D694" t="n">
+        <v>300.73</v>
+      </c>
+      <c r="E694" t="n">
+        <v>21.62</v>
+      </c>
+      <c r="F694" t="n">
+        <v>327.8</v>
+      </c>
+      <c r="G694" t="n">
+        <v>313.49</v>
+      </c>
+      <c r="H694" t="n">
+        <v>14.31</v>
+      </c>
+      <c r="I694" t="n">
+        <v>318.25</v>
+      </c>
+      <c r="J694" t="n">
+        <v>313.71</v>
+      </c>
+      <c r="K694" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="L694" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M694" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N694" t="n">
+        <v>7.19</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C695" t="n">
+        <v>545.9</v>
+      </c>
+      <c r="D695" t="n">
+        <v>520.29</v>
+      </c>
+      <c r="E695" t="n">
+        <v>25.61</v>
+      </c>
+      <c r="F695" t="n">
+        <v>554.55</v>
+      </c>
+      <c r="G695" t="n">
+        <v>525.98</v>
+      </c>
+      <c r="H695" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="I695" t="n">
+        <v>541.05</v>
+      </c>
+      <c r="J695" t="n">
+        <v>526.17</v>
+      </c>
+      <c r="K695" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="L695" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M695" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N695" t="n">
+        <v>4.92</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C696" t="n">
+        <v>988.7</v>
+      </c>
+      <c r="D696" t="n">
+        <v>903.71</v>
+      </c>
+      <c r="E696" t="n">
+        <v>84.98999999999999</v>
+      </c>
+      <c r="F696" t="n">
+        <v>1004.8</v>
+      </c>
+      <c r="G696" t="n">
+        <v>968</v>
+      </c>
+      <c r="H696" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="I696" t="n">
+        <v>976.5</v>
+      </c>
+      <c r="J696" t="n">
+        <v>968.92</v>
+      </c>
+      <c r="K696" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="L696" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M696" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N696" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C697" t="n">
+        <v>2148.5</v>
+      </c>
+      <c r="D697" t="n">
+        <v>2004.41</v>
+      </c>
+      <c r="E697" t="n">
+        <v>144.09</v>
+      </c>
+      <c r="F697" t="n">
+        <v>2170</v>
+      </c>
+      <c r="G697" t="n">
+        <v>2068.25</v>
+      </c>
+      <c r="H697" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="I697" t="n">
+        <v>2110</v>
+      </c>
+      <c r="J697" t="n">
+        <v>2068.96</v>
+      </c>
+      <c r="K697" t="n">
+        <v>41.04</v>
+      </c>
+      <c r="L697" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M697" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N697" t="n">
+        <v>7.19</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C698" t="n">
+        <v>416.5</v>
+      </c>
+      <c r="D698" t="n">
+        <v>410.88</v>
+      </c>
+      <c r="E698" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="F698" t="n">
+        <v>417.6</v>
+      </c>
+      <c r="G698" t="n">
+        <v>410.88</v>
+      </c>
+      <c r="H698" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="I698" t="n">
+        <v>412.5</v>
+      </c>
+      <c r="J698" t="n">
+        <v>407.2</v>
+      </c>
+      <c r="K698" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L698" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M698" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N698" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C699" t="n">
+        <v>116.47</v>
+      </c>
+      <c r="D699" t="n">
+        <v>110.41</v>
+      </c>
+      <c r="E699" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="F699" t="n">
+        <v>119.4</v>
+      </c>
+      <c r="G699" t="n">
+        <v>112.41</v>
+      </c>
+      <c r="H699" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="I699" t="n">
+        <v>116.36</v>
+      </c>
+      <c r="J699" t="n">
+        <v>112.46</v>
+      </c>
+      <c r="K699" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L699" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M699" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N699" t="n">
+        <v>5.49</v>
       </c>
     </row>
   </sheetData>
@@ -40191,7 +40555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41720,6 +42084,58 @@
       </c>
       <c r="N29" t="n">
         <v>10.84</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>322.35</v>
+      </c>
+      <c r="D30" t="n">
+        <v>300.73</v>
+      </c>
+      <c r="E30" t="n">
+        <v>21.62</v>
+      </c>
+      <c r="F30" t="n">
+        <v>327.8</v>
+      </c>
+      <c r="G30" t="n">
+        <v>313.49</v>
+      </c>
+      <c r="H30" t="n">
+        <v>14.31</v>
+      </c>
+      <c r="I30" t="n">
+        <v>318.25</v>
+      </c>
+      <c r="J30" t="n">
+        <v>313.71</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>7.19</v>
       </c>
     </row>
   </sheetData>
@@ -45111,7 +45527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46640,6 +47056,58 @@
       </c>
       <c r="N29" t="n">
         <v>5.95</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>116.47</v>
+      </c>
+      <c r="D30" t="n">
+        <v>110.41</v>
+      </c>
+      <c r="E30" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="F30" t="n">
+        <v>119.4</v>
+      </c>
+      <c r="G30" t="n">
+        <v>112.41</v>
+      </c>
+      <c r="H30" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="I30" t="n">
+        <v>116.36</v>
+      </c>
+      <c r="J30" t="n">
+        <v>112.46</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>5.49</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -36452,31 +36452,31 @@
         </is>
       </c>
       <c r="C693" t="n">
-        <v>3265.2</v>
+        <v>3211.2</v>
       </c>
       <c r="D693" t="n">
         <v>2542.81</v>
       </c>
       <c r="E693" t="n">
-        <v>722.39</v>
+        <v>668.39</v>
       </c>
       <c r="F693" t="n">
-        <v>3304</v>
+        <v>3224.5</v>
       </c>
       <c r="G693" t="n">
         <v>3212.2</v>
       </c>
       <c r="H693" t="n">
-        <v>91.8</v>
+        <v>12.3</v>
       </c>
       <c r="I693" t="n">
-        <v>3180.1</v>
+        <v>3056.6</v>
       </c>
       <c r="J693" t="n">
         <v>3215.78</v>
       </c>
       <c r="K693" t="n">
-        <v>-35.68</v>
+        <v>-159.18</v>
       </c>
       <c r="L693" t="inlineStr">
         <is>
@@ -36489,7 +36489,7 @@
         </is>
       </c>
       <c r="N693" t="n">
-        <v>28.41</v>
+        <v>26.29</v>
       </c>
     </row>
     <row r="694">
@@ -36504,31 +36504,31 @@
         </is>
       </c>
       <c r="C694" t="n">
-        <v>322.35</v>
+        <v>317</v>
       </c>
       <c r="D694" t="n">
         <v>300.73</v>
       </c>
       <c r="E694" t="n">
-        <v>21.62</v>
+        <v>16.27</v>
       </c>
       <c r="F694" t="n">
-        <v>327.8</v>
+        <v>318.35</v>
       </c>
       <c r="G694" t="n">
         <v>313.49</v>
       </c>
       <c r="H694" t="n">
-        <v>14.31</v>
+        <v>4.86</v>
       </c>
       <c r="I694" t="n">
-        <v>318.25</v>
+        <v>310.8</v>
       </c>
       <c r="J694" t="n">
         <v>313.71</v>
       </c>
       <c r="K694" t="n">
-        <v>4.54</v>
+        <v>-2.91</v>
       </c>
       <c r="L694" t="inlineStr">
         <is>
@@ -36537,11 +36537,11 @@
       </c>
       <c r="M694" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N694" t="n">
-        <v>7.19</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="695">
@@ -36556,31 +36556,31 @@
         </is>
       </c>
       <c r="C695" t="n">
-        <v>545.9</v>
+        <v>543</v>
       </c>
       <c r="D695" t="n">
         <v>520.29</v>
       </c>
       <c r="E695" t="n">
-        <v>25.61</v>
+        <v>22.71</v>
       </c>
       <c r="F695" t="n">
-        <v>554.55</v>
+        <v>551.45</v>
       </c>
       <c r="G695" t="n">
         <v>525.98</v>
       </c>
       <c r="H695" t="n">
-        <v>28.57</v>
+        <v>25.47</v>
       </c>
       <c r="I695" t="n">
-        <v>541.05</v>
+        <v>529.6</v>
       </c>
       <c r="J695" t="n">
         <v>526.17</v>
       </c>
       <c r="K695" t="n">
-        <v>14.88</v>
+        <v>3.43</v>
       </c>
       <c r="L695" t="inlineStr">
         <is>
@@ -36593,7 +36593,7 @@
         </is>
       </c>
       <c r="N695" t="n">
-        <v>4.92</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="696">
@@ -36608,31 +36608,31 @@
         </is>
       </c>
       <c r="C696" t="n">
-        <v>988.7</v>
+        <v>976.5</v>
       </c>
       <c r="D696" t="n">
         <v>903.71</v>
       </c>
       <c r="E696" t="n">
-        <v>84.98999999999999</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="F696" t="n">
-        <v>1004.8</v>
+        <v>989.9</v>
       </c>
       <c r="G696" t="n">
         <v>968</v>
       </c>
       <c r="H696" t="n">
-        <v>36.8</v>
+        <v>21.9</v>
       </c>
       <c r="I696" t="n">
-        <v>976.5</v>
+        <v>963.8</v>
       </c>
       <c r="J696" t="n">
         <v>968.92</v>
       </c>
       <c r="K696" t="n">
-        <v>7.58</v>
+        <v>-5.12</v>
       </c>
       <c r="L696" t="inlineStr">
         <is>
@@ -36641,11 +36641,11 @@
       </c>
       <c r="M696" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N696" t="n">
-        <v>9.4</v>
+        <v>8.050000000000001</v>
       </c>
     </row>
     <row r="697">
@@ -36660,31 +36660,31 @@
         </is>
       </c>
       <c r="C697" t="n">
-        <v>2148.5</v>
+        <v>2120</v>
       </c>
       <c r="D697" t="n">
         <v>2004.41</v>
       </c>
       <c r="E697" t="n">
-        <v>144.09</v>
+        <v>115.59</v>
       </c>
       <c r="F697" t="n">
-        <v>2170</v>
+        <v>2132.9</v>
       </c>
       <c r="G697" t="n">
         <v>2068.25</v>
       </c>
       <c r="H697" t="n">
-        <v>101.75</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="I697" t="n">
-        <v>2110</v>
+        <v>2041.3</v>
       </c>
       <c r="J697" t="n">
         <v>2068.96</v>
       </c>
       <c r="K697" t="n">
-        <v>41.04</v>
+        <v>-27.66</v>
       </c>
       <c r="L697" t="inlineStr">
         <is>
@@ -36697,7 +36697,7 @@
         </is>
       </c>
       <c r="N697" t="n">
-        <v>7.19</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="698">
@@ -36712,31 +36712,31 @@
         </is>
       </c>
       <c r="C698" t="n">
-        <v>416.5</v>
+        <v>415</v>
       </c>
       <c r="D698" t="n">
         <v>410.88</v>
       </c>
       <c r="E698" t="n">
-        <v>5.62</v>
+        <v>4.12</v>
       </c>
       <c r="F698" t="n">
-        <v>417.6</v>
+        <v>417.05</v>
       </c>
       <c r="G698" t="n">
         <v>410.88</v>
       </c>
       <c r="H698" t="n">
-        <v>6.72</v>
+        <v>6.17</v>
       </c>
       <c r="I698" t="n">
-        <v>412.5</v>
+        <v>409.35</v>
       </c>
       <c r="J698" t="n">
         <v>407.2</v>
       </c>
       <c r="K698" t="n">
-        <v>5.3</v>
+        <v>2.15</v>
       </c>
       <c r="L698" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         </is>
       </c>
       <c r="N698" t="n">
-        <v>1.37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="699">
@@ -36764,31 +36764,31 @@
         </is>
       </c>
       <c r="C699" t="n">
-        <v>116.47</v>
+        <v>116.8</v>
       </c>
       <c r="D699" t="n">
         <v>110.41</v>
       </c>
       <c r="E699" t="n">
-        <v>6.06</v>
+        <v>6.39</v>
       </c>
       <c r="F699" t="n">
-        <v>119.4</v>
+        <v>117.48</v>
       </c>
       <c r="G699" t="n">
         <v>112.41</v>
       </c>
       <c r="H699" t="n">
-        <v>6.99</v>
+        <v>5.07</v>
       </c>
       <c r="I699" t="n">
-        <v>116.36</v>
+        <v>114.63</v>
       </c>
       <c r="J699" t="n">
         <v>112.46</v>
       </c>
       <c r="K699" t="n">
-        <v>3.9</v>
+        <v>2.17</v>
       </c>
       <c r="L699" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         </is>
       </c>
       <c r="N699" t="n">
-        <v>5.49</v>
+        <v>5.79</v>
       </c>
     </row>
   </sheetData>
@@ -42098,31 +42098,31 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>322.35</v>
+        <v>317</v>
       </c>
       <c r="D30" t="n">
         <v>300.73</v>
       </c>
       <c r="E30" t="n">
-        <v>21.62</v>
+        <v>16.27</v>
       </c>
       <c r="F30" t="n">
-        <v>327.8</v>
+        <v>318.35</v>
       </c>
       <c r="G30" t="n">
         <v>313.49</v>
       </c>
       <c r="H30" t="n">
-        <v>14.31</v>
+        <v>4.86</v>
       </c>
       <c r="I30" t="n">
-        <v>318.25</v>
+        <v>310.8</v>
       </c>
       <c r="J30" t="n">
         <v>313.71</v>
       </c>
       <c r="K30" t="n">
-        <v>4.54</v>
+        <v>-2.91</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -42131,11 +42131,11 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>7.19</v>
+        <v>5.41</v>
       </c>
     </row>
   </sheetData>
@@ -47070,31 +47070,31 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>116.47</v>
+        <v>116.8</v>
       </c>
       <c r="D30" t="n">
         <v>110.41</v>
       </c>
       <c r="E30" t="n">
-        <v>6.06</v>
+        <v>6.39</v>
       </c>
       <c r="F30" t="n">
-        <v>119.4</v>
+        <v>117.48</v>
       </c>
       <c r="G30" t="n">
         <v>112.41</v>
       </c>
       <c r="H30" t="n">
-        <v>6.99</v>
+        <v>5.07</v>
       </c>
       <c r="I30" t="n">
-        <v>116.36</v>
+        <v>114.63</v>
       </c>
       <c r="J30" t="n">
         <v>112.46</v>
       </c>
       <c r="K30" t="n">
-        <v>3.9</v>
+        <v>2.17</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -47107,7 +47107,7 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>5.49</v>
+        <v>5.79</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N699"/>
+  <dimension ref="A1:N710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36802,6 +36802,578 @@
       </c>
       <c r="N699" t="n">
         <v>5.79</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C700" t="n">
+        <v>2208.8</v>
+      </c>
+      <c r="D700" t="n">
+        <v>2348.86</v>
+      </c>
+      <c r="E700" t="n">
+        <v>-140.06</v>
+      </c>
+      <c r="F700" t="n">
+        <v>2208.8</v>
+      </c>
+      <c r="G700" t="n">
+        <v>2348.86</v>
+      </c>
+      <c r="H700" t="n">
+        <v>-140.06</v>
+      </c>
+      <c r="I700" t="n">
+        <v>2155.5</v>
+      </c>
+      <c r="J700" t="n">
+        <v>2187.28</v>
+      </c>
+      <c r="K700" t="n">
+        <v>-31.78</v>
+      </c>
+      <c r="L700" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M700" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N700" t="n">
+        <v>5.96</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C701" t="n">
+        <v>3260</v>
+      </c>
+      <c r="D701" t="n">
+        <v>4172</v>
+      </c>
+      <c r="E701" t="n">
+        <v>-912</v>
+      </c>
+      <c r="F701" t="n">
+        <v>3314.9</v>
+      </c>
+      <c r="G701" t="n">
+        <v>4172</v>
+      </c>
+      <c r="H701" t="n">
+        <v>-857.1</v>
+      </c>
+      <c r="I701" t="n">
+        <v>3230.1</v>
+      </c>
+      <c r="J701" t="n">
+        <v>3260</v>
+      </c>
+      <c r="K701" t="n">
+        <v>-29.9</v>
+      </c>
+      <c r="L701" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M701" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N701" t="n">
+        <v>21.86</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C702" t="n">
+        <v>326.85</v>
+      </c>
+      <c r="D702" t="n">
+        <v>347.28</v>
+      </c>
+      <c r="E702" t="n">
+        <v>-20.43</v>
+      </c>
+      <c r="F702" t="n">
+        <v>329.75</v>
+      </c>
+      <c r="G702" t="n">
+        <v>347.28</v>
+      </c>
+      <c r="H702" t="n">
+        <v>-17.53</v>
+      </c>
+      <c r="I702" t="n">
+        <v>325.7</v>
+      </c>
+      <c r="J702" t="n">
+        <v>323.67</v>
+      </c>
+      <c r="K702" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="L702" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M702" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N702" t="n">
+        <v>5.88</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C703" t="n">
+        <v>2270.1</v>
+      </c>
+      <c r="D703" t="n">
+        <v>2440.89</v>
+      </c>
+      <c r="E703" t="n">
+        <v>-170.79</v>
+      </c>
+      <c r="F703" t="n">
+        <v>2270.1</v>
+      </c>
+      <c r="G703" t="n">
+        <v>2440.89</v>
+      </c>
+      <c r="H703" t="n">
+        <v>-170.79</v>
+      </c>
+      <c r="I703" t="n">
+        <v>2146.3</v>
+      </c>
+      <c r="J703" t="n">
+        <v>2270.1</v>
+      </c>
+      <c r="K703" t="n">
+        <v>-123.8</v>
+      </c>
+      <c r="L703" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M703" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N703" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C704" t="n">
+        <v>117.27</v>
+      </c>
+      <c r="D704" t="n">
+        <v>125.05</v>
+      </c>
+      <c r="E704" t="n">
+        <v>-7.78</v>
+      </c>
+      <c r="F704" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="G704" t="n">
+        <v>125.05</v>
+      </c>
+      <c r="H704" t="n">
+        <v>-7.55</v>
+      </c>
+      <c r="I704" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="J704" t="n">
+        <v>116.78</v>
+      </c>
+      <c r="K704" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="L704" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M704" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N704" t="n">
+        <v>6.22</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C705" t="n">
+        <v>548.15</v>
+      </c>
+      <c r="D705" t="n">
+        <v>576.66</v>
+      </c>
+      <c r="E705" t="n">
+        <v>-28.51</v>
+      </c>
+      <c r="F705" t="n">
+        <v>552</v>
+      </c>
+      <c r="G705" t="n">
+        <v>576.66</v>
+      </c>
+      <c r="H705" t="n">
+        <v>-24.66</v>
+      </c>
+      <c r="I705" t="n">
+        <v>543.6</v>
+      </c>
+      <c r="J705" t="n">
+        <v>541.51</v>
+      </c>
+      <c r="K705" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="L705" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M705" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N705" t="n">
+        <v>4.94</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C706" t="n">
+        <v>11282</v>
+      </c>
+      <c r="D706" t="n">
+        <v>12076.13</v>
+      </c>
+      <c r="E706" t="n">
+        <v>-794.13</v>
+      </c>
+      <c r="F706" t="n">
+        <v>11363</v>
+      </c>
+      <c r="G706" t="n">
+        <v>12076.13</v>
+      </c>
+      <c r="H706" t="n">
+        <v>-713.13</v>
+      </c>
+      <c r="I706" t="n">
+        <v>11070</v>
+      </c>
+      <c r="J706" t="n">
+        <v>11282</v>
+      </c>
+      <c r="K706" t="n">
+        <v>-212</v>
+      </c>
+      <c r="L706" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M706" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N706" t="n">
+        <v>6.58</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C707" t="n">
+        <v>292.6</v>
+      </c>
+      <c r="D707" t="n">
+        <v>311.15</v>
+      </c>
+      <c r="E707" t="n">
+        <v>-18.55</v>
+      </c>
+      <c r="F707" t="n">
+        <v>292.6</v>
+      </c>
+      <c r="G707" t="n">
+        <v>311.15</v>
+      </c>
+      <c r="H707" t="n">
+        <v>-18.55</v>
+      </c>
+      <c r="I707" t="n">
+        <v>284.1</v>
+      </c>
+      <c r="J707" t="n">
+        <v>286.71</v>
+      </c>
+      <c r="K707" t="n">
+        <v>-2.61</v>
+      </c>
+      <c r="L707" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M707" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N707" t="n">
+        <v>5.96</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C708" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D708" t="n">
+        <v>1105.23</v>
+      </c>
+      <c r="E708" t="n">
+        <v>-95.23</v>
+      </c>
+      <c r="F708" t="n">
+        <v>1010</v>
+      </c>
+      <c r="G708" t="n">
+        <v>1105.23</v>
+      </c>
+      <c r="H708" t="n">
+        <v>-95.23</v>
+      </c>
+      <c r="I708" t="n">
+        <v>988.7</v>
+      </c>
+      <c r="J708" t="n">
+        <v>1010</v>
+      </c>
+      <c r="K708" t="n">
+        <v>-21.3</v>
+      </c>
+      <c r="L708" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M708" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N708" t="n">
+        <v>8.619999999999999</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C709" t="n">
+        <v>412.5</v>
+      </c>
+      <c r="D709" t="n">
+        <v>419.97</v>
+      </c>
+      <c r="E709" t="n">
+        <v>-7.47</v>
+      </c>
+      <c r="F709" t="n">
+        <v>419.2</v>
+      </c>
+      <c r="G709" t="n">
+        <v>429.6</v>
+      </c>
+      <c r="H709" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="I709" t="n">
+        <v>412.5</v>
+      </c>
+      <c r="J709" t="n">
+        <v>410.12</v>
+      </c>
+      <c r="K709" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="L709" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M709" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N709" t="n">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C710" t="n">
+        <v>732.75</v>
+      </c>
+      <c r="D710" t="n">
+        <v>779.21</v>
+      </c>
+      <c r="E710" t="n">
+        <v>-46.46</v>
+      </c>
+      <c r="F710" t="n">
+        <v>743</v>
+      </c>
+      <c r="G710" t="n">
+        <v>779.21</v>
+      </c>
+      <c r="H710" t="n">
+        <v>-36.21</v>
+      </c>
+      <c r="I710" t="n">
+        <v>722.6</v>
+      </c>
+      <c r="J710" t="n">
+        <v>716.23</v>
+      </c>
+      <c r="K710" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="L710" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M710" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N710" t="n">
+        <v>5.96</v>
       </c>
     </row>
   </sheetData>
@@ -36815,7 +37387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37148,6 +37720,58 @@
       </c>
       <c r="N6" t="n">
         <v>0.62</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>732.75</v>
+      </c>
+      <c r="D7" t="n">
+        <v>779.21</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-46.46</v>
+      </c>
+      <c r="F7" t="n">
+        <v>743</v>
+      </c>
+      <c r="G7" t="n">
+        <v>779.21</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-36.21</v>
+      </c>
+      <c r="I7" t="n">
+        <v>722.6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>716.23</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>5.96</v>
       </c>
     </row>
   </sheetData>
@@ -40555,7 +41179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42136,6 +42760,58 @@
       </c>
       <c r="N30" t="n">
         <v>5.41</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>326.85</v>
+      </c>
+      <c r="D31" t="n">
+        <v>347.28</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-20.43</v>
+      </c>
+      <c r="F31" t="n">
+        <v>329.75</v>
+      </c>
+      <c r="G31" t="n">
+        <v>347.28</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-17.53</v>
+      </c>
+      <c r="I31" t="n">
+        <v>325.7</v>
+      </c>
+      <c r="J31" t="n">
+        <v>323.67</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>5.88</v>
       </c>
     </row>
   </sheetData>
@@ -45527,7 +46203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47108,6 +47784,58 @@
       </c>
       <c r="N30" t="n">
         <v>5.79</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>117.27</v>
+      </c>
+      <c r="D31" t="n">
+        <v>125.05</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-7.78</v>
+      </c>
+      <c r="F31" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>125.05</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-7.55</v>
+      </c>
+      <c r="I31" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>116.78</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>6.22</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -36816,31 +36816,31 @@
         </is>
       </c>
       <c r="C700" t="n">
-        <v>2208.8</v>
+        <v>2160</v>
       </c>
       <c r="D700" t="n">
         <v>2348.86</v>
       </c>
       <c r="E700" t="n">
-        <v>-140.06</v>
+        <v>-188.86</v>
       </c>
       <c r="F700" t="n">
-        <v>2208.8</v>
+        <v>2232.1</v>
       </c>
       <c r="G700" t="n">
         <v>2348.86</v>
       </c>
       <c r="H700" t="n">
-        <v>-140.06</v>
+        <v>-116.76</v>
       </c>
       <c r="I700" t="n">
-        <v>2155.5</v>
+        <v>2143</v>
       </c>
       <c r="J700" t="n">
         <v>2187.28</v>
       </c>
       <c r="K700" t="n">
-        <v>-31.78</v>
+        <v>-44.28</v>
       </c>
       <c r="L700" t="inlineStr">
         <is>
@@ -36849,11 +36849,11 @@
       </c>
       <c r="M700" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N700" t="n">
-        <v>5.96</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="701">
@@ -36868,31 +36868,31 @@
         </is>
       </c>
       <c r="C701" t="n">
-        <v>3260</v>
+        <v>3211.2</v>
       </c>
       <c r="D701" t="n">
         <v>4172</v>
       </c>
       <c r="E701" t="n">
-        <v>-912</v>
+        <v>-960.8</v>
       </c>
       <c r="F701" t="n">
-        <v>3314.9</v>
+        <v>3224.5</v>
       </c>
       <c r="G701" t="n">
         <v>4172</v>
       </c>
       <c r="H701" t="n">
-        <v>-857.1</v>
+        <v>-947.5</v>
       </c>
       <c r="I701" t="n">
-        <v>3230.1</v>
+        <v>3056.6</v>
       </c>
       <c r="J701" t="n">
         <v>3260</v>
       </c>
       <c r="K701" t="n">
-        <v>-29.9</v>
+        <v>-203.4</v>
       </c>
       <c r="L701" t="inlineStr">
         <is>
@@ -36901,11 +36901,11 @@
       </c>
       <c r="M701" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N701" t="n">
-        <v>21.86</v>
+        <v>23.03</v>
       </c>
     </row>
     <row r="702">
@@ -36920,31 +36920,31 @@
         </is>
       </c>
       <c r="C702" t="n">
-        <v>326.85</v>
+        <v>322.35</v>
       </c>
       <c r="D702" t="n">
         <v>347.28</v>
       </c>
       <c r="E702" t="n">
-        <v>-20.43</v>
+        <v>-24.93</v>
       </c>
       <c r="F702" t="n">
-        <v>329.75</v>
+        <v>327.8</v>
       </c>
       <c r="G702" t="n">
         <v>347.28</v>
       </c>
       <c r="H702" t="n">
-        <v>-17.53</v>
+        <v>-19.48</v>
       </c>
       <c r="I702" t="n">
-        <v>325.7</v>
+        <v>318.25</v>
       </c>
       <c r="J702" t="n">
         <v>323.67</v>
       </c>
       <c r="K702" t="n">
-        <v>2.03</v>
+        <v>-5.42</v>
       </c>
       <c r="L702" t="inlineStr">
         <is>
@@ -36953,11 +36953,11 @@
       </c>
       <c r="M702" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N702" t="n">
-        <v>5.88</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="703">
@@ -36972,31 +36972,31 @@
         </is>
       </c>
       <c r="C703" t="n">
-        <v>2270.1</v>
+        <v>2120</v>
       </c>
       <c r="D703" t="n">
         <v>2440.89</v>
       </c>
       <c r="E703" t="n">
-        <v>-170.79</v>
+        <v>-320.89</v>
       </c>
       <c r="F703" t="n">
-        <v>2270.1</v>
+        <v>2132.9</v>
       </c>
       <c r="G703" t="n">
         <v>2440.89</v>
       </c>
       <c r="H703" t="n">
-        <v>-170.79</v>
+        <v>-307.99</v>
       </c>
       <c r="I703" t="n">
-        <v>2146.3</v>
+        <v>2041.3</v>
       </c>
       <c r="J703" t="n">
         <v>2270.1</v>
       </c>
       <c r="K703" t="n">
-        <v>-123.8</v>
+        <v>-228.8</v>
       </c>
       <c r="L703" t="inlineStr">
         <is>
@@ -37009,7 +37009,7 @@
         </is>
       </c>
       <c r="N703" t="n">
-        <v>7</v>
+        <v>13.15</v>
       </c>
     </row>
     <row r="704">
@@ -37024,31 +37024,31 @@
         </is>
       </c>
       <c r="C704" t="n">
-        <v>117.27</v>
+        <v>116.47</v>
       </c>
       <c r="D704" t="n">
         <v>125.05</v>
       </c>
       <c r="E704" t="n">
-        <v>-7.78</v>
+        <v>-8.58</v>
       </c>
       <c r="F704" t="n">
-        <v>117.5</v>
+        <v>119.4</v>
       </c>
       <c r="G704" t="n">
         <v>125.05</v>
       </c>
       <c r="H704" t="n">
-        <v>-7.55</v>
+        <v>-5.65</v>
       </c>
       <c r="I704" t="n">
-        <v>116.5</v>
+        <v>116.36</v>
       </c>
       <c r="J704" t="n">
         <v>116.78</v>
       </c>
       <c r="K704" t="n">
-        <v>-0.28</v>
+        <v>-0.42</v>
       </c>
       <c r="L704" t="inlineStr">
         <is>
@@ -37061,7 +37061,7 @@
         </is>
       </c>
       <c r="N704" t="n">
-        <v>6.22</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="705">
@@ -37076,31 +37076,31 @@
         </is>
       </c>
       <c r="C705" t="n">
-        <v>548.15</v>
+        <v>543</v>
       </c>
       <c r="D705" t="n">
         <v>576.66</v>
       </c>
       <c r="E705" t="n">
-        <v>-28.51</v>
+        <v>-33.66</v>
       </c>
       <c r="F705" t="n">
-        <v>552</v>
+        <v>551.45</v>
       </c>
       <c r="G705" t="n">
         <v>576.66</v>
       </c>
       <c r="H705" t="n">
-        <v>-24.66</v>
+        <v>-25.21</v>
       </c>
       <c r="I705" t="n">
-        <v>543.6</v>
+        <v>529.6</v>
       </c>
       <c r="J705" t="n">
         <v>541.51</v>
       </c>
       <c r="K705" t="n">
-        <v>2.09</v>
+        <v>-11.91</v>
       </c>
       <c r="L705" t="inlineStr">
         <is>
@@ -37109,11 +37109,11 @@
       </c>
       <c r="M705" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N705" t="n">
-        <v>4.94</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="706">
@@ -37128,31 +37128,31 @@
         </is>
       </c>
       <c r="C706" t="n">
-        <v>11282</v>
+        <v>10930</v>
       </c>
       <c r="D706" t="n">
         <v>12076.13</v>
       </c>
       <c r="E706" t="n">
-        <v>-794.13</v>
+        <v>-1146.13</v>
       </c>
       <c r="F706" t="n">
-        <v>11363</v>
+        <v>11090</v>
       </c>
       <c r="G706" t="n">
         <v>12076.13</v>
       </c>
       <c r="H706" t="n">
-        <v>-713.13</v>
+        <v>-986.13</v>
       </c>
       <c r="I706" t="n">
-        <v>11070</v>
+        <v>10925</v>
       </c>
       <c r="J706" t="n">
         <v>11282</v>
       </c>
       <c r="K706" t="n">
-        <v>-212</v>
+        <v>-357</v>
       </c>
       <c r="L706" t="inlineStr">
         <is>
@@ -37165,7 +37165,7 @@
         </is>
       </c>
       <c r="N706" t="n">
-        <v>6.58</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="707">
@@ -37180,31 +37180,31 @@
         </is>
       </c>
       <c r="C707" t="n">
-        <v>292.6</v>
+        <v>283.45</v>
       </c>
       <c r="D707" t="n">
         <v>311.15</v>
       </c>
       <c r="E707" t="n">
-        <v>-18.55</v>
+        <v>-27.7</v>
       </c>
       <c r="F707" t="n">
-        <v>292.6</v>
+        <v>285</v>
       </c>
       <c r="G707" t="n">
         <v>311.15</v>
       </c>
       <c r="H707" t="n">
-        <v>-18.55</v>
+        <v>-26.15</v>
       </c>
       <c r="I707" t="n">
-        <v>284.1</v>
+        <v>281.7</v>
       </c>
       <c r="J707" t="n">
         <v>286.71</v>
       </c>
       <c r="K707" t="n">
-        <v>-2.61</v>
+        <v>-5.01</v>
       </c>
       <c r="L707" t="inlineStr">
         <is>
@@ -37213,11 +37213,11 @@
       </c>
       <c r="M707" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N707" t="n">
-        <v>5.96</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="708">
@@ -37232,31 +37232,31 @@
         </is>
       </c>
       <c r="C708" t="n">
-        <v>1010</v>
+        <v>976.5</v>
       </c>
       <c r="D708" t="n">
         <v>1105.23</v>
       </c>
       <c r="E708" t="n">
-        <v>-95.23</v>
+        <v>-128.73</v>
       </c>
       <c r="F708" t="n">
-        <v>1010</v>
+        <v>989.9</v>
       </c>
       <c r="G708" t="n">
         <v>1105.23</v>
       </c>
       <c r="H708" t="n">
-        <v>-95.23</v>
+        <v>-115.33</v>
       </c>
       <c r="I708" t="n">
-        <v>988.7</v>
+        <v>963.8</v>
       </c>
       <c r="J708" t="n">
         <v>1010</v>
       </c>
       <c r="K708" t="n">
-        <v>-21.3</v>
+        <v>-46.2</v>
       </c>
       <c r="L708" t="inlineStr">
         <is>
@@ -37269,7 +37269,7 @@
         </is>
       </c>
       <c r="N708" t="n">
-        <v>8.619999999999999</v>
+        <v>11.65</v>
       </c>
     </row>
     <row r="709">
@@ -37284,22 +37284,22 @@
         </is>
       </c>
       <c r="C709" t="n">
-        <v>412.5</v>
+        <v>416.5</v>
       </c>
       <c r="D709" t="n">
         <v>419.97</v>
       </c>
       <c r="E709" t="n">
-        <v>-7.47</v>
+        <v>-3.47</v>
       </c>
       <c r="F709" t="n">
-        <v>419.2</v>
+        <v>417.6</v>
       </c>
       <c r="G709" t="n">
         <v>429.6</v>
       </c>
       <c r="H709" t="n">
-        <v>-10.4</v>
+        <v>-12</v>
       </c>
       <c r="I709" t="n">
         <v>412.5</v>
@@ -37321,7 +37321,7 @@
         </is>
       </c>
       <c r="N709" t="n">
-        <v>1.78</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="710">
@@ -37336,31 +37336,31 @@
         </is>
       </c>
       <c r="C710" t="n">
-        <v>732.75</v>
+        <v>726.65</v>
       </c>
       <c r="D710" t="n">
         <v>779.21</v>
       </c>
       <c r="E710" t="n">
-        <v>-46.46</v>
+        <v>-52.56</v>
       </c>
       <c r="F710" t="n">
-        <v>743</v>
+        <v>729.8</v>
       </c>
       <c r="G710" t="n">
         <v>779.21</v>
       </c>
       <c r="H710" t="n">
-        <v>-36.21</v>
+        <v>-49.41</v>
       </c>
       <c r="I710" t="n">
-        <v>722.6</v>
+        <v>712.55</v>
       </c>
       <c r="J710" t="n">
         <v>716.23</v>
       </c>
       <c r="K710" t="n">
-        <v>6.37</v>
+        <v>-3.68</v>
       </c>
       <c r="L710" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         </is>
       </c>
       <c r="N710" t="n">
-        <v>5.96</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -37734,31 +37734,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>732.75</v>
+        <v>726.65</v>
       </c>
       <c r="D7" t="n">
         <v>779.21</v>
       </c>
       <c r="E7" t="n">
-        <v>-46.46</v>
+        <v>-52.56</v>
       </c>
       <c r="F7" t="n">
-        <v>743</v>
+        <v>729.8</v>
       </c>
       <c r="G7" t="n">
         <v>779.21</v>
       </c>
       <c r="H7" t="n">
-        <v>-36.21</v>
+        <v>-49.41</v>
       </c>
       <c r="I7" t="n">
-        <v>722.6</v>
+        <v>712.55</v>
       </c>
       <c r="J7" t="n">
         <v>716.23</v>
       </c>
       <c r="K7" t="n">
-        <v>6.37</v>
+        <v>-3.68</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>5.96</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -42774,31 +42774,31 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>326.85</v>
+        <v>322.35</v>
       </c>
       <c r="D31" t="n">
         <v>347.28</v>
       </c>
       <c r="E31" t="n">
-        <v>-20.43</v>
+        <v>-24.93</v>
       </c>
       <c r="F31" t="n">
-        <v>329.75</v>
+        <v>327.8</v>
       </c>
       <c r="G31" t="n">
         <v>347.28</v>
       </c>
       <c r="H31" t="n">
-        <v>-17.53</v>
+        <v>-19.48</v>
       </c>
       <c r="I31" t="n">
-        <v>325.7</v>
+        <v>318.25</v>
       </c>
       <c r="J31" t="n">
         <v>323.67</v>
       </c>
       <c r="K31" t="n">
-        <v>2.03</v>
+        <v>-5.42</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -42807,11 +42807,11 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>5.88</v>
+        <v>7.18</v>
       </c>
     </row>
   </sheetData>
@@ -47798,31 +47798,31 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>117.27</v>
+        <v>116.47</v>
       </c>
       <c r="D31" t="n">
         <v>125.05</v>
       </c>
       <c r="E31" t="n">
-        <v>-7.78</v>
+        <v>-8.58</v>
       </c>
       <c r="F31" t="n">
-        <v>117.5</v>
+        <v>119.4</v>
       </c>
       <c r="G31" t="n">
         <v>125.05</v>
       </c>
       <c r="H31" t="n">
-        <v>-7.55</v>
+        <v>-5.65</v>
       </c>
       <c r="I31" t="n">
-        <v>116.5</v>
+        <v>116.36</v>
       </c>
       <c r="J31" t="n">
         <v>116.78</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.28</v>
+        <v>-0.42</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -47835,7 +47835,7 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>6.22</v>
+        <v>6.86</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -36816,31 +36816,31 @@
         </is>
       </c>
       <c r="C700" t="n">
-        <v>2160</v>
+        <v>2208.8</v>
       </c>
       <c r="D700" t="n">
-        <v>2348.86</v>
+        <v>2047.46</v>
       </c>
       <c r="E700" t="n">
-        <v>-188.86</v>
+        <v>161.34</v>
       </c>
       <c r="F700" t="n">
-        <v>2232.1</v>
+        <v>2208.8</v>
       </c>
       <c r="G700" t="n">
-        <v>2348.86</v>
+        <v>2132.74</v>
       </c>
       <c r="H700" t="n">
-        <v>-116.76</v>
+        <v>76.06</v>
       </c>
       <c r="I700" t="n">
-        <v>2143</v>
+        <v>2155.5</v>
       </c>
       <c r="J700" t="n">
-        <v>2187.28</v>
+        <v>2137.07</v>
       </c>
       <c r="K700" t="n">
-        <v>-44.28</v>
+        <v>18.43</v>
       </c>
       <c r="L700" t="inlineStr">
         <is>
@@ -36853,7 +36853,7 @@
         </is>
       </c>
       <c r="N700" t="n">
-        <v>8.039999999999999</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="701">
@@ -36868,31 +36868,31 @@
         </is>
       </c>
       <c r="C701" t="n">
-        <v>3211.2</v>
+        <v>3260</v>
       </c>
       <c r="D701" t="n">
-        <v>4172</v>
+        <v>2542.79</v>
       </c>
       <c r="E701" t="n">
-        <v>-960.8</v>
+        <v>717.21</v>
       </c>
       <c r="F701" t="n">
-        <v>3224.5</v>
+        <v>3314.9</v>
       </c>
       <c r="G701" t="n">
-        <v>4172</v>
+        <v>3184.23</v>
       </c>
       <c r="H701" t="n">
-        <v>-947.5</v>
+        <v>130.67</v>
       </c>
       <c r="I701" t="n">
-        <v>3056.6</v>
+        <v>3230.1</v>
       </c>
       <c r="J701" t="n">
-        <v>3260</v>
+        <v>3191.99</v>
       </c>
       <c r="K701" t="n">
-        <v>-203.4</v>
+        <v>38.11</v>
       </c>
       <c r="L701" t="inlineStr">
         <is>
@@ -36905,7 +36905,7 @@
         </is>
       </c>
       <c r="N701" t="n">
-        <v>23.03</v>
+        <v>28.21</v>
       </c>
     </row>
     <row r="702">
@@ -36920,31 +36920,31 @@
         </is>
       </c>
       <c r="C702" t="n">
-        <v>322.35</v>
+        <v>326.85</v>
       </c>
       <c r="D702" t="n">
-        <v>347.28</v>
+        <v>305.81</v>
       </c>
       <c r="E702" t="n">
-        <v>-24.93</v>
+        <v>21.04</v>
       </c>
       <c r="F702" t="n">
-        <v>327.8</v>
+        <v>329.75</v>
       </c>
       <c r="G702" t="n">
-        <v>347.28</v>
+        <v>315.6</v>
       </c>
       <c r="H702" t="n">
-        <v>-19.48</v>
+        <v>14.15</v>
       </c>
       <c r="I702" t="n">
-        <v>318.25</v>
+        <v>325.7</v>
       </c>
       <c r="J702" t="n">
-        <v>323.67</v>
+        <v>316.24</v>
       </c>
       <c r="K702" t="n">
-        <v>-5.42</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="L702" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         </is>
       </c>
       <c r="N702" t="n">
-        <v>7.18</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="703">
@@ -36972,31 +36972,31 @@
         </is>
       </c>
       <c r="C703" t="n">
-        <v>2120</v>
+        <v>2270.1</v>
       </c>
       <c r="D703" t="n">
-        <v>2440.89</v>
+        <v>2004.42</v>
       </c>
       <c r="E703" t="n">
-        <v>-320.89</v>
+        <v>265.68</v>
       </c>
       <c r="F703" t="n">
-        <v>2132.9</v>
+        <v>2270.1</v>
       </c>
       <c r="G703" t="n">
-        <v>2440.89</v>
+        <v>2224.27</v>
       </c>
       <c r="H703" t="n">
-        <v>-307.99</v>
+        <v>45.83</v>
       </c>
       <c r="I703" t="n">
-        <v>2041.3</v>
+        <v>2146.3</v>
       </c>
       <c r="J703" t="n">
-        <v>2270.1</v>
+        <v>2229.93</v>
       </c>
       <c r="K703" t="n">
-        <v>-228.8</v>
+        <v>-83.63</v>
       </c>
       <c r="L703" t="inlineStr">
         <is>
@@ -37009,7 +37009,7 @@
         </is>
       </c>
       <c r="N703" t="n">
-        <v>13.15</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="704">
@@ -37020,35 +37020,35 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C704" t="n">
-        <v>116.47</v>
+        <v>548.15</v>
       </c>
       <c r="D704" t="n">
-        <v>125.05</v>
+        <v>520.29</v>
       </c>
       <c r="E704" t="n">
-        <v>-8.58</v>
+        <v>27.86</v>
       </c>
       <c r="F704" t="n">
-        <v>119.4</v>
+        <v>552</v>
       </c>
       <c r="G704" t="n">
-        <v>125.05</v>
+        <v>528.05</v>
       </c>
       <c r="H704" t="n">
-        <v>-5.65</v>
+        <v>23.95</v>
       </c>
       <c r="I704" t="n">
-        <v>116.36</v>
+        <v>543.6</v>
       </c>
       <c r="J704" t="n">
-        <v>116.78</v>
+        <v>529.08</v>
       </c>
       <c r="K704" t="n">
-        <v>-0.42</v>
+        <v>14.52</v>
       </c>
       <c r="L704" t="inlineStr">
         <is>
@@ -37057,11 +37057,11 @@
       </c>
       <c r="M704" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N704" t="n">
-        <v>6.86</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="705">
@@ -37072,35 +37072,35 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C705" t="n">
-        <v>543</v>
+        <v>117.27</v>
       </c>
       <c r="D705" t="n">
-        <v>576.66</v>
+        <v>110.1</v>
       </c>
       <c r="E705" t="n">
-        <v>-33.66</v>
+        <v>7.17</v>
       </c>
       <c r="F705" t="n">
-        <v>551.45</v>
+        <v>117.5</v>
       </c>
       <c r="G705" t="n">
-        <v>576.66</v>
+        <v>113.84</v>
       </c>
       <c r="H705" t="n">
-        <v>-25.21</v>
+        <v>3.66</v>
       </c>
       <c r="I705" t="n">
-        <v>529.6</v>
+        <v>116.5</v>
       </c>
       <c r="J705" t="n">
-        <v>541.51</v>
+        <v>114.1</v>
       </c>
       <c r="K705" t="n">
-        <v>-11.91</v>
+        <v>2.4</v>
       </c>
       <c r="L705" t="inlineStr">
         <is>
@@ -37113,7 +37113,7 @@
         </is>
       </c>
       <c r="N705" t="n">
-        <v>5.84</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="706">
@@ -37128,31 +37128,31 @@
         </is>
       </c>
       <c r="C706" t="n">
-        <v>10930</v>
+        <v>11282</v>
       </c>
       <c r="D706" t="n">
-        <v>12076.13</v>
+        <v>10360.47</v>
       </c>
       <c r="E706" t="n">
-        <v>-1146.13</v>
+        <v>921.53</v>
       </c>
       <c r="F706" t="n">
-        <v>11090</v>
+        <v>11363</v>
       </c>
       <c r="G706" t="n">
-        <v>12076.13</v>
+        <v>10957.24</v>
       </c>
       <c r="H706" t="n">
-        <v>-986.13</v>
+        <v>405.76</v>
       </c>
       <c r="I706" t="n">
-        <v>10925</v>
+        <v>11070</v>
       </c>
       <c r="J706" t="n">
-        <v>11282</v>
+        <v>11060.34</v>
       </c>
       <c r="K706" t="n">
-        <v>-357</v>
+        <v>9.66</v>
       </c>
       <c r="L706" t="inlineStr">
         <is>
@@ -37165,7 +37165,7 @@
         </is>
       </c>
       <c r="N706" t="n">
-        <v>9.49</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="707">
@@ -37176,35 +37176,35 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C707" t="n">
-        <v>283.45</v>
+        <v>1010</v>
       </c>
       <c r="D707" t="n">
-        <v>311.15</v>
+        <v>903.71</v>
       </c>
       <c r="E707" t="n">
-        <v>-27.7</v>
+        <v>106.29</v>
       </c>
       <c r="F707" t="n">
-        <v>285</v>
+        <v>1010</v>
       </c>
       <c r="G707" t="n">
-        <v>311.15</v>
+        <v>985.89</v>
       </c>
       <c r="H707" t="n">
-        <v>-26.15</v>
+        <v>24.11</v>
       </c>
       <c r="I707" t="n">
-        <v>281.7</v>
+        <v>988.7</v>
       </c>
       <c r="J707" t="n">
-        <v>286.71</v>
+        <v>988.27</v>
       </c>
       <c r="K707" t="n">
-        <v>-5.01</v>
+        <v>0.43</v>
       </c>
       <c r="L707" t="inlineStr">
         <is>
@@ -37213,11 +37213,11 @@
       </c>
       <c r="M707" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N707" t="n">
-        <v>8.9</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="708">
@@ -37228,39 +37228,39 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C708" t="n">
-        <v>976.5</v>
+        <v>292.6</v>
       </c>
       <c r="D708" t="n">
-        <v>1105.23</v>
+        <v>268.68</v>
       </c>
       <c r="E708" t="n">
-        <v>-128.73</v>
+        <v>23.92</v>
       </c>
       <c r="F708" t="n">
-        <v>989.9</v>
+        <v>292.6</v>
       </c>
       <c r="G708" t="n">
-        <v>1105.23</v>
+        <v>279.66</v>
       </c>
       <c r="H708" t="n">
-        <v>-115.33</v>
+        <v>12.94</v>
       </c>
       <c r="I708" t="n">
-        <v>963.8</v>
+        <v>284.1</v>
       </c>
       <c r="J708" t="n">
-        <v>1010</v>
+        <v>280.13</v>
       </c>
       <c r="K708" t="n">
-        <v>-46.2</v>
+        <v>3.97</v>
       </c>
       <c r="L708" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="M708" t="inlineStr">
@@ -37269,7 +37269,7 @@
         </is>
       </c>
       <c r="N708" t="n">
-        <v>11.65</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="709">
@@ -37284,31 +37284,31 @@
         </is>
       </c>
       <c r="C709" t="n">
-        <v>416.5</v>
+        <v>412.5</v>
       </c>
       <c r="D709" t="n">
-        <v>419.97</v>
+        <v>412.37</v>
       </c>
       <c r="E709" t="n">
-        <v>-3.47</v>
+        <v>0.13</v>
       </c>
       <c r="F709" t="n">
-        <v>417.6</v>
+        <v>419.2</v>
       </c>
       <c r="G709" t="n">
-        <v>429.6</v>
+        <v>412.37</v>
       </c>
       <c r="H709" t="n">
-        <v>-12</v>
+        <v>6.83</v>
       </c>
       <c r="I709" t="n">
         <v>412.5</v>
       </c>
       <c r="J709" t="n">
-        <v>410.12</v>
+        <v>400.72</v>
       </c>
       <c r="K709" t="n">
-        <v>2.38</v>
+        <v>11.78</v>
       </c>
       <c r="L709" t="inlineStr">
         <is>
@@ -37321,7 +37321,7 @@
         </is>
       </c>
       <c r="N709" t="n">
-        <v>0.83</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="710">
@@ -37336,31 +37336,31 @@
         </is>
       </c>
       <c r="C710" t="n">
-        <v>726.65</v>
+        <v>732.75</v>
       </c>
       <c r="D710" t="n">
-        <v>779.21</v>
+        <v>688.79</v>
       </c>
       <c r="E710" t="n">
-        <v>-52.56</v>
+        <v>43.96</v>
       </c>
       <c r="F710" t="n">
-        <v>729.8</v>
+        <v>743</v>
       </c>
       <c r="G710" t="n">
-        <v>779.21</v>
+        <v>688.79</v>
       </c>
       <c r="H710" t="n">
-        <v>-49.41</v>
+        <v>54.21</v>
       </c>
       <c r="I710" t="n">
-        <v>712.55</v>
+        <v>722.6</v>
       </c>
       <c r="J710" t="n">
-        <v>716.23</v>
+        <v>699.79</v>
       </c>
       <c r="K710" t="n">
-        <v>-3.68</v>
+        <v>22.81</v>
       </c>
       <c r="L710" t="inlineStr">
         <is>
@@ -37369,11 +37369,11 @@
       </c>
       <c r="M710" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N710" t="n">
-        <v>6.75</v>
+        <v>6.38</v>
       </c>
     </row>
   </sheetData>
@@ -37734,31 +37734,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>726.65</v>
+        <v>732.75</v>
       </c>
       <c r="D7" t="n">
-        <v>779.21</v>
+        <v>688.79</v>
       </c>
       <c r="E7" t="n">
-        <v>-52.56</v>
+        <v>43.96</v>
       </c>
       <c r="F7" t="n">
-        <v>729.8</v>
+        <v>743</v>
       </c>
       <c r="G7" t="n">
-        <v>779.21</v>
+        <v>688.79</v>
       </c>
       <c r="H7" t="n">
-        <v>-49.41</v>
+        <v>54.21</v>
       </c>
       <c r="I7" t="n">
-        <v>712.55</v>
+        <v>722.6</v>
       </c>
       <c r="J7" t="n">
-        <v>716.23</v>
+        <v>699.79</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.68</v>
+        <v>22.81</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -37767,11 +37767,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>6.75</v>
+        <v>6.38</v>
       </c>
     </row>
   </sheetData>
@@ -42774,31 +42774,31 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>322.35</v>
+        <v>326.85</v>
       </c>
       <c r="D31" t="n">
-        <v>347.28</v>
+        <v>305.81</v>
       </c>
       <c r="E31" t="n">
-        <v>-24.93</v>
+        <v>21.04</v>
       </c>
       <c r="F31" t="n">
-        <v>327.8</v>
+        <v>329.75</v>
       </c>
       <c r="G31" t="n">
-        <v>347.28</v>
+        <v>315.6</v>
       </c>
       <c r="H31" t="n">
-        <v>-19.48</v>
+        <v>14.15</v>
       </c>
       <c r="I31" t="n">
-        <v>318.25</v>
+        <v>325.7</v>
       </c>
       <c r="J31" t="n">
-        <v>323.67</v>
+        <v>316.24</v>
       </c>
       <c r="K31" t="n">
-        <v>-5.42</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -42811,7 +42811,7 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>7.18</v>
+        <v>6.88</v>
       </c>
     </row>
   </sheetData>
@@ -47798,31 +47798,31 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>116.47</v>
+        <v>117.27</v>
       </c>
       <c r="D31" t="n">
-        <v>125.05</v>
+        <v>110.1</v>
       </c>
       <c r="E31" t="n">
-        <v>-8.58</v>
+        <v>7.17</v>
       </c>
       <c r="F31" t="n">
-        <v>119.4</v>
+        <v>117.5</v>
       </c>
       <c r="G31" t="n">
-        <v>125.05</v>
+        <v>113.84</v>
       </c>
       <c r="H31" t="n">
-        <v>-5.65</v>
+        <v>3.66</v>
       </c>
       <c r="I31" t="n">
-        <v>116.36</v>
+        <v>116.5</v>
       </c>
       <c r="J31" t="n">
-        <v>116.78</v>
+        <v>114.1</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.42</v>
+        <v>2.4</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -47831,11 +47831,11 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>6.86</v>
+        <v>6.51</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N710"/>
+  <dimension ref="A1:N719"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37374,6 +37374,474 @@
       </c>
       <c r="N710" t="n">
         <v>6.38</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C711" t="n">
+        <v>414.8</v>
+      </c>
+      <c r="D711" t="n">
+        <v>418.25</v>
+      </c>
+      <c r="E711" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="F711" t="n">
+        <v>420.6</v>
+      </c>
+      <c r="G711" t="n">
+        <v>439.96</v>
+      </c>
+      <c r="H711" t="n">
+        <v>-19.36</v>
+      </c>
+      <c r="I711" t="n">
+        <v>414.55</v>
+      </c>
+      <c r="J711" t="n">
+        <v>414.8</v>
+      </c>
+      <c r="K711" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="L711" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M711" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N711" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C712" t="n">
+        <v>335.9</v>
+      </c>
+      <c r="D712" t="n">
+        <v>362.09</v>
+      </c>
+      <c r="E712" t="n">
+        <v>-26.19</v>
+      </c>
+      <c r="F712" t="n">
+        <v>336.5</v>
+      </c>
+      <c r="G712" t="n">
+        <v>362.09</v>
+      </c>
+      <c r="H712" t="n">
+        <v>-25.59</v>
+      </c>
+      <c r="I712" t="n">
+        <v>326.85</v>
+      </c>
+      <c r="J712" t="n">
+        <v>335.9</v>
+      </c>
+      <c r="K712" t="n">
+        <v>-9.050000000000001</v>
+      </c>
+      <c r="L712" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M712" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N712" t="n">
+        <v>7.23</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C713" t="n">
+        <v>11409</v>
+      </c>
+      <c r="D713" t="n">
+        <v>12523.22</v>
+      </c>
+      <c r="E713" t="n">
+        <v>-1114.22</v>
+      </c>
+      <c r="F713" t="n">
+        <v>11434</v>
+      </c>
+      <c r="G713" t="n">
+        <v>12523.22</v>
+      </c>
+      <c r="H713" t="n">
+        <v>-1089.22</v>
+      </c>
+      <c r="I713" t="n">
+        <v>11227</v>
+      </c>
+      <c r="J713" t="n">
+        <v>11366.84</v>
+      </c>
+      <c r="K713" t="n">
+        <v>-139.84</v>
+      </c>
+      <c r="L713" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M713" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N713" t="n">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C714" t="n">
+        <v>568</v>
+      </c>
+      <c r="D714" t="n">
+        <v>603.2</v>
+      </c>
+      <c r="E714" t="n">
+        <v>-35.2</v>
+      </c>
+      <c r="F714" t="n">
+        <v>574.15</v>
+      </c>
+      <c r="G714" t="n">
+        <v>603.71</v>
+      </c>
+      <c r="H714" t="n">
+        <v>-29.56</v>
+      </c>
+      <c r="I714" t="n">
+        <v>543.65</v>
+      </c>
+      <c r="J714" t="n">
+        <v>568</v>
+      </c>
+      <c r="K714" t="n">
+        <v>-24.35</v>
+      </c>
+      <c r="L714" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M714" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N714" t="n">
+        <v>5.84</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C715" t="n">
+        <v>118</v>
+      </c>
+      <c r="D715" t="n">
+        <v>126.69</v>
+      </c>
+      <c r="E715" t="n">
+        <v>-8.69</v>
+      </c>
+      <c r="F715" t="n">
+        <v>118.58</v>
+      </c>
+      <c r="G715" t="n">
+        <v>126.69</v>
+      </c>
+      <c r="H715" t="n">
+        <v>-8.109999999999999</v>
+      </c>
+      <c r="I715" t="n">
+        <v>116.64</v>
+      </c>
+      <c r="J715" t="n">
+        <v>118</v>
+      </c>
+      <c r="K715" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="L715" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M715" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N715" t="n">
+        <v>6.86</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C716" t="n">
+        <v>2181.1</v>
+      </c>
+      <c r="D716" t="n">
+        <v>2489.97</v>
+      </c>
+      <c r="E716" t="n">
+        <v>-308.87</v>
+      </c>
+      <c r="F716" t="n">
+        <v>2229</v>
+      </c>
+      <c r="G716" t="n">
+        <v>2489.97</v>
+      </c>
+      <c r="H716" t="n">
+        <v>-260.97</v>
+      </c>
+      <c r="I716" t="n">
+        <v>2178.7</v>
+      </c>
+      <c r="J716" t="n">
+        <v>2142.17</v>
+      </c>
+      <c r="K716" t="n">
+        <v>36.53</v>
+      </c>
+      <c r="L716" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M716" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N716" t="n">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C717" t="n">
+        <v>745</v>
+      </c>
+      <c r="D717" t="n">
+        <v>798.89</v>
+      </c>
+      <c r="E717" t="n">
+        <v>-53.89</v>
+      </c>
+      <c r="F717" t="n">
+        <v>755</v>
+      </c>
+      <c r="G717" t="n">
+        <v>798.89</v>
+      </c>
+      <c r="H717" t="n">
+        <v>-43.89</v>
+      </c>
+      <c r="I717" t="n">
+        <v>741</v>
+      </c>
+      <c r="J717" t="n">
+        <v>740.17</v>
+      </c>
+      <c r="K717" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L717" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M717" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N717" t="n">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C718" t="n">
+        <v>995</v>
+      </c>
+      <c r="D718" t="n">
+        <v>1120.93</v>
+      </c>
+      <c r="E718" t="n">
+        <v>-125.93</v>
+      </c>
+      <c r="F718" t="n">
+        <v>1009.8</v>
+      </c>
+      <c r="G718" t="n">
+        <v>1120.93</v>
+      </c>
+      <c r="H718" t="n">
+        <v>-111.13</v>
+      </c>
+      <c r="I718" t="n">
+        <v>993.2</v>
+      </c>
+      <c r="J718" t="n">
+        <v>995</v>
+      </c>
+      <c r="K718" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="L718" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M718" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N718" t="n">
+        <v>11.23</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C719" t="n">
+        <v>3209</v>
+      </c>
+      <c r="D719" t="n">
+        <v>4147.04</v>
+      </c>
+      <c r="E719" t="n">
+        <v>-938.04</v>
+      </c>
+      <c r="F719" t="n">
+        <v>3268</v>
+      </c>
+      <c r="G719" t="n">
+        <v>4147.04</v>
+      </c>
+      <c r="H719" t="n">
+        <v>-879.04</v>
+      </c>
+      <c r="I719" t="n">
+        <v>3155.5</v>
+      </c>
+      <c r="J719" t="n">
+        <v>3202.25</v>
+      </c>
+      <c r="K719" t="n">
+        <v>-46.75</v>
+      </c>
+      <c r="L719" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M719" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N719" t="n">
+        <v>22.62</v>
       </c>
     </row>
   </sheetData>
@@ -37387,7 +37855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37772,6 +38240,58 @@
       </c>
       <c r="N7" t="n">
         <v>6.38</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>745</v>
+      </c>
+      <c r="D8" t="n">
+        <v>798.89</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-53.89</v>
+      </c>
+      <c r="F8" t="n">
+        <v>755</v>
+      </c>
+      <c r="G8" t="n">
+        <v>798.89</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-43.89</v>
+      </c>
+      <c r="I8" t="n">
+        <v>741</v>
+      </c>
+      <c r="J8" t="n">
+        <v>740.17</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -41179,7 +41699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42812,6 +43332,58 @@
       </c>
       <c r="N31" t="n">
         <v>6.88</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>335.9</v>
+      </c>
+      <c r="D32" t="n">
+        <v>362.09</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-26.19</v>
+      </c>
+      <c r="F32" t="n">
+        <v>336.5</v>
+      </c>
+      <c r="G32" t="n">
+        <v>362.09</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-25.59</v>
+      </c>
+      <c r="I32" t="n">
+        <v>326.85</v>
+      </c>
+      <c r="J32" t="n">
+        <v>335.9</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-9.050000000000001</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>7.23</v>
       </c>
     </row>
   </sheetData>
@@ -46203,7 +46775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47836,6 +48408,58 @@
       </c>
       <c r="N31" t="n">
         <v>6.51</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>118</v>
+      </c>
+      <c r="D32" t="n">
+        <v>126.69</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-8.69</v>
+      </c>
+      <c r="F32" t="n">
+        <v>118.58</v>
+      </c>
+      <c r="G32" t="n">
+        <v>126.69</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-8.109999999999999</v>
+      </c>
+      <c r="I32" t="n">
+        <v>116.64</v>
+      </c>
+      <c r="J32" t="n">
+        <v>118</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>6.86</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -37388,31 +37388,31 @@
         </is>
       </c>
       <c r="C711" t="n">
-        <v>414.8</v>
+        <v>412.5</v>
       </c>
       <c r="D711" t="n">
         <v>418.25</v>
       </c>
       <c r="E711" t="n">
-        <v>-3.45</v>
+        <v>-5.75</v>
       </c>
       <c r="F711" t="n">
-        <v>420.6</v>
+        <v>419.2</v>
       </c>
       <c r="G711" t="n">
         <v>439.96</v>
       </c>
       <c r="H711" t="n">
-        <v>-19.36</v>
+        <v>-20.76</v>
       </c>
       <c r="I711" t="n">
-        <v>414.55</v>
+        <v>412.5</v>
       </c>
       <c r="J711" t="n">
         <v>414.8</v>
       </c>
       <c r="K711" t="n">
-        <v>-0.25</v>
+        <v>-2.3</v>
       </c>
       <c r="L711" t="inlineStr">
         <is>
@@ -37425,7 +37425,7 @@
         </is>
       </c>
       <c r="N711" t="n">
-        <v>0.82</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="712">
@@ -37440,31 +37440,31 @@
         </is>
       </c>
       <c r="C712" t="n">
-        <v>335.9</v>
+        <v>326.85</v>
       </c>
       <c r="D712" t="n">
         <v>362.09</v>
       </c>
       <c r="E712" t="n">
-        <v>-26.19</v>
+        <v>-35.24</v>
       </c>
       <c r="F712" t="n">
-        <v>336.5</v>
+        <v>329.75</v>
       </c>
       <c r="G712" t="n">
         <v>362.09</v>
       </c>
       <c r="H712" t="n">
-        <v>-25.59</v>
+        <v>-32.34</v>
       </c>
       <c r="I712" t="n">
-        <v>326.85</v>
+        <v>325.7</v>
       </c>
       <c r="J712" t="n">
         <v>335.9</v>
       </c>
       <c r="K712" t="n">
-        <v>-9.050000000000001</v>
+        <v>-10.2</v>
       </c>
       <c r="L712" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         </is>
       </c>
       <c r="N712" t="n">
-        <v>7.23</v>
+        <v>9.73</v>
       </c>
     </row>
     <row r="713">
@@ -37492,31 +37492,31 @@
         </is>
       </c>
       <c r="C713" t="n">
-        <v>11409</v>
+        <v>11217</v>
       </c>
       <c r="D713" t="n">
         <v>12523.22</v>
       </c>
       <c r="E713" t="n">
-        <v>-1114.22</v>
+        <v>-1306.22</v>
       </c>
       <c r="F713" t="n">
-        <v>11434</v>
+        <v>11297.53</v>
       </c>
       <c r="G713" t="n">
         <v>12523.22</v>
       </c>
       <c r="H713" t="n">
-        <v>-1089.22</v>
+        <v>-1225.69</v>
       </c>
       <c r="I713" t="n">
-        <v>11227</v>
+        <v>11006.22</v>
       </c>
       <c r="J713" t="n">
         <v>11366.84</v>
       </c>
       <c r="K713" t="n">
-        <v>-139.84</v>
+        <v>-360.62</v>
       </c>
       <c r="L713" t="inlineStr">
         <is>
@@ -37525,11 +37525,11 @@
       </c>
       <c r="M713" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N713" t="n">
-        <v>8.9</v>
+        <v>10.43</v>
       </c>
     </row>
     <row r="714">
@@ -37544,31 +37544,31 @@
         </is>
       </c>
       <c r="C714" t="n">
-        <v>568</v>
+        <v>548.15</v>
       </c>
       <c r="D714" t="n">
         <v>603.2</v>
       </c>
       <c r="E714" t="n">
-        <v>-35.2</v>
+        <v>-55.05</v>
       </c>
       <c r="F714" t="n">
-        <v>574.15</v>
+        <v>552</v>
       </c>
       <c r="G714" t="n">
         <v>603.71</v>
       </c>
       <c r="H714" t="n">
-        <v>-29.56</v>
+        <v>-51.71</v>
       </c>
       <c r="I714" t="n">
-        <v>543.65</v>
+        <v>543.6</v>
       </c>
       <c r="J714" t="n">
         <v>568</v>
       </c>
       <c r="K714" t="n">
-        <v>-24.35</v>
+        <v>-24.4</v>
       </c>
       <c r="L714" t="inlineStr">
         <is>
@@ -37581,7 +37581,7 @@
         </is>
       </c>
       <c r="N714" t="n">
-        <v>5.84</v>
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="715">
@@ -37596,31 +37596,31 @@
         </is>
       </c>
       <c r="C715" t="n">
-        <v>118</v>
+        <v>117.27</v>
       </c>
       <c r="D715" t="n">
         <v>126.69</v>
       </c>
       <c r="E715" t="n">
-        <v>-8.69</v>
+        <v>-9.42</v>
       </c>
       <c r="F715" t="n">
-        <v>118.58</v>
+        <v>117.5</v>
       </c>
       <c r="G715" t="n">
         <v>126.69</v>
       </c>
       <c r="H715" t="n">
-        <v>-8.109999999999999</v>
+        <v>-9.19</v>
       </c>
       <c r="I715" t="n">
-        <v>116.64</v>
+        <v>116.5</v>
       </c>
       <c r="J715" t="n">
         <v>118</v>
       </c>
       <c r="K715" t="n">
-        <v>-1.36</v>
+        <v>-1.5</v>
       </c>
       <c r="L715" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         </is>
       </c>
       <c r="N715" t="n">
-        <v>6.86</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="716">
@@ -37648,31 +37648,31 @@
         </is>
       </c>
       <c r="C716" t="n">
-        <v>2181.1</v>
+        <v>2270.1</v>
       </c>
       <c r="D716" t="n">
         <v>2489.97</v>
       </c>
       <c r="E716" t="n">
-        <v>-308.87</v>
+        <v>-219.87</v>
       </c>
       <c r="F716" t="n">
-        <v>2229</v>
+        <v>2270.1</v>
       </c>
       <c r="G716" t="n">
         <v>2489.97</v>
       </c>
       <c r="H716" t="n">
-        <v>-260.97</v>
+        <v>-219.87</v>
       </c>
       <c r="I716" t="n">
-        <v>2178.7</v>
+        <v>2146.3</v>
       </c>
       <c r="J716" t="n">
         <v>2142.17</v>
       </c>
       <c r="K716" t="n">
-        <v>36.53</v>
+        <v>4.13</v>
       </c>
       <c r="L716" t="inlineStr">
         <is>
@@ -37685,7 +37685,7 @@
         </is>
       </c>
       <c r="N716" t="n">
-        <v>12.4</v>
+        <v>8.83</v>
       </c>
     </row>
     <row r="717">
@@ -37700,31 +37700,31 @@
         </is>
       </c>
       <c r="C717" t="n">
-        <v>745</v>
+        <v>732.75</v>
       </c>
       <c r="D717" t="n">
         <v>798.89</v>
       </c>
       <c r="E717" t="n">
-        <v>-53.89</v>
+        <v>-66.14</v>
       </c>
       <c r="F717" t="n">
-        <v>755</v>
+        <v>743</v>
       </c>
       <c r="G717" t="n">
         <v>798.89</v>
       </c>
       <c r="H717" t="n">
-        <v>-43.89</v>
+        <v>-55.89</v>
       </c>
       <c r="I717" t="n">
-        <v>741</v>
+        <v>722.6</v>
       </c>
       <c r="J717" t="n">
         <v>740.17</v>
       </c>
       <c r="K717" t="n">
-        <v>0.83</v>
+        <v>-17.57</v>
       </c>
       <c r="L717" t="inlineStr">
         <is>
@@ -37733,11 +37733,11 @@
       </c>
       <c r="M717" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N717" t="n">
-        <v>6.75</v>
+        <v>8.279999999999999</v>
       </c>
     </row>
     <row r="718">
@@ -37752,31 +37752,31 @@
         </is>
       </c>
       <c r="C718" t="n">
-        <v>995</v>
+        <v>1010</v>
       </c>
       <c r="D718" t="n">
         <v>1120.93</v>
       </c>
       <c r="E718" t="n">
-        <v>-125.93</v>
+        <v>-110.93</v>
       </c>
       <c r="F718" t="n">
-        <v>1009.8</v>
+        <v>1010</v>
       </c>
       <c r="G718" t="n">
         <v>1120.93</v>
       </c>
       <c r="H718" t="n">
-        <v>-111.13</v>
+        <v>-110.93</v>
       </c>
       <c r="I718" t="n">
-        <v>993.2</v>
+        <v>988.7</v>
       </c>
       <c r="J718" t="n">
         <v>995</v>
       </c>
       <c r="K718" t="n">
-        <v>-1.8</v>
+        <v>-6.3</v>
       </c>
       <c r="L718" t="inlineStr">
         <is>
@@ -37789,7 +37789,7 @@
         </is>
       </c>
       <c r="N718" t="n">
-        <v>11.23</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="719">
@@ -37804,31 +37804,31 @@
         </is>
       </c>
       <c r="C719" t="n">
-        <v>3209</v>
+        <v>3260</v>
       </c>
       <c r="D719" t="n">
         <v>4147.04</v>
       </c>
       <c r="E719" t="n">
-        <v>-938.04</v>
+        <v>-887.04</v>
       </c>
       <c r="F719" t="n">
-        <v>3268</v>
+        <v>3314.9</v>
       </c>
       <c r="G719" t="n">
         <v>4147.04</v>
       </c>
       <c r="H719" t="n">
-        <v>-879.04</v>
+        <v>-832.14</v>
       </c>
       <c r="I719" t="n">
-        <v>3155.5</v>
+        <v>3230.1</v>
       </c>
       <c r="J719" t="n">
         <v>3202.25</v>
       </c>
       <c r="K719" t="n">
-        <v>-46.75</v>
+        <v>27.85</v>
       </c>
       <c r="L719" t="inlineStr">
         <is>
@@ -37841,7 +37841,7 @@
         </is>
       </c>
       <c r="N719" t="n">
-        <v>22.62</v>
+        <v>21.39</v>
       </c>
     </row>
   </sheetData>
@@ -38254,31 +38254,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>745</v>
+        <v>732.75</v>
       </c>
       <c r="D8" t="n">
         <v>798.89</v>
       </c>
       <c r="E8" t="n">
-        <v>-53.89</v>
+        <v>-66.14</v>
       </c>
       <c r="F8" t="n">
-        <v>755</v>
+        <v>743</v>
       </c>
       <c r="G8" t="n">
         <v>798.89</v>
       </c>
       <c r="H8" t="n">
-        <v>-43.89</v>
+        <v>-55.89</v>
       </c>
       <c r="I8" t="n">
-        <v>741</v>
+        <v>722.6</v>
       </c>
       <c r="J8" t="n">
         <v>740.17</v>
       </c>
       <c r="K8" t="n">
-        <v>0.83</v>
+        <v>-17.57</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -38287,11 +38287,11 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>6.75</v>
+        <v>8.279999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -43346,31 +43346,31 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>335.9</v>
+        <v>326.85</v>
       </c>
       <c r="D32" t="n">
         <v>362.09</v>
       </c>
       <c r="E32" t="n">
-        <v>-26.19</v>
+        <v>-35.24</v>
       </c>
       <c r="F32" t="n">
-        <v>336.5</v>
+        <v>329.75</v>
       </c>
       <c r="G32" t="n">
         <v>362.09</v>
       </c>
       <c r="H32" t="n">
-        <v>-25.59</v>
+        <v>-32.34</v>
       </c>
       <c r="I32" t="n">
-        <v>326.85</v>
+        <v>325.7</v>
       </c>
       <c r="J32" t="n">
         <v>335.9</v>
       </c>
       <c r="K32" t="n">
-        <v>-9.050000000000001</v>
+        <v>-10.2</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -43383,7 +43383,7 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>7.23</v>
+        <v>9.73</v>
       </c>
     </row>
   </sheetData>
@@ -48422,31 +48422,31 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>118</v>
+        <v>117.27</v>
       </c>
       <c r="D32" t="n">
         <v>126.69</v>
       </c>
       <c r="E32" t="n">
-        <v>-8.69</v>
+        <v>-9.42</v>
       </c>
       <c r="F32" t="n">
-        <v>118.58</v>
+        <v>117.5</v>
       </c>
       <c r="G32" t="n">
         <v>126.69</v>
       </c>
       <c r="H32" t="n">
-        <v>-8.109999999999999</v>
+        <v>-9.19</v>
       </c>
       <c r="I32" t="n">
-        <v>116.64</v>
+        <v>116.5</v>
       </c>
       <c r="J32" t="n">
         <v>118</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.36</v>
+        <v>-1.5</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -48459,7 +48459,7 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>6.86</v>
+        <v>7.44</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N719"/>
+  <dimension ref="A1:N728"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37842,6 +37842,474 @@
       </c>
       <c r="N719" t="n">
         <v>21.39</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C720" t="n">
+        <v>342</v>
+      </c>
+      <c r="D720" t="n">
+        <v>311.19</v>
+      </c>
+      <c r="E720" t="n">
+        <v>30.81</v>
+      </c>
+      <c r="F720" t="n">
+        <v>342</v>
+      </c>
+      <c r="G720" t="n">
+        <v>326.69</v>
+      </c>
+      <c r="H720" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="I720" t="n">
+        <v>334.65</v>
+      </c>
+      <c r="J720" t="n">
+        <v>333.75</v>
+      </c>
+      <c r="K720" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L720" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M720" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N720" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C721" t="n">
+        <v>2195</v>
+      </c>
+      <c r="D721" t="n">
+        <v>2017.19</v>
+      </c>
+      <c r="E721" t="n">
+        <v>177.81</v>
+      </c>
+      <c r="F721" t="n">
+        <v>2199.3</v>
+      </c>
+      <c r="G721" t="n">
+        <v>2056.08</v>
+      </c>
+      <c r="H721" t="n">
+        <v>143.22</v>
+      </c>
+      <c r="I721" t="n">
+        <v>2159.9</v>
+      </c>
+      <c r="J721" t="n">
+        <v>2099.05</v>
+      </c>
+      <c r="K721" t="n">
+        <v>60.85</v>
+      </c>
+      <c r="L721" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M721" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N721" t="n">
+        <v>8.81</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C722" t="n">
+        <v>3262.6</v>
+      </c>
+      <c r="D722" t="n">
+        <v>2585.25</v>
+      </c>
+      <c r="E722" t="n">
+        <v>677.35</v>
+      </c>
+      <c r="F722" t="n">
+        <v>3289.8</v>
+      </c>
+      <c r="G722" t="n">
+        <v>3126.44</v>
+      </c>
+      <c r="H722" t="n">
+        <v>163.36</v>
+      </c>
+      <c r="I722" t="n">
+        <v>3212.8</v>
+      </c>
+      <c r="J722" t="n">
+        <v>3194.38</v>
+      </c>
+      <c r="K722" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="L722" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M722" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N722" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C723" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D723" t="n">
+        <v>914.61</v>
+      </c>
+      <c r="E723" t="n">
+        <v>92.39</v>
+      </c>
+      <c r="F723" t="n">
+        <v>1025</v>
+      </c>
+      <c r="G723" t="n">
+        <v>960.98</v>
+      </c>
+      <c r="H723" t="n">
+        <v>64.02</v>
+      </c>
+      <c r="I723" t="n">
+        <v>995.6</v>
+      </c>
+      <c r="J723" t="n">
+        <v>981.71</v>
+      </c>
+      <c r="K723" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="L723" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M723" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N723" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C724" t="n">
+        <v>1805</v>
+      </c>
+      <c r="D724" t="n">
+        <v>1646.63</v>
+      </c>
+      <c r="E724" t="n">
+        <v>158.37</v>
+      </c>
+      <c r="F724" t="n">
+        <v>1806.4</v>
+      </c>
+      <c r="G724" t="n">
+        <v>1646.63</v>
+      </c>
+      <c r="H724" t="n">
+        <v>159.77</v>
+      </c>
+      <c r="I724" t="n">
+        <v>1773.7</v>
+      </c>
+      <c r="J724" t="n">
+        <v>1711.38</v>
+      </c>
+      <c r="K724" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="L724" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M724" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N724" t="n">
+        <v>9.619999999999999</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C725" t="n">
+        <v>412.65</v>
+      </c>
+      <c r="D725" t="n">
+        <v>410.23</v>
+      </c>
+      <c r="E725" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="F725" t="n">
+        <v>417.8</v>
+      </c>
+      <c r="G725" t="n">
+        <v>410.23</v>
+      </c>
+      <c r="H725" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="I725" t="n">
+        <v>412.55</v>
+      </c>
+      <c r="J725" t="n">
+        <v>400.19</v>
+      </c>
+      <c r="K725" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="L725" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M725" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N725" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C726" t="n">
+        <v>117</v>
+      </c>
+      <c r="D726" t="n">
+        <v>109.17</v>
+      </c>
+      <c r="E726" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="F726" t="n">
+        <v>118.74</v>
+      </c>
+      <c r="G726" t="n">
+        <v>111.44</v>
+      </c>
+      <c r="H726" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="I726" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="J726" t="n">
+        <v>113.84</v>
+      </c>
+      <c r="K726" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="L726" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M726" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N726" t="n">
+        <v>7.17</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C727" t="n">
+        <v>565</v>
+      </c>
+      <c r="D727" t="n">
+        <v>517.55</v>
+      </c>
+      <c r="E727" t="n">
+        <v>47.45</v>
+      </c>
+      <c r="F727" t="n">
+        <v>573.95</v>
+      </c>
+      <c r="G727" t="n">
+        <v>518.02</v>
+      </c>
+      <c r="H727" t="n">
+        <v>55.93</v>
+      </c>
+      <c r="I727" t="n">
+        <v>563.2</v>
+      </c>
+      <c r="J727" t="n">
+        <v>536.4</v>
+      </c>
+      <c r="K727" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="L727" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M727" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N727" t="n">
+        <v>9.17</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C728" t="n">
+        <v>736.25</v>
+      </c>
+      <c r="D728" t="n">
+        <v>680.7</v>
+      </c>
+      <c r="E728" t="n">
+        <v>55.55</v>
+      </c>
+      <c r="F728" t="n">
+        <v>749.4</v>
+      </c>
+      <c r="G728" t="n">
+        <v>680.7</v>
+      </c>
+      <c r="H728" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="I728" t="n">
+        <v>735.75</v>
+      </c>
+      <c r="J728" t="n">
+        <v>709.86</v>
+      </c>
+      <c r="K728" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="L728" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M728" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N728" t="n">
+        <v>8.16</v>
       </c>
     </row>
   </sheetData>
@@ -37855,7 +38323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38292,6 +38760,58 @@
       </c>
       <c r="N8" t="n">
         <v>8.279999999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>736.25</v>
+      </c>
+      <c r="D9" t="n">
+        <v>680.7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>55.55</v>
+      </c>
+      <c r="F9" t="n">
+        <v>749.4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>680.7</v>
+      </c>
+      <c r="H9" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>735.75</v>
+      </c>
+      <c r="J9" t="n">
+        <v>709.86</v>
+      </c>
+      <c r="K9" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>8.16</v>
       </c>
     </row>
   </sheetData>
@@ -41699,7 +42219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43384,6 +43904,58 @@
       </c>
       <c r="N32" t="n">
         <v>9.73</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>342</v>
+      </c>
+      <c r="D33" t="n">
+        <v>311.19</v>
+      </c>
+      <c r="E33" t="n">
+        <v>30.81</v>
+      </c>
+      <c r="F33" t="n">
+        <v>342</v>
+      </c>
+      <c r="G33" t="n">
+        <v>326.69</v>
+      </c>
+      <c r="H33" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="I33" t="n">
+        <v>334.65</v>
+      </c>
+      <c r="J33" t="n">
+        <v>333.75</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>🟢 HIGH CONVICTION BUY</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>9.9</v>
       </c>
     </row>
   </sheetData>
@@ -46775,7 +47347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48460,6 +49032,58 @@
       </c>
       <c r="N32" t="n">
         <v>7.44</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>117</v>
+      </c>
+      <c r="D33" t="n">
+        <v>109.17</v>
+      </c>
+      <c r="E33" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="F33" t="n">
+        <v>118.74</v>
+      </c>
+      <c r="G33" t="n">
+        <v>111.44</v>
+      </c>
+      <c r="H33" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="I33" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="J33" t="n">
+        <v>113.84</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>7.17</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -37856,31 +37856,31 @@
         </is>
       </c>
       <c r="C720" t="n">
-        <v>342</v>
+        <v>335.9</v>
       </c>
       <c r="D720" t="n">
         <v>311.19</v>
       </c>
       <c r="E720" t="n">
-        <v>30.81</v>
+        <v>24.71</v>
       </c>
       <c r="F720" t="n">
-        <v>342</v>
+        <v>336.5</v>
       </c>
       <c r="G720" t="n">
         <v>326.69</v>
       </c>
       <c r="H720" t="n">
-        <v>15.31</v>
+        <v>9.81</v>
       </c>
       <c r="I720" t="n">
-        <v>334.65</v>
+        <v>326.85</v>
       </c>
       <c r="J720" t="n">
         <v>333.75</v>
       </c>
       <c r="K720" t="n">
-        <v>0.9</v>
+        <v>-6.9</v>
       </c>
       <c r="L720" t="inlineStr">
         <is>
@@ -37893,7 +37893,7 @@
         </is>
       </c>
       <c r="N720" t="n">
-        <v>9.9</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="721">
@@ -37908,31 +37908,31 @@
         </is>
       </c>
       <c r="C721" t="n">
-        <v>2195</v>
+        <v>2181.1</v>
       </c>
       <c r="D721" t="n">
         <v>2017.19</v>
       </c>
       <c r="E721" t="n">
-        <v>177.81</v>
+        <v>163.91</v>
       </c>
       <c r="F721" t="n">
-        <v>2199.3</v>
+        <v>2229</v>
       </c>
       <c r="G721" t="n">
         <v>2056.08</v>
       </c>
       <c r="H721" t="n">
-        <v>143.22</v>
+        <v>172.92</v>
       </c>
       <c r="I721" t="n">
-        <v>2159.9</v>
+        <v>2178.7</v>
       </c>
       <c r="J721" t="n">
         <v>2099.05</v>
       </c>
       <c r="K721" t="n">
-        <v>60.85</v>
+        <v>79.65000000000001</v>
       </c>
       <c r="L721" t="inlineStr">
         <is>
@@ -37945,7 +37945,7 @@
         </is>
       </c>
       <c r="N721" t="n">
-        <v>8.81</v>
+        <v>8.130000000000001</v>
       </c>
     </row>
     <row r="722">
@@ -37960,31 +37960,31 @@
         </is>
       </c>
       <c r="C722" t="n">
-        <v>3262.6</v>
+        <v>3209</v>
       </c>
       <c r="D722" t="n">
         <v>2585.25</v>
       </c>
       <c r="E722" t="n">
-        <v>677.35</v>
+        <v>623.75</v>
       </c>
       <c r="F722" t="n">
-        <v>3289.8</v>
+        <v>3268</v>
       </c>
       <c r="G722" t="n">
         <v>3126.44</v>
       </c>
       <c r="H722" t="n">
-        <v>163.36</v>
+        <v>141.56</v>
       </c>
       <c r="I722" t="n">
-        <v>3212.8</v>
+        <v>3155.5</v>
       </c>
       <c r="J722" t="n">
         <v>3194.38</v>
       </c>
       <c r="K722" t="n">
-        <v>18.42</v>
+        <v>-38.88</v>
       </c>
       <c r="L722" t="inlineStr">
         <is>
@@ -37997,7 +37997,7 @@
         </is>
       </c>
       <c r="N722" t="n">
-        <v>26.2</v>
+        <v>24.13</v>
       </c>
     </row>
     <row r="723">
@@ -38012,31 +38012,31 @@
         </is>
       </c>
       <c r="C723" t="n">
-        <v>1007</v>
+        <v>995</v>
       </c>
       <c r="D723" t="n">
         <v>914.61</v>
       </c>
       <c r="E723" t="n">
-        <v>92.39</v>
+        <v>80.39</v>
       </c>
       <c r="F723" t="n">
-        <v>1025</v>
+        <v>1009.8</v>
       </c>
       <c r="G723" t="n">
         <v>960.98</v>
       </c>
       <c r="H723" t="n">
-        <v>64.02</v>
+        <v>48.82</v>
       </c>
       <c r="I723" t="n">
-        <v>995.6</v>
+        <v>993.2</v>
       </c>
       <c r="J723" t="n">
         <v>981.71</v>
       </c>
       <c r="K723" t="n">
-        <v>13.89</v>
+        <v>11.49</v>
       </c>
       <c r="L723" t="inlineStr">
         <is>
@@ -38049,7 +38049,7 @@
         </is>
       </c>
       <c r="N723" t="n">
-        <v>10.1</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="724">
@@ -38064,31 +38064,31 @@
         </is>
       </c>
       <c r="C724" t="n">
-        <v>1805</v>
+        <v>1793</v>
       </c>
       <c r="D724" t="n">
         <v>1646.63</v>
       </c>
       <c r="E724" t="n">
-        <v>158.37</v>
+        <v>146.37</v>
       </c>
       <c r="F724" t="n">
-        <v>1806.4</v>
+        <v>1804.4</v>
       </c>
       <c r="G724" t="n">
         <v>1646.63</v>
       </c>
       <c r="H724" t="n">
-        <v>159.77</v>
+        <v>157.77</v>
       </c>
       <c r="I724" t="n">
-        <v>1773.7</v>
+        <v>1745</v>
       </c>
       <c r="J724" t="n">
         <v>1711.38</v>
       </c>
       <c r="K724" t="n">
-        <v>62.32</v>
+        <v>33.62</v>
       </c>
       <c r="L724" t="inlineStr">
         <is>
@@ -38101,7 +38101,7 @@
         </is>
       </c>
       <c r="N724" t="n">
-        <v>9.619999999999999</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="725">
@@ -38116,31 +38116,31 @@
         </is>
       </c>
       <c r="C725" t="n">
-        <v>412.65</v>
+        <v>414.8</v>
       </c>
       <c r="D725" t="n">
         <v>410.23</v>
       </c>
       <c r="E725" t="n">
-        <v>2.42</v>
+        <v>4.57</v>
       </c>
       <c r="F725" t="n">
-        <v>417.8</v>
+        <v>420.6</v>
       </c>
       <c r="G725" t="n">
         <v>410.23</v>
       </c>
       <c r="H725" t="n">
-        <v>7.57</v>
+        <v>10.37</v>
       </c>
       <c r="I725" t="n">
-        <v>412.55</v>
+        <v>414.55</v>
       </c>
       <c r="J725" t="n">
         <v>400.19</v>
       </c>
       <c r="K725" t="n">
-        <v>12.36</v>
+        <v>14.36</v>
       </c>
       <c r="L725" t="inlineStr">
         <is>
@@ -38153,7 +38153,7 @@
         </is>
       </c>
       <c r="N725" t="n">
-        <v>0.59</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="726">
@@ -38168,31 +38168,31 @@
         </is>
       </c>
       <c r="C726" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D726" t="n">
         <v>109.17</v>
       </c>
       <c r="E726" t="n">
-        <v>7.83</v>
+        <v>8.83</v>
       </c>
       <c r="F726" t="n">
-        <v>118.74</v>
+        <v>118.58</v>
       </c>
       <c r="G726" t="n">
         <v>111.44</v>
       </c>
       <c r="H726" t="n">
-        <v>7.3</v>
+        <v>7.14</v>
       </c>
       <c r="I726" t="n">
-        <v>116.7</v>
+        <v>116.64</v>
       </c>
       <c r="J726" t="n">
         <v>113.84</v>
       </c>
       <c r="K726" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="L726" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         </is>
       </c>
       <c r="N726" t="n">
-        <v>7.17</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="727">
@@ -38220,31 +38220,31 @@
         </is>
       </c>
       <c r="C727" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D727" t="n">
         <v>517.55</v>
       </c>
       <c r="E727" t="n">
-        <v>47.45</v>
+        <v>50.45</v>
       </c>
       <c r="F727" t="n">
-        <v>573.95</v>
+        <v>574.15</v>
       </c>
       <c r="G727" t="n">
         <v>518.02</v>
       </c>
       <c r="H727" t="n">
-        <v>55.93</v>
+        <v>56.13</v>
       </c>
       <c r="I727" t="n">
-        <v>563.2</v>
+        <v>543.65</v>
       </c>
       <c r="J727" t="n">
         <v>536.4</v>
       </c>
       <c r="K727" t="n">
-        <v>26.8</v>
+        <v>7.25</v>
       </c>
       <c r="L727" t="inlineStr">
         <is>
@@ -38257,7 +38257,7 @@
         </is>
       </c>
       <c r="N727" t="n">
-        <v>9.17</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="728">
@@ -38272,31 +38272,31 @@
         </is>
       </c>
       <c r="C728" t="n">
-        <v>736.25</v>
+        <v>745</v>
       </c>
       <c r="D728" t="n">
         <v>680.7</v>
       </c>
       <c r="E728" t="n">
-        <v>55.55</v>
+        <v>64.3</v>
       </c>
       <c r="F728" t="n">
-        <v>749.4</v>
+        <v>755</v>
       </c>
       <c r="G728" t="n">
         <v>680.7</v>
       </c>
       <c r="H728" t="n">
-        <v>68.7</v>
+        <v>74.3</v>
       </c>
       <c r="I728" t="n">
-        <v>735.75</v>
+        <v>741</v>
       </c>
       <c r="J728" t="n">
         <v>709.86</v>
       </c>
       <c r="K728" t="n">
-        <v>25.89</v>
+        <v>31.14</v>
       </c>
       <c r="L728" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         </is>
       </c>
       <c r="N728" t="n">
-        <v>8.16</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -38774,31 +38774,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>736.25</v>
+        <v>745</v>
       </c>
       <c r="D9" t="n">
         <v>680.7</v>
       </c>
       <c r="E9" t="n">
-        <v>55.55</v>
+        <v>64.3</v>
       </c>
       <c r="F9" t="n">
-        <v>749.4</v>
+        <v>755</v>
       </c>
       <c r="G9" t="n">
         <v>680.7</v>
       </c>
       <c r="H9" t="n">
-        <v>68.7</v>
+        <v>74.3</v>
       </c>
       <c r="I9" t="n">
-        <v>735.75</v>
+        <v>741</v>
       </c>
       <c r="J9" t="n">
         <v>709.86</v>
       </c>
       <c r="K9" t="n">
-        <v>25.89</v>
+        <v>31.14</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -38811,7 +38811,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>8.16</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -43918,31 +43918,31 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>342</v>
+        <v>335.9</v>
       </c>
       <c r="D33" t="n">
         <v>311.19</v>
       </c>
       <c r="E33" t="n">
-        <v>30.81</v>
+        <v>24.71</v>
       </c>
       <c r="F33" t="n">
-        <v>342</v>
+        <v>336.5</v>
       </c>
       <c r="G33" t="n">
         <v>326.69</v>
       </c>
       <c r="H33" t="n">
-        <v>15.31</v>
+        <v>9.81</v>
       </c>
       <c r="I33" t="n">
-        <v>334.65</v>
+        <v>326.85</v>
       </c>
       <c r="J33" t="n">
         <v>333.75</v>
       </c>
       <c r="K33" t="n">
-        <v>0.9</v>
+        <v>-6.9</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>9.9</v>
+        <v>7.94</v>
       </c>
     </row>
   </sheetData>
@@ -49046,31 +49046,31 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D33" t="n">
         <v>109.17</v>
       </c>
       <c r="E33" t="n">
-        <v>7.83</v>
+        <v>8.83</v>
       </c>
       <c r="F33" t="n">
-        <v>118.74</v>
+        <v>118.58</v>
       </c>
       <c r="G33" t="n">
         <v>111.44</v>
       </c>
       <c r="H33" t="n">
-        <v>7.3</v>
+        <v>7.14</v>
       </c>
       <c r="I33" t="n">
-        <v>116.7</v>
+        <v>116.64</v>
       </c>
       <c r="J33" t="n">
         <v>113.84</v>
       </c>
       <c r="K33" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -49083,7 +49083,7 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>7.17</v>
+        <v>8.09</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N728"/>
+  <dimension ref="A1:N738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38310,6 +38310,526 @@
       </c>
       <c r="N728" t="n">
         <v>9.449999999999999</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C729" t="n">
+        <v>413.25</v>
+      </c>
+      <c r="D729" t="n">
+        <v>421.2</v>
+      </c>
+      <c r="E729" t="n">
+        <v>-7.95</v>
+      </c>
+      <c r="F729" t="n">
+        <v>417.25</v>
+      </c>
+      <c r="G729" t="n">
+        <v>435.67</v>
+      </c>
+      <c r="H729" t="n">
+        <v>-18.42</v>
+      </c>
+      <c r="I729" t="n">
+        <v>411.35</v>
+      </c>
+      <c r="J729" t="n">
+        <v>413.25</v>
+      </c>
+      <c r="K729" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="L729" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M729" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N729" t="n">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C730" t="n">
+        <v>118.3</v>
+      </c>
+      <c r="D730" t="n">
+        <v>129.19</v>
+      </c>
+      <c r="E730" t="n">
+        <v>-10.89</v>
+      </c>
+      <c r="F730" t="n">
+        <v>118.9</v>
+      </c>
+      <c r="G730" t="n">
+        <v>129.19</v>
+      </c>
+      <c r="H730" t="n">
+        <v>-10.29</v>
+      </c>
+      <c r="I730" t="n">
+        <v>116.61</v>
+      </c>
+      <c r="J730" t="n">
+        <v>118.3</v>
+      </c>
+      <c r="K730" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="L730" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M730" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N730" t="n">
+        <v>8.43</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C731" t="n">
+        <v>342.65</v>
+      </c>
+      <c r="D731" t="n">
+        <v>372.81</v>
+      </c>
+      <c r="E731" t="n">
+        <v>-30.16</v>
+      </c>
+      <c r="F731" t="n">
+        <v>344.4</v>
+      </c>
+      <c r="G731" t="n">
+        <v>372.81</v>
+      </c>
+      <c r="H731" t="n">
+        <v>-28.41</v>
+      </c>
+      <c r="I731" t="n">
+        <v>340.55</v>
+      </c>
+      <c r="J731" t="n">
+        <v>342.65</v>
+      </c>
+      <c r="K731" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="L731" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M731" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N731" t="n">
+        <v>8.09</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C732" t="n">
+        <v>3374</v>
+      </c>
+      <c r="D732" t="n">
+        <v>4234.94</v>
+      </c>
+      <c r="E732" t="n">
+        <v>-860.9400000000001</v>
+      </c>
+      <c r="F732" t="n">
+        <v>3374</v>
+      </c>
+      <c r="G732" t="n">
+        <v>4234.94</v>
+      </c>
+      <c r="H732" t="n">
+        <v>-860.9400000000001</v>
+      </c>
+      <c r="I732" t="n">
+        <v>3237.5</v>
+      </c>
+      <c r="J732" t="n">
+        <v>3374</v>
+      </c>
+      <c r="K732" t="n">
+        <v>-136.5</v>
+      </c>
+      <c r="L732" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M732" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N732" t="n">
+        <v>20.33</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C733" t="n">
+        <v>1886.3</v>
+      </c>
+      <c r="D733" t="n">
+        <v>2070.4</v>
+      </c>
+      <c r="E733" t="n">
+        <v>-184.1</v>
+      </c>
+      <c r="F733" t="n">
+        <v>1904.9</v>
+      </c>
+      <c r="G733" t="n">
+        <v>2070.4</v>
+      </c>
+      <c r="H733" t="n">
+        <v>-165.5</v>
+      </c>
+      <c r="I733" t="n">
+        <v>1793</v>
+      </c>
+      <c r="J733" t="n">
+        <v>1856.48</v>
+      </c>
+      <c r="K733" t="n">
+        <v>-63.48</v>
+      </c>
+      <c r="L733" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M733" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N733" t="n">
+        <v>8.890000000000001</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C734" t="n">
+        <v>1042.5</v>
+      </c>
+      <c r="D734" t="n">
+        <v>1148.51</v>
+      </c>
+      <c r="E734" t="n">
+        <v>-106.01</v>
+      </c>
+      <c r="F734" t="n">
+        <v>1058</v>
+      </c>
+      <c r="G734" t="n">
+        <v>1148.51</v>
+      </c>
+      <c r="H734" t="n">
+        <v>-90.51000000000001</v>
+      </c>
+      <c r="I734" t="n">
+        <v>1009.2</v>
+      </c>
+      <c r="J734" t="n">
+        <v>1042.5</v>
+      </c>
+      <c r="K734" t="n">
+        <v>-33.3</v>
+      </c>
+      <c r="L734" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M734" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N734" t="n">
+        <v>9.23</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C735" t="n">
+        <v>11449</v>
+      </c>
+      <c r="D735" t="n">
+        <v>12466.15</v>
+      </c>
+      <c r="E735" t="n">
+        <v>-1017.15</v>
+      </c>
+      <c r="F735" t="n">
+        <v>11449</v>
+      </c>
+      <c r="G735" t="n">
+        <v>12466.15</v>
+      </c>
+      <c r="H735" t="n">
+        <v>-1017.15</v>
+      </c>
+      <c r="I735" t="n">
+        <v>11195</v>
+      </c>
+      <c r="J735" t="n">
+        <v>11449</v>
+      </c>
+      <c r="K735" t="n">
+        <v>-254</v>
+      </c>
+      <c r="L735" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M735" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N735" t="n">
+        <v>8.16</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C736" t="n">
+        <v>572.5</v>
+      </c>
+      <c r="D736" t="n">
+        <v>633.33</v>
+      </c>
+      <c r="E736" t="n">
+        <v>-60.83</v>
+      </c>
+      <c r="F736" t="n">
+        <v>576.7</v>
+      </c>
+      <c r="G736" t="n">
+        <v>633.33</v>
+      </c>
+      <c r="H736" t="n">
+        <v>-56.63</v>
+      </c>
+      <c r="I736" t="n">
+        <v>564.05</v>
+      </c>
+      <c r="J736" t="n">
+        <v>563.5599999999999</v>
+      </c>
+      <c r="K736" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="L736" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M736" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N736" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C737" t="n">
+        <v>2195</v>
+      </c>
+      <c r="D737" t="n">
+        <v>2392.35</v>
+      </c>
+      <c r="E737" t="n">
+        <v>-197.35</v>
+      </c>
+      <c r="F737" t="n">
+        <v>2204</v>
+      </c>
+      <c r="G737" t="n">
+        <v>2392.35</v>
+      </c>
+      <c r="H737" t="n">
+        <v>-188.35</v>
+      </c>
+      <c r="I737" t="n">
+        <v>2178</v>
+      </c>
+      <c r="J737" t="n">
+        <v>2162.51</v>
+      </c>
+      <c r="K737" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="L737" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M737" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N737" t="n">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C738" t="n">
+        <v>743.7</v>
+      </c>
+      <c r="D738" t="n">
+        <v>820.46</v>
+      </c>
+      <c r="E738" t="n">
+        <v>-76.76000000000001</v>
+      </c>
+      <c r="F738" t="n">
+        <v>744</v>
+      </c>
+      <c r="G738" t="n">
+        <v>820.46</v>
+      </c>
+      <c r="H738" t="n">
+        <v>-76.45999999999999</v>
+      </c>
+      <c r="I738" t="n">
+        <v>736.15</v>
+      </c>
+      <c r="J738" t="n">
+        <v>743.7</v>
+      </c>
+      <c r="K738" t="n">
+        <v>-7.55</v>
+      </c>
+      <c r="L738" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M738" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N738" t="n">
+        <v>9.359999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -38323,7 +38843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38812,6 +39332,58 @@
       </c>
       <c r="N9" t="n">
         <v>9.449999999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>743.7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>820.46</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-76.76000000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>744</v>
+      </c>
+      <c r="G10" t="n">
+        <v>820.46</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-76.45999999999999</v>
+      </c>
+      <c r="I10" t="n">
+        <v>736.15</v>
+      </c>
+      <c r="J10" t="n">
+        <v>743.7</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-7.55</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>9.359999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -42219,7 +42791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43956,6 +44528,58 @@
       </c>
       <c r="N33" t="n">
         <v>7.94</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>342.65</v>
+      </c>
+      <c r="D34" t="n">
+        <v>372.81</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-30.16</v>
+      </c>
+      <c r="F34" t="n">
+        <v>344.4</v>
+      </c>
+      <c r="G34" t="n">
+        <v>372.81</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-28.41</v>
+      </c>
+      <c r="I34" t="n">
+        <v>340.55</v>
+      </c>
+      <c r="J34" t="n">
+        <v>342.65</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>8.09</v>
       </c>
     </row>
   </sheetData>
@@ -47347,7 +47971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49084,6 +49708,58 @@
       </c>
       <c r="N33" t="n">
         <v>8.09</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>118.3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>129.19</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-10.89</v>
+      </c>
+      <c r="F34" t="n">
+        <v>118.9</v>
+      </c>
+      <c r="G34" t="n">
+        <v>129.19</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-10.29</v>
+      </c>
+      <c r="I34" t="n">
+        <v>116.61</v>
+      </c>
+      <c r="J34" t="n">
+        <v>118.3</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>8.43</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -38324,31 +38324,31 @@
         </is>
       </c>
       <c r="C729" t="n">
-        <v>413.25</v>
+        <v>412.65</v>
       </c>
       <c r="D729" t="n">
         <v>421.2</v>
       </c>
       <c r="E729" t="n">
-        <v>-7.95</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="F729" t="n">
-        <v>417.25</v>
+        <v>417.8</v>
       </c>
       <c r="G729" t="n">
         <v>435.67</v>
       </c>
       <c r="H729" t="n">
-        <v>-18.42</v>
+        <v>-17.87</v>
       </c>
       <c r="I729" t="n">
-        <v>411.35</v>
+        <v>412.55</v>
       </c>
       <c r="J729" t="n">
         <v>413.25</v>
       </c>
       <c r="K729" t="n">
-        <v>-1.9</v>
+        <v>-0.7</v>
       </c>
       <c r="L729" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         </is>
       </c>
       <c r="N729" t="n">
-        <v>1.89</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="730">
@@ -38376,31 +38376,31 @@
         </is>
       </c>
       <c r="C730" t="n">
-        <v>118.3</v>
+        <v>117</v>
       </c>
       <c r="D730" t="n">
         <v>129.19</v>
       </c>
       <c r="E730" t="n">
-        <v>-10.89</v>
+        <v>-12.19</v>
       </c>
       <c r="F730" t="n">
-        <v>118.9</v>
+        <v>118.74</v>
       </c>
       <c r="G730" t="n">
         <v>129.19</v>
       </c>
       <c r="H730" t="n">
-        <v>-10.29</v>
+        <v>-10.45</v>
       </c>
       <c r="I730" t="n">
-        <v>116.61</v>
+        <v>116.7</v>
       </c>
       <c r="J730" t="n">
         <v>118.3</v>
       </c>
       <c r="K730" t="n">
-        <v>-1.69</v>
+        <v>-1.6</v>
       </c>
       <c r="L730" t="inlineStr">
         <is>
@@ -38413,7 +38413,7 @@
         </is>
       </c>
       <c r="N730" t="n">
-        <v>8.43</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="731">
@@ -38428,31 +38428,31 @@
         </is>
       </c>
       <c r="C731" t="n">
-        <v>342.65</v>
+        <v>342</v>
       </c>
       <c r="D731" t="n">
         <v>372.81</v>
       </c>
       <c r="E731" t="n">
-        <v>-30.16</v>
+        <v>-30.81</v>
       </c>
       <c r="F731" t="n">
-        <v>344.4</v>
+        <v>342</v>
       </c>
       <c r="G731" t="n">
         <v>372.81</v>
       </c>
       <c r="H731" t="n">
-        <v>-28.41</v>
+        <v>-30.81</v>
       </c>
       <c r="I731" t="n">
-        <v>340.55</v>
+        <v>334.65</v>
       </c>
       <c r="J731" t="n">
         <v>342.65</v>
       </c>
       <c r="K731" t="n">
-        <v>-2.1</v>
+        <v>-8</v>
       </c>
       <c r="L731" t="inlineStr">
         <is>
@@ -38461,11 +38461,11 @@
       </c>
       <c r="M731" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N731" t="n">
-        <v>8.09</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="732">
@@ -38480,31 +38480,31 @@
         </is>
       </c>
       <c r="C732" t="n">
-        <v>3374</v>
+        <v>3262.6</v>
       </c>
       <c r="D732" t="n">
         <v>4234.94</v>
       </c>
       <c r="E732" t="n">
-        <v>-860.9400000000001</v>
+        <v>-972.34</v>
       </c>
       <c r="F732" t="n">
-        <v>3374</v>
+        <v>3289.8</v>
       </c>
       <c r="G732" t="n">
         <v>4234.94</v>
       </c>
       <c r="H732" t="n">
-        <v>-860.9400000000001</v>
+        <v>-945.14</v>
       </c>
       <c r="I732" t="n">
-        <v>3237.5</v>
+        <v>3212.8</v>
       </c>
       <c r="J732" t="n">
         <v>3374</v>
       </c>
       <c r="K732" t="n">
-        <v>-136.5</v>
+        <v>-161.2</v>
       </c>
       <c r="L732" t="inlineStr">
         <is>
@@ -38517,7 +38517,7 @@
         </is>
       </c>
       <c r="N732" t="n">
-        <v>20.33</v>
+        <v>22.96</v>
       </c>
     </row>
     <row r="733">
@@ -38532,31 +38532,31 @@
         </is>
       </c>
       <c r="C733" t="n">
-        <v>1886.3</v>
+        <v>1805</v>
       </c>
       <c r="D733" t="n">
         <v>2070.4</v>
       </c>
       <c r="E733" t="n">
-        <v>-184.1</v>
+        <v>-265.4</v>
       </c>
       <c r="F733" t="n">
-        <v>1904.9</v>
+        <v>1806.4</v>
       </c>
       <c r="G733" t="n">
         <v>2070.4</v>
       </c>
       <c r="H733" t="n">
-        <v>-165.5</v>
+        <v>-264</v>
       </c>
       <c r="I733" t="n">
-        <v>1793</v>
+        <v>1773.7</v>
       </c>
       <c r="J733" t="n">
         <v>1856.48</v>
       </c>
       <c r="K733" t="n">
-        <v>-63.48</v>
+        <v>-82.78</v>
       </c>
       <c r="L733" t="inlineStr">
         <is>
@@ -38569,7 +38569,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>8.890000000000001</v>
+        <v>12.82</v>
       </c>
     </row>
     <row r="734">
@@ -38584,31 +38584,31 @@
         </is>
       </c>
       <c r="C734" t="n">
-        <v>1042.5</v>
+        <v>1007</v>
       </c>
       <c r="D734" t="n">
         <v>1148.51</v>
       </c>
       <c r="E734" t="n">
-        <v>-106.01</v>
+        <v>-141.51</v>
       </c>
       <c r="F734" t="n">
-        <v>1058</v>
+        <v>1025</v>
       </c>
       <c r="G734" t="n">
         <v>1148.51</v>
       </c>
       <c r="H734" t="n">
-        <v>-90.51000000000001</v>
+        <v>-123.51</v>
       </c>
       <c r="I734" t="n">
-        <v>1009.2</v>
+        <v>995.6</v>
       </c>
       <c r="J734" t="n">
         <v>1042.5</v>
       </c>
       <c r="K734" t="n">
-        <v>-33.3</v>
+        <v>-46.9</v>
       </c>
       <c r="L734" t="inlineStr">
         <is>
@@ -38621,7 +38621,7 @@
         </is>
       </c>
       <c r="N734" t="n">
-        <v>9.23</v>
+        <v>12.32</v>
       </c>
     </row>
     <row r="735">
@@ -38636,31 +38636,31 @@
         </is>
       </c>
       <c r="C735" t="n">
-        <v>11449</v>
+        <v>11185</v>
       </c>
       <c r="D735" t="n">
         <v>12466.15</v>
       </c>
       <c r="E735" t="n">
-        <v>-1017.15</v>
+        <v>-1281.15</v>
       </c>
       <c r="F735" t="n">
-        <v>11449</v>
+        <v>11389</v>
       </c>
       <c r="G735" t="n">
         <v>12466.15</v>
       </c>
       <c r="H735" t="n">
-        <v>-1017.15</v>
+        <v>-1077.15</v>
       </c>
       <c r="I735" t="n">
-        <v>11195</v>
+        <v>11103</v>
       </c>
       <c r="J735" t="n">
         <v>11449</v>
       </c>
       <c r="K735" t="n">
-        <v>-254</v>
+        <v>-346</v>
       </c>
       <c r="L735" t="inlineStr">
         <is>
@@ -38673,7 +38673,7 @@
         </is>
       </c>
       <c r="N735" t="n">
-        <v>8.16</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="736">
@@ -38688,31 +38688,31 @@
         </is>
       </c>
       <c r="C736" t="n">
-        <v>572.5</v>
+        <v>565</v>
       </c>
       <c r="D736" t="n">
         <v>633.33</v>
       </c>
       <c r="E736" t="n">
-        <v>-60.83</v>
+        <v>-68.33</v>
       </c>
       <c r="F736" t="n">
-        <v>576.7</v>
+        <v>573.95</v>
       </c>
       <c r="G736" t="n">
         <v>633.33</v>
       </c>
       <c r="H736" t="n">
-        <v>-56.63</v>
+        <v>-59.38</v>
       </c>
       <c r="I736" t="n">
-        <v>564.05</v>
+        <v>563.2</v>
       </c>
       <c r="J736" t="n">
         <v>563.5599999999999</v>
       </c>
       <c r="K736" t="n">
-        <v>0.49</v>
+        <v>-0.36</v>
       </c>
       <c r="L736" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         </is>
       </c>
       <c r="N736" t="n">
-        <v>9.6</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="737">
@@ -38749,22 +38749,22 @@
         <v>-197.35</v>
       </c>
       <c r="F737" t="n">
-        <v>2204</v>
+        <v>2199.3</v>
       </c>
       <c r="G737" t="n">
         <v>2392.35</v>
       </c>
       <c r="H737" t="n">
-        <v>-188.35</v>
+        <v>-193.05</v>
       </c>
       <c r="I737" t="n">
-        <v>2178</v>
+        <v>2159.9</v>
       </c>
       <c r="J737" t="n">
         <v>2162.51</v>
       </c>
       <c r="K737" t="n">
-        <v>15.49</v>
+        <v>-2.61</v>
       </c>
       <c r="L737" t="inlineStr">
         <is>
@@ -38792,31 +38792,31 @@
         </is>
       </c>
       <c r="C738" t="n">
-        <v>743.7</v>
+        <v>736.25</v>
       </c>
       <c r="D738" t="n">
         <v>820.46</v>
       </c>
       <c r="E738" t="n">
-        <v>-76.76000000000001</v>
+        <v>-84.20999999999999</v>
       </c>
       <c r="F738" t="n">
-        <v>744</v>
+        <v>749.4</v>
       </c>
       <c r="G738" t="n">
         <v>820.46</v>
       </c>
       <c r="H738" t="n">
-        <v>-76.45999999999999</v>
+        <v>-71.06</v>
       </c>
       <c r="I738" t="n">
-        <v>736.15</v>
+        <v>735.75</v>
       </c>
       <c r="J738" t="n">
         <v>743.7</v>
       </c>
       <c r="K738" t="n">
-        <v>-7.55</v>
+        <v>-7.95</v>
       </c>
       <c r="L738" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         </is>
       </c>
       <c r="N738" t="n">
-        <v>9.359999999999999</v>
+        <v>10.26</v>
       </c>
     </row>
   </sheetData>
@@ -39346,31 +39346,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>743.7</v>
+        <v>736.25</v>
       </c>
       <c r="D10" t="n">
         <v>820.46</v>
       </c>
       <c r="E10" t="n">
-        <v>-76.76000000000001</v>
+        <v>-84.20999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>744</v>
+        <v>749.4</v>
       </c>
       <c r="G10" t="n">
         <v>820.46</v>
       </c>
       <c r="H10" t="n">
-        <v>-76.45999999999999</v>
+        <v>-71.06</v>
       </c>
       <c r="I10" t="n">
-        <v>736.15</v>
+        <v>735.75</v>
       </c>
       <c r="J10" t="n">
         <v>743.7</v>
       </c>
       <c r="K10" t="n">
-        <v>-7.55</v>
+        <v>-7.95</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -39383,7 +39383,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>9.359999999999999</v>
+        <v>10.26</v>
       </c>
     </row>
   </sheetData>
@@ -44542,31 +44542,31 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>342.65</v>
+        <v>342</v>
       </c>
       <c r="D34" t="n">
         <v>372.81</v>
       </c>
       <c r="E34" t="n">
-        <v>-30.16</v>
+        <v>-30.81</v>
       </c>
       <c r="F34" t="n">
-        <v>344.4</v>
+        <v>342</v>
       </c>
       <c r="G34" t="n">
         <v>372.81</v>
       </c>
       <c r="H34" t="n">
-        <v>-28.41</v>
+        <v>-30.81</v>
       </c>
       <c r="I34" t="n">
-        <v>340.55</v>
+        <v>334.65</v>
       </c>
       <c r="J34" t="n">
         <v>342.65</v>
       </c>
       <c r="K34" t="n">
-        <v>-2.1</v>
+        <v>-8</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -44575,11 +44575,11 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>8.09</v>
+        <v>8.26</v>
       </c>
     </row>
   </sheetData>
@@ -49722,31 +49722,31 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>118.3</v>
+        <v>117</v>
       </c>
       <c r="D34" t="n">
         <v>129.19</v>
       </c>
       <c r="E34" t="n">
-        <v>-10.89</v>
+        <v>-12.19</v>
       </c>
       <c r="F34" t="n">
-        <v>118.9</v>
+        <v>118.74</v>
       </c>
       <c r="G34" t="n">
         <v>129.19</v>
       </c>
       <c r="H34" t="n">
-        <v>-10.29</v>
+        <v>-10.45</v>
       </c>
       <c r="I34" t="n">
-        <v>116.61</v>
+        <v>116.7</v>
       </c>
       <c r="J34" t="n">
         <v>118.3</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.69</v>
+        <v>-1.6</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -49759,7 +49759,7 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>8.43</v>
+        <v>9.44</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N738"/>
+  <dimension ref="A1:N743"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38830,6 +38830,266 @@
       </c>
       <c r="N738" t="n">
         <v>10.26</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C739" t="n">
+        <v>335.5</v>
+      </c>
+      <c r="D739" t="n">
+        <v>310.23</v>
+      </c>
+      <c r="E739" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="F739" t="n">
+        <v>343.6</v>
+      </c>
+      <c r="G739" t="n">
+        <v>316.21</v>
+      </c>
+      <c r="H739" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="I739" t="n">
+        <v>333.55</v>
+      </c>
+      <c r="J739" t="n">
+        <v>326.2</v>
+      </c>
+      <c r="K739" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="L739" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M739" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N739" t="n">
+        <v>8.15</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C740" t="n">
+        <v>117.12</v>
+      </c>
+      <c r="D740" t="n">
+        <v>106.94</v>
+      </c>
+      <c r="E740" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="F740" t="n">
+        <v>118.67</v>
+      </c>
+      <c r="G740" t="n">
+        <v>110.58</v>
+      </c>
+      <c r="H740" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="I740" t="n">
+        <v>117.06</v>
+      </c>
+      <c r="J740" t="n">
+        <v>114.33</v>
+      </c>
+      <c r="K740" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="L740" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M740" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N740" t="n">
+        <v>9.52</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C741" t="n">
+        <v>2184.8</v>
+      </c>
+      <c r="D741" t="n">
+        <v>2020.61</v>
+      </c>
+      <c r="E741" t="n">
+        <v>164.19</v>
+      </c>
+      <c r="F741" t="n">
+        <v>2204.9</v>
+      </c>
+      <c r="G741" t="n">
+        <v>2020.61</v>
+      </c>
+      <c r="H741" t="n">
+        <v>184.29</v>
+      </c>
+      <c r="I741" t="n">
+        <v>2158.2</v>
+      </c>
+      <c r="J741" t="n">
+        <v>2074.47</v>
+      </c>
+      <c r="K741" t="n">
+        <v>83.73</v>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M741" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N741" t="n">
+        <v>8.130000000000001</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C742" t="n">
+        <v>1022</v>
+      </c>
+      <c r="D742" t="n">
+        <v>903.25</v>
+      </c>
+      <c r="E742" t="n">
+        <v>118.75</v>
+      </c>
+      <c r="F742" t="n">
+        <v>1044.9</v>
+      </c>
+      <c r="G742" t="n">
+        <v>964.13</v>
+      </c>
+      <c r="H742" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="I742" t="n">
+        <v>1014</v>
+      </c>
+      <c r="J742" t="n">
+        <v>994.59</v>
+      </c>
+      <c r="K742" t="n">
+        <v>19.41</v>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M742" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N742" t="n">
+        <v>13.15</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C743" t="n">
+        <v>564.25</v>
+      </c>
+      <c r="D743" t="n">
+        <v>507.4</v>
+      </c>
+      <c r="E743" t="n">
+        <v>56.85</v>
+      </c>
+      <c r="F743" t="n">
+        <v>571.9</v>
+      </c>
+      <c r="G743" t="n">
+        <v>507.47</v>
+      </c>
+      <c r="H743" t="n">
+        <v>64.43000000000001</v>
+      </c>
+      <c r="I743" t="n">
+        <v>563.8</v>
+      </c>
+      <c r="J743" t="n">
+        <v>534.17</v>
+      </c>
+      <c r="K743" t="n">
+        <v>29.63</v>
+      </c>
+      <c r="L743" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M743" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N743" t="n">
+        <v>11.2</v>
       </c>
     </row>
   </sheetData>
@@ -42791,7 +43051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44580,6 +44840,58 @@
       </c>
       <c r="N34" t="n">
         <v>8.26</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>335.5</v>
+      </c>
+      <c r="D35" t="n">
+        <v>310.23</v>
+      </c>
+      <c r="E35" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="F35" t="n">
+        <v>343.6</v>
+      </c>
+      <c r="G35" t="n">
+        <v>316.21</v>
+      </c>
+      <c r="H35" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="I35" t="n">
+        <v>333.55</v>
+      </c>
+      <c r="J35" t="n">
+        <v>326.2</v>
+      </c>
+      <c r="K35" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>8.15</v>
       </c>
     </row>
   </sheetData>
@@ -47971,7 +48283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49760,6 +50072,58 @@
       </c>
       <c r="N34" t="n">
         <v>9.44</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>117.12</v>
+      </c>
+      <c r="D35" t="n">
+        <v>106.94</v>
+      </c>
+      <c r="E35" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="F35" t="n">
+        <v>118.67</v>
+      </c>
+      <c r="G35" t="n">
+        <v>110.58</v>
+      </c>
+      <c r="H35" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="I35" t="n">
+        <v>117.06</v>
+      </c>
+      <c r="J35" t="n">
+        <v>114.33</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>9.52</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -38844,31 +38844,31 @@
         </is>
       </c>
       <c r="C739" t="n">
-        <v>335.5</v>
+        <v>342.65</v>
       </c>
       <c r="D739" t="n">
         <v>310.23</v>
       </c>
       <c r="E739" t="n">
-        <v>25.27</v>
+        <v>32.42</v>
       </c>
       <c r="F739" t="n">
-        <v>343.6</v>
+        <v>344.4</v>
       </c>
       <c r="G739" t="n">
         <v>316.21</v>
       </c>
       <c r="H739" t="n">
-        <v>27.39</v>
+        <v>28.19</v>
       </c>
       <c r="I739" t="n">
-        <v>333.55</v>
+        <v>340.55</v>
       </c>
       <c r="J739" t="n">
         <v>326.2</v>
       </c>
       <c r="K739" t="n">
-        <v>7.35</v>
+        <v>14.35</v>
       </c>
       <c r="L739" t="inlineStr">
         <is>
@@ -38881,7 +38881,7 @@
         </is>
       </c>
       <c r="N739" t="n">
-        <v>8.15</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="740">
@@ -38896,31 +38896,31 @@
         </is>
       </c>
       <c r="C740" t="n">
-        <v>117.12</v>
+        <v>118.3</v>
       </c>
       <c r="D740" t="n">
         <v>106.94</v>
       </c>
       <c r="E740" t="n">
-        <v>10.18</v>
+        <v>11.36</v>
       </c>
       <c r="F740" t="n">
-        <v>118.67</v>
+        <v>118.9</v>
       </c>
       <c r="G740" t="n">
         <v>110.58</v>
       </c>
       <c r="H740" t="n">
-        <v>8.09</v>
+        <v>8.32</v>
       </c>
       <c r="I740" t="n">
-        <v>117.06</v>
+        <v>116.61</v>
       </c>
       <c r="J740" t="n">
         <v>114.33</v>
       </c>
       <c r="K740" t="n">
-        <v>2.73</v>
+        <v>2.28</v>
       </c>
       <c r="L740" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         </is>
       </c>
       <c r="N740" t="n">
-        <v>9.52</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="741">
@@ -38948,31 +38948,31 @@
         </is>
       </c>
       <c r="C741" t="n">
-        <v>2184.8</v>
+        <v>2195</v>
       </c>
       <c r="D741" t="n">
         <v>2020.61</v>
       </c>
       <c r="E741" t="n">
-        <v>164.19</v>
+        <v>174.39</v>
       </c>
       <c r="F741" t="n">
-        <v>2204.9</v>
+        <v>2204</v>
       </c>
       <c r="G741" t="n">
         <v>2020.61</v>
       </c>
       <c r="H741" t="n">
-        <v>184.29</v>
+        <v>183.39</v>
       </c>
       <c r="I741" t="n">
-        <v>2158.2</v>
+        <v>2178</v>
       </c>
       <c r="J741" t="n">
         <v>2074.47</v>
       </c>
       <c r="K741" t="n">
-        <v>83.73</v>
+        <v>103.53</v>
       </c>
       <c r="L741" t="inlineStr">
         <is>
@@ -38985,7 +38985,7 @@
         </is>
       </c>
       <c r="N741" t="n">
-        <v>8.130000000000001</v>
+        <v>8.630000000000001</v>
       </c>
     </row>
     <row r="742">
@@ -39000,31 +39000,31 @@
         </is>
       </c>
       <c r="C742" t="n">
-        <v>1022</v>
+        <v>1042.5</v>
       </c>
       <c r="D742" t="n">
         <v>903.25</v>
       </c>
       <c r="E742" t="n">
-        <v>118.75</v>
+        <v>139.25</v>
       </c>
       <c r="F742" t="n">
-        <v>1044.9</v>
+        <v>1058</v>
       </c>
       <c r="G742" t="n">
         <v>964.13</v>
       </c>
       <c r="H742" t="n">
-        <v>80.77</v>
+        <v>93.87</v>
       </c>
       <c r="I742" t="n">
-        <v>1014</v>
+        <v>1009.2</v>
       </c>
       <c r="J742" t="n">
         <v>994.59</v>
       </c>
       <c r="K742" t="n">
-        <v>19.41</v>
+        <v>14.61</v>
       </c>
       <c r="L742" t="inlineStr">
         <is>
@@ -39037,7 +39037,7 @@
         </is>
       </c>
       <c r="N742" t="n">
-        <v>13.15</v>
+        <v>15.42</v>
       </c>
     </row>
     <row r="743">
@@ -39052,31 +39052,31 @@
         </is>
       </c>
       <c r="C743" t="n">
-        <v>564.25</v>
+        <v>572.5</v>
       </c>
       <c r="D743" t="n">
         <v>507.4</v>
       </c>
       <c r="E743" t="n">
-        <v>56.85</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="F743" t="n">
-        <v>571.9</v>
+        <v>576.7</v>
       </c>
       <c r="G743" t="n">
         <v>507.47</v>
       </c>
       <c r="H743" t="n">
-        <v>64.43000000000001</v>
+        <v>69.23</v>
       </c>
       <c r="I743" t="n">
-        <v>563.8</v>
+        <v>564.05</v>
       </c>
       <c r="J743" t="n">
         <v>534.17</v>
       </c>
       <c r="K743" t="n">
-        <v>29.63</v>
+        <v>29.88</v>
       </c>
       <c r="L743" t="inlineStr">
         <is>
@@ -39089,7 +39089,7 @@
         </is>
       </c>
       <c r="N743" t="n">
-        <v>11.2</v>
+        <v>12.83</v>
       </c>
     </row>
   </sheetData>
@@ -44854,31 +44854,31 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>335.5</v>
+        <v>342.65</v>
       </c>
       <c r="D35" t="n">
         <v>310.23</v>
       </c>
       <c r="E35" t="n">
-        <v>25.27</v>
+        <v>32.42</v>
       </c>
       <c r="F35" t="n">
-        <v>343.6</v>
+        <v>344.4</v>
       </c>
       <c r="G35" t="n">
         <v>316.21</v>
       </c>
       <c r="H35" t="n">
-        <v>27.39</v>
+        <v>28.19</v>
       </c>
       <c r="I35" t="n">
-        <v>333.55</v>
+        <v>340.55</v>
       </c>
       <c r="J35" t="n">
         <v>326.2</v>
       </c>
       <c r="K35" t="n">
-        <v>7.35</v>
+        <v>14.35</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -44891,7 +44891,7 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>8.15</v>
+        <v>10.45</v>
       </c>
     </row>
   </sheetData>
@@ -50086,31 +50086,31 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>117.12</v>
+        <v>118.3</v>
       </c>
       <c r="D35" t="n">
         <v>106.94</v>
       </c>
       <c r="E35" t="n">
-        <v>10.18</v>
+        <v>11.36</v>
       </c>
       <c r="F35" t="n">
-        <v>118.67</v>
+        <v>118.9</v>
       </c>
       <c r="G35" t="n">
         <v>110.58</v>
       </c>
       <c r="H35" t="n">
-        <v>8.09</v>
+        <v>8.32</v>
       </c>
       <c r="I35" t="n">
-        <v>117.06</v>
+        <v>116.61</v>
       </c>
       <c r="J35" t="n">
         <v>114.33</v>
       </c>
       <c r="K35" t="n">
-        <v>2.73</v>
+        <v>2.28</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -50123,7 +50123,7 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>9.52</v>
+        <v>10.62</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N743"/>
+  <dimension ref="A1:N748"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39090,6 +39090,266 @@
       </c>
       <c r="N743" t="n">
         <v>12.83</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C744" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="D744" t="n">
+        <v>130.3</v>
+      </c>
+      <c r="E744" t="n">
+        <v>-13.7</v>
+      </c>
+      <c r="F744" t="n">
+        <v>118.01</v>
+      </c>
+      <c r="G744" t="n">
+        <v>130.3</v>
+      </c>
+      <c r="H744" t="n">
+        <v>-12.29</v>
+      </c>
+      <c r="I744" t="n">
+        <v>116.23</v>
+      </c>
+      <c r="J744" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="K744" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M744" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N744" t="n">
+        <v>10.51</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C745" t="n">
+        <v>2214.7</v>
+      </c>
+      <c r="D745" t="n">
+        <v>2425.1</v>
+      </c>
+      <c r="E745" t="n">
+        <v>-210.4</v>
+      </c>
+      <c r="F745" t="n">
+        <v>2219</v>
+      </c>
+      <c r="G745" t="n">
+        <v>2425.1</v>
+      </c>
+      <c r="H745" t="n">
+        <v>-206.1</v>
+      </c>
+      <c r="I745" t="n">
+        <v>2176.5</v>
+      </c>
+      <c r="J745" t="n">
+        <v>2214.7</v>
+      </c>
+      <c r="K745" t="n">
+        <v>-38.2</v>
+      </c>
+      <c r="L745" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M745" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N745" t="n">
+        <v>8.68</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C746" t="n">
+        <v>1029</v>
+      </c>
+      <c r="D746" t="n">
+        <v>1197.14</v>
+      </c>
+      <c r="E746" t="n">
+        <v>-168.14</v>
+      </c>
+      <c r="F746" t="n">
+        <v>1047</v>
+      </c>
+      <c r="G746" t="n">
+        <v>1197.14</v>
+      </c>
+      <c r="H746" t="n">
+        <v>-150.14</v>
+      </c>
+      <c r="I746" t="n">
+        <v>1019.4</v>
+      </c>
+      <c r="J746" t="n">
+        <v>1029</v>
+      </c>
+      <c r="K746" t="n">
+        <v>-9.6</v>
+      </c>
+      <c r="L746" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M746" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N746" t="n">
+        <v>14.05</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C747" t="n">
+        <v>335</v>
+      </c>
+      <c r="D747" t="n">
+        <v>372.97</v>
+      </c>
+      <c r="E747" t="n">
+        <v>-37.97</v>
+      </c>
+      <c r="F747" t="n">
+        <v>339.9</v>
+      </c>
+      <c r="G747" t="n">
+        <v>372.97</v>
+      </c>
+      <c r="H747" t="n">
+        <v>-33.07</v>
+      </c>
+      <c r="I747" t="n">
+        <v>331.7</v>
+      </c>
+      <c r="J747" t="n">
+        <v>335</v>
+      </c>
+      <c r="K747" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="L747" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M747" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N747" t="n">
+        <v>10.18</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C748" t="n">
+        <v>566</v>
+      </c>
+      <c r="D748" t="n">
+        <v>643.73</v>
+      </c>
+      <c r="E748" t="n">
+        <v>-77.73</v>
+      </c>
+      <c r="F748" t="n">
+        <v>569.55</v>
+      </c>
+      <c r="G748" t="n">
+        <v>643.73</v>
+      </c>
+      <c r="H748" t="n">
+        <v>-74.18000000000001</v>
+      </c>
+      <c r="I748" t="n">
+        <v>558.6</v>
+      </c>
+      <c r="J748" t="n">
+        <v>566</v>
+      </c>
+      <c r="K748" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M748" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N748" t="n">
+        <v>12.07</v>
       </c>
     </row>
   </sheetData>
@@ -43051,7 +43311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44892,6 +45152,58 @@
       </c>
       <c r="N35" t="n">
         <v>10.45</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>335</v>
+      </c>
+      <c r="D36" t="n">
+        <v>372.97</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-37.97</v>
+      </c>
+      <c r="F36" t="n">
+        <v>339.9</v>
+      </c>
+      <c r="G36" t="n">
+        <v>372.97</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-33.07</v>
+      </c>
+      <c r="I36" t="n">
+        <v>331.7</v>
+      </c>
+      <c r="J36" t="n">
+        <v>335</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>10.18</v>
       </c>
     </row>
   </sheetData>
@@ -48283,7 +48595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50124,6 +50436,58 @@
       </c>
       <c r="N35" t="n">
         <v>10.62</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="D36" t="n">
+        <v>130.3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-13.7</v>
+      </c>
+      <c r="F36" t="n">
+        <v>118.01</v>
+      </c>
+      <c r="G36" t="n">
+        <v>130.3</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-12.29</v>
+      </c>
+      <c r="I36" t="n">
+        <v>116.23</v>
+      </c>
+      <c r="J36" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>10.51</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -39104,31 +39104,31 @@
         </is>
       </c>
       <c r="C744" t="n">
-        <v>116.6</v>
+        <v>117.12</v>
       </c>
       <c r="D744" t="n">
         <v>130.3</v>
       </c>
       <c r="E744" t="n">
-        <v>-13.7</v>
+        <v>-13.18</v>
       </c>
       <c r="F744" t="n">
-        <v>118.01</v>
+        <v>118.67</v>
       </c>
       <c r="G744" t="n">
         <v>130.3</v>
       </c>
       <c r="H744" t="n">
-        <v>-12.29</v>
+        <v>-11.63</v>
       </c>
       <c r="I744" t="n">
-        <v>116.23</v>
+        <v>117.06</v>
       </c>
       <c r="J744" t="n">
         <v>116.6</v>
       </c>
       <c r="K744" t="n">
-        <v>-0.37</v>
+        <v>0.46</v>
       </c>
       <c r="L744" t="inlineStr">
         <is>
@@ -39141,7 +39141,7 @@
         </is>
       </c>
       <c r="N744" t="n">
-        <v>10.51</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="745">
@@ -39156,31 +39156,31 @@
         </is>
       </c>
       <c r="C745" t="n">
-        <v>2214.7</v>
+        <v>2184.8</v>
       </c>
       <c r="D745" t="n">
         <v>2425.1</v>
       </c>
       <c r="E745" t="n">
-        <v>-210.4</v>
+        <v>-240.3</v>
       </c>
       <c r="F745" t="n">
-        <v>2219</v>
+        <v>2204.9</v>
       </c>
       <c r="G745" t="n">
         <v>2425.1</v>
       </c>
       <c r="H745" t="n">
-        <v>-206.1</v>
+        <v>-220.2</v>
       </c>
       <c r="I745" t="n">
-        <v>2176.5</v>
+        <v>2158.2</v>
       </c>
       <c r="J745" t="n">
         <v>2214.7</v>
       </c>
       <c r="K745" t="n">
-        <v>-38.2</v>
+        <v>-56.5</v>
       </c>
       <c r="L745" t="inlineStr">
         <is>
@@ -39193,7 +39193,7 @@
         </is>
       </c>
       <c r="N745" t="n">
-        <v>8.68</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="746">
@@ -39208,31 +39208,31 @@
         </is>
       </c>
       <c r="C746" t="n">
-        <v>1029</v>
+        <v>1022</v>
       </c>
       <c r="D746" t="n">
         <v>1197.14</v>
       </c>
       <c r="E746" t="n">
-        <v>-168.14</v>
+        <v>-175.14</v>
       </c>
       <c r="F746" t="n">
-        <v>1047</v>
+        <v>1044.9</v>
       </c>
       <c r="G746" t="n">
         <v>1197.14</v>
       </c>
       <c r="H746" t="n">
-        <v>-150.14</v>
+        <v>-152.24</v>
       </c>
       <c r="I746" t="n">
-        <v>1019.4</v>
+        <v>1014</v>
       </c>
       <c r="J746" t="n">
         <v>1029</v>
       </c>
       <c r="K746" t="n">
-        <v>-9.6</v>
+        <v>-15</v>
       </c>
       <c r="L746" t="inlineStr">
         <is>
@@ -39245,7 +39245,7 @@
         </is>
       </c>
       <c r="N746" t="n">
-        <v>14.05</v>
+        <v>14.63</v>
       </c>
     </row>
     <row r="747">
@@ -39260,31 +39260,31 @@
         </is>
       </c>
       <c r="C747" t="n">
-        <v>335</v>
+        <v>335.5</v>
       </c>
       <c r="D747" t="n">
         <v>372.97</v>
       </c>
       <c r="E747" t="n">
-        <v>-37.97</v>
+        <v>-37.47</v>
       </c>
       <c r="F747" t="n">
-        <v>339.9</v>
+        <v>343.6</v>
       </c>
       <c r="G747" t="n">
         <v>372.97</v>
       </c>
       <c r="H747" t="n">
-        <v>-33.07</v>
+        <v>-29.37</v>
       </c>
       <c r="I747" t="n">
-        <v>331.7</v>
+        <v>333.55</v>
       </c>
       <c r="J747" t="n">
         <v>335</v>
       </c>
       <c r="K747" t="n">
-        <v>-3.3</v>
+        <v>-1.45</v>
       </c>
       <c r="L747" t="inlineStr">
         <is>
@@ -39297,7 +39297,7 @@
         </is>
       </c>
       <c r="N747" t="n">
-        <v>10.18</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="748">
@@ -39312,31 +39312,31 @@
         </is>
       </c>
       <c r="C748" t="n">
-        <v>566</v>
+        <v>564.25</v>
       </c>
       <c r="D748" t="n">
         <v>643.73</v>
       </c>
       <c r="E748" t="n">
-        <v>-77.73</v>
+        <v>-79.48</v>
       </c>
       <c r="F748" t="n">
-        <v>569.55</v>
+        <v>571.9</v>
       </c>
       <c r="G748" t="n">
         <v>643.73</v>
       </c>
       <c r="H748" t="n">
-        <v>-74.18000000000001</v>
+        <v>-71.83</v>
       </c>
       <c r="I748" t="n">
-        <v>558.6</v>
+        <v>563.8</v>
       </c>
       <c r="J748" t="n">
         <v>566</v>
       </c>
       <c r="K748" t="n">
-        <v>-7.4</v>
+        <v>-2.2</v>
       </c>
       <c r="L748" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         </is>
       </c>
       <c r="N748" t="n">
-        <v>12.07</v>
+        <v>12.35</v>
       </c>
     </row>
   </sheetData>
@@ -45166,31 +45166,31 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>335</v>
+        <v>335.5</v>
       </c>
       <c r="D36" t="n">
         <v>372.97</v>
       </c>
       <c r="E36" t="n">
-        <v>-37.97</v>
+        <v>-37.47</v>
       </c>
       <c r="F36" t="n">
-        <v>339.9</v>
+        <v>343.6</v>
       </c>
       <c r="G36" t="n">
         <v>372.97</v>
       </c>
       <c r="H36" t="n">
-        <v>-33.07</v>
+        <v>-29.37</v>
       </c>
       <c r="I36" t="n">
-        <v>331.7</v>
+        <v>333.55</v>
       </c>
       <c r="J36" t="n">
         <v>335</v>
       </c>
       <c r="K36" t="n">
-        <v>-3.3</v>
+        <v>-1.45</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -45203,7 +45203,7 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>10.18</v>
+        <v>10.05</v>
       </c>
     </row>
   </sheetData>
@@ -50450,31 +50450,31 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>116.6</v>
+        <v>117.12</v>
       </c>
       <c r="D36" t="n">
         <v>130.3</v>
       </c>
       <c r="E36" t="n">
-        <v>-13.7</v>
+        <v>-13.18</v>
       </c>
       <c r="F36" t="n">
-        <v>118.01</v>
+        <v>118.67</v>
       </c>
       <c r="G36" t="n">
         <v>130.3</v>
       </c>
       <c r="H36" t="n">
-        <v>-12.29</v>
+        <v>-11.63</v>
       </c>
       <c r="I36" t="n">
-        <v>116.23</v>
+        <v>117.06</v>
       </c>
       <c r="J36" t="n">
         <v>116.6</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.37</v>
+        <v>0.46</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -50487,7 +50487,7 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>10.51</v>
+        <v>10.12</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -39104,31 +39104,31 @@
         </is>
       </c>
       <c r="C744" t="n">
-        <v>117.12</v>
+        <v>116.6</v>
       </c>
       <c r="D744" t="n">
-        <v>130.3</v>
+        <v>105.88</v>
       </c>
       <c r="E744" t="n">
-        <v>-13.18</v>
+        <v>10.72</v>
       </c>
       <c r="F744" t="n">
-        <v>118.67</v>
+        <v>118.01</v>
       </c>
       <c r="G744" t="n">
-        <v>130.3</v>
+        <v>110.44</v>
       </c>
       <c r="H744" t="n">
-        <v>-11.63</v>
+        <v>7.57</v>
       </c>
       <c r="I744" t="n">
-        <v>117.06</v>
+        <v>116.23</v>
       </c>
       <c r="J744" t="n">
-        <v>116.6</v>
+        <v>113.51</v>
       </c>
       <c r="K744" t="n">
-        <v>0.46</v>
+        <v>2.72</v>
       </c>
       <c r="L744" t="inlineStr">
         <is>
@@ -39137,7 +39137,7 @@
       </c>
       <c r="M744" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N744" t="n">
@@ -39156,31 +39156,31 @@
         </is>
       </c>
       <c r="C745" t="n">
-        <v>2184.8</v>
+        <v>2214.7</v>
       </c>
       <c r="D745" t="n">
-        <v>2425.1</v>
+        <v>2011.21</v>
       </c>
       <c r="E745" t="n">
-        <v>-240.3</v>
+        <v>203.49</v>
       </c>
       <c r="F745" t="n">
-        <v>2204.9</v>
+        <v>2219</v>
       </c>
       <c r="G745" t="n">
-        <v>2425.1</v>
+        <v>2062.42</v>
       </c>
       <c r="H745" t="n">
-        <v>-220.2</v>
+        <v>156.58</v>
       </c>
       <c r="I745" t="n">
-        <v>2158.2</v>
+        <v>2176.5</v>
       </c>
       <c r="J745" t="n">
-        <v>2214.7</v>
+        <v>2109.91</v>
       </c>
       <c r="K745" t="n">
-        <v>-56.5</v>
+        <v>66.59</v>
       </c>
       <c r="L745" t="inlineStr">
         <is>
@@ -39193,7 +39193,7 @@
         </is>
       </c>
       <c r="N745" t="n">
-        <v>9.91</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="746">
@@ -39208,31 +39208,31 @@
         </is>
       </c>
       <c r="C746" t="n">
-        <v>1022</v>
+        <v>1029</v>
       </c>
       <c r="D746" t="n">
-        <v>1197.14</v>
+        <v>885.48</v>
       </c>
       <c r="E746" t="n">
-        <v>-175.14</v>
+        <v>143.52</v>
       </c>
       <c r="F746" t="n">
-        <v>1044.9</v>
+        <v>1047</v>
       </c>
       <c r="G746" t="n">
-        <v>1197.14</v>
+        <v>972.63</v>
       </c>
       <c r="H746" t="n">
-        <v>-152.24</v>
+        <v>74.37</v>
       </c>
       <c r="I746" t="n">
-        <v>1014</v>
+        <v>1019.4</v>
       </c>
       <c r="J746" t="n">
-        <v>1029</v>
+        <v>995.54</v>
       </c>
       <c r="K746" t="n">
-        <v>-15</v>
+        <v>23.86</v>
       </c>
       <c r="L746" t="inlineStr">
         <is>
@@ -39241,11 +39241,11 @@
       </c>
       <c r="M746" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N746" t="n">
-        <v>14.63</v>
+        <v>16.21</v>
       </c>
     </row>
     <row r="747">
@@ -39260,31 +39260,31 @@
         </is>
       </c>
       <c r="C747" t="n">
-        <v>335.5</v>
+        <v>335</v>
       </c>
       <c r="D747" t="n">
-        <v>372.97</v>
+        <v>303.76</v>
       </c>
       <c r="E747" t="n">
-        <v>-37.47</v>
+        <v>31.24</v>
       </c>
       <c r="F747" t="n">
-        <v>343.6</v>
+        <v>339.9</v>
       </c>
       <c r="G747" t="n">
-        <v>372.97</v>
+        <v>313.46</v>
       </c>
       <c r="H747" t="n">
-        <v>-29.37</v>
+        <v>26.44</v>
       </c>
       <c r="I747" t="n">
-        <v>333.55</v>
+        <v>331.7</v>
       </c>
       <c r="J747" t="n">
-        <v>335</v>
+        <v>320.72</v>
       </c>
       <c r="K747" t="n">
-        <v>-1.45</v>
+        <v>10.98</v>
       </c>
       <c r="L747" t="inlineStr">
         <is>
@@ -39293,11 +39293,11 @@
       </c>
       <c r="M747" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N747" t="n">
-        <v>10.05</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="748">
@@ -39312,31 +39312,31 @@
         </is>
       </c>
       <c r="C748" t="n">
-        <v>564.25</v>
+        <v>566</v>
       </c>
       <c r="D748" t="n">
-        <v>643.73</v>
+        <v>500.09</v>
       </c>
       <c r="E748" t="n">
-        <v>-79.48</v>
+        <v>65.91</v>
       </c>
       <c r="F748" t="n">
-        <v>571.9</v>
+        <v>569.55</v>
       </c>
       <c r="G748" t="n">
-        <v>643.73</v>
+        <v>513.4</v>
       </c>
       <c r="H748" t="n">
-        <v>-71.83</v>
+        <v>56.15</v>
       </c>
       <c r="I748" t="n">
-        <v>563.8</v>
+        <v>558.6</v>
       </c>
       <c r="J748" t="n">
-        <v>566</v>
+        <v>534.8</v>
       </c>
       <c r="K748" t="n">
-        <v>-2.2</v>
+        <v>23.8</v>
       </c>
       <c r="L748" t="inlineStr">
         <is>
@@ -39345,11 +39345,11 @@
       </c>
       <c r="M748" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N748" t="n">
-        <v>12.35</v>
+        <v>13.18</v>
       </c>
     </row>
   </sheetData>
@@ -45166,31 +45166,31 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>335.5</v>
+        <v>335</v>
       </c>
       <c r="D36" t="n">
-        <v>372.97</v>
+        <v>303.76</v>
       </c>
       <c r="E36" t="n">
-        <v>-37.47</v>
+        <v>31.24</v>
       </c>
       <c r="F36" t="n">
-        <v>343.6</v>
+        <v>339.9</v>
       </c>
       <c r="G36" t="n">
-        <v>372.97</v>
+        <v>313.46</v>
       </c>
       <c r="H36" t="n">
-        <v>-29.37</v>
+        <v>26.44</v>
       </c>
       <c r="I36" t="n">
-        <v>333.55</v>
+        <v>331.7</v>
       </c>
       <c r="J36" t="n">
-        <v>335</v>
+        <v>320.72</v>
       </c>
       <c r="K36" t="n">
-        <v>-1.45</v>
+        <v>10.98</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -45199,11 +45199,11 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>10.05</v>
+        <v>10.28</v>
       </c>
     </row>
   </sheetData>
@@ -50450,31 +50450,31 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>117.12</v>
+        <v>116.6</v>
       </c>
       <c r="D36" t="n">
-        <v>130.3</v>
+        <v>105.88</v>
       </c>
       <c r="E36" t="n">
-        <v>-13.18</v>
+        <v>10.72</v>
       </c>
       <c r="F36" t="n">
-        <v>118.67</v>
+        <v>118.01</v>
       </c>
       <c r="G36" t="n">
-        <v>130.3</v>
+        <v>110.44</v>
       </c>
       <c r="H36" t="n">
-        <v>-11.63</v>
+        <v>7.57</v>
       </c>
       <c r="I36" t="n">
-        <v>117.06</v>
+        <v>116.23</v>
       </c>
       <c r="J36" t="n">
-        <v>116.6</v>
+        <v>113.51</v>
       </c>
       <c r="K36" t="n">
-        <v>0.46</v>
+        <v>2.72</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -50483,7 +50483,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N36" t="n">

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N748"/>
+  <dimension ref="A1:N752"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39350,6 +39350,214 @@
       </c>
       <c r="N748" t="n">
         <v>13.18</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C749" t="n">
+        <v>289.85</v>
+      </c>
+      <c r="D749" t="n">
+        <v>317.85</v>
+      </c>
+      <c r="E749" t="n">
+        <v>-28</v>
+      </c>
+      <c r="F749" t="n">
+        <v>293.05</v>
+      </c>
+      <c r="G749" t="n">
+        <v>317.85</v>
+      </c>
+      <c r="H749" t="n">
+        <v>-24.8</v>
+      </c>
+      <c r="I749" t="n">
+        <v>285.75</v>
+      </c>
+      <c r="J749" t="n">
+        <v>289.85</v>
+      </c>
+      <c r="K749" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="L749" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M749" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N749" t="n">
+        <v>8.81</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C750" t="n">
+        <v>2197</v>
+      </c>
+      <c r="D750" t="n">
+        <v>2438.65</v>
+      </c>
+      <c r="E750" t="n">
+        <v>-241.65</v>
+      </c>
+      <c r="F750" t="n">
+        <v>2210.2</v>
+      </c>
+      <c r="G750" t="n">
+        <v>2438.65</v>
+      </c>
+      <c r="H750" t="n">
+        <v>-228.45</v>
+      </c>
+      <c r="I750" t="n">
+        <v>2174.9</v>
+      </c>
+      <c r="J750" t="n">
+        <v>2197</v>
+      </c>
+      <c r="K750" t="n">
+        <v>-22.1</v>
+      </c>
+      <c r="L750" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M750" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N750" t="n">
+        <v>9.91</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C751" t="n">
+        <v>330.95</v>
+      </c>
+      <c r="D751" t="n">
+        <v>367.91</v>
+      </c>
+      <c r="E751" t="n">
+        <v>-36.96</v>
+      </c>
+      <c r="F751" t="n">
+        <v>335.1</v>
+      </c>
+      <c r="G751" t="n">
+        <v>367.91</v>
+      </c>
+      <c r="H751" t="n">
+        <v>-32.81</v>
+      </c>
+      <c r="I751" t="n">
+        <v>328.45</v>
+      </c>
+      <c r="J751" t="n">
+        <v>330.95</v>
+      </c>
+      <c r="K751" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="L751" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M751" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N751" t="n">
+        <v>10.05</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C752" t="n">
+        <v>564.15</v>
+      </c>
+      <c r="D752" t="n">
+        <v>643.61</v>
+      </c>
+      <c r="E752" t="n">
+        <v>-79.45999999999999</v>
+      </c>
+      <c r="F752" t="n">
+        <v>574.7</v>
+      </c>
+      <c r="G752" t="n">
+        <v>643.61</v>
+      </c>
+      <c r="H752" t="n">
+        <v>-68.91</v>
+      </c>
+      <c r="I752" t="n">
+        <v>562.5</v>
+      </c>
+      <c r="J752" t="n">
+        <v>558.45</v>
+      </c>
+      <c r="K752" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="L752" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M752" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N752" t="n">
+        <v>12.35</v>
       </c>
     </row>
   </sheetData>
@@ -43311,7 +43519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45204,6 +45412,58 @@
       </c>
       <c r="N36" t="n">
         <v>10.28</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>330.95</v>
+      </c>
+      <c r="D37" t="n">
+        <v>367.91</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-36.96</v>
+      </c>
+      <c r="F37" t="n">
+        <v>335.1</v>
+      </c>
+      <c r="G37" t="n">
+        <v>367.91</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-32.81</v>
+      </c>
+      <c r="I37" t="n">
+        <v>328.45</v>
+      </c>
+      <c r="J37" t="n">
+        <v>330.95</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>10.05</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -39364,31 +39364,31 @@
         </is>
       </c>
       <c r="C749" t="n">
-        <v>289.85</v>
+        <v>286.5</v>
       </c>
       <c r="D749" t="n">
         <v>317.85</v>
       </c>
       <c r="E749" t="n">
-        <v>-28</v>
+        <v>-31.35</v>
       </c>
       <c r="F749" t="n">
-        <v>293.05</v>
+        <v>286.5</v>
       </c>
       <c r="G749" t="n">
         <v>317.85</v>
       </c>
       <c r="H749" t="n">
-        <v>-24.8</v>
+        <v>-31.35</v>
       </c>
       <c r="I749" t="n">
-        <v>285.75</v>
+        <v>283.4</v>
       </c>
       <c r="J749" t="n">
         <v>289.85</v>
       </c>
       <c r="K749" t="n">
-        <v>-4.1</v>
+        <v>-6.45</v>
       </c>
       <c r="L749" t="inlineStr">
         <is>
@@ -39397,11 +39397,11 @@
       </c>
       <c r="M749" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N749" t="n">
-        <v>8.81</v>
+        <v>9.859999999999999</v>
       </c>
     </row>
     <row r="750">
@@ -39416,31 +39416,31 @@
         </is>
       </c>
       <c r="C750" t="n">
-        <v>2197</v>
+        <v>2214.7</v>
       </c>
       <c r="D750" t="n">
         <v>2438.65</v>
       </c>
       <c r="E750" t="n">
-        <v>-241.65</v>
+        <v>-223.95</v>
       </c>
       <c r="F750" t="n">
-        <v>2210.2</v>
+        <v>2219</v>
       </c>
       <c r="G750" t="n">
         <v>2438.65</v>
       </c>
       <c r="H750" t="n">
-        <v>-228.45</v>
+        <v>-219.65</v>
       </c>
       <c r="I750" t="n">
-        <v>2174.9</v>
+        <v>2176.5</v>
       </c>
       <c r="J750" t="n">
         <v>2197</v>
       </c>
       <c r="K750" t="n">
-        <v>-22.1</v>
+        <v>-20.5</v>
       </c>
       <c r="L750" t="inlineStr">
         <is>
@@ -39453,7 +39453,7 @@
         </is>
       </c>
       <c r="N750" t="n">
-        <v>9.91</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="751">
@@ -39468,31 +39468,31 @@
         </is>
       </c>
       <c r="C751" t="n">
-        <v>330.95</v>
+        <v>335</v>
       </c>
       <c r="D751" t="n">
         <v>367.91</v>
       </c>
       <c r="E751" t="n">
-        <v>-36.96</v>
+        <v>-32.91</v>
       </c>
       <c r="F751" t="n">
-        <v>335.1</v>
+        <v>339.9</v>
       </c>
       <c r="G751" t="n">
         <v>367.91</v>
       </c>
       <c r="H751" t="n">
-        <v>-32.81</v>
+        <v>-28.01</v>
       </c>
       <c r="I751" t="n">
-        <v>328.45</v>
+        <v>331.7</v>
       </c>
       <c r="J751" t="n">
         <v>330.95</v>
       </c>
       <c r="K751" t="n">
-        <v>-2.5</v>
+        <v>0.75</v>
       </c>
       <c r="L751" t="inlineStr">
         <is>
@@ -39505,7 +39505,7 @@
         </is>
       </c>
       <c r="N751" t="n">
-        <v>10.05</v>
+        <v>8.949999999999999</v>
       </c>
     </row>
     <row r="752">
@@ -39520,31 +39520,31 @@
         </is>
       </c>
       <c r="C752" t="n">
-        <v>564.15</v>
+        <v>566</v>
       </c>
       <c r="D752" t="n">
         <v>643.61</v>
       </c>
       <c r="E752" t="n">
-        <v>-79.45999999999999</v>
+        <v>-77.61</v>
       </c>
       <c r="F752" t="n">
-        <v>574.7</v>
+        <v>569.55</v>
       </c>
       <c r="G752" t="n">
         <v>643.61</v>
       </c>
       <c r="H752" t="n">
-        <v>-68.91</v>
+        <v>-74.06</v>
       </c>
       <c r="I752" t="n">
-        <v>562.5</v>
+        <v>558.6</v>
       </c>
       <c r="J752" t="n">
         <v>558.45</v>
       </c>
       <c r="K752" t="n">
-        <v>4.05</v>
+        <v>0.15</v>
       </c>
       <c r="L752" t="inlineStr">
         <is>
@@ -39557,7 +39557,7 @@
         </is>
       </c>
       <c r="N752" t="n">
-        <v>12.35</v>
+        <v>12.06</v>
       </c>
     </row>
   </sheetData>
@@ -45426,31 +45426,31 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>330.95</v>
+        <v>335</v>
       </c>
       <c r="D37" t="n">
         <v>367.91</v>
       </c>
       <c r="E37" t="n">
-        <v>-36.96</v>
+        <v>-32.91</v>
       </c>
       <c r="F37" t="n">
-        <v>335.1</v>
+        <v>339.9</v>
       </c>
       <c r="G37" t="n">
         <v>367.91</v>
       </c>
       <c r="H37" t="n">
-        <v>-32.81</v>
+        <v>-28.01</v>
       </c>
       <c r="I37" t="n">
-        <v>328.45</v>
+        <v>331.7</v>
       </c>
       <c r="J37" t="n">
         <v>330.95</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.5</v>
+        <v>0.75</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -45463,7 +45463,7 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>10.05</v>
+        <v>8.949999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N752"/>
+  <dimension ref="A1:N755"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39558,6 +39558,162 @@
       </c>
       <c r="N752" t="n">
         <v>12.06</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C753" t="n">
+        <v>2188.6</v>
+      </c>
+      <c r="D753" t="n">
+        <v>2003.52</v>
+      </c>
+      <c r="E753" t="n">
+        <v>185.08</v>
+      </c>
+      <c r="F753" t="n">
+        <v>2217.8</v>
+      </c>
+      <c r="G753" t="n">
+        <v>2051.83</v>
+      </c>
+      <c r="H753" t="n">
+        <v>165.97</v>
+      </c>
+      <c r="I753" t="n">
+        <v>2172.1</v>
+      </c>
+      <c r="J753" t="n">
+        <v>2120.68</v>
+      </c>
+      <c r="K753" t="n">
+        <v>51.42</v>
+      </c>
+      <c r="L753" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M753" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N753" t="n">
+        <v>9.24</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C754" t="n">
+        <v>327.85</v>
+      </c>
+      <c r="D754" t="n">
+        <v>300.91</v>
+      </c>
+      <c r="E754" t="n">
+        <v>26.94</v>
+      </c>
+      <c r="F754" t="n">
+        <v>333</v>
+      </c>
+      <c r="G754" t="n">
+        <v>311.19</v>
+      </c>
+      <c r="H754" t="n">
+        <v>21.81</v>
+      </c>
+      <c r="I754" t="n">
+        <v>323.65</v>
+      </c>
+      <c r="J754" t="n">
+        <v>321.78</v>
+      </c>
+      <c r="K754" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="L754" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M754" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N754" t="n">
+        <v>8.949999999999999</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C755" t="n">
+        <v>548.5</v>
+      </c>
+      <c r="D755" t="n">
+        <v>486.22</v>
+      </c>
+      <c r="E755" t="n">
+        <v>62.28</v>
+      </c>
+      <c r="F755" t="n">
+        <v>566.75</v>
+      </c>
+      <c r="G755" t="n">
+        <v>493.58</v>
+      </c>
+      <c r="H755" t="n">
+        <v>73.17</v>
+      </c>
+      <c r="I755" t="n">
+        <v>548.5</v>
+      </c>
+      <c r="J755" t="n">
+        <v>526.5</v>
+      </c>
+      <c r="K755" t="n">
+        <v>22</v>
+      </c>
+      <c r="L755" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M755" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N755" t="n">
+        <v>12.81</v>
       </c>
     </row>
   </sheetData>
@@ -43519,7 +43675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45463,6 +45619,58 @@
         </is>
       </c>
       <c r="N37" t="n">
+        <v>8.949999999999999</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>327.85</v>
+      </c>
+      <c r="D38" t="n">
+        <v>300.91</v>
+      </c>
+      <c r="E38" t="n">
+        <v>26.94</v>
+      </c>
+      <c r="F38" t="n">
+        <v>333</v>
+      </c>
+      <c r="G38" t="n">
+        <v>311.19</v>
+      </c>
+      <c r="H38" t="n">
+        <v>21.81</v>
+      </c>
+      <c r="I38" t="n">
+        <v>323.65</v>
+      </c>
+      <c r="J38" t="n">
+        <v>321.78</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
         <v>8.949999999999999</v>
       </c>
     </row>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -39572,31 +39572,31 @@
         </is>
       </c>
       <c r="C753" t="n">
-        <v>2188.6</v>
+        <v>2197</v>
       </c>
       <c r="D753" t="n">
         <v>2003.52</v>
       </c>
       <c r="E753" t="n">
-        <v>185.08</v>
+        <v>193.48</v>
       </c>
       <c r="F753" t="n">
-        <v>2217.8</v>
+        <v>2210.2</v>
       </c>
       <c r="G753" t="n">
         <v>2051.83</v>
       </c>
       <c r="H753" t="n">
-        <v>165.97</v>
+        <v>158.37</v>
       </c>
       <c r="I753" t="n">
-        <v>2172.1</v>
+        <v>2174.9</v>
       </c>
       <c r="J753" t="n">
         <v>2120.68</v>
       </c>
       <c r="K753" t="n">
-        <v>51.42</v>
+        <v>54.22</v>
       </c>
       <c r="L753" t="inlineStr">
         <is>
@@ -39609,7 +39609,7 @@
         </is>
       </c>
       <c r="N753" t="n">
-        <v>9.24</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="754">
@@ -39624,31 +39624,31 @@
         </is>
       </c>
       <c r="C754" t="n">
-        <v>327.85</v>
+        <v>330.95</v>
       </c>
       <c r="D754" t="n">
         <v>300.91</v>
       </c>
       <c r="E754" t="n">
-        <v>26.94</v>
+        <v>30.04</v>
       </c>
       <c r="F754" t="n">
-        <v>333</v>
+        <v>335.1</v>
       </c>
       <c r="G754" t="n">
         <v>311.19</v>
       </c>
       <c r="H754" t="n">
-        <v>21.81</v>
+        <v>23.91</v>
       </c>
       <c r="I754" t="n">
-        <v>323.65</v>
+        <v>328.45</v>
       </c>
       <c r="J754" t="n">
         <v>321.78</v>
       </c>
       <c r="K754" t="n">
-        <v>1.87</v>
+        <v>6.67</v>
       </c>
       <c r="L754" t="inlineStr">
         <is>
@@ -39661,7 +39661,7 @@
         </is>
       </c>
       <c r="N754" t="n">
-        <v>8.949999999999999</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="755">
@@ -39676,31 +39676,31 @@
         </is>
       </c>
       <c r="C755" t="n">
-        <v>548.5</v>
+        <v>564.15</v>
       </c>
       <c r="D755" t="n">
         <v>486.22</v>
       </c>
       <c r="E755" t="n">
-        <v>62.28</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="F755" t="n">
-        <v>566.75</v>
+        <v>574.7</v>
       </c>
       <c r="G755" t="n">
         <v>493.58</v>
       </c>
       <c r="H755" t="n">
-        <v>73.17</v>
+        <v>81.12</v>
       </c>
       <c r="I755" t="n">
-        <v>548.5</v>
+        <v>562.5</v>
       </c>
       <c r="J755" t="n">
         <v>526.5</v>
       </c>
       <c r="K755" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="L755" t="inlineStr">
         <is>
@@ -39713,7 +39713,7 @@
         </is>
       </c>
       <c r="N755" t="n">
-        <v>12.81</v>
+        <v>16.03</v>
       </c>
     </row>
   </sheetData>
@@ -45634,31 +45634,31 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>327.85</v>
+        <v>330.95</v>
       </c>
       <c r="D38" t="n">
         <v>300.91</v>
       </c>
       <c r="E38" t="n">
-        <v>26.94</v>
+        <v>30.04</v>
       </c>
       <c r="F38" t="n">
-        <v>333</v>
+        <v>335.1</v>
       </c>
       <c r="G38" t="n">
         <v>311.19</v>
       </c>
       <c r="H38" t="n">
-        <v>21.81</v>
+        <v>23.91</v>
       </c>
       <c r="I38" t="n">
-        <v>323.65</v>
+        <v>328.45</v>
       </c>
       <c r="J38" t="n">
         <v>321.78</v>
       </c>
       <c r="K38" t="n">
-        <v>1.87</v>
+        <v>6.67</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -45671,7 +45671,7 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>8.949999999999999</v>
+        <v>9.98</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N755"/>
+  <dimension ref="A1:N758"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39714,6 +39714,162 @@
       </c>
       <c r="N755" t="n">
         <v>16.03</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C756" t="n">
+        <v>674</v>
+      </c>
+      <c r="D756" t="n">
+        <v>731.29</v>
+      </c>
+      <c r="E756" t="n">
+        <v>-57.29</v>
+      </c>
+      <c r="F756" t="n">
+        <v>674</v>
+      </c>
+      <c r="G756" t="n">
+        <v>731.29</v>
+      </c>
+      <c r="H756" t="n">
+        <v>-57.29</v>
+      </c>
+      <c r="I756" t="n">
+        <v>653</v>
+      </c>
+      <c r="J756" t="n">
+        <v>669.98</v>
+      </c>
+      <c r="K756" t="n">
+        <v>-16.98</v>
+      </c>
+      <c r="L756" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M756" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N756" t="n">
+        <v>7.83</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C757" t="n">
+        <v>2190.1</v>
+      </c>
+      <c r="D757" t="n">
+        <v>2420.81</v>
+      </c>
+      <c r="E757" t="n">
+        <v>-230.71</v>
+      </c>
+      <c r="F757" t="n">
+        <v>2224.5</v>
+      </c>
+      <c r="G757" t="n">
+        <v>2420.81</v>
+      </c>
+      <c r="H757" t="n">
+        <v>-196.31</v>
+      </c>
+      <c r="I757" t="n">
+        <v>2181.6</v>
+      </c>
+      <c r="J757" t="n">
+        <v>2190.1</v>
+      </c>
+      <c r="K757" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="L757" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M757" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N757" t="n">
+        <v>9.529999999999999</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+      <c r="C758" t="n">
+        <v>178.23</v>
+      </c>
+      <c r="D758" t="n">
+        <v>193.38</v>
+      </c>
+      <c r="E758" t="n">
+        <v>-15.15</v>
+      </c>
+      <c r="F758" t="n">
+        <v>184.37</v>
+      </c>
+      <c r="G758" t="n">
+        <v>193.38</v>
+      </c>
+      <c r="H758" t="n">
+        <v>-9.01</v>
+      </c>
+      <c r="I758" t="n">
+        <v>177.26</v>
+      </c>
+      <c r="J758" t="n">
+        <v>177.37</v>
+      </c>
+      <c r="K758" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="L758" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M758" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N758" t="n">
+        <v>7.83</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -39728,22 +39728,22 @@
         </is>
       </c>
       <c r="C756" t="n">
-        <v>674</v>
+        <v>653</v>
       </c>
       <c r="D756" t="n">
         <v>731.29</v>
       </c>
       <c r="E756" t="n">
-        <v>-57.29</v>
+        <v>-78.29000000000001</v>
       </c>
       <c r="F756" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="G756" t="n">
         <v>731.29</v>
       </c>
       <c r="H756" t="n">
-        <v>-57.29</v>
+        <v>-56.29</v>
       </c>
       <c r="I756" t="n">
         <v>653</v>
@@ -39765,7 +39765,7 @@
         </is>
       </c>
       <c r="N756" t="n">
-        <v>7.83</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="757">
@@ -39780,31 +39780,31 @@
         </is>
       </c>
       <c r="C757" t="n">
-        <v>2190.1</v>
+        <v>2188.6</v>
       </c>
       <c r="D757" t="n">
         <v>2420.81</v>
       </c>
       <c r="E757" t="n">
-        <v>-230.71</v>
+        <v>-232.21</v>
       </c>
       <c r="F757" t="n">
-        <v>2224.5</v>
+        <v>2217.8</v>
       </c>
       <c r="G757" t="n">
         <v>2420.81</v>
       </c>
       <c r="H757" t="n">
-        <v>-196.31</v>
+        <v>-203.01</v>
       </c>
       <c r="I757" t="n">
-        <v>2181.6</v>
+        <v>2172.1</v>
       </c>
       <c r="J757" t="n">
         <v>2190.1</v>
       </c>
       <c r="K757" t="n">
-        <v>-8.5</v>
+        <v>-18</v>
       </c>
       <c r="L757" t="inlineStr">
         <is>
@@ -39817,7 +39817,7 @@
         </is>
       </c>
       <c r="N757" t="n">
-        <v>9.529999999999999</v>
+        <v>9.59</v>
       </c>
     </row>
     <row r="758">
@@ -39832,31 +39832,31 @@
         </is>
       </c>
       <c r="C758" t="n">
-        <v>178.23</v>
+        <v>185.31</v>
       </c>
       <c r="D758" t="n">
         <v>193.38</v>
       </c>
       <c r="E758" t="n">
-        <v>-15.15</v>
+        <v>-8.07</v>
       </c>
       <c r="F758" t="n">
-        <v>184.37</v>
+        <v>185.31</v>
       </c>
       <c r="G758" t="n">
         <v>193.38</v>
       </c>
       <c r="H758" t="n">
-        <v>-9.01</v>
+        <v>-8.07</v>
       </c>
       <c r="I758" t="n">
-        <v>177.26</v>
+        <v>179.3</v>
       </c>
       <c r="J758" t="n">
         <v>177.37</v>
       </c>
       <c r="K758" t="n">
-        <v>-0.11</v>
+        <v>1.93</v>
       </c>
       <c r="L758" t="inlineStr">
         <is>
@@ -39869,7 +39869,7 @@
         </is>
       </c>
       <c r="N758" t="n">
-        <v>7.83</v>
+        <v>4.17</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N758"/>
+  <dimension ref="A1:N759"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39870,6 +39870,58 @@
       </c>
       <c r="N758" t="n">
         <v>4.17</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="C759" t="n">
+        <v>2535</v>
+      </c>
+      <c r="D759" t="n">
+        <v>2338.52</v>
+      </c>
+      <c r="E759" t="n">
+        <v>196.48</v>
+      </c>
+      <c r="F759" t="n">
+        <v>2535</v>
+      </c>
+      <c r="G759" t="n">
+        <v>2406.77</v>
+      </c>
+      <c r="H759" t="n">
+        <v>128.23</v>
+      </c>
+      <c r="I759" t="n">
+        <v>2476.1</v>
+      </c>
+      <c r="J759" t="n">
+        <v>2466.59</v>
+      </c>
+      <c r="K759" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="L759" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M759" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N759" t="n">
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -39884,31 +39884,31 @@
         </is>
       </c>
       <c r="C759" t="n">
-        <v>2535</v>
+        <v>2503.8</v>
       </c>
       <c r="D759" t="n">
         <v>2338.52</v>
       </c>
       <c r="E759" t="n">
-        <v>196.48</v>
+        <v>165.28</v>
       </c>
       <c r="F759" t="n">
-        <v>2535</v>
+        <v>2552</v>
       </c>
       <c r="G759" t="n">
         <v>2406.77</v>
       </c>
       <c r="H759" t="n">
-        <v>128.23</v>
+        <v>145.23</v>
       </c>
       <c r="I759" t="n">
-        <v>2476.1</v>
+        <v>2455</v>
       </c>
       <c r="J759" t="n">
         <v>2466.59</v>
       </c>
       <c r="K759" t="n">
-        <v>9.51</v>
+        <v>-11.59</v>
       </c>
       <c r="L759" t="inlineStr">
         <is>
@@ -39921,7 +39921,7 @@
         </is>
       </c>
       <c r="N759" t="n">
-        <v>8.4</v>
+        <v>7.07</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -39884,31 +39884,31 @@
         </is>
       </c>
       <c r="C759" t="n">
-        <v>2503.8</v>
+        <v>2535</v>
       </c>
       <c r="D759" t="n">
-        <v>2338.52</v>
+        <v>2735.89</v>
       </c>
       <c r="E759" t="n">
-        <v>165.28</v>
+        <v>-200.89</v>
       </c>
       <c r="F759" t="n">
-        <v>2552</v>
+        <v>2535</v>
       </c>
       <c r="G759" t="n">
-        <v>2406.77</v>
+        <v>2735.89</v>
       </c>
       <c r="H759" t="n">
-        <v>145.23</v>
+        <v>-200.89</v>
       </c>
       <c r="I759" t="n">
-        <v>2455</v>
+        <v>2476.1</v>
       </c>
       <c r="J759" t="n">
-        <v>2466.59</v>
+        <v>2535</v>
       </c>
       <c r="K759" t="n">
-        <v>-11.59</v>
+        <v>-58.9</v>
       </c>
       <c r="L759" t="inlineStr">
         <is>
@@ -39921,7 +39921,7 @@
         </is>
       </c>
       <c r="N759" t="n">
-        <v>7.07</v>
+        <v>7.34</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -39887,28 +39887,28 @@
         <v>2535</v>
       </c>
       <c r="D759" t="n">
-        <v>2735.89</v>
+        <v>2367.65</v>
       </c>
       <c r="E759" t="n">
-        <v>-200.89</v>
+        <v>167.35</v>
       </c>
       <c r="F759" t="n">
         <v>2535</v>
       </c>
       <c r="G759" t="n">
-        <v>2735.89</v>
+        <v>2494.26</v>
       </c>
       <c r="H759" t="n">
-        <v>-200.89</v>
+        <v>40.74</v>
       </c>
       <c r="I759" t="n">
         <v>2476.1</v>
       </c>
       <c r="J759" t="n">
-        <v>2535</v>
+        <v>2463</v>
       </c>
       <c r="K759" t="n">
-        <v>-58.9</v>
+        <v>13.1</v>
       </c>
       <c r="L759" t="inlineStr">
         <is>
@@ -39917,11 +39917,11 @@
       </c>
       <c r="M759" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N759" t="n">
-        <v>7.34</v>
+        <v>7.07</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N759"/>
+  <dimension ref="A1:N762"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39922,6 +39922,162 @@
       </c>
       <c r="N759" t="n">
         <v>7.07</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C760" t="n">
+        <v>658.4</v>
+      </c>
+      <c r="D760" t="n">
+        <v>701.3200000000001</v>
+      </c>
+      <c r="E760" t="n">
+        <v>-42.92</v>
+      </c>
+      <c r="F760" t="n">
+        <v>671.1</v>
+      </c>
+      <c r="G760" t="n">
+        <v>701.3200000000001</v>
+      </c>
+      <c r="H760" t="n">
+        <v>-30.22</v>
+      </c>
+      <c r="I760" t="n">
+        <v>650.55</v>
+      </c>
+      <c r="J760" t="n">
+        <v>658.6799999999999</v>
+      </c>
+      <c r="K760" t="n">
+        <v>-8.130000000000001</v>
+      </c>
+      <c r="L760" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M760" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N760" t="n">
+        <v>6.12</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C761" t="n">
+        <v>285.5</v>
+      </c>
+      <c r="D761" t="n">
+        <v>301.96</v>
+      </c>
+      <c r="E761" t="n">
+        <v>-16.46</v>
+      </c>
+      <c r="F761" t="n">
+        <v>287.5</v>
+      </c>
+      <c r="G761" t="n">
+        <v>301.96</v>
+      </c>
+      <c r="H761" t="n">
+        <v>-14.46</v>
+      </c>
+      <c r="I761" t="n">
+        <v>283.45</v>
+      </c>
+      <c r="J761" t="n">
+        <v>285.5</v>
+      </c>
+      <c r="K761" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="L761" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M761" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N761" t="n">
+        <v>5.45</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="C762" t="n">
+        <v>2535</v>
+      </c>
+      <c r="D762" t="n">
+        <v>2714.2</v>
+      </c>
+      <c r="E762" t="n">
+        <v>-179.2</v>
+      </c>
+      <c r="F762" t="n">
+        <v>2535</v>
+      </c>
+      <c r="G762" t="n">
+        <v>2714.2</v>
+      </c>
+      <c r="H762" t="n">
+        <v>-179.2</v>
+      </c>
+      <c r="I762" t="n">
+        <v>2476.1</v>
+      </c>
+      <c r="J762" t="n">
+        <v>2479.87</v>
+      </c>
+      <c r="K762" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="L762" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M762" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N762" t="n">
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -39936,31 +39936,31 @@
         </is>
       </c>
       <c r="C760" t="n">
-        <v>658.4</v>
+        <v>673</v>
       </c>
       <c r="D760" t="n">
         <v>701.3200000000001</v>
       </c>
       <c r="E760" t="n">
-        <v>-42.92</v>
+        <v>-28.32</v>
       </c>
       <c r="F760" t="n">
-        <v>671.1</v>
+        <v>676.5</v>
       </c>
       <c r="G760" t="n">
         <v>701.3200000000001</v>
       </c>
       <c r="H760" t="n">
-        <v>-30.22</v>
+        <v>-24.82</v>
       </c>
       <c r="I760" t="n">
-        <v>650.55</v>
+        <v>664</v>
       </c>
       <c r="J760" t="n">
         <v>658.6799999999999</v>
       </c>
       <c r="K760" t="n">
-        <v>-8.130000000000001</v>
+        <v>5.32</v>
       </c>
       <c r="L760" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         </is>
       </c>
       <c r="N760" t="n">
-        <v>6.12</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="761">
@@ -40040,31 +40040,31 @@
         </is>
       </c>
       <c r="C762" t="n">
-        <v>2535</v>
+        <v>2479</v>
       </c>
       <c r="D762" t="n">
         <v>2714.2</v>
       </c>
       <c r="E762" t="n">
-        <v>-179.2</v>
+        <v>-235.2</v>
       </c>
       <c r="F762" t="n">
-        <v>2535</v>
+        <v>2539.3</v>
       </c>
       <c r="G762" t="n">
         <v>2714.2</v>
       </c>
       <c r="H762" t="n">
-        <v>-179.2</v>
+        <v>-174.9</v>
       </c>
       <c r="I762" t="n">
-        <v>2476.1</v>
+        <v>2464.7</v>
       </c>
       <c r="J762" t="n">
         <v>2479.87</v>
       </c>
       <c r="K762" t="n">
-        <v>-3.77</v>
+        <v>-15.17</v>
       </c>
       <c r="L762" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         </is>
       </c>
       <c r="N762" t="n">
-        <v>6.6</v>
+        <v>8.67</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N762"/>
+  <dimension ref="A1:N767"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40078,6 +40078,266 @@
       </c>
       <c r="N762" t="n">
         <v>8.67</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C763" t="n">
+        <v>297.5</v>
+      </c>
+      <c r="D763" t="n">
+        <v>283.53</v>
+      </c>
+      <c r="E763" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="F763" t="n">
+        <v>297.85</v>
+      </c>
+      <c r="G763" t="n">
+        <v>286.43</v>
+      </c>
+      <c r="H763" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="I763" t="n">
+        <v>291</v>
+      </c>
+      <c r="J763" t="n">
+        <v>289.45</v>
+      </c>
+      <c r="K763" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L763" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M763" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N763" t="n">
+        <v>4.93</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C764" t="n">
+        <v>329</v>
+      </c>
+      <c r="D764" t="n">
+        <v>313.17</v>
+      </c>
+      <c r="E764" t="n">
+        <v>15.83</v>
+      </c>
+      <c r="F764" t="n">
+        <v>330.2</v>
+      </c>
+      <c r="G764" t="n">
+        <v>321.15</v>
+      </c>
+      <c r="H764" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="I764" t="n">
+        <v>319.1</v>
+      </c>
+      <c r="J764" t="n">
+        <v>323.31</v>
+      </c>
+      <c r="K764" t="n">
+        <v>-4.21</v>
+      </c>
+      <c r="L764" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M764" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N764" t="n">
+        <v>5.05</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C765" t="n">
+        <v>666.1</v>
+      </c>
+      <c r="D765" t="n">
+        <v>644.3200000000001</v>
+      </c>
+      <c r="E765" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="F765" t="n">
+        <v>675.5</v>
+      </c>
+      <c r="G765" t="n">
+        <v>644.3200000000001</v>
+      </c>
+      <c r="H765" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="I765" t="n">
+        <v>664.95</v>
+      </c>
+      <c r="J765" t="n">
+        <v>645.47</v>
+      </c>
+      <c r="K765" t="n">
+        <v>19.48</v>
+      </c>
+      <c r="L765" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M765" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N765" t="n">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C766" t="n">
+        <v>1081.15</v>
+      </c>
+      <c r="D766" t="n">
+        <v>1029.87</v>
+      </c>
+      <c r="E766" t="n">
+        <v>51.28</v>
+      </c>
+      <c r="F766" t="n">
+        <v>1086</v>
+      </c>
+      <c r="G766" t="n">
+        <v>1064.98</v>
+      </c>
+      <c r="H766" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="I766" t="n">
+        <v>1017.1</v>
+      </c>
+      <c r="J766" t="n">
+        <v>1072.47</v>
+      </c>
+      <c r="K766" t="n">
+        <v>-55.37</v>
+      </c>
+      <c r="L766" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M766" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N766" t="n">
+        <v>4.98</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="C767" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D767" t="n">
+        <v>2301.62</v>
+      </c>
+      <c r="E767" t="n">
+        <v>198.38</v>
+      </c>
+      <c r="F767" t="n">
+        <v>2508.9</v>
+      </c>
+      <c r="G767" t="n">
+        <v>2388.74</v>
+      </c>
+      <c r="H767" t="n">
+        <v>120.16</v>
+      </c>
+      <c r="I767" t="n">
+        <v>2464.5</v>
+      </c>
+      <c r="J767" t="n">
+        <v>2416.47</v>
+      </c>
+      <c r="K767" t="n">
+        <v>48.03</v>
+      </c>
+      <c r="L767" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M767" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N767" t="n">
+        <v>8.619999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -44039,7 +44299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46036,6 +46296,58 @@
       </c>
       <c r="N38" t="n">
         <v>9.98</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>329</v>
+      </c>
+      <c r="D39" t="n">
+        <v>313.17</v>
+      </c>
+      <c r="E39" t="n">
+        <v>15.83</v>
+      </c>
+      <c r="F39" t="n">
+        <v>330.2</v>
+      </c>
+      <c r="G39" t="n">
+        <v>321.15</v>
+      </c>
+      <c r="H39" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="I39" t="n">
+        <v>319.1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>323.31</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-4.21</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>5.05</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -40092,31 +40092,31 @@
         </is>
       </c>
       <c r="C763" t="n">
-        <v>297.5</v>
+        <v>290</v>
       </c>
       <c r="D763" t="n">
         <v>283.53</v>
       </c>
       <c r="E763" t="n">
-        <v>13.97</v>
+        <v>6.47</v>
       </c>
       <c r="F763" t="n">
-        <v>297.85</v>
+        <v>294</v>
       </c>
       <c r="G763" t="n">
         <v>286.43</v>
       </c>
       <c r="H763" t="n">
-        <v>11.42</v>
+        <v>7.57</v>
       </c>
       <c r="I763" t="n">
-        <v>291</v>
+        <v>286.5</v>
       </c>
       <c r="J763" t="n">
         <v>289.45</v>
       </c>
       <c r="K763" t="n">
-        <v>1.55</v>
+        <v>-2.95</v>
       </c>
       <c r="L763" t="inlineStr">
         <is>
@@ -40125,11 +40125,11 @@
       </c>
       <c r="M763" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N763" t="n">
-        <v>4.93</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="764">
@@ -40144,31 +40144,31 @@
         </is>
       </c>
       <c r="C764" t="n">
-        <v>329</v>
+        <v>320.8</v>
       </c>
       <c r="D764" t="n">
         <v>313.17</v>
       </c>
       <c r="E764" t="n">
-        <v>15.83</v>
+        <v>7.63</v>
       </c>
       <c r="F764" t="n">
-        <v>330.2</v>
+        <v>322.85</v>
       </c>
       <c r="G764" t="n">
         <v>321.15</v>
       </c>
       <c r="H764" t="n">
-        <v>9.050000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="I764" t="n">
-        <v>319.1</v>
+        <v>308.1</v>
       </c>
       <c r="J764" t="n">
         <v>323.31</v>
       </c>
       <c r="K764" t="n">
-        <v>-4.21</v>
+        <v>-15.21</v>
       </c>
       <c r="L764" t="inlineStr">
         <is>
@@ -40177,11 +40177,11 @@
       </c>
       <c r="M764" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N764" t="n">
-        <v>5.05</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="765">
@@ -40196,31 +40196,31 @@
         </is>
       </c>
       <c r="C765" t="n">
-        <v>666.1</v>
+        <v>673</v>
       </c>
       <c r="D765" t="n">
         <v>644.3200000000001</v>
       </c>
       <c r="E765" t="n">
-        <v>21.78</v>
+        <v>28.68</v>
       </c>
       <c r="F765" t="n">
-        <v>675.5</v>
+        <v>676.5</v>
       </c>
       <c r="G765" t="n">
         <v>644.3200000000001</v>
       </c>
       <c r="H765" t="n">
-        <v>31.18</v>
+        <v>32.18</v>
       </c>
       <c r="I765" t="n">
-        <v>664.95</v>
+        <v>664</v>
       </c>
       <c r="J765" t="n">
         <v>645.47</v>
       </c>
       <c r="K765" t="n">
-        <v>19.48</v>
+        <v>18.53</v>
       </c>
       <c r="L765" t="inlineStr">
         <is>
@@ -40233,7 +40233,7 @@
         </is>
       </c>
       <c r="N765" t="n">
-        <v>3.38</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="766">
@@ -40248,31 +40248,31 @@
         </is>
       </c>
       <c r="C766" t="n">
-        <v>1081.15</v>
+        <v>1011.1</v>
       </c>
       <c r="D766" t="n">
         <v>1029.87</v>
       </c>
       <c r="E766" t="n">
-        <v>51.28</v>
+        <v>-18.77</v>
       </c>
       <c r="F766" t="n">
-        <v>1086</v>
+        <v>1018.9</v>
       </c>
       <c r="G766" t="n">
         <v>1064.98</v>
       </c>
       <c r="H766" t="n">
-        <v>21.02</v>
+        <v>-46.08</v>
       </c>
       <c r="I766" t="n">
-        <v>1017.1</v>
+        <v>987.9</v>
       </c>
       <c r="J766" t="n">
         <v>1072.47</v>
       </c>
       <c r="K766" t="n">
-        <v>-55.37</v>
+        <v>-84.56999999999999</v>
       </c>
       <c r="L766" t="inlineStr">
         <is>
@@ -40281,11 +40281,11 @@
       </c>
       <c r="M766" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N766" t="n">
-        <v>4.98</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="767">
@@ -40300,31 +40300,31 @@
         </is>
       </c>
       <c r="C767" t="n">
-        <v>2500</v>
+        <v>2479</v>
       </c>
       <c r="D767" t="n">
         <v>2301.62</v>
       </c>
       <c r="E767" t="n">
-        <v>198.38</v>
+        <v>177.38</v>
       </c>
       <c r="F767" t="n">
-        <v>2508.9</v>
+        <v>2539.3</v>
       </c>
       <c r="G767" t="n">
         <v>2388.74</v>
       </c>
       <c r="H767" t="n">
-        <v>120.16</v>
+        <v>150.56</v>
       </c>
       <c r="I767" t="n">
-        <v>2464.5</v>
+        <v>2464.7</v>
       </c>
       <c r="J767" t="n">
         <v>2416.47</v>
       </c>
       <c r="K767" t="n">
-        <v>48.03</v>
+        <v>48.23</v>
       </c>
       <c r="L767" t="inlineStr">
         <is>
@@ -40337,7 +40337,7 @@
         </is>
       </c>
       <c r="N767" t="n">
-        <v>8.619999999999999</v>
+        <v>7.71</v>
       </c>
     </row>
   </sheetData>
@@ -46310,31 +46310,31 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>329</v>
+        <v>320.8</v>
       </c>
       <c r="D39" t="n">
         <v>313.17</v>
       </c>
       <c r="E39" t="n">
-        <v>15.83</v>
+        <v>7.63</v>
       </c>
       <c r="F39" t="n">
-        <v>330.2</v>
+        <v>322.85</v>
       </c>
       <c r="G39" t="n">
         <v>321.15</v>
       </c>
       <c r="H39" t="n">
-        <v>9.050000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="I39" t="n">
-        <v>319.1</v>
+        <v>308.1</v>
       </c>
       <c r="J39" t="n">
         <v>323.31</v>
       </c>
       <c r="K39" t="n">
-        <v>-4.21</v>
+        <v>-15.21</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -46343,11 +46343,11 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>5.05</v>
+        <v>2.44</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N767"/>
+  <dimension ref="A1:N770"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40338,6 +40338,162 @@
       </c>
       <c r="N767" t="n">
         <v>7.71</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C768" t="n">
+        <v>328</v>
+      </c>
+      <c r="D768" t="n">
+        <v>338.67</v>
+      </c>
+      <c r="E768" t="n">
+        <v>-10.67</v>
+      </c>
+      <c r="F768" t="n">
+        <v>332.7</v>
+      </c>
+      <c r="G768" t="n">
+        <v>338.67</v>
+      </c>
+      <c r="H768" t="n">
+        <v>-5.97</v>
+      </c>
+      <c r="I768" t="n">
+        <v>324.6</v>
+      </c>
+      <c r="J768" t="n">
+        <v>320.57</v>
+      </c>
+      <c r="K768" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="L768" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M768" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N768" t="n">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C769" t="n">
+        <v>297</v>
+      </c>
+      <c r="D769" t="n">
+        <v>306.21</v>
+      </c>
+      <c r="E769" t="n">
+        <v>-9.210000000000001</v>
+      </c>
+      <c r="F769" t="n">
+        <v>299.6</v>
+      </c>
+      <c r="G769" t="n">
+        <v>306.21</v>
+      </c>
+      <c r="H769" t="n">
+        <v>-6.61</v>
+      </c>
+      <c r="I769" t="n">
+        <v>294.25</v>
+      </c>
+      <c r="J769" t="n">
+        <v>289.16</v>
+      </c>
+      <c r="K769" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="L769" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M769" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N769" t="n">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="C770" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D770" t="n">
+        <v>2714.22</v>
+      </c>
+      <c r="E770" t="n">
+        <v>-214.22</v>
+      </c>
+      <c r="F770" t="n">
+        <v>2530</v>
+      </c>
+      <c r="G770" t="n">
+        <v>2714.22</v>
+      </c>
+      <c r="H770" t="n">
+        <v>-184.22</v>
+      </c>
+      <c r="I770" t="n">
+        <v>2480.1</v>
+      </c>
+      <c r="J770" t="n">
+        <v>2413.41</v>
+      </c>
+      <c r="K770" t="n">
+        <v>66.69</v>
+      </c>
+      <c r="L770" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M770" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N770" t="n">
+        <v>7.89</v>
       </c>
     </row>
   </sheetData>
@@ -44299,7 +44455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:N40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46348,6 +46504,58 @@
       </c>
       <c r="N39" t="n">
         <v>2.44</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>328</v>
+      </c>
+      <c r="D40" t="n">
+        <v>338.67</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-10.67</v>
+      </c>
+      <c r="F40" t="n">
+        <v>332.7</v>
+      </c>
+      <c r="G40" t="n">
+        <v>338.67</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-5.97</v>
+      </c>
+      <c r="I40" t="n">
+        <v>324.6</v>
+      </c>
+      <c r="J40" t="n">
+        <v>320.57</v>
+      </c>
+      <c r="K40" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>3.15</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -40352,31 +40352,31 @@
         </is>
       </c>
       <c r="C768" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D768" t="n">
         <v>338.67</v>
       </c>
       <c r="E768" t="n">
-        <v>-10.67</v>
+        <v>-9.67</v>
       </c>
       <c r="F768" t="n">
-        <v>332.7</v>
+        <v>330.2</v>
       </c>
       <c r="G768" t="n">
         <v>338.67</v>
       </c>
       <c r="H768" t="n">
-        <v>-5.97</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="I768" t="n">
-        <v>324.6</v>
+        <v>319.1</v>
       </c>
       <c r="J768" t="n">
         <v>320.57</v>
       </c>
       <c r="K768" t="n">
-        <v>4.03</v>
+        <v>-1.47</v>
       </c>
       <c r="L768" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         </is>
       </c>
       <c r="N768" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="769">
@@ -40404,31 +40404,31 @@
         </is>
       </c>
       <c r="C769" t="n">
-        <v>297</v>
+        <v>297.5</v>
       </c>
       <c r="D769" t="n">
         <v>306.21</v>
       </c>
       <c r="E769" t="n">
-        <v>-9.210000000000001</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="F769" t="n">
-        <v>299.6</v>
+        <v>297.85</v>
       </c>
       <c r="G769" t="n">
         <v>306.21</v>
       </c>
       <c r="H769" t="n">
-        <v>-6.61</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="I769" t="n">
-        <v>294.25</v>
+        <v>291</v>
       </c>
       <c r="J769" t="n">
         <v>289.16</v>
       </c>
       <c r="K769" t="n">
-        <v>5.09</v>
+        <v>1.84</v>
       </c>
       <c r="L769" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         </is>
       </c>
       <c r="N769" t="n">
-        <v>3.01</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="770">
@@ -46518,31 +46518,31 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D40" t="n">
         <v>338.67</v>
       </c>
       <c r="E40" t="n">
-        <v>-10.67</v>
+        <v>-9.67</v>
       </c>
       <c r="F40" t="n">
-        <v>332.7</v>
+        <v>330.2</v>
       </c>
       <c r="G40" t="n">
         <v>338.67</v>
       </c>
       <c r="H40" t="n">
-        <v>-5.97</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>324.6</v>
+        <v>319.1</v>
       </c>
       <c r="J40" t="n">
         <v>320.57</v>
       </c>
       <c r="K40" t="n">
-        <v>4.03</v>
+        <v>-1.47</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -46555,7 +46555,7 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N770"/>
+  <dimension ref="A1:N771"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40494,6 +40494,58 @@
       </c>
       <c r="N770" t="n">
         <v>7.89</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C771" t="n">
+        <v>288.5</v>
+      </c>
+      <c r="D771" t="n">
+        <v>282.54</v>
+      </c>
+      <c r="E771" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="F771" t="n">
+        <v>296.95</v>
+      </c>
+      <c r="G771" t="n">
+        <v>286.25</v>
+      </c>
+      <c r="H771" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="I771" t="n">
+        <v>288</v>
+      </c>
+      <c r="J771" t="n">
+        <v>288.4</v>
+      </c>
+      <c r="K771" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="L771" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M771" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N771" t="n">
+        <v>2.11</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N771"/>
+  <dimension ref="A1:N772"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40546,6 +40546,58 @@
       </c>
       <c r="N771" t="n">
         <v>2.11</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C772" t="n">
+        <v>291.5</v>
+      </c>
+      <c r="D772" t="n">
+        <v>300.03</v>
+      </c>
+      <c r="E772" t="n">
+        <v>-8.529999999999999</v>
+      </c>
+      <c r="F772" t="n">
+        <v>295.45</v>
+      </c>
+      <c r="G772" t="n">
+        <v>300.03</v>
+      </c>
+      <c r="H772" t="n">
+        <v>-4.58</v>
+      </c>
+      <c r="I772" t="n">
+        <v>289.15</v>
+      </c>
+      <c r="J772" t="n">
+        <v>284.73</v>
+      </c>
+      <c r="K772" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="L772" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M772" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N772" t="n">
+        <v>2.84</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -40560,31 +40560,31 @@
         </is>
       </c>
       <c r="C772" t="n">
-        <v>291.5</v>
+        <v>288.5</v>
       </c>
       <c r="D772" t="n">
         <v>300.03</v>
       </c>
       <c r="E772" t="n">
-        <v>-8.529999999999999</v>
+        <v>-11.53</v>
       </c>
       <c r="F772" t="n">
-        <v>295.45</v>
+        <v>296.95</v>
       </c>
       <c r="G772" t="n">
         <v>300.03</v>
       </c>
       <c r="H772" t="n">
-        <v>-4.58</v>
+        <v>-3.08</v>
       </c>
       <c r="I772" t="n">
-        <v>289.15</v>
+        <v>288</v>
       </c>
       <c r="J772" t="n">
         <v>284.73</v>
       </c>
       <c r="K772" t="n">
-        <v>4.42</v>
+        <v>3.27</v>
       </c>
       <c r="L772" t="inlineStr">
         <is>
@@ -40597,7 +40597,7 @@
         </is>
       </c>
       <c r="N772" t="n">
-        <v>2.84</v>
+        <v>3.84</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -40560,31 +40560,31 @@
         </is>
       </c>
       <c r="C772" t="n">
-        <v>288.5</v>
+        <v>291.5</v>
       </c>
       <c r="D772" t="n">
-        <v>300.03</v>
+        <v>282.54</v>
       </c>
       <c r="E772" t="n">
-        <v>-11.53</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="F772" t="n">
-        <v>296.95</v>
+        <v>295.45</v>
       </c>
       <c r="G772" t="n">
-        <v>300.03</v>
+        <v>287.22</v>
       </c>
       <c r="H772" t="n">
-        <v>-3.08</v>
+        <v>8.23</v>
       </c>
       <c r="I772" t="n">
-        <v>288</v>
+        <v>289.15</v>
       </c>
       <c r="J772" t="n">
-        <v>284.73</v>
+        <v>281.63</v>
       </c>
       <c r="K772" t="n">
-        <v>3.27</v>
+        <v>7.52</v>
       </c>
       <c r="L772" t="inlineStr">
         <is>
@@ -40593,11 +40593,11 @@
       </c>
       <c r="M772" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N772" t="n">
-        <v>3.84</v>
+        <v>3.17</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N772"/>
+  <dimension ref="A1:N774"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40598,6 +40598,110 @@
       </c>
       <c r="N772" t="n">
         <v>3.17</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C773" t="n">
+        <v>441</v>
+      </c>
+      <c r="D773" t="n">
+        <v>450.22</v>
+      </c>
+      <c r="E773" t="n">
+        <v>-9.220000000000001</v>
+      </c>
+      <c r="F773" t="n">
+        <v>445.25</v>
+      </c>
+      <c r="G773" t="n">
+        <v>450.22</v>
+      </c>
+      <c r="H773" t="n">
+        <v>-4.97</v>
+      </c>
+      <c r="I773" t="n">
+        <v>437.85</v>
+      </c>
+      <c r="J773" t="n">
+        <v>430.76</v>
+      </c>
+      <c r="K773" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="L773" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M773" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N773" t="n">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C774" t="n">
+        <v>291.5</v>
+      </c>
+      <c r="D774" t="n">
+        <v>300.75</v>
+      </c>
+      <c r="E774" t="n">
+        <v>-9.25</v>
+      </c>
+      <c r="F774" t="n">
+        <v>295.45</v>
+      </c>
+      <c r="G774" t="n">
+        <v>300.75</v>
+      </c>
+      <c r="H774" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="I774" t="n">
+        <v>289.15</v>
+      </c>
+      <c r="J774" t="n">
+        <v>283.47</v>
+      </c>
+      <c r="K774" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="L774" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M774" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N774" t="n">
+        <v>3.08</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N774"/>
+  <dimension ref="A1:N777"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40702,6 +40702,162 @@
       </c>
       <c r="N774" t="n">
         <v>3.08</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C775" t="n">
+        <v>2185</v>
+      </c>
+      <c r="D775" t="n">
+        <v>2135.91</v>
+      </c>
+      <c r="E775" t="n">
+        <v>49.09</v>
+      </c>
+      <c r="F775" t="n">
+        <v>2188.7</v>
+      </c>
+      <c r="G775" t="n">
+        <v>2209.02</v>
+      </c>
+      <c r="H775" t="n">
+        <v>-20.32</v>
+      </c>
+      <c r="I775" t="n">
+        <v>2130.5</v>
+      </c>
+      <c r="J775" t="n">
+        <v>2185</v>
+      </c>
+      <c r="K775" t="n">
+        <v>-54.5</v>
+      </c>
+      <c r="L775" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M775" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N775" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C776" t="n">
+        <v>290</v>
+      </c>
+      <c r="D776" t="n">
+        <v>283.33</v>
+      </c>
+      <c r="E776" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="F776" t="n">
+        <v>291.35</v>
+      </c>
+      <c r="G776" t="n">
+        <v>287.59</v>
+      </c>
+      <c r="H776" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="I776" t="n">
+        <v>288.15</v>
+      </c>
+      <c r="J776" t="n">
+        <v>284.6</v>
+      </c>
+      <c r="K776" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L776" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M776" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N776" t="n">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C777" t="n">
+        <v>439</v>
+      </c>
+      <c r="D777" t="n">
+        <v>433.45</v>
+      </c>
+      <c r="E777" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="F777" t="n">
+        <v>443.35</v>
+      </c>
+      <c r="G777" t="n">
+        <v>433.45</v>
+      </c>
+      <c r="H777" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="I777" t="n">
+        <v>437.5</v>
+      </c>
+      <c r="J777" t="n">
+        <v>428.79</v>
+      </c>
+      <c r="K777" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="L777" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M777" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N777" t="n">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -40716,31 +40716,31 @@
         </is>
       </c>
       <c r="C775" t="n">
-        <v>2185</v>
+        <v>2157.4</v>
       </c>
       <c r="D775" t="n">
         <v>2135.91</v>
       </c>
       <c r="E775" t="n">
-        <v>49.09</v>
+        <v>21.49</v>
       </c>
       <c r="F775" t="n">
-        <v>2188.7</v>
+        <v>2170</v>
       </c>
       <c r="G775" t="n">
         <v>2209.02</v>
       </c>
       <c r="H775" t="n">
-        <v>-20.32</v>
+        <v>-39.02</v>
       </c>
       <c r="I775" t="n">
-        <v>2130.5</v>
+        <v>2109.4</v>
       </c>
       <c r="J775" t="n">
         <v>2185</v>
       </c>
       <c r="K775" t="n">
-        <v>-54.5</v>
+        <v>-75.59999999999999</v>
       </c>
       <c r="L775" t="inlineStr">
         <is>
@@ -40753,7 +40753,7 @@
         </is>
       </c>
       <c r="N775" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="776">
@@ -40768,31 +40768,31 @@
         </is>
       </c>
       <c r="C776" t="n">
-        <v>290</v>
+        <v>290.5</v>
       </c>
       <c r="D776" t="n">
         <v>283.33</v>
       </c>
       <c r="E776" t="n">
-        <v>6.67</v>
+        <v>7.17</v>
       </c>
       <c r="F776" t="n">
-        <v>291.35</v>
+        <v>294.05</v>
       </c>
       <c r="G776" t="n">
         <v>287.59</v>
       </c>
       <c r="H776" t="n">
-        <v>3.76</v>
+        <v>6.46</v>
       </c>
       <c r="I776" t="n">
-        <v>288.15</v>
+        <v>288.5</v>
       </c>
       <c r="J776" t="n">
         <v>284.6</v>
       </c>
       <c r="K776" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="L776" t="inlineStr">
         <is>
@@ -40805,7 +40805,7 @@
         </is>
       </c>
       <c r="N776" t="n">
-        <v>2.35</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="777">
@@ -40820,31 +40820,31 @@
         </is>
       </c>
       <c r="C777" t="n">
-        <v>439</v>
+        <v>443.4</v>
       </c>
       <c r="D777" t="n">
         <v>433.45</v>
       </c>
       <c r="E777" t="n">
-        <v>5.55</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="F777" t="n">
-        <v>443.35</v>
+        <v>443.65</v>
       </c>
       <c r="G777" t="n">
         <v>433.45</v>
       </c>
       <c r="H777" t="n">
-        <v>9.9</v>
+        <v>10.2</v>
       </c>
       <c r="I777" t="n">
-        <v>437.5</v>
+        <v>438.9</v>
       </c>
       <c r="J777" t="n">
         <v>428.79</v>
       </c>
       <c r="K777" t="n">
-        <v>8.710000000000001</v>
+        <v>10.11</v>
       </c>
       <c r="L777" t="inlineStr">
         <is>
@@ -40857,7 +40857,7 @@
         </is>
       </c>
       <c r="N777" t="n">
-        <v>1.28</v>
+        <v>2.3</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N777"/>
+  <dimension ref="A1:N780"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40858,6 +40858,162 @@
       </c>
       <c r="N777" t="n">
         <v>2.3</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C778" t="n">
+        <v>292.95</v>
+      </c>
+      <c r="D778" t="n">
+        <v>302.76</v>
+      </c>
+      <c r="E778" t="n">
+        <v>-9.81</v>
+      </c>
+      <c r="F778" t="n">
+        <v>295.05</v>
+      </c>
+      <c r="G778" t="n">
+        <v>302.76</v>
+      </c>
+      <c r="H778" t="n">
+        <v>-7.71</v>
+      </c>
+      <c r="I778" t="n">
+        <v>288.45</v>
+      </c>
+      <c r="J778" t="n">
+        <v>290.92</v>
+      </c>
+      <c r="K778" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="L778" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M778" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N778" t="n">
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C779" t="n">
+        <v>5898</v>
+      </c>
+      <c r="D779" t="n">
+        <v>5989.53</v>
+      </c>
+      <c r="E779" t="n">
+        <v>-91.53</v>
+      </c>
+      <c r="F779" t="n">
+        <v>6078</v>
+      </c>
+      <c r="G779" t="n">
+        <v>6000.96</v>
+      </c>
+      <c r="H779" t="n">
+        <v>77.04000000000001</v>
+      </c>
+      <c r="I779" t="n">
+        <v>5882.5</v>
+      </c>
+      <c r="J779" t="n">
+        <v>5822.94</v>
+      </c>
+      <c r="K779" t="n">
+        <v>59.56</v>
+      </c>
+      <c r="L779" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M779" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N779" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C780" t="n">
+        <v>438.05</v>
+      </c>
+      <c r="D780" t="n">
+        <v>451.69</v>
+      </c>
+      <c r="E780" t="n">
+        <v>-13.64</v>
+      </c>
+      <c r="F780" t="n">
+        <v>444.9</v>
+      </c>
+      <c r="G780" t="n">
+        <v>451.69</v>
+      </c>
+      <c r="H780" t="n">
+        <v>-6.79</v>
+      </c>
+      <c r="I780" t="n">
+        <v>437.2</v>
+      </c>
+      <c r="J780" t="n">
+        <v>427.29</v>
+      </c>
+      <c r="K780" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="L780" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M780" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N780" t="n">
+        <v>3.02</v>
       </c>
     </row>
   </sheetData>
@@ -49133,7 +49289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50298,6 +50454,58 @@
       </c>
       <c r="N22" t="n">
         <v>8.949999999999999</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>5898</v>
+      </c>
+      <c r="D23" t="n">
+        <v>5989.53</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-91.53</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6078</v>
+      </c>
+      <c r="G23" t="n">
+        <v>6000.96</v>
+      </c>
+      <c r="H23" t="n">
+        <v>77.04000000000001</v>
+      </c>
+      <c r="I23" t="n">
+        <v>5882.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>5822.94</v>
+      </c>
+      <c r="K23" t="n">
+        <v>59.56</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1.53</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -40872,31 +40872,31 @@
         </is>
       </c>
       <c r="C778" t="n">
-        <v>292.95</v>
+        <v>290</v>
       </c>
       <c r="D778" t="n">
         <v>302.76</v>
       </c>
       <c r="E778" t="n">
-        <v>-9.81</v>
+        <v>-12.76</v>
       </c>
       <c r="F778" t="n">
-        <v>295.05</v>
+        <v>291.35</v>
       </c>
       <c r="G778" t="n">
         <v>302.76</v>
       </c>
       <c r="H778" t="n">
-        <v>-7.71</v>
+        <v>-11.41</v>
       </c>
       <c r="I778" t="n">
-        <v>288.45</v>
+        <v>288.15</v>
       </c>
       <c r="J778" t="n">
         <v>290.92</v>
       </c>
       <c r="K778" t="n">
-        <v>-2.47</v>
+        <v>-2.77</v>
       </c>
       <c r="L778" t="inlineStr">
         <is>
@@ -40909,7 +40909,7 @@
         </is>
       </c>
       <c r="N778" t="n">
-        <v>3.24</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="779">
@@ -40924,31 +40924,31 @@
         </is>
       </c>
       <c r="C779" t="n">
-        <v>5898</v>
+        <v>5988</v>
       </c>
       <c r="D779" t="n">
         <v>5989.53</v>
       </c>
       <c r="E779" t="n">
-        <v>-91.53</v>
+        <v>-1.53</v>
       </c>
       <c r="F779" t="n">
-        <v>6078</v>
+        <v>6008.5</v>
       </c>
       <c r="G779" t="n">
         <v>6000.96</v>
       </c>
       <c r="H779" t="n">
-        <v>77.04000000000001</v>
+        <v>7.54</v>
       </c>
       <c r="I779" t="n">
-        <v>5882.5</v>
+        <v>5787</v>
       </c>
       <c r="J779" t="n">
         <v>5822.94</v>
       </c>
       <c r="K779" t="n">
-        <v>59.56</v>
+        <v>-35.94</v>
       </c>
       <c r="L779" t="inlineStr">
         <is>
@@ -40961,7 +40961,7 @@
         </is>
       </c>
       <c r="N779" t="n">
-        <v>1.53</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="780">
@@ -40976,31 +40976,31 @@
         </is>
       </c>
       <c r="C780" t="n">
-        <v>438.05</v>
+        <v>439</v>
       </c>
       <c r="D780" t="n">
         <v>451.69</v>
       </c>
       <c r="E780" t="n">
-        <v>-13.64</v>
+        <v>-12.69</v>
       </c>
       <c r="F780" t="n">
-        <v>444.9</v>
+        <v>443.35</v>
       </c>
       <c r="G780" t="n">
         <v>451.69</v>
       </c>
       <c r="H780" t="n">
-        <v>-6.79</v>
+        <v>-8.34</v>
       </c>
       <c r="I780" t="n">
-        <v>437.2</v>
+        <v>437.5</v>
       </c>
       <c r="J780" t="n">
         <v>427.29</v>
       </c>
       <c r="K780" t="n">
-        <v>9.91</v>
+        <v>10.21</v>
       </c>
       <c r="L780" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         </is>
       </c>
       <c r="N780" t="n">
-        <v>3.02</v>
+        <v>2.81</v>
       </c>
     </row>
   </sheetData>
@@ -50468,31 +50468,31 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5898</v>
+        <v>5988</v>
       </c>
       <c r="D23" t="n">
         <v>5989.53</v>
       </c>
       <c r="E23" t="n">
-        <v>-91.53</v>
+        <v>-1.53</v>
       </c>
       <c r="F23" t="n">
-        <v>6078</v>
+        <v>6008.5</v>
       </c>
       <c r="G23" t="n">
         <v>6000.96</v>
       </c>
       <c r="H23" t="n">
-        <v>77.04000000000001</v>
+        <v>7.54</v>
       </c>
       <c r="I23" t="n">
-        <v>5882.5</v>
+        <v>5787</v>
       </c>
       <c r="J23" t="n">
         <v>5822.94</v>
       </c>
       <c r="K23" t="n">
-        <v>59.56</v>
+        <v>-35.94</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -50505,7 +50505,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.53</v>
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N780"/>
+  <dimension ref="A1:N784"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41014,6 +41014,214 @@
       </c>
       <c r="N780" t="n">
         <v>2.81</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C781" t="n">
+        <v>447.95</v>
+      </c>
+      <c r="D781" t="n">
+        <v>438.85</v>
+      </c>
+      <c r="E781" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F781" t="n">
+        <v>447.95</v>
+      </c>
+      <c r="G781" t="n">
+        <v>438.85</v>
+      </c>
+      <c r="H781" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="I781" t="n">
+        <v>437.6</v>
+      </c>
+      <c r="J781" t="n">
+        <v>437.52</v>
+      </c>
+      <c r="K781" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="L781" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M781" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N781" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C782" t="n">
+        <v>5840</v>
+      </c>
+      <c r="D782" t="n">
+        <v>5885.19</v>
+      </c>
+      <c r="E782" t="n">
+        <v>-45.19</v>
+      </c>
+      <c r="F782" t="n">
+        <v>6010</v>
+      </c>
+      <c r="G782" t="n">
+        <v>5885.19</v>
+      </c>
+      <c r="H782" t="n">
+        <v>124.81</v>
+      </c>
+      <c r="I782" t="n">
+        <v>5791.5</v>
+      </c>
+      <c r="J782" t="n">
+        <v>5722</v>
+      </c>
+      <c r="K782" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="L782" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M782" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N782" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C783" t="n">
+        <v>295.2</v>
+      </c>
+      <c r="D783" t="n">
+        <v>285.02</v>
+      </c>
+      <c r="E783" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="F783" t="n">
+        <v>295.2</v>
+      </c>
+      <c r="G783" t="n">
+        <v>298.2</v>
+      </c>
+      <c r="H783" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I783" t="n">
+        <v>290.85</v>
+      </c>
+      <c r="J783" t="n">
+        <v>294.09</v>
+      </c>
+      <c r="K783" t="n">
+        <v>-3.24</v>
+      </c>
+      <c r="L783" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M783" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N783" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C784" t="n">
+        <v>2453.2</v>
+      </c>
+      <c r="D784" t="n">
+        <v>2414.33</v>
+      </c>
+      <c r="E784" t="n">
+        <v>38.87</v>
+      </c>
+      <c r="F784" t="n">
+        <v>2485.2</v>
+      </c>
+      <c r="G784" t="n">
+        <v>2487.37</v>
+      </c>
+      <c r="H784" t="n">
+        <v>-2.17</v>
+      </c>
+      <c r="I784" t="n">
+        <v>2424.3</v>
+      </c>
+      <c r="J784" t="n">
+        <v>2453.2</v>
+      </c>
+      <c r="K784" t="n">
+        <v>-28.9</v>
+      </c>
+      <c r="L784" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M784" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N784" t="n">
+        <v>1.61</v>
       </c>
     </row>
   </sheetData>
@@ -49289,7 +49497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50506,6 +50714,58 @@
       </c>
       <c r="N23" t="n">
         <v>0.03</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>5840</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5885.19</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-45.19</v>
+      </c>
+      <c r="F24" t="n">
+        <v>6010</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5885.19</v>
+      </c>
+      <c r="H24" t="n">
+        <v>124.81</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5791.5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>5722</v>
+      </c>
+      <c r="K24" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>0.77</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -41028,31 +41028,31 @@
         </is>
       </c>
       <c r="C781" t="n">
-        <v>447.95</v>
+        <v>438.05</v>
       </c>
       <c r="D781" t="n">
         <v>438.85</v>
       </c>
       <c r="E781" t="n">
-        <v>9.1</v>
+        <v>-0.8</v>
       </c>
       <c r="F781" t="n">
-        <v>447.95</v>
+        <v>444.9</v>
       </c>
       <c r="G781" t="n">
         <v>438.85</v>
       </c>
       <c r="H781" t="n">
-        <v>9.1</v>
+        <v>6.05</v>
       </c>
       <c r="I781" t="n">
-        <v>437.6</v>
+        <v>437.2</v>
       </c>
       <c r="J781" t="n">
         <v>437.52</v>
       </c>
       <c r="K781" t="n">
-        <v>0.08</v>
+        <v>-0.32</v>
       </c>
       <c r="L781" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         </is>
       </c>
       <c r="N781" t="n">
-        <v>2.07</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="782">
@@ -41080,31 +41080,31 @@
         </is>
       </c>
       <c r="C782" t="n">
-        <v>5840</v>
+        <v>5898</v>
       </c>
       <c r="D782" t="n">
         <v>5885.19</v>
       </c>
       <c r="E782" t="n">
-        <v>-45.19</v>
+        <v>12.81</v>
       </c>
       <c r="F782" t="n">
-        <v>6010</v>
+        <v>6078</v>
       </c>
       <c r="G782" t="n">
         <v>5885.19</v>
       </c>
       <c r="H782" t="n">
-        <v>124.81</v>
+        <v>192.81</v>
       </c>
       <c r="I782" t="n">
-        <v>5791.5</v>
+        <v>5882.5</v>
       </c>
       <c r="J782" t="n">
         <v>5722</v>
       </c>
       <c r="K782" t="n">
-        <v>69.5</v>
+        <v>160.5</v>
       </c>
       <c r="L782" t="inlineStr">
         <is>
@@ -41117,7 +41117,7 @@
         </is>
       </c>
       <c r="N782" t="n">
-        <v>0.77</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="783">
@@ -41132,31 +41132,31 @@
         </is>
       </c>
       <c r="C783" t="n">
-        <v>295.2</v>
+        <v>292.95</v>
       </c>
       <c r="D783" t="n">
         <v>285.02</v>
       </c>
       <c r="E783" t="n">
-        <v>10.18</v>
+        <v>7.93</v>
       </c>
       <c r="F783" t="n">
-        <v>295.2</v>
+        <v>295.05</v>
       </c>
       <c r="G783" t="n">
         <v>298.2</v>
       </c>
       <c r="H783" t="n">
-        <v>-3</v>
+        <v>-3.15</v>
       </c>
       <c r="I783" t="n">
-        <v>290.85</v>
+        <v>288.45</v>
       </c>
       <c r="J783" t="n">
         <v>294.09</v>
       </c>
       <c r="K783" t="n">
-        <v>-3.24</v>
+        <v>-5.64</v>
       </c>
       <c r="L783" t="inlineStr">
         <is>
@@ -41165,11 +41165,11 @@
       </c>
       <c r="M783" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N783" t="n">
-        <v>3.57</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="784">
@@ -41184,31 +41184,31 @@
         </is>
       </c>
       <c r="C784" t="n">
-        <v>2453.2</v>
+        <v>2435.3</v>
       </c>
       <c r="D784" t="n">
         <v>2414.33</v>
       </c>
       <c r="E784" t="n">
-        <v>38.87</v>
+        <v>20.97</v>
       </c>
       <c r="F784" t="n">
-        <v>2485.2</v>
+        <v>2512.7</v>
       </c>
       <c r="G784" t="n">
         <v>2487.37</v>
       </c>
       <c r="H784" t="n">
-        <v>-2.17</v>
+        <v>25.33</v>
       </c>
       <c r="I784" t="n">
-        <v>2424.3</v>
+        <v>2420</v>
       </c>
       <c r="J784" t="n">
         <v>2453.2</v>
       </c>
       <c r="K784" t="n">
-        <v>-28.9</v>
+        <v>-33.2</v>
       </c>
       <c r="L784" t="inlineStr">
         <is>
@@ -41221,7 +41221,7 @@
         </is>
       </c>
       <c r="N784" t="n">
-        <v>1.61</v>
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>
@@ -50728,31 +50728,31 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5840</v>
+        <v>5898</v>
       </c>
       <c r="D24" t="n">
         <v>5885.19</v>
       </c>
       <c r="E24" t="n">
-        <v>-45.19</v>
+        <v>12.81</v>
       </c>
       <c r="F24" t="n">
-        <v>6010</v>
+        <v>6078</v>
       </c>
       <c r="G24" t="n">
         <v>5885.19</v>
       </c>
       <c r="H24" t="n">
-        <v>124.81</v>
+        <v>192.81</v>
       </c>
       <c r="I24" t="n">
-        <v>5791.5</v>
+        <v>5882.5</v>
       </c>
       <c r="J24" t="n">
         <v>5722</v>
       </c>
       <c r="K24" t="n">
-        <v>69.5</v>
+        <v>160.5</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -50765,7 +50765,7 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0.77</v>
+        <v>0.22</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N784"/>
+  <dimension ref="A1:N789"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41222,6 +41222,266 @@
       </c>
       <c r="N784" t="n">
         <v>0.87</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C785" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="D785" t="n">
+        <v>116.89</v>
+      </c>
+      <c r="E785" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="F785" t="n">
+        <v>116.4</v>
+      </c>
+      <c r="G785" t="n">
+        <v>116.89</v>
+      </c>
+      <c r="H785" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="I785" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="J785" t="n">
+        <v>112.47</v>
+      </c>
+      <c r="K785" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="L785" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M785" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N785" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C786" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D786" t="n">
+        <v>2541.9</v>
+      </c>
+      <c r="E786" t="n">
+        <v>-41.9</v>
+      </c>
+      <c r="F786" t="n">
+        <v>2521.7</v>
+      </c>
+      <c r="G786" t="n">
+        <v>2547.58</v>
+      </c>
+      <c r="H786" t="n">
+        <v>-25.88</v>
+      </c>
+      <c r="I786" t="n">
+        <v>2455.1</v>
+      </c>
+      <c r="J786" t="n">
+        <v>2471.86</v>
+      </c>
+      <c r="K786" t="n">
+        <v>-16.76</v>
+      </c>
+      <c r="L786" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M786" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N786" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C787" t="n">
+        <v>325.3</v>
+      </c>
+      <c r="D787" t="n">
+        <v>326.96</v>
+      </c>
+      <c r="E787" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="F787" t="n">
+        <v>327.45</v>
+      </c>
+      <c r="G787" t="n">
+        <v>328.91</v>
+      </c>
+      <c r="H787" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="I787" t="n">
+        <v>321.35</v>
+      </c>
+      <c r="J787" t="n">
+        <v>319.04</v>
+      </c>
+      <c r="K787" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="L787" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M787" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N787" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C788" t="n">
+        <v>5741</v>
+      </c>
+      <c r="D788" t="n">
+        <v>5799.55</v>
+      </c>
+      <c r="E788" t="n">
+        <v>-58.55</v>
+      </c>
+      <c r="F788" t="n">
+        <v>5755</v>
+      </c>
+      <c r="G788" t="n">
+        <v>5799.55</v>
+      </c>
+      <c r="H788" t="n">
+        <v>-44.55</v>
+      </c>
+      <c r="I788" t="n">
+        <v>5492</v>
+      </c>
+      <c r="J788" t="n">
+        <v>5576.1</v>
+      </c>
+      <c r="K788" t="n">
+        <v>-84.09999999999999</v>
+      </c>
+      <c r="L788" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M788" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N788" t="n">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C789" t="n">
+        <v>293</v>
+      </c>
+      <c r="D789" t="n">
+        <v>303.56</v>
+      </c>
+      <c r="E789" t="n">
+        <v>-10.56</v>
+      </c>
+      <c r="F789" t="n">
+        <v>295.2</v>
+      </c>
+      <c r="G789" t="n">
+        <v>303.56</v>
+      </c>
+      <c r="H789" t="n">
+        <v>-8.359999999999999</v>
+      </c>
+      <c r="I789" t="n">
+        <v>290.1</v>
+      </c>
+      <c r="J789" t="n">
+        <v>288.24</v>
+      </c>
+      <c r="K789" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="L789" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M789" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N789" t="n">
+        <v>3.48</v>
       </c>
     </row>
   </sheetData>
@@ -45183,7 +45443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47284,6 +47544,58 @@
       </c>
       <c r="N40" t="n">
         <v>2.86</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>325.3</v>
+      </c>
+      <c r="D41" t="n">
+        <v>326.96</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="F41" t="n">
+        <v>327.45</v>
+      </c>
+      <c r="G41" t="n">
+        <v>328.91</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="I41" t="n">
+        <v>321.35</v>
+      </c>
+      <c r="J41" t="n">
+        <v>319.04</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>0.51</v>
       </c>
     </row>
   </sheetData>
@@ -49497,7 +49809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50766,6 +51078,58 @@
       </c>
       <c r="N24" t="n">
         <v>0.22</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5741</v>
+      </c>
+      <c r="D25" t="n">
+        <v>5799.55</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-58.55</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5755</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5799.55</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-44.55</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5492</v>
+      </c>
+      <c r="J25" t="n">
+        <v>5576.1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-84.09999999999999</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>1.01</v>
       </c>
     </row>
   </sheetData>
@@ -50779,7 +51143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52672,6 +53036,58 @@
       </c>
       <c r="N36" t="n">
         <v>10.12</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="D37" t="n">
+        <v>116.89</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="F37" t="n">
+        <v>116.4</v>
+      </c>
+      <c r="G37" t="n">
+        <v>116.89</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="I37" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>112.47</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -41236,31 +41236,31 @@
         </is>
       </c>
       <c r="C785" t="n">
-        <v>116.3</v>
+        <v>115.05</v>
       </c>
       <c r="D785" t="n">
         <v>116.89</v>
       </c>
       <c r="E785" t="n">
-        <v>-0.59</v>
+        <v>-1.84</v>
       </c>
       <c r="F785" t="n">
-        <v>116.4</v>
+        <v>118.79</v>
       </c>
       <c r="G785" t="n">
         <v>116.89</v>
       </c>
       <c r="H785" t="n">
-        <v>-0.49</v>
+        <v>1.9</v>
       </c>
       <c r="I785" t="n">
-        <v>114.1</v>
+        <v>114.63</v>
       </c>
       <c r="J785" t="n">
         <v>112.47</v>
       </c>
       <c r="K785" t="n">
-        <v>1.63</v>
+        <v>2.16</v>
       </c>
       <c r="L785" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         </is>
       </c>
       <c r="N785" t="n">
-        <v>0.5</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="786">
@@ -41288,31 +41288,31 @@
         </is>
       </c>
       <c r="C786" t="n">
-        <v>2500</v>
+        <v>2453.2</v>
       </c>
       <c r="D786" t="n">
         <v>2541.9</v>
       </c>
       <c r="E786" t="n">
-        <v>-41.9</v>
+        <v>-88.7</v>
       </c>
       <c r="F786" t="n">
-        <v>2521.7</v>
+        <v>2485.2</v>
       </c>
       <c r="G786" t="n">
         <v>2547.58</v>
       </c>
       <c r="H786" t="n">
-        <v>-25.88</v>
+        <v>-62.38</v>
       </c>
       <c r="I786" t="n">
-        <v>2455.1</v>
+        <v>2424.3</v>
       </c>
       <c r="J786" t="n">
         <v>2471.86</v>
       </c>
       <c r="K786" t="n">
-        <v>-16.76</v>
+        <v>-47.56</v>
       </c>
       <c r="L786" t="inlineStr">
         <is>
@@ -41321,11 +41321,11 @@
       </c>
       <c r="M786" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N786" t="n">
-        <v>1.65</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="787">
@@ -41340,31 +41340,31 @@
         </is>
       </c>
       <c r="C787" t="n">
-        <v>325.3</v>
+        <v>323</v>
       </c>
       <c r="D787" t="n">
         <v>326.96</v>
       </c>
       <c r="E787" t="n">
-        <v>-1.66</v>
+        <v>-3.96</v>
       </c>
       <c r="F787" t="n">
-        <v>327.45</v>
+        <v>323</v>
       </c>
       <c r="G787" t="n">
         <v>328.91</v>
       </c>
       <c r="H787" t="n">
-        <v>-1.46</v>
+        <v>-5.91</v>
       </c>
       <c r="I787" t="n">
-        <v>321.35</v>
+        <v>313.6</v>
       </c>
       <c r="J787" t="n">
         <v>319.04</v>
       </c>
       <c r="K787" t="n">
-        <v>2.31</v>
+        <v>-5.44</v>
       </c>
       <c r="L787" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         </is>
       </c>
       <c r="N787" t="n">
-        <v>0.51</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="788">
@@ -41392,31 +41392,31 @@
         </is>
       </c>
       <c r="C788" t="n">
-        <v>5741</v>
+        <v>5840</v>
       </c>
       <c r="D788" t="n">
         <v>5799.55</v>
       </c>
       <c r="E788" t="n">
-        <v>-58.55</v>
+        <v>40.45</v>
       </c>
       <c r="F788" t="n">
-        <v>5755</v>
+        <v>6010</v>
       </c>
       <c r="G788" t="n">
         <v>5799.55</v>
       </c>
       <c r="H788" t="n">
-        <v>-44.55</v>
+        <v>210.45</v>
       </c>
       <c r="I788" t="n">
-        <v>5492</v>
+        <v>5791.5</v>
       </c>
       <c r="J788" t="n">
         <v>5576.1</v>
       </c>
       <c r="K788" t="n">
-        <v>-84.09999999999999</v>
+        <v>215.4</v>
       </c>
       <c r="L788" t="inlineStr">
         <is>
@@ -41429,7 +41429,7 @@
         </is>
       </c>
       <c r="N788" t="n">
-        <v>1.01</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="789">
@@ -41444,13 +41444,13 @@
         </is>
       </c>
       <c r="C789" t="n">
-        <v>293</v>
+        <v>295.2</v>
       </c>
       <c r="D789" t="n">
         <v>303.56</v>
       </c>
       <c r="E789" t="n">
-        <v>-10.56</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="F789" t="n">
         <v>295.2</v>
@@ -41462,13 +41462,13 @@
         <v>-8.359999999999999</v>
       </c>
       <c r="I789" t="n">
-        <v>290.1</v>
+        <v>290.85</v>
       </c>
       <c r="J789" t="n">
         <v>288.24</v>
       </c>
       <c r="K789" t="n">
-        <v>1.86</v>
+        <v>2.61</v>
       </c>
       <c r="L789" t="inlineStr">
         <is>
@@ -41481,7 +41481,7 @@
         </is>
       </c>
       <c r="N789" t="n">
-        <v>3.48</v>
+        <v>2.75</v>
       </c>
     </row>
   </sheetData>
@@ -47558,31 +47558,31 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>325.3</v>
+        <v>323</v>
       </c>
       <c r="D41" t="n">
         <v>326.96</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.66</v>
+        <v>-3.96</v>
       </c>
       <c r="F41" t="n">
-        <v>327.45</v>
+        <v>323</v>
       </c>
       <c r="G41" t="n">
         <v>328.91</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.46</v>
+        <v>-5.91</v>
       </c>
       <c r="I41" t="n">
-        <v>321.35</v>
+        <v>313.6</v>
       </c>
       <c r="J41" t="n">
         <v>319.04</v>
       </c>
       <c r="K41" t="n">
-        <v>2.31</v>
+        <v>-5.44</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -47595,7 +47595,7 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0.51</v>
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>
@@ -51092,31 +51092,31 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5741</v>
+        <v>5840</v>
       </c>
       <c r="D25" t="n">
         <v>5799.55</v>
       </c>
       <c r="E25" t="n">
-        <v>-58.55</v>
+        <v>40.45</v>
       </c>
       <c r="F25" t="n">
-        <v>5755</v>
+        <v>6010</v>
       </c>
       <c r="G25" t="n">
         <v>5799.55</v>
       </c>
       <c r="H25" t="n">
-        <v>-44.55</v>
+        <v>210.45</v>
       </c>
       <c r="I25" t="n">
-        <v>5492</v>
+        <v>5791.5</v>
       </c>
       <c r="J25" t="n">
         <v>5576.1</v>
       </c>
       <c r="K25" t="n">
-        <v>-84.09999999999999</v>
+        <v>215.4</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -51129,7 +51129,7 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.01</v>
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -53050,31 +53050,31 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>116.3</v>
+        <v>115.05</v>
       </c>
       <c r="D37" t="n">
         <v>116.89</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.59</v>
+        <v>-1.84</v>
       </c>
       <c r="F37" t="n">
-        <v>116.4</v>
+        <v>118.79</v>
       </c>
       <c r="G37" t="n">
         <v>116.89</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.49</v>
+        <v>1.9</v>
       </c>
       <c r="I37" t="n">
-        <v>114.1</v>
+        <v>114.63</v>
       </c>
       <c r="J37" t="n">
         <v>112.47</v>
       </c>
       <c r="K37" t="n">
-        <v>1.63</v>
+        <v>2.16</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -53087,7 +53087,7 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0.5</v>
+        <v>1.57</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -41236,31 +41236,31 @@
         </is>
       </c>
       <c r="C785" t="n">
-        <v>115.05</v>
+        <v>116.3</v>
       </c>
       <c r="D785" t="n">
-        <v>116.89</v>
+        <v>115.38</v>
       </c>
       <c r="E785" t="n">
-        <v>-1.84</v>
+        <v>0.92</v>
       </c>
       <c r="F785" t="n">
-        <v>118.79</v>
+        <v>116.4</v>
       </c>
       <c r="G785" t="n">
-        <v>116.89</v>
+        <v>115.38</v>
       </c>
       <c r="H785" t="n">
-        <v>1.9</v>
+        <v>1.02</v>
       </c>
       <c r="I785" t="n">
-        <v>114.63</v>
+        <v>114.1</v>
       </c>
       <c r="J785" t="n">
-        <v>112.47</v>
+        <v>112.62</v>
       </c>
       <c r="K785" t="n">
-        <v>2.16</v>
+        <v>1.48</v>
       </c>
       <c r="L785" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         </is>
       </c>
       <c r="N785" t="n">
-        <v>1.57</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="786">
@@ -41284,35 +41284,35 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C786" t="n">
-        <v>2453.2</v>
+        <v>5741</v>
       </c>
       <c r="D786" t="n">
-        <v>2541.9</v>
+        <v>5827.26</v>
       </c>
       <c r="E786" t="n">
-        <v>-88.7</v>
+        <v>-86.26000000000001</v>
       </c>
       <c r="F786" t="n">
-        <v>2485.2</v>
+        <v>5755</v>
       </c>
       <c r="G786" t="n">
-        <v>2547.58</v>
+        <v>5827.26</v>
       </c>
       <c r="H786" t="n">
-        <v>-62.38</v>
+        <v>-72.26000000000001</v>
       </c>
       <c r="I786" t="n">
-        <v>2424.3</v>
+        <v>5492</v>
       </c>
       <c r="J786" t="n">
-        <v>2471.86</v>
+        <v>5583.31</v>
       </c>
       <c r="K786" t="n">
-        <v>-47.56</v>
+        <v>-91.31</v>
       </c>
       <c r="L786" t="inlineStr">
         <is>
@@ -41321,11 +41321,11 @@
       </c>
       <c r="M786" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N786" t="n">
-        <v>3.49</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="787">
@@ -41336,35 +41336,35 @@
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C787" t="n">
-        <v>323</v>
+        <v>293</v>
       </c>
       <c r="D787" t="n">
-        <v>326.96</v>
+        <v>287.21</v>
       </c>
       <c r="E787" t="n">
-        <v>-3.96</v>
+        <v>5.79</v>
       </c>
       <c r="F787" t="n">
-        <v>323</v>
+        <v>295.2</v>
       </c>
       <c r="G787" t="n">
-        <v>328.91</v>
+        <v>296.72</v>
       </c>
       <c r="H787" t="n">
-        <v>-5.91</v>
+        <v>-1.52</v>
       </c>
       <c r="I787" t="n">
-        <v>313.6</v>
+        <v>290.1</v>
       </c>
       <c r="J787" t="n">
-        <v>319.04</v>
+        <v>288.62</v>
       </c>
       <c r="K787" t="n">
-        <v>-5.44</v>
+        <v>1.48</v>
       </c>
       <c r="L787" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         </is>
       </c>
       <c r="N787" t="n">
-        <v>1.21</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="788">
@@ -41388,35 +41388,35 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C788" t="n">
-        <v>5840</v>
+        <v>2500</v>
       </c>
       <c r="D788" t="n">
-        <v>5799.55</v>
+        <v>2432.05</v>
       </c>
       <c r="E788" t="n">
-        <v>40.45</v>
+        <v>67.95</v>
       </c>
       <c r="F788" t="n">
-        <v>6010</v>
+        <v>2521.7</v>
       </c>
       <c r="G788" t="n">
-        <v>5799.55</v>
+        <v>2544.05</v>
       </c>
       <c r="H788" t="n">
-        <v>210.45</v>
+        <v>-22.35</v>
       </c>
       <c r="I788" t="n">
-        <v>5791.5</v>
+        <v>2455.1</v>
       </c>
       <c r="J788" t="n">
-        <v>5576.1</v>
+        <v>2475.07</v>
       </c>
       <c r="K788" t="n">
-        <v>215.4</v>
+        <v>-19.97</v>
       </c>
       <c r="L788" t="inlineStr">
         <is>
@@ -41429,7 +41429,7 @@
         </is>
       </c>
       <c r="N788" t="n">
-        <v>0.7</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="789">
@@ -41440,35 +41440,35 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C789" t="n">
-        <v>295.2</v>
+        <v>325.3</v>
       </c>
       <c r="D789" t="n">
-        <v>303.56</v>
+        <v>323.93</v>
       </c>
       <c r="E789" t="n">
-        <v>-8.359999999999999</v>
+        <v>1.37</v>
       </c>
       <c r="F789" t="n">
-        <v>295.2</v>
+        <v>327.45</v>
       </c>
       <c r="G789" t="n">
-        <v>303.56</v>
+        <v>328.46</v>
       </c>
       <c r="H789" t="n">
-        <v>-8.359999999999999</v>
+        <v>-1.01</v>
       </c>
       <c r="I789" t="n">
-        <v>290.85</v>
+        <v>321.35</v>
       </c>
       <c r="J789" t="n">
-        <v>288.24</v>
+        <v>319.46</v>
       </c>
       <c r="K789" t="n">
-        <v>2.61</v>
+        <v>1.89</v>
       </c>
       <c r="L789" t="inlineStr">
         <is>
@@ -41481,7 +41481,7 @@
         </is>
       </c>
       <c r="N789" t="n">
-        <v>2.75</v>
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>
@@ -47558,31 +47558,31 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>323</v>
+        <v>325.3</v>
       </c>
       <c r="D41" t="n">
-        <v>326.96</v>
+        <v>323.93</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.96</v>
+        <v>1.37</v>
       </c>
       <c r="F41" t="n">
-        <v>323</v>
+        <v>327.45</v>
       </c>
       <c r="G41" t="n">
-        <v>328.91</v>
+        <v>328.46</v>
       </c>
       <c r="H41" t="n">
-        <v>-5.91</v>
+        <v>-1.01</v>
       </c>
       <c r="I41" t="n">
-        <v>313.6</v>
+        <v>321.35</v>
       </c>
       <c r="J41" t="n">
-        <v>319.04</v>
+        <v>319.46</v>
       </c>
       <c r="K41" t="n">
-        <v>-5.44</v>
+        <v>1.89</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -47595,7 +47595,7 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.21</v>
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>
@@ -51092,31 +51092,31 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5840</v>
+        <v>5741</v>
       </c>
       <c r="D25" t="n">
-        <v>5799.55</v>
+        <v>5827.26</v>
       </c>
       <c r="E25" t="n">
-        <v>40.45</v>
+        <v>-86.26000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>6010</v>
+        <v>5755</v>
       </c>
       <c r="G25" t="n">
-        <v>5799.55</v>
+        <v>5827.26</v>
       </c>
       <c r="H25" t="n">
-        <v>210.45</v>
+        <v>-72.26000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>5791.5</v>
+        <v>5492</v>
       </c>
       <c r="J25" t="n">
-        <v>5576.1</v>
+        <v>5583.31</v>
       </c>
       <c r="K25" t="n">
-        <v>215.4</v>
+        <v>-91.31</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -51129,7 +51129,7 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0.7</v>
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>
@@ -53050,31 +53050,31 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>115.05</v>
+        <v>116.3</v>
       </c>
       <c r="D37" t="n">
-        <v>116.89</v>
+        <v>115.38</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.84</v>
+        <v>0.92</v>
       </c>
       <c r="F37" t="n">
-        <v>118.79</v>
+        <v>116.4</v>
       </c>
       <c r="G37" t="n">
-        <v>116.89</v>
+        <v>115.38</v>
       </c>
       <c r="H37" t="n">
-        <v>1.9</v>
+        <v>1.02</v>
       </c>
       <c r="I37" t="n">
-        <v>114.63</v>
+        <v>114.1</v>
       </c>
       <c r="J37" t="n">
-        <v>112.47</v>
+        <v>112.62</v>
       </c>
       <c r="K37" t="n">
-        <v>2.16</v>
+        <v>1.48</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -53087,7 +53087,7 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.57</v>
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N789"/>
+  <dimension ref="A1:N793"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41482,6 +41482,214 @@
       </c>
       <c r="N789" t="n">
         <v>0.42</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C790" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="D790" t="n">
+        <v>123.86</v>
+      </c>
+      <c r="E790" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="F790" t="n">
+        <v>125.22</v>
+      </c>
+      <c r="G790" t="n">
+        <v>123.86</v>
+      </c>
+      <c r="H790" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I790" t="n">
+        <v>120</v>
+      </c>
+      <c r="J790" t="n">
+        <v>117.48</v>
+      </c>
+      <c r="K790" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="L790" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M790" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N790" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C791" t="n">
+        <v>293.65</v>
+      </c>
+      <c r="D791" t="n">
+        <v>301.97</v>
+      </c>
+      <c r="E791" t="n">
+        <v>-8.32</v>
+      </c>
+      <c r="F791" t="n">
+        <v>295.4</v>
+      </c>
+      <c r="G791" t="n">
+        <v>301.97</v>
+      </c>
+      <c r="H791" t="n">
+        <v>-6.57</v>
+      </c>
+      <c r="I791" t="n">
+        <v>291.05</v>
+      </c>
+      <c r="J791" t="n">
+        <v>286.67</v>
+      </c>
+      <c r="K791" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="L791" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M791" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N791" t="n">
+        <v>2.76</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C792" t="n">
+        <v>5690</v>
+      </c>
+      <c r="D792" t="n">
+        <v>5650.63</v>
+      </c>
+      <c r="E792" t="n">
+        <v>39.37</v>
+      </c>
+      <c r="F792" t="n">
+        <v>5909</v>
+      </c>
+      <c r="G792" t="n">
+        <v>5650.63</v>
+      </c>
+      <c r="H792" t="n">
+        <v>258.37</v>
+      </c>
+      <c r="I792" t="n">
+        <v>5635</v>
+      </c>
+      <c r="J792" t="n">
+        <v>5443.83</v>
+      </c>
+      <c r="K792" t="n">
+        <v>191.17</v>
+      </c>
+      <c r="L792" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M792" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N792" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C793" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D793" t="n">
+        <v>2590.41</v>
+      </c>
+      <c r="E793" t="n">
+        <v>-90.41</v>
+      </c>
+      <c r="F793" t="n">
+        <v>2515.8</v>
+      </c>
+      <c r="G793" t="n">
+        <v>2590.41</v>
+      </c>
+      <c r="H793" t="n">
+        <v>-74.61</v>
+      </c>
+      <c r="I793" t="n">
+        <v>2453</v>
+      </c>
+      <c r="J793" t="n">
+        <v>2439.34</v>
+      </c>
+      <c r="K793" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="L793" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M793" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N793" t="n">
+        <v>3.49</v>
       </c>
     </row>
   </sheetData>
@@ -49809,7 +50017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51130,6 +51338,58 @@
       </c>
       <c r="N25" t="n">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>5690</v>
+      </c>
+      <c r="D26" t="n">
+        <v>5650.63</v>
+      </c>
+      <c r="E26" t="n">
+        <v>39.37</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5909</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5650.63</v>
+      </c>
+      <c r="H26" t="n">
+        <v>258.37</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5635</v>
+      </c>
+      <c r="J26" t="n">
+        <v>5443.83</v>
+      </c>
+      <c r="K26" t="n">
+        <v>191.17</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -51143,7 +51403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53088,6 +53348,58 @@
       </c>
       <c r="N37" t="n">
         <v>0.8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="D38" t="n">
+        <v>123.86</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="F38" t="n">
+        <v>125.22</v>
+      </c>
+      <c r="G38" t="n">
+        <v>123.86</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I38" t="n">
+        <v>120</v>
+      </c>
+      <c r="J38" t="n">
+        <v>117.48</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>1.58</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -41496,31 +41496,31 @@
         </is>
       </c>
       <c r="C790" t="n">
-        <v>121.9</v>
+        <v>116.3</v>
       </c>
       <c r="D790" t="n">
         <v>123.86</v>
       </c>
       <c r="E790" t="n">
-        <v>-1.96</v>
+        <v>-7.56</v>
       </c>
       <c r="F790" t="n">
-        <v>125.22</v>
+        <v>116.4</v>
       </c>
       <c r="G790" t="n">
         <v>123.86</v>
       </c>
       <c r="H790" t="n">
-        <v>1.36</v>
+        <v>-7.46</v>
       </c>
       <c r="I790" t="n">
-        <v>120</v>
+        <v>114.1</v>
       </c>
       <c r="J790" t="n">
         <v>117.48</v>
       </c>
       <c r="K790" t="n">
-        <v>2.52</v>
+        <v>-3.38</v>
       </c>
       <c r="L790" t="inlineStr">
         <is>
@@ -41529,11 +41529,11 @@
       </c>
       <c r="M790" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N790" t="n">
-        <v>1.58</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="791">
@@ -41548,31 +41548,31 @@
         </is>
       </c>
       <c r="C791" t="n">
-        <v>293.65</v>
+        <v>293</v>
       </c>
       <c r="D791" t="n">
         <v>301.97</v>
       </c>
       <c r="E791" t="n">
-        <v>-8.32</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="F791" t="n">
-        <v>295.4</v>
+        <v>295.2</v>
       </c>
       <c r="G791" t="n">
         <v>301.97</v>
       </c>
       <c r="H791" t="n">
-        <v>-6.57</v>
+        <v>-6.77</v>
       </c>
       <c r="I791" t="n">
-        <v>291.05</v>
+        <v>290.1</v>
       </c>
       <c r="J791" t="n">
         <v>286.67</v>
       </c>
       <c r="K791" t="n">
-        <v>4.38</v>
+        <v>3.43</v>
       </c>
       <c r="L791" t="inlineStr">
         <is>
@@ -41585,7 +41585,7 @@
         </is>
       </c>
       <c r="N791" t="n">
-        <v>2.76</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="792">
@@ -41600,31 +41600,31 @@
         </is>
       </c>
       <c r="C792" t="n">
-        <v>5690</v>
+        <v>5741</v>
       </c>
       <c r="D792" t="n">
         <v>5650.63</v>
       </c>
       <c r="E792" t="n">
-        <v>39.37</v>
+        <v>90.37</v>
       </c>
       <c r="F792" t="n">
-        <v>5909</v>
+        <v>5755</v>
       </c>
       <c r="G792" t="n">
         <v>5650.63</v>
       </c>
       <c r="H792" t="n">
-        <v>258.37</v>
+        <v>104.37</v>
       </c>
       <c r="I792" t="n">
-        <v>5635</v>
+        <v>5492</v>
       </c>
       <c r="J792" t="n">
         <v>5443.83</v>
       </c>
       <c r="K792" t="n">
-        <v>191.17</v>
+        <v>48.17</v>
       </c>
       <c r="L792" t="inlineStr">
         <is>
@@ -41637,7 +41637,7 @@
         </is>
       </c>
       <c r="N792" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="793">
@@ -41661,22 +41661,22 @@
         <v>-90.41</v>
       </c>
       <c r="F793" t="n">
-        <v>2515.8</v>
+        <v>2521.7</v>
       </c>
       <c r="G793" t="n">
         <v>2590.41</v>
       </c>
       <c r="H793" t="n">
-        <v>-74.61</v>
+        <v>-68.70999999999999</v>
       </c>
       <c r="I793" t="n">
-        <v>2453</v>
+        <v>2455.1</v>
       </c>
       <c r="J793" t="n">
         <v>2439.34</v>
       </c>
       <c r="K793" t="n">
-        <v>13.66</v>
+        <v>15.76</v>
       </c>
       <c r="L793" t="inlineStr">
         <is>
@@ -51352,31 +51352,31 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5690</v>
+        <v>5741</v>
       </c>
       <c r="D26" t="n">
         <v>5650.63</v>
       </c>
       <c r="E26" t="n">
-        <v>39.37</v>
+        <v>90.37</v>
       </c>
       <c r="F26" t="n">
-        <v>5909</v>
+        <v>5755</v>
       </c>
       <c r="G26" t="n">
         <v>5650.63</v>
       </c>
       <c r="H26" t="n">
-        <v>258.37</v>
+        <v>104.37</v>
       </c>
       <c r="I26" t="n">
-        <v>5635</v>
+        <v>5492</v>
       </c>
       <c r="J26" t="n">
         <v>5443.83</v>
       </c>
       <c r="K26" t="n">
-        <v>191.17</v>
+        <v>48.17</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -51389,7 +51389,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>
@@ -53362,31 +53362,31 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>121.9</v>
+        <v>116.3</v>
       </c>
       <c r="D38" t="n">
         <v>123.86</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.96</v>
+        <v>-7.56</v>
       </c>
       <c r="F38" t="n">
-        <v>125.22</v>
+        <v>116.4</v>
       </c>
       <c r="G38" t="n">
         <v>123.86</v>
       </c>
       <c r="H38" t="n">
-        <v>1.36</v>
+        <v>-7.46</v>
       </c>
       <c r="I38" t="n">
-        <v>120</v>
+        <v>114.1</v>
       </c>
       <c r="J38" t="n">
         <v>117.48</v>
       </c>
       <c r="K38" t="n">
-        <v>2.52</v>
+        <v>-3.38</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -53395,11 +53395,11 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.58</v>
+        <v>6.1</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -41492,35 +41492,35 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C790" t="n">
-        <v>116.3</v>
+        <v>293.65</v>
       </c>
       <c r="D790" t="n">
-        <v>123.86</v>
+        <v>287.21</v>
       </c>
       <c r="E790" t="n">
-        <v>-7.56</v>
+        <v>6.44</v>
       </c>
       <c r="F790" t="n">
-        <v>116.4</v>
+        <v>295.4</v>
       </c>
       <c r="G790" t="n">
-        <v>123.86</v>
+        <v>294.23</v>
       </c>
       <c r="H790" t="n">
-        <v>-7.46</v>
+        <v>1.17</v>
       </c>
       <c r="I790" t="n">
-        <v>114.1</v>
+        <v>291.05</v>
       </c>
       <c r="J790" t="n">
-        <v>117.48</v>
+        <v>288.65</v>
       </c>
       <c r="K790" t="n">
-        <v>-3.38</v>
+        <v>2.4</v>
       </c>
       <c r="L790" t="inlineStr">
         <is>
@@ -41529,11 +41529,11 @@
       </c>
       <c r="M790" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N790" t="n">
-        <v>6.1</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="791">
@@ -41544,35 +41544,35 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C791" t="n">
-        <v>293</v>
+        <v>121.9</v>
       </c>
       <c r="D791" t="n">
-        <v>301.97</v>
+        <v>115.38</v>
       </c>
       <c r="E791" t="n">
-        <v>-8.970000000000001</v>
+        <v>6.52</v>
       </c>
       <c r="F791" t="n">
-        <v>295.2</v>
+        <v>125.22</v>
       </c>
       <c r="G791" t="n">
-        <v>301.97</v>
+        <v>117.17</v>
       </c>
       <c r="H791" t="n">
-        <v>-6.77</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I791" t="n">
-        <v>290.1</v>
+        <v>120</v>
       </c>
       <c r="J791" t="n">
-        <v>286.67</v>
+        <v>118.29</v>
       </c>
       <c r="K791" t="n">
-        <v>3.43</v>
+        <v>1.71</v>
       </c>
       <c r="L791" t="inlineStr">
         <is>
@@ -41581,11 +41581,11 @@
       </c>
       <c r="M791" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N791" t="n">
-        <v>2.97</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="792">
@@ -41600,31 +41600,31 @@
         </is>
       </c>
       <c r="C792" t="n">
-        <v>5741</v>
+        <v>5690</v>
       </c>
       <c r="D792" t="n">
-        <v>5650.63</v>
+        <v>5827.23</v>
       </c>
       <c r="E792" t="n">
-        <v>90.37</v>
+        <v>-137.23</v>
       </c>
       <c r="F792" t="n">
-        <v>5755</v>
+        <v>5909</v>
       </c>
       <c r="G792" t="n">
-        <v>5650.63</v>
+        <v>5827.23</v>
       </c>
       <c r="H792" t="n">
-        <v>104.37</v>
+        <v>81.77</v>
       </c>
       <c r="I792" t="n">
-        <v>5492</v>
+        <v>5635</v>
       </c>
       <c r="J792" t="n">
-        <v>5443.83</v>
+        <v>5481.45</v>
       </c>
       <c r="K792" t="n">
-        <v>48.17</v>
+        <v>153.55</v>
       </c>
       <c r="L792" t="inlineStr">
         <is>
@@ -41637,7 +41637,7 @@
         </is>
       </c>
       <c r="N792" t="n">
-        <v>1.6</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="793">
@@ -41655,28 +41655,28 @@
         <v>2500</v>
       </c>
       <c r="D793" t="n">
-        <v>2590.41</v>
+        <v>2432.05</v>
       </c>
       <c r="E793" t="n">
-        <v>-90.41</v>
+        <v>67.95</v>
       </c>
       <c r="F793" t="n">
-        <v>2521.7</v>
+        <v>2515.8</v>
       </c>
       <c r="G793" t="n">
-        <v>2590.41</v>
+        <v>2503.64</v>
       </c>
       <c r="H793" t="n">
-        <v>-68.70999999999999</v>
+        <v>12.16</v>
       </c>
       <c r="I793" t="n">
-        <v>2455.1</v>
+        <v>2453</v>
       </c>
       <c r="J793" t="n">
-        <v>2439.34</v>
+        <v>2456.14</v>
       </c>
       <c r="K793" t="n">
-        <v>15.76</v>
+        <v>-3.14</v>
       </c>
       <c r="L793" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         </is>
       </c>
       <c r="N793" t="n">
-        <v>3.49</v>
+        <v>2.79</v>
       </c>
     </row>
   </sheetData>
@@ -51352,31 +51352,31 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5741</v>
+        <v>5690</v>
       </c>
       <c r="D26" t="n">
-        <v>5650.63</v>
+        <v>5827.23</v>
       </c>
       <c r="E26" t="n">
-        <v>90.37</v>
+        <v>-137.23</v>
       </c>
       <c r="F26" t="n">
-        <v>5755</v>
+        <v>5909</v>
       </c>
       <c r="G26" t="n">
-        <v>5650.63</v>
+        <v>5827.23</v>
       </c>
       <c r="H26" t="n">
-        <v>104.37</v>
+        <v>81.77</v>
       </c>
       <c r="I26" t="n">
-        <v>5492</v>
+        <v>5635</v>
       </c>
       <c r="J26" t="n">
-        <v>5443.83</v>
+        <v>5481.45</v>
       </c>
       <c r="K26" t="n">
-        <v>48.17</v>
+        <v>153.55</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -51389,7 +51389,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.6</v>
+        <v>2.35</v>
       </c>
     </row>
   </sheetData>
@@ -53362,31 +53362,31 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>116.3</v>
+        <v>121.9</v>
       </c>
       <c r="D38" t="n">
-        <v>123.86</v>
+        <v>115.38</v>
       </c>
       <c r="E38" t="n">
-        <v>-7.56</v>
+        <v>6.52</v>
       </c>
       <c r="F38" t="n">
-        <v>116.4</v>
+        <v>125.22</v>
       </c>
       <c r="G38" t="n">
-        <v>123.86</v>
+        <v>117.17</v>
       </c>
       <c r="H38" t="n">
-        <v>-7.46</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>114.1</v>
+        <v>120</v>
       </c>
       <c r="J38" t="n">
-        <v>117.48</v>
+        <v>118.29</v>
       </c>
       <c r="K38" t="n">
-        <v>-3.38</v>
+        <v>1.71</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -53399,7 +53399,7 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>6.1</v>
+        <v>5.65</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N793"/>
+  <dimension ref="A1:N797"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41690,6 +41690,214 @@
       </c>
       <c r="N793" t="n">
         <v>2.79</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C794" t="n">
+        <v>295</v>
+      </c>
+      <c r="D794" t="n">
+        <v>304.03</v>
+      </c>
+      <c r="E794" t="n">
+        <v>-9.029999999999999</v>
+      </c>
+      <c r="F794" t="n">
+        <v>299.2</v>
+      </c>
+      <c r="G794" t="n">
+        <v>304.03</v>
+      </c>
+      <c r="H794" t="n">
+        <v>-4.83</v>
+      </c>
+      <c r="I794" t="n">
+        <v>294.1</v>
+      </c>
+      <c r="J794" t="n">
+        <v>292.51</v>
+      </c>
+      <c r="K794" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="L794" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M794" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N794" t="n">
+        <v>2.97</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C795" t="n">
+        <v>2575</v>
+      </c>
+      <c r="D795" t="n">
+        <v>2668.12</v>
+      </c>
+      <c r="E795" t="n">
+        <v>-93.12</v>
+      </c>
+      <c r="F795" t="n">
+        <v>2580</v>
+      </c>
+      <c r="G795" t="n">
+        <v>2668.12</v>
+      </c>
+      <c r="H795" t="n">
+        <v>-88.12</v>
+      </c>
+      <c r="I795" t="n">
+        <v>2491</v>
+      </c>
+      <c r="J795" t="n">
+        <v>2566.89</v>
+      </c>
+      <c r="K795" t="n">
+        <v>-75.89</v>
+      </c>
+      <c r="L795" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M795" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N795" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C796" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="D796" t="n">
+        <v>130.46</v>
+      </c>
+      <c r="E796" t="n">
+        <v>-7.96</v>
+      </c>
+      <c r="F796" t="n">
+        <v>124.2</v>
+      </c>
+      <c r="G796" t="n">
+        <v>130.46</v>
+      </c>
+      <c r="H796" t="n">
+        <v>-6.26</v>
+      </c>
+      <c r="I796" t="n">
+        <v>121.38</v>
+      </c>
+      <c r="J796" t="n">
+        <v>119.28</v>
+      </c>
+      <c r="K796" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L796" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M796" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N796" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C797" t="n">
+        <v>5858.5</v>
+      </c>
+      <c r="D797" t="n">
+        <v>5766.3</v>
+      </c>
+      <c r="E797" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="F797" t="n">
+        <v>5868</v>
+      </c>
+      <c r="G797" t="n">
+        <v>5830.86</v>
+      </c>
+      <c r="H797" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="I797" t="n">
+        <v>5690</v>
+      </c>
+      <c r="J797" t="n">
+        <v>5673.85</v>
+      </c>
+      <c r="K797" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="L797" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M797" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N797" t="n">
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>
@@ -50017,7 +50225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51390,6 +51598,58 @@
       </c>
       <c r="N26" t="n">
         <v>2.35</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5858.5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5766.3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5868</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5830.86</v>
+      </c>
+      <c r="H27" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="I27" t="n">
+        <v>5690</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5673.85</v>
+      </c>
+      <c r="K27" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>
@@ -51403,7 +51663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53400,6 +53660,58 @@
       </c>
       <c r="N38" t="n">
         <v>5.65</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="D39" t="n">
+        <v>130.46</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-7.96</v>
+      </c>
+      <c r="F39" t="n">
+        <v>124.2</v>
+      </c>
+      <c r="G39" t="n">
+        <v>130.46</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-6.26</v>
+      </c>
+      <c r="I39" t="n">
+        <v>121.38</v>
+      </c>
+      <c r="J39" t="n">
+        <v>119.28</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>6.1</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -41704,31 +41704,31 @@
         </is>
       </c>
       <c r="C794" t="n">
-        <v>295</v>
+        <v>293.65</v>
       </c>
       <c r="D794" t="n">
         <v>304.03</v>
       </c>
       <c r="E794" t="n">
-        <v>-9.029999999999999</v>
+        <v>-10.38</v>
       </c>
       <c r="F794" t="n">
-        <v>299.2</v>
+        <v>295.4</v>
       </c>
       <c r="G794" t="n">
         <v>304.03</v>
       </c>
       <c r="H794" t="n">
-        <v>-4.83</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="I794" t="n">
-        <v>294.1</v>
+        <v>291.05</v>
       </c>
       <c r="J794" t="n">
         <v>292.51</v>
       </c>
       <c r="K794" t="n">
-        <v>1.59</v>
+        <v>-1.46</v>
       </c>
       <c r="L794" t="inlineStr">
         <is>
@@ -41741,7 +41741,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>2.97</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="795">
@@ -41756,31 +41756,31 @@
         </is>
       </c>
       <c r="C795" t="n">
-        <v>2575</v>
+        <v>2500</v>
       </c>
       <c r="D795" t="n">
         <v>2668.12</v>
       </c>
       <c r="E795" t="n">
-        <v>-93.12</v>
+        <v>-168.12</v>
       </c>
       <c r="F795" t="n">
-        <v>2580</v>
+        <v>2515.8</v>
       </c>
       <c r="G795" t="n">
         <v>2668.12</v>
       </c>
       <c r="H795" t="n">
-        <v>-88.12</v>
+        <v>-152.32</v>
       </c>
       <c r="I795" t="n">
-        <v>2491</v>
+        <v>2453</v>
       </c>
       <c r="J795" t="n">
         <v>2566.89</v>
       </c>
       <c r="K795" t="n">
-        <v>-75.89</v>
+        <v>-113.89</v>
       </c>
       <c r="L795" t="inlineStr">
         <is>
@@ -41793,7 +41793,7 @@
         </is>
       </c>
       <c r="N795" t="n">
-        <v>3.49</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="796">
@@ -41808,31 +41808,31 @@
         </is>
       </c>
       <c r="C796" t="n">
-        <v>122.5</v>
+        <v>121.9</v>
       </c>
       <c r="D796" t="n">
         <v>130.46</v>
       </c>
       <c r="E796" t="n">
-        <v>-7.96</v>
+        <v>-8.56</v>
       </c>
       <c r="F796" t="n">
-        <v>124.2</v>
+        <v>125.22</v>
       </c>
       <c r="G796" t="n">
         <v>130.46</v>
       </c>
       <c r="H796" t="n">
-        <v>-6.26</v>
+        <v>-5.24</v>
       </c>
       <c r="I796" t="n">
-        <v>121.38</v>
+        <v>120</v>
       </c>
       <c r="J796" t="n">
         <v>119.28</v>
       </c>
       <c r="K796" t="n">
-        <v>2.1</v>
+        <v>0.72</v>
       </c>
       <c r="L796" t="inlineStr">
         <is>
@@ -41845,7 +41845,7 @@
         </is>
       </c>
       <c r="N796" t="n">
-        <v>6.1</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="797">
@@ -41860,31 +41860,31 @@
         </is>
       </c>
       <c r="C797" t="n">
-        <v>5858.5</v>
+        <v>5690</v>
       </c>
       <c r="D797" t="n">
         <v>5766.3</v>
       </c>
       <c r="E797" t="n">
-        <v>92.2</v>
+        <v>-76.3</v>
       </c>
       <c r="F797" t="n">
-        <v>5868</v>
+        <v>5909</v>
       </c>
       <c r="G797" t="n">
         <v>5830.86</v>
       </c>
       <c r="H797" t="n">
-        <v>37.14</v>
+        <v>78.14</v>
       </c>
       <c r="I797" t="n">
-        <v>5690</v>
+        <v>5635</v>
       </c>
       <c r="J797" t="n">
         <v>5673.85</v>
       </c>
       <c r="K797" t="n">
-        <v>16.15</v>
+        <v>-38.85</v>
       </c>
       <c r="L797" t="inlineStr">
         <is>
@@ -41897,7 +41897,7 @@
         </is>
       </c>
       <c r="N797" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>
@@ -51612,31 +51612,31 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5858.5</v>
+        <v>5690</v>
       </c>
       <c r="D27" t="n">
         <v>5766.3</v>
       </c>
       <c r="E27" t="n">
-        <v>92.2</v>
+        <v>-76.3</v>
       </c>
       <c r="F27" t="n">
-        <v>5868</v>
+        <v>5909</v>
       </c>
       <c r="G27" t="n">
         <v>5830.86</v>
       </c>
       <c r="H27" t="n">
-        <v>37.14</v>
+        <v>78.14</v>
       </c>
       <c r="I27" t="n">
-        <v>5690</v>
+        <v>5635</v>
       </c>
       <c r="J27" t="n">
         <v>5673.85</v>
       </c>
       <c r="K27" t="n">
-        <v>16.15</v>
+        <v>-38.85</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -51649,7 +51649,7 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>
@@ -53674,31 +53674,31 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>122.5</v>
+        <v>121.9</v>
       </c>
       <c r="D39" t="n">
         <v>130.46</v>
       </c>
       <c r="E39" t="n">
-        <v>-7.96</v>
+        <v>-8.56</v>
       </c>
       <c r="F39" t="n">
-        <v>124.2</v>
+        <v>125.22</v>
       </c>
       <c r="G39" t="n">
         <v>130.46</v>
       </c>
       <c r="H39" t="n">
-        <v>-6.26</v>
+        <v>-5.24</v>
       </c>
       <c r="I39" t="n">
-        <v>121.38</v>
+        <v>120</v>
       </c>
       <c r="J39" t="n">
         <v>119.28</v>
       </c>
       <c r="K39" t="n">
-        <v>2.1</v>
+        <v>0.72</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -53711,7 +53711,7 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>6.1</v>
+        <v>6.56</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N797"/>
+  <dimension ref="A1:N802"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41898,6 +41898,266 @@
       </c>
       <c r="N797" t="n">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C798" t="n">
+        <v>290.4</v>
+      </c>
+      <c r="D798" t="n">
+        <v>282.73</v>
+      </c>
+      <c r="E798" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="F798" t="n">
+        <v>293.1</v>
+      </c>
+      <c r="G798" t="n">
+        <v>284.13</v>
+      </c>
+      <c r="H798" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="I798" t="n">
+        <v>288.5</v>
+      </c>
+      <c r="J798" t="n">
+        <v>281.75</v>
+      </c>
+      <c r="K798" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="L798" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M798" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N798" t="n">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C799" t="n">
+        <v>11293</v>
+      </c>
+      <c r="D799" t="n">
+        <v>10933.7</v>
+      </c>
+      <c r="E799" t="n">
+        <v>359.3</v>
+      </c>
+      <c r="F799" t="n">
+        <v>11420</v>
+      </c>
+      <c r="G799" t="n">
+        <v>10933.7</v>
+      </c>
+      <c r="H799" t="n">
+        <v>486.3</v>
+      </c>
+      <c r="I799" t="n">
+        <v>10834</v>
+      </c>
+      <c r="J799" t="n">
+        <v>10899.86</v>
+      </c>
+      <c r="K799" t="n">
+        <v>-65.86</v>
+      </c>
+      <c r="L799" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M799" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N799" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C800" t="n">
+        <v>5740.5</v>
+      </c>
+      <c r="D800" t="n">
+        <v>5709.87</v>
+      </c>
+      <c r="E800" t="n">
+        <v>30.63</v>
+      </c>
+      <c r="F800" t="n">
+        <v>5906.5</v>
+      </c>
+      <c r="G800" t="n">
+        <v>5709.87</v>
+      </c>
+      <c r="H800" t="n">
+        <v>196.63</v>
+      </c>
+      <c r="I800" t="n">
+        <v>5733.5</v>
+      </c>
+      <c r="J800" t="n">
+        <v>5464.94</v>
+      </c>
+      <c r="K800" t="n">
+        <v>268.56</v>
+      </c>
+      <c r="L800" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M800" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N800" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C801" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="D801" t="n">
+        <v>115.38</v>
+      </c>
+      <c r="E801" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="F801" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="G801" t="n">
+        <v>120.13</v>
+      </c>
+      <c r="H801" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="I801" t="n">
+        <v>120.55</v>
+      </c>
+      <c r="J801" t="n">
+        <v>118.25</v>
+      </c>
+      <c r="K801" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L801" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M801" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N801" t="n">
+        <v>6.17</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C802" t="n">
+        <v>2499.5</v>
+      </c>
+      <c r="D802" t="n">
+        <v>2360.75</v>
+      </c>
+      <c r="E802" t="n">
+        <v>138.75</v>
+      </c>
+      <c r="F802" t="n">
+        <v>2601.4</v>
+      </c>
+      <c r="G802" t="n">
+        <v>2423.86</v>
+      </c>
+      <c r="H802" t="n">
+        <v>177.54</v>
+      </c>
+      <c r="I802" t="n">
+        <v>2499.5</v>
+      </c>
+      <c r="J802" t="n">
+        <v>2390.22</v>
+      </c>
+      <c r="K802" t="n">
+        <v>109.28</v>
+      </c>
+      <c r="L802" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M802" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N802" t="n">
+        <v>5.88</v>
       </c>
     </row>
   </sheetData>
@@ -50225,7 +50485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51650,6 +51910,58 @@
       </c>
       <c r="N27" t="n">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>5740.5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5709.87</v>
+      </c>
+      <c r="E28" t="n">
+        <v>30.63</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5906.5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>5709.87</v>
+      </c>
+      <c r="H28" t="n">
+        <v>196.63</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5733.5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>5464.94</v>
+      </c>
+      <c r="K28" t="n">
+        <v>268.56</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>0.54</v>
       </c>
     </row>
   </sheetData>
@@ -51663,7 +51975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:N40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53712,6 +54024,58 @@
       </c>
       <c r="N39" t="n">
         <v>6.56</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="D40" t="n">
+        <v>115.38</v>
+      </c>
+      <c r="E40" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="F40" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="G40" t="n">
+        <v>120.13</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="I40" t="n">
+        <v>120.55</v>
+      </c>
+      <c r="J40" t="n">
+        <v>118.25</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>6.17</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -41912,31 +41912,31 @@
         </is>
       </c>
       <c r="C798" t="n">
-        <v>290.4</v>
+        <v>295</v>
       </c>
       <c r="D798" t="n">
         <v>282.73</v>
       </c>
       <c r="E798" t="n">
-        <v>7.67</v>
+        <v>12.27</v>
       </c>
       <c r="F798" t="n">
-        <v>293.1</v>
+        <v>299.2</v>
       </c>
       <c r="G798" t="n">
         <v>284.13</v>
       </c>
       <c r="H798" t="n">
-        <v>8.970000000000001</v>
+        <v>15.07</v>
       </c>
       <c r="I798" t="n">
-        <v>288.5</v>
+        <v>294.1</v>
       </c>
       <c r="J798" t="n">
         <v>281.75</v>
       </c>
       <c r="K798" t="n">
-        <v>6.75</v>
+        <v>12.35</v>
       </c>
       <c r="L798" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         </is>
       </c>
       <c r="N798" t="n">
-        <v>2.71</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="799">
@@ -41964,31 +41964,31 @@
         </is>
       </c>
       <c r="C799" t="n">
-        <v>11293</v>
+        <v>10975</v>
       </c>
       <c r="D799" t="n">
         <v>10933.7</v>
       </c>
       <c r="E799" t="n">
-        <v>359.3</v>
+        <v>41.3</v>
       </c>
       <c r="F799" t="n">
-        <v>11420</v>
+        <v>11255</v>
       </c>
       <c r="G799" t="n">
         <v>10933.7</v>
       </c>
       <c r="H799" t="n">
-        <v>486.3</v>
+        <v>321.3</v>
       </c>
       <c r="I799" t="n">
-        <v>10834</v>
+        <v>10924</v>
       </c>
       <c r="J799" t="n">
         <v>10899.86</v>
       </c>
       <c r="K799" t="n">
-        <v>-65.86</v>
+        <v>24.14</v>
       </c>
       <c r="L799" t="inlineStr">
         <is>
@@ -41997,11 +41997,11 @@
       </c>
       <c r="M799" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N799" t="n">
-        <v>3.29</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="800">
@@ -42016,31 +42016,31 @@
         </is>
       </c>
       <c r="C800" t="n">
-        <v>5740.5</v>
+        <v>5858.5</v>
       </c>
       <c r="D800" t="n">
         <v>5709.87</v>
       </c>
       <c r="E800" t="n">
-        <v>30.63</v>
+        <v>148.63</v>
       </c>
       <c r="F800" t="n">
-        <v>5906.5</v>
+        <v>5868</v>
       </c>
       <c r="G800" t="n">
         <v>5709.87</v>
       </c>
       <c r="H800" t="n">
-        <v>196.63</v>
+        <v>158.13</v>
       </c>
       <c r="I800" t="n">
-        <v>5733.5</v>
+        <v>5690</v>
       </c>
       <c r="J800" t="n">
         <v>5464.94</v>
       </c>
       <c r="K800" t="n">
-        <v>268.56</v>
+        <v>225.06</v>
       </c>
       <c r="L800" t="inlineStr">
         <is>
@@ -42049,11 +42049,11 @@
       </c>
       <c r="M800" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N800" t="n">
-        <v>0.54</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="801">
@@ -42077,22 +42077,22 @@
         <v>7.12</v>
       </c>
       <c r="F801" t="n">
-        <v>122.5</v>
+        <v>124.2</v>
       </c>
       <c r="G801" t="n">
         <v>120.13</v>
       </c>
       <c r="H801" t="n">
-        <v>2.37</v>
+        <v>4.07</v>
       </c>
       <c r="I801" t="n">
-        <v>120.55</v>
+        <v>121.38</v>
       </c>
       <c r="J801" t="n">
         <v>118.25</v>
       </c>
       <c r="K801" t="n">
-        <v>2.3</v>
+        <v>3.13</v>
       </c>
       <c r="L801" t="inlineStr">
         <is>
@@ -42101,7 +42101,7 @@
       </c>
       <c r="M801" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N801" t="n">
@@ -42120,31 +42120,31 @@
         </is>
       </c>
       <c r="C802" t="n">
-        <v>2499.5</v>
+        <v>2575</v>
       </c>
       <c r="D802" t="n">
         <v>2360.75</v>
       </c>
       <c r="E802" t="n">
-        <v>138.75</v>
+        <v>214.25</v>
       </c>
       <c r="F802" t="n">
-        <v>2601.4</v>
+        <v>2580</v>
       </c>
       <c r="G802" t="n">
         <v>2423.86</v>
       </c>
       <c r="H802" t="n">
-        <v>177.54</v>
+        <v>156.14</v>
       </c>
       <c r="I802" t="n">
-        <v>2499.5</v>
+        <v>2491</v>
       </c>
       <c r="J802" t="n">
         <v>2390.22</v>
       </c>
       <c r="K802" t="n">
-        <v>109.28</v>
+        <v>100.78</v>
       </c>
       <c r="L802" t="inlineStr">
         <is>
@@ -42157,7 +42157,7 @@
         </is>
       </c>
       <c r="N802" t="n">
-        <v>5.88</v>
+        <v>9.08</v>
       </c>
     </row>
   </sheetData>
@@ -51924,31 +51924,31 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5740.5</v>
+        <v>5858.5</v>
       </c>
       <c r="D28" t="n">
         <v>5709.87</v>
       </c>
       <c r="E28" t="n">
-        <v>30.63</v>
+        <v>148.63</v>
       </c>
       <c r="F28" t="n">
-        <v>5906.5</v>
+        <v>5868</v>
       </c>
       <c r="G28" t="n">
         <v>5709.87</v>
       </c>
       <c r="H28" t="n">
-        <v>196.63</v>
+        <v>158.13</v>
       </c>
       <c r="I28" t="n">
-        <v>5733.5</v>
+        <v>5690</v>
       </c>
       <c r="J28" t="n">
         <v>5464.94</v>
       </c>
       <c r="K28" t="n">
-        <v>268.56</v>
+        <v>225.06</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -51957,11 +51957,11 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0.54</v>
+        <v>2.6</v>
       </c>
     </row>
   </sheetData>
@@ -54047,22 +54047,22 @@
         <v>7.12</v>
       </c>
       <c r="F40" t="n">
-        <v>122.5</v>
+        <v>124.2</v>
       </c>
       <c r="G40" t="n">
         <v>120.13</v>
       </c>
       <c r="H40" t="n">
-        <v>2.37</v>
+        <v>4.07</v>
       </c>
       <c r="I40" t="n">
-        <v>120.55</v>
+        <v>121.38</v>
       </c>
       <c r="J40" t="n">
         <v>118.25</v>
       </c>
       <c r="K40" t="n">
-        <v>2.3</v>
+        <v>3.13</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -54071,7 +54071,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N40" t="n">

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N802"/>
+  <dimension ref="A1:N806"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42158,6 +42158,214 @@
       </c>
       <c r="N802" t="n">
         <v>9.08</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C803" t="n">
+        <v>5727.5</v>
+      </c>
+      <c r="D803" t="n">
+        <v>5923.6</v>
+      </c>
+      <c r="E803" t="n">
+        <v>-196.1</v>
+      </c>
+      <c r="F803" t="n">
+        <v>5914.5</v>
+      </c>
+      <c r="G803" t="n">
+        <v>5923.6</v>
+      </c>
+      <c r="H803" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="I803" t="n">
+        <v>5674.5</v>
+      </c>
+      <c r="J803" t="n">
+        <v>5591.1</v>
+      </c>
+      <c r="K803" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="L803" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M803" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N803" t="n">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C804" t="n">
+        <v>11175</v>
+      </c>
+      <c r="D804" t="n">
+        <v>11306.98</v>
+      </c>
+      <c r="E804" t="n">
+        <v>-131.98</v>
+      </c>
+      <c r="F804" t="n">
+        <v>11299</v>
+      </c>
+      <c r="G804" t="n">
+        <v>11306.98</v>
+      </c>
+      <c r="H804" t="n">
+        <v>-7.98</v>
+      </c>
+      <c r="I804" t="n">
+        <v>11029</v>
+      </c>
+      <c r="J804" t="n">
+        <v>11013.61</v>
+      </c>
+      <c r="K804" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="L804" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M804" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N804" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C805" t="n">
+        <v>120.37</v>
+      </c>
+      <c r="D805" t="n">
+        <v>128.82</v>
+      </c>
+      <c r="E805" t="n">
+        <v>-8.449999999999999</v>
+      </c>
+      <c r="F805" t="n">
+        <v>122.3</v>
+      </c>
+      <c r="G805" t="n">
+        <v>128.82</v>
+      </c>
+      <c r="H805" t="n">
+        <v>-6.52</v>
+      </c>
+      <c r="I805" t="n">
+        <v>119.06</v>
+      </c>
+      <c r="J805" t="n">
+        <v>118.26</v>
+      </c>
+      <c r="K805" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L805" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M805" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N805" t="n">
+        <v>6.56</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C806" t="n">
+        <v>2480</v>
+      </c>
+      <c r="D806" t="n">
+        <v>2726.73</v>
+      </c>
+      <c r="E806" t="n">
+        <v>-246.73</v>
+      </c>
+      <c r="F806" t="n">
+        <v>2585.6</v>
+      </c>
+      <c r="G806" t="n">
+        <v>2726.73</v>
+      </c>
+      <c r="H806" t="n">
+        <v>-141.13</v>
+      </c>
+      <c r="I806" t="n">
+        <v>2470.1</v>
+      </c>
+      <c r="J806" t="n">
+        <v>2429.48</v>
+      </c>
+      <c r="K806" t="n">
+        <v>40.62</v>
+      </c>
+      <c r="L806" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M806" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N806" t="n">
+        <v>9.050000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -50485,7 +50693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51962,6 +52170,58 @@
       </c>
       <c r="N28" t="n">
         <v>2.6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>5727.5</v>
+      </c>
+      <c r="D29" t="n">
+        <v>5923.6</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-196.1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5914.5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5923.6</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>5674.5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>5591.1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>3.31</v>
       </c>
     </row>
   </sheetData>
@@ -51975,7 +52235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54076,6 +54336,58 @@
       </c>
       <c r="N40" t="n">
         <v>6.17</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>120.37</v>
+      </c>
+      <c r="D41" t="n">
+        <v>128.82</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-8.449999999999999</v>
+      </c>
+      <c r="F41" t="n">
+        <v>122.3</v>
+      </c>
+      <c r="G41" t="n">
+        <v>128.82</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-6.52</v>
+      </c>
+      <c r="I41" t="n">
+        <v>119.06</v>
+      </c>
+      <c r="J41" t="n">
+        <v>118.26</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>6.56</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -42172,31 +42172,31 @@
         </is>
       </c>
       <c r="C803" t="n">
-        <v>5727.5</v>
+        <v>5740.5</v>
       </c>
       <c r="D803" t="n">
         <v>5923.6</v>
       </c>
       <c r="E803" t="n">
-        <v>-196.1</v>
+        <v>-183.1</v>
       </c>
       <c r="F803" t="n">
-        <v>5914.5</v>
+        <v>5906.5</v>
       </c>
       <c r="G803" t="n">
         <v>5923.6</v>
       </c>
       <c r="H803" t="n">
-        <v>-9.1</v>
+        <v>-17.1</v>
       </c>
       <c r="I803" t="n">
-        <v>5674.5</v>
+        <v>5733.5</v>
       </c>
       <c r="J803" t="n">
         <v>5591.1</v>
       </c>
       <c r="K803" t="n">
-        <v>83.40000000000001</v>
+        <v>142.4</v>
       </c>
       <c r="L803" t="inlineStr">
         <is>
@@ -42209,7 +42209,7 @@
         </is>
       </c>
       <c r="N803" t="n">
-        <v>3.31</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="804">
@@ -42224,31 +42224,31 @@
         </is>
       </c>
       <c r="C804" t="n">
-        <v>11175</v>
+        <v>11293</v>
       </c>
       <c r="D804" t="n">
         <v>11306.98</v>
       </c>
       <c r="E804" t="n">
-        <v>-131.98</v>
+        <v>-13.98</v>
       </c>
       <c r="F804" t="n">
-        <v>11299</v>
+        <v>11420</v>
       </c>
       <c r="G804" t="n">
         <v>11306.98</v>
       </c>
       <c r="H804" t="n">
-        <v>-7.98</v>
+        <v>113.02</v>
       </c>
       <c r="I804" t="n">
-        <v>11029</v>
+        <v>10834</v>
       </c>
       <c r="J804" t="n">
         <v>11013.61</v>
       </c>
       <c r="K804" t="n">
-        <v>15.39</v>
+        <v>-179.61</v>
       </c>
       <c r="L804" t="inlineStr">
         <is>
@@ -42261,7 +42261,7 @@
         </is>
       </c>
       <c r="N804" t="n">
-        <v>1.17</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="805">
@@ -42276,31 +42276,31 @@
         </is>
       </c>
       <c r="C805" t="n">
-        <v>120.37</v>
+        <v>122.5</v>
       </c>
       <c r="D805" t="n">
         <v>128.82</v>
       </c>
       <c r="E805" t="n">
-        <v>-8.449999999999999</v>
+        <v>-6.32</v>
       </c>
       <c r="F805" t="n">
-        <v>122.3</v>
+        <v>122.5</v>
       </c>
       <c r="G805" t="n">
         <v>128.82</v>
       </c>
       <c r="H805" t="n">
-        <v>-6.52</v>
+        <v>-6.32</v>
       </c>
       <c r="I805" t="n">
-        <v>119.06</v>
+        <v>120.55</v>
       </c>
       <c r="J805" t="n">
         <v>118.26</v>
       </c>
       <c r="K805" t="n">
-        <v>0.8</v>
+        <v>2.29</v>
       </c>
       <c r="L805" t="inlineStr">
         <is>
@@ -42313,7 +42313,7 @@
         </is>
       </c>
       <c r="N805" t="n">
-        <v>6.56</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="806">
@@ -42328,31 +42328,31 @@
         </is>
       </c>
       <c r="C806" t="n">
-        <v>2480</v>
+        <v>2499.5</v>
       </c>
       <c r="D806" t="n">
         <v>2726.73</v>
       </c>
       <c r="E806" t="n">
-        <v>-246.73</v>
+        <v>-227.23</v>
       </c>
       <c r="F806" t="n">
-        <v>2585.6</v>
+        <v>2601.4</v>
       </c>
       <c r="G806" t="n">
         <v>2726.73</v>
       </c>
       <c r="H806" t="n">
-        <v>-141.13</v>
+        <v>-125.33</v>
       </c>
       <c r="I806" t="n">
-        <v>2470.1</v>
+        <v>2499.5</v>
       </c>
       <c r="J806" t="n">
         <v>2429.48</v>
       </c>
       <c r="K806" t="n">
-        <v>40.62</v>
+        <v>70.02</v>
       </c>
       <c r="L806" t="inlineStr">
         <is>
@@ -42365,7 +42365,7 @@
         </is>
       </c>
       <c r="N806" t="n">
-        <v>9.050000000000001</v>
+        <v>8.33</v>
       </c>
     </row>
   </sheetData>
@@ -52184,31 +52184,31 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5727.5</v>
+        <v>5740.5</v>
       </c>
       <c r="D29" t="n">
         <v>5923.6</v>
       </c>
       <c r="E29" t="n">
-        <v>-196.1</v>
+        <v>-183.1</v>
       </c>
       <c r="F29" t="n">
-        <v>5914.5</v>
+        <v>5906.5</v>
       </c>
       <c r="G29" t="n">
         <v>5923.6</v>
       </c>
       <c r="H29" t="n">
-        <v>-9.1</v>
+        <v>-17.1</v>
       </c>
       <c r="I29" t="n">
-        <v>5674.5</v>
+        <v>5733.5</v>
       </c>
       <c r="J29" t="n">
         <v>5591.1</v>
       </c>
       <c r="K29" t="n">
-        <v>83.40000000000001</v>
+        <v>142.4</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -52221,7 +52221,7 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>3.31</v>
+        <v>3.09</v>
       </c>
     </row>
   </sheetData>
@@ -54350,31 +54350,31 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>120.37</v>
+        <v>122.5</v>
       </c>
       <c r="D41" t="n">
         <v>128.82</v>
       </c>
       <c r="E41" t="n">
-        <v>-8.449999999999999</v>
+        <v>-6.32</v>
       </c>
       <c r="F41" t="n">
-        <v>122.3</v>
+        <v>122.5</v>
       </c>
       <c r="G41" t="n">
         <v>128.82</v>
       </c>
       <c r="H41" t="n">
-        <v>-6.52</v>
+        <v>-6.32</v>
       </c>
       <c r="I41" t="n">
-        <v>119.06</v>
+        <v>120.55</v>
       </c>
       <c r="J41" t="n">
         <v>118.26</v>
       </c>
       <c r="K41" t="n">
-        <v>0.8</v>
+        <v>2.29</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -54387,7 +54387,7 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>6.56</v>
+        <v>4.91</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -42172,31 +42172,31 @@
         </is>
       </c>
       <c r="C803" t="n">
-        <v>5740.5</v>
+        <v>5727.5</v>
       </c>
       <c r="D803" t="n">
-        <v>5923.6</v>
+        <v>5594.87</v>
       </c>
       <c r="E803" t="n">
-        <v>-183.1</v>
+        <v>132.63</v>
       </c>
       <c r="F803" t="n">
-        <v>5906.5</v>
+        <v>5914.5</v>
       </c>
       <c r="G803" t="n">
-        <v>5923.6</v>
+        <v>5594.87</v>
       </c>
       <c r="H803" t="n">
-        <v>-17.1</v>
+        <v>319.63</v>
       </c>
       <c r="I803" t="n">
-        <v>5733.5</v>
+        <v>5674.5</v>
       </c>
       <c r="J803" t="n">
-        <v>5591.1</v>
+        <v>5477.93</v>
       </c>
       <c r="K803" t="n">
-        <v>142.4</v>
+        <v>196.57</v>
       </c>
       <c r="L803" t="inlineStr">
         <is>
@@ -42209,7 +42209,7 @@
         </is>
       </c>
       <c r="N803" t="n">
-        <v>3.09</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="804">
@@ -42224,31 +42224,31 @@
         </is>
       </c>
       <c r="C804" t="n">
-        <v>11293</v>
+        <v>11175</v>
       </c>
       <c r="D804" t="n">
-        <v>11306.98</v>
+        <v>11250.43</v>
       </c>
       <c r="E804" t="n">
-        <v>-13.98</v>
+        <v>-75.43000000000001</v>
       </c>
       <c r="F804" t="n">
-        <v>11420</v>
+        <v>11299</v>
       </c>
       <c r="G804" t="n">
-        <v>11306.98</v>
+        <v>11250.43</v>
       </c>
       <c r="H804" t="n">
-        <v>113.02</v>
+        <v>48.57</v>
       </c>
       <c r="I804" t="n">
-        <v>10834</v>
+        <v>11029</v>
       </c>
       <c r="J804" t="n">
-        <v>11013.61</v>
+        <v>10790.69</v>
       </c>
       <c r="K804" t="n">
-        <v>-179.61</v>
+        <v>238.31</v>
       </c>
       <c r="L804" t="inlineStr">
         <is>
@@ -42261,7 +42261,7 @@
         </is>
       </c>
       <c r="N804" t="n">
-        <v>0.12</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="805">
@@ -42276,31 +42276,31 @@
         </is>
       </c>
       <c r="C805" t="n">
-        <v>122.5</v>
+        <v>120.37</v>
       </c>
       <c r="D805" t="n">
-        <v>128.82</v>
+        <v>115.38</v>
       </c>
       <c r="E805" t="n">
-        <v>-6.32</v>
+        <v>4.99</v>
       </c>
       <c r="F805" t="n">
-        <v>122.5</v>
+        <v>122.3</v>
       </c>
       <c r="G805" t="n">
-        <v>128.82</v>
+        <v>118.16</v>
       </c>
       <c r="H805" t="n">
-        <v>-6.32</v>
+        <v>4.14</v>
       </c>
       <c r="I805" t="n">
-        <v>120.55</v>
+        <v>119.06</v>
       </c>
       <c r="J805" t="n">
-        <v>118.26</v>
+        <v>115.86</v>
       </c>
       <c r="K805" t="n">
-        <v>2.29</v>
+        <v>3.2</v>
       </c>
       <c r="L805" t="inlineStr">
         <is>
@@ -42309,11 +42309,11 @@
       </c>
       <c r="M805" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N805" t="n">
-        <v>4.91</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="806">
@@ -42328,31 +42328,31 @@
         </is>
       </c>
       <c r="C806" t="n">
-        <v>2499.5</v>
+        <v>2480</v>
       </c>
       <c r="D806" t="n">
-        <v>2726.73</v>
+        <v>2291.53</v>
       </c>
       <c r="E806" t="n">
-        <v>-227.23</v>
+        <v>188.47</v>
       </c>
       <c r="F806" t="n">
-        <v>2601.4</v>
+        <v>2585.6</v>
       </c>
       <c r="G806" t="n">
-        <v>2726.73</v>
+        <v>2426.66</v>
       </c>
       <c r="H806" t="n">
-        <v>-125.33</v>
+        <v>158.94</v>
       </c>
       <c r="I806" t="n">
-        <v>2499.5</v>
+        <v>2470.1</v>
       </c>
       <c r="J806" t="n">
-        <v>2429.48</v>
+        <v>2380.3</v>
       </c>
       <c r="K806" t="n">
-        <v>70.02</v>
+        <v>89.8</v>
       </c>
       <c r="L806" t="inlineStr">
         <is>
@@ -42361,11 +42361,11 @@
       </c>
       <c r="M806" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N806" t="n">
-        <v>8.33</v>
+        <v>8.220000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -52184,31 +52184,31 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5740.5</v>
+        <v>5727.5</v>
       </c>
       <c r="D29" t="n">
-        <v>5923.6</v>
+        <v>5594.87</v>
       </c>
       <c r="E29" t="n">
-        <v>-183.1</v>
+        <v>132.63</v>
       </c>
       <c r="F29" t="n">
-        <v>5906.5</v>
+        <v>5914.5</v>
       </c>
       <c r="G29" t="n">
-        <v>5923.6</v>
+        <v>5594.87</v>
       </c>
       <c r="H29" t="n">
-        <v>-17.1</v>
+        <v>319.63</v>
       </c>
       <c r="I29" t="n">
-        <v>5733.5</v>
+        <v>5674.5</v>
       </c>
       <c r="J29" t="n">
-        <v>5591.1</v>
+        <v>5477.93</v>
       </c>
       <c r="K29" t="n">
-        <v>142.4</v>
+        <v>196.57</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -52221,7 +52221,7 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>3.09</v>
+        <v>2.37</v>
       </c>
     </row>
   </sheetData>
@@ -54350,31 +54350,31 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>122.5</v>
+        <v>120.37</v>
       </c>
       <c r="D41" t="n">
-        <v>128.82</v>
+        <v>115.38</v>
       </c>
       <c r="E41" t="n">
-        <v>-6.32</v>
+        <v>4.99</v>
       </c>
       <c r="F41" t="n">
-        <v>122.5</v>
+        <v>122.3</v>
       </c>
       <c r="G41" t="n">
-        <v>128.82</v>
+        <v>118.16</v>
       </c>
       <c r="H41" t="n">
-        <v>-6.32</v>
+        <v>4.14</v>
       </c>
       <c r="I41" t="n">
-        <v>120.55</v>
+        <v>119.06</v>
       </c>
       <c r="J41" t="n">
-        <v>118.26</v>
+        <v>115.86</v>
       </c>
       <c r="K41" t="n">
-        <v>2.29</v>
+        <v>3.2</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -54383,11 +54383,11 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>4.91</v>
+        <v>4.32</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N806"/>
+  <dimension ref="A1:N814"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42366,6 +42366,422 @@
       </c>
       <c r="N806" t="n">
         <v>8.220000000000001</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C807" t="n">
+        <v>291.75</v>
+      </c>
+      <c r="D807" t="n">
+        <v>299.88</v>
+      </c>
+      <c r="E807" t="n">
+        <v>-8.130000000000001</v>
+      </c>
+      <c r="F807" t="n">
+        <v>292.75</v>
+      </c>
+      <c r="G807" t="n">
+        <v>305.34</v>
+      </c>
+      <c r="H807" t="n">
+        <v>-12.59</v>
+      </c>
+      <c r="I807" t="n">
+        <v>282.05</v>
+      </c>
+      <c r="J807" t="n">
+        <v>291.75</v>
+      </c>
+      <c r="K807" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="L807" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M807" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N807" t="n">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="C808" t="n">
+        <v>1310.9</v>
+      </c>
+      <c r="D808" t="n">
+        <v>1342.85</v>
+      </c>
+      <c r="E808" t="n">
+        <v>-31.95</v>
+      </c>
+      <c r="F808" t="n">
+        <v>1319</v>
+      </c>
+      <c r="G808" t="n">
+        <v>1343.98</v>
+      </c>
+      <c r="H808" t="n">
+        <v>-24.98</v>
+      </c>
+      <c r="I808" t="n">
+        <v>1224</v>
+      </c>
+      <c r="J808" t="n">
+        <v>1295.15</v>
+      </c>
+      <c r="K808" t="n">
+        <v>-71.15000000000001</v>
+      </c>
+      <c r="L808" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M808" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N808" t="n">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C809" t="n">
+        <v>120.89</v>
+      </c>
+      <c r="D809" t="n">
+        <v>127.13</v>
+      </c>
+      <c r="E809" t="n">
+        <v>-6.24</v>
+      </c>
+      <c r="F809" t="n">
+        <v>120.89</v>
+      </c>
+      <c r="G809" t="n">
+        <v>127.13</v>
+      </c>
+      <c r="H809" t="n">
+        <v>-6.24</v>
+      </c>
+      <c r="I809" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="J809" t="n">
+        <v>120.25</v>
+      </c>
+      <c r="K809" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="L809" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M809" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N809" t="n">
+        <v>4.91</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C810" t="n">
+        <v>1993</v>
+      </c>
+      <c r="D810" t="n">
+        <v>2041.57</v>
+      </c>
+      <c r="E810" t="n">
+        <v>-48.57</v>
+      </c>
+      <c r="F810" t="n">
+        <v>1997.6</v>
+      </c>
+      <c r="G810" t="n">
+        <v>2077.29</v>
+      </c>
+      <c r="H810" t="n">
+        <v>-79.69</v>
+      </c>
+      <c r="I810" t="n">
+        <v>1812.2</v>
+      </c>
+      <c r="J810" t="n">
+        <v>1993</v>
+      </c>
+      <c r="K810" t="n">
+        <v>-180.8</v>
+      </c>
+      <c r="L810" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M810" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N810" t="n">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C811" t="n">
+        <v>325.55</v>
+      </c>
+      <c r="D811" t="n">
+        <v>333.48</v>
+      </c>
+      <c r="E811" t="n">
+        <v>-7.93</v>
+      </c>
+      <c r="F811" t="n">
+        <v>327.95</v>
+      </c>
+      <c r="G811" t="n">
+        <v>333.48</v>
+      </c>
+      <c r="H811" t="n">
+        <v>-5.53</v>
+      </c>
+      <c r="I811" t="n">
+        <v>313.65</v>
+      </c>
+      <c r="J811" t="n">
+        <v>316.72</v>
+      </c>
+      <c r="K811" t="n">
+        <v>-3.07</v>
+      </c>
+      <c r="L811" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M811" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N811" t="n">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C812" t="n">
+        <v>5850</v>
+      </c>
+      <c r="D812" t="n">
+        <v>6036.61</v>
+      </c>
+      <c r="E812" t="n">
+        <v>-186.61</v>
+      </c>
+      <c r="F812" t="n">
+        <v>5873.5</v>
+      </c>
+      <c r="G812" t="n">
+        <v>6036.61</v>
+      </c>
+      <c r="H812" t="n">
+        <v>-163.11</v>
+      </c>
+      <c r="I812" t="n">
+        <v>5600</v>
+      </c>
+      <c r="J812" t="n">
+        <v>5744.8</v>
+      </c>
+      <c r="K812" t="n">
+        <v>-144.8</v>
+      </c>
+      <c r="L812" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M812" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N812" t="n">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="C813" t="n">
+        <v>1417</v>
+      </c>
+      <c r="D813" t="n">
+        <v>1451.54</v>
+      </c>
+      <c r="E813" t="n">
+        <v>-34.54</v>
+      </c>
+      <c r="F813" t="n">
+        <v>1422.7</v>
+      </c>
+      <c r="G813" t="n">
+        <v>1451.54</v>
+      </c>
+      <c r="H813" t="n">
+        <v>-28.84</v>
+      </c>
+      <c r="I813" t="n">
+        <v>1386</v>
+      </c>
+      <c r="J813" t="n">
+        <v>1387.05</v>
+      </c>
+      <c r="K813" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="L813" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M813" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N813" t="n">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C814" t="n">
+        <v>2557.6</v>
+      </c>
+      <c r="D814" t="n">
+        <v>2790.11</v>
+      </c>
+      <c r="E814" t="n">
+        <v>-232.51</v>
+      </c>
+      <c r="F814" t="n">
+        <v>2563.3</v>
+      </c>
+      <c r="G814" t="n">
+        <v>2790.11</v>
+      </c>
+      <c r="H814" t="n">
+        <v>-226.81</v>
+      </c>
+      <c r="I814" t="n">
+        <v>2435</v>
+      </c>
+      <c r="J814" t="n">
+        <v>2498.67</v>
+      </c>
+      <c r="K814" t="n">
+        <v>-63.67</v>
+      </c>
+      <c r="L814" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M814" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N814" t="n">
+        <v>8.33</v>
       </c>
     </row>
   </sheetData>
@@ -46327,7 +46743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48480,6 +48896,58 @@
       </c>
       <c r="N41" t="n">
         <v>0.42</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>325.55</v>
+      </c>
+      <c r="D42" t="n">
+        <v>333.48</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-7.93</v>
+      </c>
+      <c r="F42" t="n">
+        <v>327.95</v>
+      </c>
+      <c r="G42" t="n">
+        <v>333.48</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-5.53</v>
+      </c>
+      <c r="I42" t="n">
+        <v>313.65</v>
+      </c>
+      <c r="J42" t="n">
+        <v>316.72</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-3.07</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>2.38</v>
       </c>
     </row>
   </sheetData>
@@ -49723,7 +50191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50680,6 +51148,58 @@
       </c>
       <c r="N18" t="n">
         <v>1.54</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1993</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2041.57</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-48.57</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1997.6</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2077.29</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-79.69</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1812.2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1993</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-180.8</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>2.38</v>
       </c>
     </row>
   </sheetData>
@@ -50693,7 +51213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52222,6 +52742,58 @@
       </c>
       <c r="N29" t="n">
         <v>2.37</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>5850</v>
+      </c>
+      <c r="D30" t="n">
+        <v>6036.61</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-186.61</v>
+      </c>
+      <c r="F30" t="n">
+        <v>5873.5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>6036.61</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-163.11</v>
+      </c>
+      <c r="I30" t="n">
+        <v>5600</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5744.8</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-144.8</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>3.09</v>
       </c>
     </row>
   </sheetData>
@@ -52235,7 +52807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54388,6 +54960,58 @@
       </c>
       <c r="N41" t="n">
         <v>4.32</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>120.89</v>
+      </c>
+      <c r="D42" t="n">
+        <v>127.13</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-6.24</v>
+      </c>
+      <c r="F42" t="n">
+        <v>120.89</v>
+      </c>
+      <c r="G42" t="n">
+        <v>127.13</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-6.24</v>
+      </c>
+      <c r="I42" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="J42" t="n">
+        <v>120.25</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>4.91</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -42380,31 +42380,31 @@
         </is>
       </c>
       <c r="C807" t="n">
-        <v>291.75</v>
+        <v>286.3</v>
       </c>
       <c r="D807" t="n">
         <v>299.88</v>
       </c>
       <c r="E807" t="n">
-        <v>-8.130000000000001</v>
+        <v>-13.58</v>
       </c>
       <c r="F807" t="n">
-        <v>292.75</v>
+        <v>292</v>
       </c>
       <c r="G807" t="n">
         <v>305.34</v>
       </c>
       <c r="H807" t="n">
-        <v>-12.59</v>
+        <v>-13.34</v>
       </c>
       <c r="I807" t="n">
-        <v>282.05</v>
+        <v>279.35</v>
       </c>
       <c r="J807" t="n">
         <v>291.75</v>
       </c>
       <c r="K807" t="n">
-        <v>-9.699999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="L807" t="inlineStr">
         <is>
@@ -42417,7 +42417,7 @@
         </is>
       </c>
       <c r="N807" t="n">
-        <v>2.71</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="808">
@@ -42432,31 +42432,31 @@
         </is>
       </c>
       <c r="C808" t="n">
-        <v>1310.9</v>
+        <v>1229.5</v>
       </c>
       <c r="D808" t="n">
         <v>1342.85</v>
       </c>
       <c r="E808" t="n">
-        <v>-31.95</v>
+        <v>-113.35</v>
       </c>
       <c r="F808" t="n">
-        <v>1319</v>
+        <v>1250.6</v>
       </c>
       <c r="G808" t="n">
         <v>1343.98</v>
       </c>
       <c r="H808" t="n">
-        <v>-24.98</v>
+        <v>-93.38</v>
       </c>
       <c r="I808" t="n">
-        <v>1224</v>
+        <v>1215.6</v>
       </c>
       <c r="J808" t="n">
         <v>1295.15</v>
       </c>
       <c r="K808" t="n">
-        <v>-71.15000000000001</v>
+        <v>-79.55</v>
       </c>
       <c r="L808" t="inlineStr">
         <is>
@@ -42465,11 +42465,11 @@
       </c>
       <c r="M808" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N808" t="n">
-        <v>2.38</v>
+        <v>8.44</v>
       </c>
     </row>
     <row r="809">
@@ -42484,31 +42484,31 @@
         </is>
       </c>
       <c r="C809" t="n">
-        <v>120.89</v>
+        <v>120.37</v>
       </c>
       <c r="D809" t="n">
         <v>127.13</v>
       </c>
       <c r="E809" t="n">
-        <v>-6.24</v>
+        <v>-6.76</v>
       </c>
       <c r="F809" t="n">
-        <v>120.89</v>
+        <v>122.3</v>
       </c>
       <c r="G809" t="n">
         <v>127.13</v>
       </c>
       <c r="H809" t="n">
-        <v>-6.24</v>
+        <v>-4.83</v>
       </c>
       <c r="I809" t="n">
-        <v>118.2</v>
+        <v>119.06</v>
       </c>
       <c r="J809" t="n">
         <v>120.25</v>
       </c>
       <c r="K809" t="n">
-        <v>-2.05</v>
+        <v>-1.19</v>
       </c>
       <c r="L809" t="inlineStr">
         <is>
@@ -42517,11 +42517,11 @@
       </c>
       <c r="M809" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N809" t="n">
-        <v>4.91</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="810">
@@ -42536,31 +42536,31 @@
         </is>
       </c>
       <c r="C810" t="n">
-        <v>1993</v>
+        <v>1900.5</v>
       </c>
       <c r="D810" t="n">
         <v>2041.57</v>
       </c>
       <c r="E810" t="n">
-        <v>-48.57</v>
+        <v>-141.07</v>
       </c>
       <c r="F810" t="n">
-        <v>1997.6</v>
+        <v>1992.4</v>
       </c>
       <c r="G810" t="n">
         <v>2077.29</v>
       </c>
       <c r="H810" t="n">
-        <v>-79.69</v>
+        <v>-84.89</v>
       </c>
       <c r="I810" t="n">
-        <v>1812.2</v>
+        <v>1890</v>
       </c>
       <c r="J810" t="n">
         <v>1993</v>
       </c>
       <c r="K810" t="n">
-        <v>-180.8</v>
+        <v>-103</v>
       </c>
       <c r="L810" t="inlineStr">
         <is>
@@ -42569,11 +42569,11 @@
       </c>
       <c r="M810" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N810" t="n">
-        <v>2.38</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="811">
@@ -42588,31 +42588,31 @@
         </is>
       </c>
       <c r="C811" t="n">
-        <v>325.55</v>
+        <v>317.4</v>
       </c>
       <c r="D811" t="n">
         <v>333.48</v>
       </c>
       <c r="E811" t="n">
-        <v>-7.93</v>
+        <v>-16.08</v>
       </c>
       <c r="F811" t="n">
-        <v>327.95</v>
+        <v>318</v>
       </c>
       <c r="G811" t="n">
         <v>333.48</v>
       </c>
       <c r="H811" t="n">
-        <v>-5.53</v>
+        <v>-15.48</v>
       </c>
       <c r="I811" t="n">
-        <v>313.65</v>
+        <v>301.75</v>
       </c>
       <c r="J811" t="n">
         <v>316.72</v>
       </c>
       <c r="K811" t="n">
-        <v>-3.07</v>
+        <v>-14.97</v>
       </c>
       <c r="L811" t="inlineStr">
         <is>
@@ -42621,11 +42621,11 @@
       </c>
       <c r="M811" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N811" t="n">
-        <v>2.38</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="812">
@@ -42640,31 +42640,31 @@
         </is>
       </c>
       <c r="C812" t="n">
-        <v>5850</v>
+        <v>5727.5</v>
       </c>
       <c r="D812" t="n">
         <v>6036.61</v>
       </c>
       <c r="E812" t="n">
-        <v>-186.61</v>
+        <v>-309.11</v>
       </c>
       <c r="F812" t="n">
-        <v>5873.5</v>
+        <v>5914.5</v>
       </c>
       <c r="G812" t="n">
         <v>6036.61</v>
       </c>
       <c r="H812" t="n">
-        <v>-163.11</v>
+        <v>-122.11</v>
       </c>
       <c r="I812" t="n">
-        <v>5600</v>
+        <v>5674.5</v>
       </c>
       <c r="J812" t="n">
         <v>5744.8</v>
       </c>
       <c r="K812" t="n">
-        <v>-144.8</v>
+        <v>-70.3</v>
       </c>
       <c r="L812" t="inlineStr">
         <is>
@@ -42673,11 +42673,11 @@
       </c>
       <c r="M812" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N812" t="n">
-        <v>3.09</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="813">
@@ -42692,31 +42692,31 @@
         </is>
       </c>
       <c r="C813" t="n">
-        <v>1417</v>
+        <v>1422.2</v>
       </c>
       <c r="D813" t="n">
         <v>1451.54</v>
       </c>
       <c r="E813" t="n">
-        <v>-34.54</v>
+        <v>-29.34</v>
       </c>
       <c r="F813" t="n">
-        <v>1422.7</v>
+        <v>1467.5</v>
       </c>
       <c r="G813" t="n">
         <v>1451.54</v>
       </c>
       <c r="H813" t="n">
-        <v>-28.84</v>
+        <v>15.96</v>
       </c>
       <c r="I813" t="n">
-        <v>1386</v>
+        <v>1415</v>
       </c>
       <c r="J813" t="n">
         <v>1387.05</v>
       </c>
       <c r="K813" t="n">
-        <v>-1.05</v>
+        <v>27.95</v>
       </c>
       <c r="L813" t="inlineStr">
         <is>
@@ -42729,7 +42729,7 @@
         </is>
       </c>
       <c r="N813" t="n">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="814">
@@ -42744,31 +42744,31 @@
         </is>
       </c>
       <c r="C814" t="n">
-        <v>2557.6</v>
+        <v>2480</v>
       </c>
       <c r="D814" t="n">
         <v>2790.11</v>
       </c>
       <c r="E814" t="n">
-        <v>-232.51</v>
+        <v>-310.11</v>
       </c>
       <c r="F814" t="n">
-        <v>2563.3</v>
+        <v>2585.6</v>
       </c>
       <c r="G814" t="n">
         <v>2790.11</v>
       </c>
       <c r="H814" t="n">
-        <v>-226.81</v>
+        <v>-204.51</v>
       </c>
       <c r="I814" t="n">
-        <v>2435</v>
+        <v>2470.1</v>
       </c>
       <c r="J814" t="n">
         <v>2498.67</v>
       </c>
       <c r="K814" t="n">
-        <v>-63.67</v>
+        <v>-28.57</v>
       </c>
       <c r="L814" t="inlineStr">
         <is>
@@ -42777,11 +42777,11 @@
       </c>
       <c r="M814" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N814" t="n">
-        <v>8.33</v>
+        <v>11.11</v>
       </c>
     </row>
   </sheetData>
@@ -48910,31 +48910,31 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>325.55</v>
+        <v>317.4</v>
       </c>
       <c r="D42" t="n">
         <v>333.48</v>
       </c>
       <c r="E42" t="n">
-        <v>-7.93</v>
+        <v>-16.08</v>
       </c>
       <c r="F42" t="n">
-        <v>327.95</v>
+        <v>318</v>
       </c>
       <c r="G42" t="n">
         <v>333.48</v>
       </c>
       <c r="H42" t="n">
-        <v>-5.53</v>
+        <v>-15.48</v>
       </c>
       <c r="I42" t="n">
-        <v>313.65</v>
+        <v>301.75</v>
       </c>
       <c r="J42" t="n">
         <v>316.72</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.07</v>
+        <v>-14.97</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -48943,11 +48943,11 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.38</v>
+        <v>4.82</v>
       </c>
     </row>
   </sheetData>
@@ -51162,31 +51162,31 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1993</v>
+        <v>1900.5</v>
       </c>
       <c r="D19" t="n">
         <v>2041.57</v>
       </c>
       <c r="E19" t="n">
-        <v>-48.57</v>
+        <v>-141.07</v>
       </c>
       <c r="F19" t="n">
-        <v>1997.6</v>
+        <v>1992.4</v>
       </c>
       <c r="G19" t="n">
         <v>2077.29</v>
       </c>
       <c r="H19" t="n">
-        <v>-79.69</v>
+        <v>-84.89</v>
       </c>
       <c r="I19" t="n">
-        <v>1812.2</v>
+        <v>1890</v>
       </c>
       <c r="J19" t="n">
         <v>1993</v>
       </c>
       <c r="K19" t="n">
-        <v>-180.8</v>
+        <v>-103</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -51195,11 +51195,11 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.38</v>
+        <v>6.91</v>
       </c>
     </row>
   </sheetData>
@@ -52756,31 +52756,31 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5850</v>
+        <v>5727.5</v>
       </c>
       <c r="D30" t="n">
         <v>6036.61</v>
       </c>
       <c r="E30" t="n">
-        <v>-186.61</v>
+        <v>-309.11</v>
       </c>
       <c r="F30" t="n">
-        <v>5873.5</v>
+        <v>5914.5</v>
       </c>
       <c r="G30" t="n">
         <v>6036.61</v>
       </c>
       <c r="H30" t="n">
-        <v>-163.11</v>
+        <v>-122.11</v>
       </c>
       <c r="I30" t="n">
-        <v>5600</v>
+        <v>5674.5</v>
       </c>
       <c r="J30" t="n">
         <v>5744.8</v>
       </c>
       <c r="K30" t="n">
-        <v>-144.8</v>
+        <v>-70.3</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -52789,11 +52789,11 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>3.09</v>
+        <v>5.12</v>
       </c>
     </row>
   </sheetData>
@@ -54974,31 +54974,31 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>120.89</v>
+        <v>120.37</v>
       </c>
       <c r="D42" t="n">
         <v>127.13</v>
       </c>
       <c r="E42" t="n">
-        <v>-6.24</v>
+        <v>-6.76</v>
       </c>
       <c r="F42" t="n">
-        <v>120.89</v>
+        <v>122.3</v>
       </c>
       <c r="G42" t="n">
         <v>127.13</v>
       </c>
       <c r="H42" t="n">
-        <v>-6.24</v>
+        <v>-4.83</v>
       </c>
       <c r="I42" t="n">
-        <v>118.2</v>
+        <v>119.06</v>
       </c>
       <c r="J42" t="n">
         <v>120.25</v>
       </c>
       <c r="K42" t="n">
-        <v>-2.05</v>
+        <v>-1.19</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -55007,11 +55007,11 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>4.91</v>
+        <v>5.32</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N814"/>
+  <dimension ref="A1:N824"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42782,6 +42782,526 @@
       </c>
       <c r="N814" t="n">
         <v>11.11</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C815" t="n">
+        <v>671</v>
+      </c>
+      <c r="D815" t="n">
+        <v>635.33</v>
+      </c>
+      <c r="E815" t="n">
+        <v>35.67</v>
+      </c>
+      <c r="F815" t="n">
+        <v>673</v>
+      </c>
+      <c r="G815" t="n">
+        <v>643.85</v>
+      </c>
+      <c r="H815" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="I815" t="n">
+        <v>659</v>
+      </c>
+      <c r="J815" t="n">
+        <v>640.04</v>
+      </c>
+      <c r="K815" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="L815" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M815" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N815" t="n">
+        <v>5.61</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C816" t="n">
+        <v>121.27</v>
+      </c>
+      <c r="D816" t="n">
+        <v>115.74</v>
+      </c>
+      <c r="E816" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="F816" t="n">
+        <v>122.34</v>
+      </c>
+      <c r="G816" t="n">
+        <v>118.22</v>
+      </c>
+      <c r="H816" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="I816" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="J816" t="n">
+        <v>116.94</v>
+      </c>
+      <c r="K816" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="L816" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M816" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N816" t="n">
+        <v>4.78</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C817" t="n">
+        <v>296</v>
+      </c>
+      <c r="D817" t="n">
+        <v>285.03</v>
+      </c>
+      <c r="E817" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="F817" t="n">
+        <v>296</v>
+      </c>
+      <c r="G817" t="n">
+        <v>291.98</v>
+      </c>
+      <c r="H817" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="I817" t="n">
+        <v>288.1</v>
+      </c>
+      <c r="J817" t="n">
+        <v>288.95</v>
+      </c>
+      <c r="K817" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="L817" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M817" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N817" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C818" t="n">
+        <v>2213.9</v>
+      </c>
+      <c r="D818" t="n">
+        <v>2123.74</v>
+      </c>
+      <c r="E818" t="n">
+        <v>90.16</v>
+      </c>
+      <c r="F818" t="n">
+        <v>2213.9</v>
+      </c>
+      <c r="G818" t="n">
+        <v>2209.51</v>
+      </c>
+      <c r="H818" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="I818" t="n">
+        <v>2100</v>
+      </c>
+      <c r="J818" t="n">
+        <v>2188.64</v>
+      </c>
+      <c r="K818" t="n">
+        <v>-88.64</v>
+      </c>
+      <c r="L818" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M818" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N818" t="n">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="C819" t="n">
+        <v>1420</v>
+      </c>
+      <c r="D819" t="n">
+        <v>1402.43</v>
+      </c>
+      <c r="E819" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="F819" t="n">
+        <v>1420</v>
+      </c>
+      <c r="G819" t="n">
+        <v>1402.43</v>
+      </c>
+      <c r="H819" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="I819" t="n">
+        <v>1391</v>
+      </c>
+      <c r="J819" t="n">
+        <v>1367.03</v>
+      </c>
+      <c r="K819" t="n">
+        <v>23.97</v>
+      </c>
+      <c r="L819" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M819" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N819" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C820" t="n">
+        <v>2618.4</v>
+      </c>
+      <c r="D820" t="n">
+        <v>2345.99</v>
+      </c>
+      <c r="E820" t="n">
+        <v>272.41</v>
+      </c>
+      <c r="F820" t="n">
+        <v>2618.4</v>
+      </c>
+      <c r="G820" t="n">
+        <v>2500.03</v>
+      </c>
+      <c r="H820" t="n">
+        <v>118.37</v>
+      </c>
+      <c r="I820" t="n">
+        <v>2498.7</v>
+      </c>
+      <c r="J820" t="n">
+        <v>2476.32</v>
+      </c>
+      <c r="K820" t="n">
+        <v>22.38</v>
+      </c>
+      <c r="L820" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M820" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N820" t="n">
+        <v>11.61</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C821" t="n">
+        <v>1997</v>
+      </c>
+      <c r="D821" t="n">
+        <v>1873.88</v>
+      </c>
+      <c r="E821" t="n">
+        <v>123.12</v>
+      </c>
+      <c r="F821" t="n">
+        <v>2008.8</v>
+      </c>
+      <c r="G821" t="n">
+        <v>1934.19</v>
+      </c>
+      <c r="H821" t="n">
+        <v>74.61</v>
+      </c>
+      <c r="I821" t="n">
+        <v>1953</v>
+      </c>
+      <c r="J821" t="n">
+        <v>1912.91</v>
+      </c>
+      <c r="K821" t="n">
+        <v>40.09</v>
+      </c>
+      <c r="L821" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M821" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N821" t="n">
+        <v>6.57</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C822" t="n">
+        <v>331</v>
+      </c>
+      <c r="D822" t="n">
+        <v>317.56</v>
+      </c>
+      <c r="E822" t="n">
+        <v>13.44</v>
+      </c>
+      <c r="F822" t="n">
+        <v>331.45</v>
+      </c>
+      <c r="G822" t="n">
+        <v>317.56</v>
+      </c>
+      <c r="H822" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="I822" t="n">
+        <v>323.35</v>
+      </c>
+      <c r="J822" t="n">
+        <v>312.6</v>
+      </c>
+      <c r="K822" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="L822" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M822" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N822" t="n">
+        <v>4.23</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C823" t="n">
+        <v>5832.5</v>
+      </c>
+      <c r="D823" t="n">
+        <v>5578.09</v>
+      </c>
+      <c r="E823" t="n">
+        <v>254.41</v>
+      </c>
+      <c r="F823" t="n">
+        <v>5861</v>
+      </c>
+      <c r="G823" t="n">
+        <v>5618.54</v>
+      </c>
+      <c r="H823" t="n">
+        <v>242.46</v>
+      </c>
+      <c r="I823" t="n">
+        <v>5690</v>
+      </c>
+      <c r="J823" t="n">
+        <v>5555.6</v>
+      </c>
+      <c r="K823" t="n">
+        <v>134.4</v>
+      </c>
+      <c r="L823" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M823" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N823" t="n">
+        <v>4.56</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="C824" t="n">
+        <v>1310</v>
+      </c>
+      <c r="D824" t="n">
+        <v>1209.02</v>
+      </c>
+      <c r="E824" t="n">
+        <v>100.98</v>
+      </c>
+      <c r="F824" t="n">
+        <v>1323.7</v>
+      </c>
+      <c r="G824" t="n">
+        <v>1227.88</v>
+      </c>
+      <c r="H824" t="n">
+        <v>95.81999999999999</v>
+      </c>
+      <c r="I824" t="n">
+        <v>1299.4</v>
+      </c>
+      <c r="J824" t="n">
+        <v>1248.15</v>
+      </c>
+      <c r="K824" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="L824" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M824" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N824" t="n">
+        <v>8.35</v>
       </c>
     </row>
   </sheetData>
@@ -46743,7 +47263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48948,6 +49468,58 @@
       </c>
       <c r="N42" t="n">
         <v>4.82</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>331</v>
+      </c>
+      <c r="D43" t="n">
+        <v>317.56</v>
+      </c>
+      <c r="E43" t="n">
+        <v>13.44</v>
+      </c>
+      <c r="F43" t="n">
+        <v>331.45</v>
+      </c>
+      <c r="G43" t="n">
+        <v>317.56</v>
+      </c>
+      <c r="H43" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="I43" t="n">
+        <v>323.35</v>
+      </c>
+      <c r="J43" t="n">
+        <v>312.6</v>
+      </c>
+      <c r="K43" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>4.23</v>
       </c>
     </row>
   </sheetData>
@@ -50191,7 +50763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51200,6 +51772,58 @@
       </c>
       <c r="N19" t="n">
         <v>6.91</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1997</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1873.88</v>
+      </c>
+      <c r="E20" t="n">
+        <v>123.12</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2008.8</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1934.19</v>
+      </c>
+      <c r="H20" t="n">
+        <v>74.61</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1953</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1912.91</v>
+      </c>
+      <c r="K20" t="n">
+        <v>40.09</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>6.57</v>
       </c>
     </row>
   </sheetData>
@@ -51213,7 +51837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52794,6 +53418,58 @@
       </c>
       <c r="N30" t="n">
         <v>5.12</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>5832.5</v>
+      </c>
+      <c r="D31" t="n">
+        <v>5578.09</v>
+      </c>
+      <c r="E31" t="n">
+        <v>254.41</v>
+      </c>
+      <c r="F31" t="n">
+        <v>5861</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5618.54</v>
+      </c>
+      <c r="H31" t="n">
+        <v>242.46</v>
+      </c>
+      <c r="I31" t="n">
+        <v>5690</v>
+      </c>
+      <c r="J31" t="n">
+        <v>5555.6</v>
+      </c>
+      <c r="K31" t="n">
+        <v>134.4</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>4.56</v>
       </c>
     </row>
   </sheetData>
@@ -52807,7 +53483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55012,6 +55688,58 @@
       </c>
       <c r="N42" t="n">
         <v>5.32</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>121.27</v>
+      </c>
+      <c r="D43" t="n">
+        <v>115.74</v>
+      </c>
+      <c r="E43" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="F43" t="n">
+        <v>122.34</v>
+      </c>
+      <c r="G43" t="n">
+        <v>118.22</v>
+      </c>
+      <c r="H43" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="I43" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="J43" t="n">
+        <v>116.94</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>4.78</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -42796,31 +42796,31 @@
         </is>
       </c>
       <c r="C815" t="n">
-        <v>671</v>
+        <v>662.3</v>
       </c>
       <c r="D815" t="n">
         <v>635.33</v>
       </c>
       <c r="E815" t="n">
-        <v>35.67</v>
+        <v>26.97</v>
       </c>
       <c r="F815" t="n">
-        <v>673</v>
+        <v>664.9</v>
       </c>
       <c r="G815" t="n">
         <v>643.85</v>
       </c>
       <c r="H815" t="n">
-        <v>29.15</v>
+        <v>21.05</v>
       </c>
       <c r="I815" t="n">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="J815" t="n">
         <v>640.04</v>
       </c>
       <c r="K815" t="n">
-        <v>18.96</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="L815" t="inlineStr">
         <is>
@@ -42833,7 +42833,7 @@
         </is>
       </c>
       <c r="N815" t="n">
-        <v>5.61</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="816">
@@ -42848,31 +42848,31 @@
         </is>
       </c>
       <c r="C816" t="n">
-        <v>121.27</v>
+        <v>120.89</v>
       </c>
       <c r="D816" t="n">
         <v>115.74</v>
       </c>
       <c r="E816" t="n">
-        <v>5.53</v>
+        <v>5.15</v>
       </c>
       <c r="F816" t="n">
-        <v>122.34</v>
+        <v>120.89</v>
       </c>
       <c r="G816" t="n">
         <v>118.22</v>
       </c>
       <c r="H816" t="n">
-        <v>4.12</v>
+        <v>2.67</v>
       </c>
       <c r="I816" t="n">
-        <v>120.2</v>
+        <v>118.2</v>
       </c>
       <c r="J816" t="n">
         <v>116.94</v>
       </c>
       <c r="K816" t="n">
-        <v>3.26</v>
+        <v>1.26</v>
       </c>
       <c r="L816" t="inlineStr">
         <is>
@@ -42881,11 +42881,11 @@
       </c>
       <c r="M816" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N816" t="n">
-        <v>4.78</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="817">
@@ -42900,31 +42900,31 @@
         </is>
       </c>
       <c r="C817" t="n">
-        <v>296</v>
+        <v>291.75</v>
       </c>
       <c r="D817" t="n">
         <v>285.03</v>
       </c>
       <c r="E817" t="n">
-        <v>10.97</v>
+        <v>6.72</v>
       </c>
       <c r="F817" t="n">
-        <v>296</v>
+        <v>292.75</v>
       </c>
       <c r="G817" t="n">
         <v>291.98</v>
       </c>
       <c r="H817" t="n">
-        <v>4.02</v>
+        <v>0.77</v>
       </c>
       <c r="I817" t="n">
-        <v>288.1</v>
+        <v>282.05</v>
       </c>
       <c r="J817" t="n">
         <v>288.95</v>
       </c>
       <c r="K817" t="n">
-        <v>-0.85</v>
+        <v>-6.9</v>
       </c>
       <c r="L817" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         </is>
       </c>
       <c r="N817" t="n">
-        <v>3.85</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="818">
@@ -42952,31 +42952,31 @@
         </is>
       </c>
       <c r="C818" t="n">
-        <v>2213.9</v>
+        <v>2077.9</v>
       </c>
       <c r="D818" t="n">
         <v>2123.74</v>
       </c>
       <c r="E818" t="n">
-        <v>90.16</v>
+        <v>-45.84</v>
       </c>
       <c r="F818" t="n">
-        <v>2213.9</v>
+        <v>2084.9</v>
       </c>
       <c r="G818" t="n">
         <v>2209.51</v>
       </c>
       <c r="H818" t="n">
-        <v>4.39</v>
+        <v>-124.61</v>
       </c>
       <c r="I818" t="n">
-        <v>2100</v>
+        <v>2025.1</v>
       </c>
       <c r="J818" t="n">
         <v>2188.64</v>
       </c>
       <c r="K818" t="n">
-        <v>-88.64</v>
+        <v>-163.54</v>
       </c>
       <c r="L818" t="inlineStr">
         <is>
@@ -42985,11 +42985,11 @@
       </c>
       <c r="M818" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N818" t="n">
-        <v>4.25</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="819">
@@ -43004,31 +43004,31 @@
         </is>
       </c>
       <c r="C819" t="n">
-        <v>1420</v>
+        <v>1417</v>
       </c>
       <c r="D819" t="n">
         <v>1402.43</v>
       </c>
       <c r="E819" t="n">
-        <v>17.57</v>
+        <v>14.57</v>
       </c>
       <c r="F819" t="n">
-        <v>1420</v>
+        <v>1422.7</v>
       </c>
       <c r="G819" t="n">
         <v>1402.43</v>
       </c>
       <c r="H819" t="n">
-        <v>17.57</v>
+        <v>20.27</v>
       </c>
       <c r="I819" t="n">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="J819" t="n">
         <v>1367.03</v>
       </c>
       <c r="K819" t="n">
-        <v>23.97</v>
+        <v>18.97</v>
       </c>
       <c r="L819" t="inlineStr">
         <is>
@@ -43041,7 +43041,7 @@
         </is>
       </c>
       <c r="N819" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="820">
@@ -43056,31 +43056,31 @@
         </is>
       </c>
       <c r="C820" t="n">
-        <v>2618.4</v>
+        <v>2557.6</v>
       </c>
       <c r="D820" t="n">
         <v>2345.99</v>
       </c>
       <c r="E820" t="n">
-        <v>272.41</v>
+        <v>211.61</v>
       </c>
       <c r="F820" t="n">
-        <v>2618.4</v>
+        <v>2563.3</v>
       </c>
       <c r="G820" t="n">
         <v>2500.03</v>
       </c>
       <c r="H820" t="n">
-        <v>118.37</v>
+        <v>63.27</v>
       </c>
       <c r="I820" t="n">
-        <v>2498.7</v>
+        <v>2435</v>
       </c>
       <c r="J820" t="n">
         <v>2476.32</v>
       </c>
       <c r="K820" t="n">
-        <v>22.38</v>
+        <v>-41.32</v>
       </c>
       <c r="L820" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
         </is>
       </c>
       <c r="N820" t="n">
-        <v>11.61</v>
+        <v>9.02</v>
       </c>
     </row>
     <row r="821">
@@ -43108,31 +43108,31 @@
         </is>
       </c>
       <c r="C821" t="n">
-        <v>1997</v>
+        <v>1993</v>
       </c>
       <c r="D821" t="n">
         <v>1873.88</v>
       </c>
       <c r="E821" t="n">
-        <v>123.12</v>
+        <v>119.12</v>
       </c>
       <c r="F821" t="n">
-        <v>2008.8</v>
+        <v>1997.6</v>
       </c>
       <c r="G821" t="n">
         <v>1934.19</v>
       </c>
       <c r="H821" t="n">
-        <v>74.61</v>
+        <v>63.41</v>
       </c>
       <c r="I821" t="n">
-        <v>1953</v>
+        <v>1812.2</v>
       </c>
       <c r="J821" t="n">
         <v>1912.91</v>
       </c>
       <c r="K821" t="n">
-        <v>40.09</v>
+        <v>-100.71</v>
       </c>
       <c r="L821" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         </is>
       </c>
       <c r="N821" t="n">
-        <v>6.57</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="822">
@@ -43160,31 +43160,31 @@
         </is>
       </c>
       <c r="C822" t="n">
-        <v>331</v>
+        <v>325.55</v>
       </c>
       <c r="D822" t="n">
         <v>317.56</v>
       </c>
       <c r="E822" t="n">
-        <v>13.44</v>
+        <v>7.99</v>
       </c>
       <c r="F822" t="n">
-        <v>331.45</v>
+        <v>327.95</v>
       </c>
       <c r="G822" t="n">
         <v>317.56</v>
       </c>
       <c r="H822" t="n">
-        <v>13.89</v>
+        <v>10.39</v>
       </c>
       <c r="I822" t="n">
-        <v>323.35</v>
+        <v>313.65</v>
       </c>
       <c r="J822" t="n">
         <v>312.6</v>
       </c>
       <c r="K822" t="n">
-        <v>10.75</v>
+        <v>1.05</v>
       </c>
       <c r="L822" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         </is>
       </c>
       <c r="N822" t="n">
-        <v>4.23</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="823">
@@ -43212,31 +43212,31 @@
         </is>
       </c>
       <c r="C823" t="n">
-        <v>5832.5</v>
+        <v>5850</v>
       </c>
       <c r="D823" t="n">
         <v>5578.09</v>
       </c>
       <c r="E823" t="n">
-        <v>254.41</v>
+        <v>271.91</v>
       </c>
       <c r="F823" t="n">
-        <v>5861</v>
+        <v>5873.5</v>
       </c>
       <c r="G823" t="n">
         <v>5618.54</v>
       </c>
       <c r="H823" t="n">
-        <v>242.46</v>
+        <v>254.96</v>
       </c>
       <c r="I823" t="n">
-        <v>5690</v>
+        <v>5600</v>
       </c>
       <c r="J823" t="n">
         <v>5555.6</v>
       </c>
       <c r="K823" t="n">
-        <v>134.4</v>
+        <v>44.4</v>
       </c>
       <c r="L823" t="inlineStr">
         <is>
@@ -43249,7 +43249,7 @@
         </is>
       </c>
       <c r="N823" t="n">
-        <v>4.56</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="824">
@@ -43264,31 +43264,31 @@
         </is>
       </c>
       <c r="C824" t="n">
-        <v>1310</v>
+        <v>1310.9</v>
       </c>
       <c r="D824" t="n">
         <v>1209.02</v>
       </c>
       <c r="E824" t="n">
-        <v>100.98</v>
+        <v>101.88</v>
       </c>
       <c r="F824" t="n">
-        <v>1323.7</v>
+        <v>1319</v>
       </c>
       <c r="G824" t="n">
         <v>1227.88</v>
       </c>
       <c r="H824" t="n">
-        <v>95.81999999999999</v>
+        <v>91.12</v>
       </c>
       <c r="I824" t="n">
-        <v>1299.4</v>
+        <v>1224</v>
       </c>
       <c r="J824" t="n">
         <v>1248.15</v>
       </c>
       <c r="K824" t="n">
-        <v>51.25</v>
+        <v>-24.15</v>
       </c>
       <c r="L824" t="inlineStr">
         <is>
@@ -43301,7 +43301,7 @@
         </is>
       </c>
       <c r="N824" t="n">
-        <v>8.35</v>
+        <v>8.43</v>
       </c>
     </row>
   </sheetData>
@@ -49482,31 +49482,31 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>331</v>
+        <v>325.55</v>
       </c>
       <c r="D43" t="n">
         <v>317.56</v>
       </c>
       <c r="E43" t="n">
-        <v>13.44</v>
+        <v>7.99</v>
       </c>
       <c r="F43" t="n">
-        <v>331.45</v>
+        <v>327.95</v>
       </c>
       <c r="G43" t="n">
         <v>317.56</v>
       </c>
       <c r="H43" t="n">
-        <v>13.89</v>
+        <v>10.39</v>
       </c>
       <c r="I43" t="n">
-        <v>323.35</v>
+        <v>313.65</v>
       </c>
       <c r="J43" t="n">
         <v>312.6</v>
       </c>
       <c r="K43" t="n">
-        <v>10.75</v>
+        <v>1.05</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -49519,7 +49519,7 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>4.23</v>
+        <v>2.52</v>
       </c>
     </row>
   </sheetData>
@@ -51786,31 +51786,31 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1997</v>
+        <v>1993</v>
       </c>
       <c r="D20" t="n">
         <v>1873.88</v>
       </c>
       <c r="E20" t="n">
-        <v>123.12</v>
+        <v>119.12</v>
       </c>
       <c r="F20" t="n">
-        <v>2008.8</v>
+        <v>1997.6</v>
       </c>
       <c r="G20" t="n">
         <v>1934.19</v>
       </c>
       <c r="H20" t="n">
-        <v>74.61</v>
+        <v>63.41</v>
       </c>
       <c r="I20" t="n">
-        <v>1953</v>
+        <v>1812.2</v>
       </c>
       <c r="J20" t="n">
         <v>1912.91</v>
       </c>
       <c r="K20" t="n">
-        <v>40.09</v>
+        <v>-100.71</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -51823,7 +51823,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>6.57</v>
+        <v>6.36</v>
       </c>
     </row>
   </sheetData>
@@ -53432,31 +53432,31 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5832.5</v>
+        <v>5850</v>
       </c>
       <c r="D31" t="n">
         <v>5578.09</v>
       </c>
       <c r="E31" t="n">
-        <v>254.41</v>
+        <v>271.91</v>
       </c>
       <c r="F31" t="n">
-        <v>5861</v>
+        <v>5873.5</v>
       </c>
       <c r="G31" t="n">
         <v>5618.54</v>
       </c>
       <c r="H31" t="n">
-        <v>242.46</v>
+        <v>254.96</v>
       </c>
       <c r="I31" t="n">
-        <v>5690</v>
+        <v>5600</v>
       </c>
       <c r="J31" t="n">
         <v>5555.6</v>
       </c>
       <c r="K31" t="n">
-        <v>134.4</v>
+        <v>44.4</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -53469,7 +53469,7 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>4.56</v>
+        <v>4.87</v>
       </c>
     </row>
   </sheetData>
@@ -55702,31 +55702,31 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>121.27</v>
+        <v>120.89</v>
       </c>
       <c r="D43" t="n">
         <v>115.74</v>
       </c>
       <c r="E43" t="n">
-        <v>5.53</v>
+        <v>5.15</v>
       </c>
       <c r="F43" t="n">
-        <v>122.34</v>
+        <v>120.89</v>
       </c>
       <c r="G43" t="n">
         <v>118.22</v>
       </c>
       <c r="H43" t="n">
-        <v>4.12</v>
+        <v>2.67</v>
       </c>
       <c r="I43" t="n">
-        <v>120.2</v>
+        <v>118.2</v>
       </c>
       <c r="J43" t="n">
         <v>116.94</v>
       </c>
       <c r="K43" t="n">
-        <v>3.26</v>
+        <v>1.26</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -55735,11 +55735,11 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>4.78</v>
+        <v>4.45</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N824"/>
+  <dimension ref="A1:N833"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43302,6 +43302,474 @@
       </c>
       <c r="N824" t="n">
         <v>8.43</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="C825" t="n">
+        <v>1335.4</v>
+      </c>
+      <c r="D825" t="n">
+        <v>1459.51</v>
+      </c>
+      <c r="E825" t="n">
+        <v>-124.11</v>
+      </c>
+      <c r="F825" t="n">
+        <v>1338.2</v>
+      </c>
+      <c r="G825" t="n">
+        <v>1459.51</v>
+      </c>
+      <c r="H825" t="n">
+        <v>-121.31</v>
+      </c>
+      <c r="I825" t="n">
+        <v>1301</v>
+      </c>
+      <c r="J825" t="n">
+        <v>1305.41</v>
+      </c>
+      <c r="K825" t="n">
+        <v>-4.41</v>
+      </c>
+      <c r="L825" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M825" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N825" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C826" t="n">
+        <v>120.31</v>
+      </c>
+      <c r="D826" t="n">
+        <v>126.67</v>
+      </c>
+      <c r="E826" t="n">
+        <v>-6.36</v>
+      </c>
+      <c r="F826" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="G826" t="n">
+        <v>126.67</v>
+      </c>
+      <c r="H826" t="n">
+        <v>-5.17</v>
+      </c>
+      <c r="I826" t="n">
+        <v>119.42</v>
+      </c>
+      <c r="J826" t="n">
+        <v>118.87</v>
+      </c>
+      <c r="K826" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L826" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M826" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N826" t="n">
+        <v>5.02</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C827" t="n">
+        <v>666.3</v>
+      </c>
+      <c r="D827" t="n">
+        <v>700.14</v>
+      </c>
+      <c r="E827" t="n">
+        <v>-33.84</v>
+      </c>
+      <c r="F827" t="n">
+        <v>671.4</v>
+      </c>
+      <c r="G827" t="n">
+        <v>700.14</v>
+      </c>
+      <c r="H827" t="n">
+        <v>-28.74</v>
+      </c>
+      <c r="I827" t="n">
+        <v>663.95</v>
+      </c>
+      <c r="J827" t="n">
+        <v>647.64</v>
+      </c>
+      <c r="K827" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="L827" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M827" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N827" t="n">
+        <v>4.83</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C828" t="n">
+        <v>5848</v>
+      </c>
+      <c r="D828" t="n">
+        <v>6182.15</v>
+      </c>
+      <c r="E828" t="n">
+        <v>-334.15</v>
+      </c>
+      <c r="F828" t="n">
+        <v>5872.5</v>
+      </c>
+      <c r="G828" t="n">
+        <v>6182.15</v>
+      </c>
+      <c r="H828" t="n">
+        <v>-309.65</v>
+      </c>
+      <c r="I828" t="n">
+        <v>5650</v>
+      </c>
+      <c r="J828" t="n">
+        <v>5614.44</v>
+      </c>
+      <c r="K828" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="L828" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M828" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N828" t="n">
+        <v>5.41</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C829" t="n">
+        <v>2165.3</v>
+      </c>
+      <c r="D829" t="n">
+        <v>2135.52</v>
+      </c>
+      <c r="E829" t="n">
+        <v>29.78</v>
+      </c>
+      <c r="F829" t="n">
+        <v>2219</v>
+      </c>
+      <c r="G829" t="n">
+        <v>2135.52</v>
+      </c>
+      <c r="H829" t="n">
+        <v>83.48</v>
+      </c>
+      <c r="I829" t="n">
+        <v>2156.3</v>
+      </c>
+      <c r="J829" t="n">
+        <v>2089.74</v>
+      </c>
+      <c r="K829" t="n">
+        <v>66.56</v>
+      </c>
+      <c r="L829" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M829" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N829" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C830" t="n">
+        <v>1961.9</v>
+      </c>
+      <c r="D830" t="n">
+        <v>2103.32</v>
+      </c>
+      <c r="E830" t="n">
+        <v>-141.42</v>
+      </c>
+      <c r="F830" t="n">
+        <v>1977.8</v>
+      </c>
+      <c r="G830" t="n">
+        <v>2103.32</v>
+      </c>
+      <c r="H830" t="n">
+        <v>-125.52</v>
+      </c>
+      <c r="I830" t="n">
+        <v>1903.8</v>
+      </c>
+      <c r="J830" t="n">
+        <v>1887.63</v>
+      </c>
+      <c r="K830" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="L830" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M830" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N830" t="n">
+        <v>6.72</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="C831" t="n">
+        <v>1400.5</v>
+      </c>
+      <c r="D831" t="n">
+        <v>1426.37</v>
+      </c>
+      <c r="E831" t="n">
+        <v>-25.87</v>
+      </c>
+      <c r="F831" t="n">
+        <v>1401.4</v>
+      </c>
+      <c r="G831" t="n">
+        <v>1427.07</v>
+      </c>
+      <c r="H831" t="n">
+        <v>-25.67</v>
+      </c>
+      <c r="I831" t="n">
+        <v>1364</v>
+      </c>
+      <c r="J831" t="n">
+        <v>1363.3</v>
+      </c>
+      <c r="K831" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L831" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M831" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N831" t="n">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C832" t="n">
+        <v>2518</v>
+      </c>
+      <c r="D832" t="n">
+        <v>2767.08</v>
+      </c>
+      <c r="E832" t="n">
+        <v>-249.08</v>
+      </c>
+      <c r="F832" t="n">
+        <v>2563.9</v>
+      </c>
+      <c r="G832" t="n">
+        <v>2767.08</v>
+      </c>
+      <c r="H832" t="n">
+        <v>-203.18</v>
+      </c>
+      <c r="I832" t="n">
+        <v>2455.2</v>
+      </c>
+      <c r="J832" t="n">
+        <v>2417.66</v>
+      </c>
+      <c r="K832" t="n">
+        <v>37.54</v>
+      </c>
+      <c r="L832" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M832" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N832" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="C833" t="n">
+        <v>2460</v>
+      </c>
+      <c r="D833" t="n">
+        <v>2550.72</v>
+      </c>
+      <c r="E833" t="n">
+        <v>-90.72</v>
+      </c>
+      <c r="F833" t="n">
+        <v>2461.3</v>
+      </c>
+      <c r="G833" t="n">
+        <v>2550.72</v>
+      </c>
+      <c r="H833" t="n">
+        <v>-89.42</v>
+      </c>
+      <c r="I833" t="n">
+        <v>2408.2</v>
+      </c>
+      <c r="J833" t="n">
+        <v>2362.5</v>
+      </c>
+      <c r="K833" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="L833" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M833" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N833" t="n">
+        <v>3.56</v>
       </c>
     </row>
   </sheetData>
@@ -50763,7 +51231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51824,6 +52292,58 @@
       </c>
       <c r="N20" t="n">
         <v>6.36</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1961.9</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2103.32</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-141.42</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1977.8</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2103.32</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-125.52</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1903.8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1887.63</v>
+      </c>
+      <c r="K21" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>6.72</v>
       </c>
     </row>
   </sheetData>
@@ -51837,7 +52357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53470,6 +53990,58 @@
       </c>
       <c r="N31" t="n">
         <v>4.87</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>5848</v>
+      </c>
+      <c r="D32" t="n">
+        <v>6182.15</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-334.15</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5872.5</v>
+      </c>
+      <c r="G32" t="n">
+        <v>6182.15</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-309.65</v>
+      </c>
+      <c r="I32" t="n">
+        <v>5650</v>
+      </c>
+      <c r="J32" t="n">
+        <v>5614.44</v>
+      </c>
+      <c r="K32" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>5.41</v>
       </c>
     </row>
   </sheetData>
@@ -53483,7 +54055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55740,6 +56312,58 @@
       </c>
       <c r="N43" t="n">
         <v>4.45</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>120.31</v>
+      </c>
+      <c r="D44" t="n">
+        <v>126.67</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-6.36</v>
+      </c>
+      <c r="F44" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="G44" t="n">
+        <v>126.67</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-5.17</v>
+      </c>
+      <c r="I44" t="n">
+        <v>119.42</v>
+      </c>
+      <c r="J44" t="n">
+        <v>118.87</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>5.02</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -43316,31 +43316,31 @@
         </is>
       </c>
       <c r="C825" t="n">
-        <v>1335.4</v>
+        <v>1310</v>
       </c>
       <c r="D825" t="n">
         <v>1459.51</v>
       </c>
       <c r="E825" t="n">
-        <v>-124.11</v>
+        <v>-149.51</v>
       </c>
       <c r="F825" t="n">
-        <v>1338.2</v>
+        <v>1323.7</v>
       </c>
       <c r="G825" t="n">
         <v>1459.51</v>
       </c>
       <c r="H825" t="n">
-        <v>-121.31</v>
+        <v>-135.81</v>
       </c>
       <c r="I825" t="n">
-        <v>1301</v>
+        <v>1299.4</v>
       </c>
       <c r="J825" t="n">
         <v>1305.41</v>
       </c>
       <c r="K825" t="n">
-        <v>-4.41</v>
+        <v>-6.01</v>
       </c>
       <c r="L825" t="inlineStr">
         <is>
@@ -43353,7 +43353,7 @@
         </is>
       </c>
       <c r="N825" t="n">
-        <v>8.5</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="826">
@@ -43368,31 +43368,31 @@
         </is>
       </c>
       <c r="C826" t="n">
-        <v>120.31</v>
+        <v>121.27</v>
       </c>
       <c r="D826" t="n">
         <v>126.67</v>
       </c>
       <c r="E826" t="n">
-        <v>-6.36</v>
+        <v>-5.4</v>
       </c>
       <c r="F826" t="n">
-        <v>121.5</v>
+        <v>122.34</v>
       </c>
       <c r="G826" t="n">
         <v>126.67</v>
       </c>
       <c r="H826" t="n">
-        <v>-5.17</v>
+        <v>-4.33</v>
       </c>
       <c r="I826" t="n">
-        <v>119.42</v>
+        <v>120.2</v>
       </c>
       <c r="J826" t="n">
         <v>118.87</v>
       </c>
       <c r="K826" t="n">
-        <v>0.55</v>
+        <v>1.33</v>
       </c>
       <c r="L826" t="inlineStr">
         <is>
@@ -43405,7 +43405,7 @@
         </is>
       </c>
       <c r="N826" t="n">
-        <v>5.02</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="827">
@@ -43420,31 +43420,31 @@
         </is>
       </c>
       <c r="C827" t="n">
-        <v>666.3</v>
+        <v>671</v>
       </c>
       <c r="D827" t="n">
         <v>700.14</v>
       </c>
       <c r="E827" t="n">
-        <v>-33.84</v>
+        <v>-29.14</v>
       </c>
       <c r="F827" t="n">
-        <v>671.4</v>
+        <v>673</v>
       </c>
       <c r="G827" t="n">
         <v>700.14</v>
       </c>
       <c r="H827" t="n">
-        <v>-28.74</v>
+        <v>-27.14</v>
       </c>
       <c r="I827" t="n">
-        <v>663.95</v>
+        <v>659</v>
       </c>
       <c r="J827" t="n">
         <v>647.64</v>
       </c>
       <c r="K827" t="n">
-        <v>16.31</v>
+        <v>11.36</v>
       </c>
       <c r="L827" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         </is>
       </c>
       <c r="N827" t="n">
-        <v>4.83</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="828">
@@ -43472,31 +43472,31 @@
         </is>
       </c>
       <c r="C828" t="n">
-        <v>5848</v>
+        <v>5832.5</v>
       </c>
       <c r="D828" t="n">
         <v>6182.15</v>
       </c>
       <c r="E828" t="n">
-        <v>-334.15</v>
+        <v>-349.65</v>
       </c>
       <c r="F828" t="n">
-        <v>5872.5</v>
+        <v>5861</v>
       </c>
       <c r="G828" t="n">
         <v>6182.15</v>
       </c>
       <c r="H828" t="n">
-        <v>-309.65</v>
+        <v>-321.15</v>
       </c>
       <c r="I828" t="n">
-        <v>5650</v>
+        <v>5690</v>
       </c>
       <c r="J828" t="n">
         <v>5614.44</v>
       </c>
       <c r="K828" t="n">
-        <v>35.56</v>
+        <v>75.56</v>
       </c>
       <c r="L828" t="inlineStr">
         <is>
@@ -43509,7 +43509,7 @@
         </is>
       </c>
       <c r="N828" t="n">
-        <v>5.41</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="829">
@@ -43524,31 +43524,31 @@
         </is>
       </c>
       <c r="C829" t="n">
-        <v>2165.3</v>
+        <v>2213.9</v>
       </c>
       <c r="D829" t="n">
         <v>2135.52</v>
       </c>
       <c r="E829" t="n">
-        <v>29.78</v>
+        <v>78.38</v>
       </c>
       <c r="F829" t="n">
-        <v>2219</v>
+        <v>2213.9</v>
       </c>
       <c r="G829" t="n">
         <v>2135.52</v>
       </c>
       <c r="H829" t="n">
-        <v>83.48</v>
+        <v>78.38</v>
       </c>
       <c r="I829" t="n">
-        <v>2156.3</v>
+        <v>2100</v>
       </c>
       <c r="J829" t="n">
         <v>2089.74</v>
       </c>
       <c r="K829" t="n">
-        <v>66.56</v>
+        <v>10.26</v>
       </c>
       <c r="L829" t="inlineStr">
         <is>
@@ -43557,11 +43557,11 @@
       </c>
       <c r="M829" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N829" t="n">
-        <v>1.39</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="830">
@@ -43576,31 +43576,31 @@
         </is>
       </c>
       <c r="C830" t="n">
-        <v>1961.9</v>
+        <v>1997</v>
       </c>
       <c r="D830" t="n">
         <v>2103.32</v>
       </c>
       <c r="E830" t="n">
-        <v>-141.42</v>
+        <v>-106.32</v>
       </c>
       <c r="F830" t="n">
-        <v>1977.8</v>
+        <v>2008.8</v>
       </c>
       <c r="G830" t="n">
         <v>2103.32</v>
       </c>
       <c r="H830" t="n">
-        <v>-125.52</v>
+        <v>-94.52</v>
       </c>
       <c r="I830" t="n">
-        <v>1903.8</v>
+        <v>1953</v>
       </c>
       <c r="J830" t="n">
         <v>1887.63</v>
       </c>
       <c r="K830" t="n">
-        <v>16.17</v>
+        <v>65.37</v>
       </c>
       <c r="L830" t="inlineStr">
         <is>
@@ -43613,7 +43613,7 @@
         </is>
       </c>
       <c r="N830" t="n">
-        <v>6.72</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="831">
@@ -43628,31 +43628,31 @@
         </is>
       </c>
       <c r="C831" t="n">
-        <v>1400.5</v>
+        <v>1420</v>
       </c>
       <c r="D831" t="n">
         <v>1426.37</v>
       </c>
       <c r="E831" t="n">
-        <v>-25.87</v>
+        <v>-6.37</v>
       </c>
       <c r="F831" t="n">
-        <v>1401.4</v>
+        <v>1420</v>
       </c>
       <c r="G831" t="n">
         <v>1427.07</v>
       </c>
       <c r="H831" t="n">
-        <v>-25.67</v>
+        <v>-7.07</v>
       </c>
       <c r="I831" t="n">
-        <v>1364</v>
+        <v>1391</v>
       </c>
       <c r="J831" t="n">
         <v>1363.3</v>
       </c>
       <c r="K831" t="n">
-        <v>0.7</v>
+        <v>27.7</v>
       </c>
       <c r="L831" t="inlineStr">
         <is>
@@ -43665,7 +43665,7 @@
         </is>
       </c>
       <c r="N831" t="n">
-        <v>1.81</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="832">
@@ -43680,31 +43680,31 @@
         </is>
       </c>
       <c r="C832" t="n">
-        <v>2518</v>
+        <v>2618.4</v>
       </c>
       <c r="D832" t="n">
         <v>2767.08</v>
       </c>
       <c r="E832" t="n">
-        <v>-249.08</v>
+        <v>-148.68</v>
       </c>
       <c r="F832" t="n">
-        <v>2563.9</v>
+        <v>2618.4</v>
       </c>
       <c r="G832" t="n">
         <v>2767.08</v>
       </c>
       <c r="H832" t="n">
-        <v>-203.18</v>
+        <v>-148.68</v>
       </c>
       <c r="I832" t="n">
-        <v>2455.2</v>
+        <v>2498.7</v>
       </c>
       <c r="J832" t="n">
         <v>2417.66</v>
       </c>
       <c r="K832" t="n">
-        <v>37.54</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="L832" t="inlineStr">
         <is>
@@ -43717,7 +43717,7 @@
         </is>
       </c>
       <c r="N832" t="n">
-        <v>9</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="833">
@@ -43732,31 +43732,31 @@
         </is>
       </c>
       <c r="C833" t="n">
-        <v>2460</v>
+        <v>2496.9</v>
       </c>
       <c r="D833" t="n">
         <v>2550.72</v>
       </c>
       <c r="E833" t="n">
-        <v>-90.72</v>
+        <v>-53.82</v>
       </c>
       <c r="F833" t="n">
-        <v>2461.3</v>
+        <v>2534.9</v>
       </c>
       <c r="G833" t="n">
         <v>2550.72</v>
       </c>
       <c r="H833" t="n">
-        <v>-89.42</v>
+        <v>-15.82</v>
       </c>
       <c r="I833" t="n">
-        <v>2408.2</v>
+        <v>2465.4</v>
       </c>
       <c r="J833" t="n">
         <v>2362.5</v>
       </c>
       <c r="K833" t="n">
-        <v>45.7</v>
+        <v>102.9</v>
       </c>
       <c r="L833" t="inlineStr">
         <is>
@@ -43769,7 +43769,7 @@
         </is>
       </c>
       <c r="N833" t="n">
-        <v>3.56</v>
+        <v>2.11</v>
       </c>
     </row>
   </sheetData>
@@ -52306,31 +52306,31 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1961.9</v>
+        <v>1997</v>
       </c>
       <c r="D21" t="n">
         <v>2103.32</v>
       </c>
       <c r="E21" t="n">
-        <v>-141.42</v>
+        <v>-106.32</v>
       </c>
       <c r="F21" t="n">
-        <v>1977.8</v>
+        <v>2008.8</v>
       </c>
       <c r="G21" t="n">
         <v>2103.32</v>
       </c>
       <c r="H21" t="n">
-        <v>-125.52</v>
+        <v>-94.52</v>
       </c>
       <c r="I21" t="n">
-        <v>1903.8</v>
+        <v>1953</v>
       </c>
       <c r="J21" t="n">
         <v>1887.63</v>
       </c>
       <c r="K21" t="n">
-        <v>16.17</v>
+        <v>65.37</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -52343,7 +52343,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>6.72</v>
+        <v>5.05</v>
       </c>
     </row>
   </sheetData>
@@ -54004,31 +54004,31 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5848</v>
+        <v>5832.5</v>
       </c>
       <c r="D32" t="n">
         <v>6182.15</v>
       </c>
       <c r="E32" t="n">
-        <v>-334.15</v>
+        <v>-349.65</v>
       </c>
       <c r="F32" t="n">
-        <v>5872.5</v>
+        <v>5861</v>
       </c>
       <c r="G32" t="n">
         <v>6182.15</v>
       </c>
       <c r="H32" t="n">
-        <v>-309.65</v>
+        <v>-321.15</v>
       </c>
       <c r="I32" t="n">
-        <v>5650</v>
+        <v>5690</v>
       </c>
       <c r="J32" t="n">
         <v>5614.44</v>
       </c>
       <c r="K32" t="n">
-        <v>35.56</v>
+        <v>75.56</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -54041,7 +54041,7 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>5.41</v>
+        <v>5.66</v>
       </c>
     </row>
   </sheetData>
@@ -56326,31 +56326,31 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>120.31</v>
+        <v>121.27</v>
       </c>
       <c r="D44" t="n">
         <v>126.67</v>
       </c>
       <c r="E44" t="n">
-        <v>-6.36</v>
+        <v>-5.4</v>
       </c>
       <c r="F44" t="n">
-        <v>121.5</v>
+        <v>122.34</v>
       </c>
       <c r="G44" t="n">
         <v>126.67</v>
       </c>
       <c r="H44" t="n">
-        <v>-5.17</v>
+        <v>-4.33</v>
       </c>
       <c r="I44" t="n">
-        <v>119.42</v>
+        <v>120.2</v>
       </c>
       <c r="J44" t="n">
         <v>118.87</v>
       </c>
       <c r="K44" t="n">
-        <v>0.55</v>
+        <v>1.33</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -56363,7 +56363,7 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>5.02</v>
+        <v>4.26</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N833"/>
+  <dimension ref="A1:N842"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43770,6 +43770,474 @@
       </c>
       <c r="N833" t="n">
         <v>2.11</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C834" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="D834" t="n">
+        <v>119.72</v>
+      </c>
+      <c r="E834" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="F834" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="G834" t="n">
+        <v>123.39</v>
+      </c>
+      <c r="H834" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="I834" t="n">
+        <v>119.62</v>
+      </c>
+      <c r="J834" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="K834" t="n">
+        <v>-4.28</v>
+      </c>
+      <c r="L834" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M834" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N834" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C835" t="n">
+        <v>694.35</v>
+      </c>
+      <c r="D835" t="n">
+        <v>670.77</v>
+      </c>
+      <c r="E835" t="n">
+        <v>23.58</v>
+      </c>
+      <c r="F835" t="n">
+        <v>696</v>
+      </c>
+      <c r="G835" t="n">
+        <v>686.61</v>
+      </c>
+      <c r="H835" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="I835" t="n">
+        <v>665</v>
+      </c>
+      <c r="J835" t="n">
+        <v>694.35</v>
+      </c>
+      <c r="K835" t="n">
+        <v>-29.35</v>
+      </c>
+      <c r="L835" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M835" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N835" t="n">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="C836" t="n">
+        <v>1403.9</v>
+      </c>
+      <c r="D836" t="n">
+        <v>1408.8</v>
+      </c>
+      <c r="E836" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="F836" t="n">
+        <v>1421.9</v>
+      </c>
+      <c r="G836" t="n">
+        <v>1408.8</v>
+      </c>
+      <c r="H836" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="I836" t="n">
+        <v>1391.1</v>
+      </c>
+      <c r="J836" t="n">
+        <v>1368.32</v>
+      </c>
+      <c r="K836" t="n">
+        <v>22.78</v>
+      </c>
+      <c r="L836" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M836" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N836" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="C837" t="n">
+        <v>1345</v>
+      </c>
+      <c r="D837" t="n">
+        <v>1216.88</v>
+      </c>
+      <c r="E837" t="n">
+        <v>128.12</v>
+      </c>
+      <c r="F837" t="n">
+        <v>1352.8</v>
+      </c>
+      <c r="G837" t="n">
+        <v>1306.39</v>
+      </c>
+      <c r="H837" t="n">
+        <v>46.41</v>
+      </c>
+      <c r="I837" t="n">
+        <v>1336.1</v>
+      </c>
+      <c r="J837" t="n">
+        <v>1321.6</v>
+      </c>
+      <c r="K837" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="L837" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M837" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N837" t="n">
+        <v>10.53</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C838" t="n">
+        <v>1962</v>
+      </c>
+      <c r="D838" t="n">
+        <v>1877.73</v>
+      </c>
+      <c r="E838" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="F838" t="n">
+        <v>1978.5</v>
+      </c>
+      <c r="G838" t="n">
+        <v>1924.25</v>
+      </c>
+      <c r="H838" t="n">
+        <v>54.25</v>
+      </c>
+      <c r="I838" t="n">
+        <v>1939</v>
+      </c>
+      <c r="J838" t="n">
+        <v>1945.66</v>
+      </c>
+      <c r="K838" t="n">
+        <v>-6.66</v>
+      </c>
+      <c r="L838" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M838" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N838" t="n">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C839" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D839" t="n">
+        <v>5591.81</v>
+      </c>
+      <c r="E839" t="n">
+        <v>288.19</v>
+      </c>
+      <c r="F839" t="n">
+        <v>5905.5</v>
+      </c>
+      <c r="G839" t="n">
+        <v>5749.84</v>
+      </c>
+      <c r="H839" t="n">
+        <v>155.66</v>
+      </c>
+      <c r="I839" t="n">
+        <v>5800</v>
+      </c>
+      <c r="J839" t="n">
+        <v>5813.2</v>
+      </c>
+      <c r="K839" t="n">
+        <v>-13.2</v>
+      </c>
+      <c r="L839" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M839" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N839" t="n">
+        <v>5.15</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C840" t="n">
+        <v>2195</v>
+      </c>
+      <c r="D840" t="n">
+        <v>2293.76</v>
+      </c>
+      <c r="E840" t="n">
+        <v>-98.76000000000001</v>
+      </c>
+      <c r="F840" t="n">
+        <v>2239</v>
+      </c>
+      <c r="G840" t="n">
+        <v>2293.76</v>
+      </c>
+      <c r="H840" t="n">
+        <v>-54.76</v>
+      </c>
+      <c r="I840" t="n">
+        <v>2158.9</v>
+      </c>
+      <c r="J840" t="n">
+        <v>2152.56</v>
+      </c>
+      <c r="K840" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="L840" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M840" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N840" t="n">
+        <v>4.31</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C841" t="n">
+        <v>2561.3</v>
+      </c>
+      <c r="D841" t="n">
+        <v>2443.07</v>
+      </c>
+      <c r="E841" t="n">
+        <v>118.23</v>
+      </c>
+      <c r="F841" t="n">
+        <v>2562</v>
+      </c>
+      <c r="G841" t="n">
+        <v>2443.07</v>
+      </c>
+      <c r="H841" t="n">
+        <v>118.93</v>
+      </c>
+      <c r="I841" t="n">
+        <v>2501.7</v>
+      </c>
+      <c r="J841" t="n">
+        <v>2478.79</v>
+      </c>
+      <c r="K841" t="n">
+        <v>22.91</v>
+      </c>
+      <c r="L841" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M841" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N841" t="n">
+        <v>4.84</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="C842" t="n">
+        <v>2478</v>
+      </c>
+      <c r="D842" t="n">
+        <v>2445.12</v>
+      </c>
+      <c r="E842" t="n">
+        <v>32.88</v>
+      </c>
+      <c r="F842" t="n">
+        <v>2509.5</v>
+      </c>
+      <c r="G842" t="n">
+        <v>2445.12</v>
+      </c>
+      <c r="H842" t="n">
+        <v>64.38</v>
+      </c>
+      <c r="I842" t="n">
+        <v>2464</v>
+      </c>
+      <c r="J842" t="n">
+        <v>2402.59</v>
+      </c>
+      <c r="K842" t="n">
+        <v>61.41</v>
+      </c>
+      <c r="L842" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M842" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N842" t="n">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>
@@ -51231,7 +51699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52344,6 +52812,58 @@
       </c>
       <c r="N21" t="n">
         <v>5.05</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1962</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1877.73</v>
+      </c>
+      <c r="E22" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1978.5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1924.25</v>
+      </c>
+      <c r="H22" t="n">
+        <v>54.25</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1939</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1945.66</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-6.66</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>4.49</v>
       </c>
     </row>
   </sheetData>
@@ -52357,7 +52877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54042,6 +54562,58 @@
       </c>
       <c r="N32" t="n">
         <v>5.66</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D33" t="n">
+        <v>5591.81</v>
+      </c>
+      <c r="E33" t="n">
+        <v>288.19</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5905.5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5749.84</v>
+      </c>
+      <c r="H33" t="n">
+        <v>155.66</v>
+      </c>
+      <c r="I33" t="n">
+        <v>5800</v>
+      </c>
+      <c r="J33" t="n">
+        <v>5813.2</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-13.2</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>5.15</v>
       </c>
     </row>
   </sheetData>
@@ -54055,7 +54627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56364,6 +56936,58 @@
       </c>
       <c r="N44" t="n">
         <v>4.26</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="D45" t="n">
+        <v>119.72</v>
+      </c>
+      <c r="E45" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="F45" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="G45" t="n">
+        <v>123.39</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="I45" t="n">
+        <v>119.62</v>
+      </c>
+      <c r="J45" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-4.28</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>3.49</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -43784,31 +43784,31 @@
         </is>
       </c>
       <c r="C834" t="n">
-        <v>123.9</v>
+        <v>120.31</v>
       </c>
       <c r="D834" t="n">
         <v>119.72</v>
       </c>
       <c r="E834" t="n">
-        <v>4.18</v>
+        <v>0.59</v>
       </c>
       <c r="F834" t="n">
-        <v>123.9</v>
+        <v>121.5</v>
       </c>
       <c r="G834" t="n">
         <v>123.39</v>
       </c>
       <c r="H834" t="n">
-        <v>0.51</v>
+        <v>-1.89</v>
       </c>
       <c r="I834" t="n">
-        <v>119.62</v>
+        <v>119.42</v>
       </c>
       <c r="J834" t="n">
         <v>123.9</v>
       </c>
       <c r="K834" t="n">
-        <v>-4.28</v>
+        <v>-4.48</v>
       </c>
       <c r="L834" t="inlineStr">
         <is>
@@ -43817,11 +43817,11 @@
       </c>
       <c r="M834" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N834" t="n">
-        <v>3.49</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="835">
@@ -43836,31 +43836,31 @@
         </is>
       </c>
       <c r="C835" t="n">
-        <v>694.35</v>
+        <v>666.3</v>
       </c>
       <c r="D835" t="n">
         <v>670.77</v>
       </c>
       <c r="E835" t="n">
-        <v>23.58</v>
+        <v>-4.47</v>
       </c>
       <c r="F835" t="n">
-        <v>696</v>
+        <v>671.4</v>
       </c>
       <c r="G835" t="n">
         <v>686.61</v>
       </c>
       <c r="H835" t="n">
-        <v>9.390000000000001</v>
+        <v>-15.21</v>
       </c>
       <c r="I835" t="n">
-        <v>665</v>
+        <v>663.95</v>
       </c>
       <c r="J835" t="n">
         <v>694.35</v>
       </c>
       <c r="K835" t="n">
-        <v>-29.35</v>
+        <v>-30.4</v>
       </c>
       <c r="L835" t="inlineStr">
         <is>
@@ -43869,11 +43869,11 @@
       </c>
       <c r="M835" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N835" t="n">
-        <v>3.52</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="836">
@@ -43888,31 +43888,31 @@
         </is>
       </c>
       <c r="C836" t="n">
-        <v>1403.9</v>
+        <v>1400.5</v>
       </c>
       <c r="D836" t="n">
         <v>1408.8</v>
       </c>
       <c r="E836" t="n">
-        <v>-4.9</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="F836" t="n">
-        <v>1421.9</v>
+        <v>1401.4</v>
       </c>
       <c r="G836" t="n">
         <v>1408.8</v>
       </c>
       <c r="H836" t="n">
-        <v>13.1</v>
+        <v>-7.4</v>
       </c>
       <c r="I836" t="n">
-        <v>1391.1</v>
+        <v>1364</v>
       </c>
       <c r="J836" t="n">
         <v>1368.32</v>
       </c>
       <c r="K836" t="n">
-        <v>22.78</v>
+        <v>-4.32</v>
       </c>
       <c r="L836" t="inlineStr">
         <is>
@@ -43925,7 +43925,7 @@
         </is>
       </c>
       <c r="N836" t="n">
-        <v>0.35</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="837">
@@ -43940,31 +43940,31 @@
         </is>
       </c>
       <c r="C837" t="n">
-        <v>1345</v>
+        <v>1335.4</v>
       </c>
       <c r="D837" t="n">
         <v>1216.88</v>
       </c>
       <c r="E837" t="n">
-        <v>128.12</v>
+        <v>118.52</v>
       </c>
       <c r="F837" t="n">
-        <v>1352.8</v>
+        <v>1338.2</v>
       </c>
       <c r="G837" t="n">
         <v>1306.39</v>
       </c>
       <c r="H837" t="n">
-        <v>46.41</v>
+        <v>31.81</v>
       </c>
       <c r="I837" t="n">
-        <v>1336.1</v>
+        <v>1301</v>
       </c>
       <c r="J837" t="n">
         <v>1321.6</v>
       </c>
       <c r="K837" t="n">
-        <v>14.5</v>
+        <v>-20.6</v>
       </c>
       <c r="L837" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         </is>
       </c>
       <c r="N837" t="n">
-        <v>10.53</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="838">
@@ -43992,31 +43992,31 @@
         </is>
       </c>
       <c r="C838" t="n">
-        <v>1962</v>
+        <v>1961.9</v>
       </c>
       <c r="D838" t="n">
         <v>1877.73</v>
       </c>
       <c r="E838" t="n">
-        <v>84.27</v>
+        <v>84.17</v>
       </c>
       <c r="F838" t="n">
-        <v>1978.5</v>
+        <v>1977.8</v>
       </c>
       <c r="G838" t="n">
         <v>1924.25</v>
       </c>
       <c r="H838" t="n">
-        <v>54.25</v>
+        <v>53.55</v>
       </c>
       <c r="I838" t="n">
-        <v>1939</v>
+        <v>1903.8</v>
       </c>
       <c r="J838" t="n">
         <v>1945.66</v>
       </c>
       <c r="K838" t="n">
-        <v>-6.66</v>
+        <v>-41.86</v>
       </c>
       <c r="L838" t="inlineStr">
         <is>
@@ -44029,7 +44029,7 @@
         </is>
       </c>
       <c r="N838" t="n">
-        <v>4.49</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="839">
@@ -44044,31 +44044,31 @@
         </is>
       </c>
       <c r="C839" t="n">
-        <v>5880</v>
+        <v>5848</v>
       </c>
       <c r="D839" t="n">
         <v>5591.81</v>
       </c>
       <c r="E839" t="n">
-        <v>288.19</v>
+        <v>256.19</v>
       </c>
       <c r="F839" t="n">
-        <v>5905.5</v>
+        <v>5872.5</v>
       </c>
       <c r="G839" t="n">
         <v>5749.84</v>
       </c>
       <c r="H839" t="n">
-        <v>155.66</v>
+        <v>122.66</v>
       </c>
       <c r="I839" t="n">
-        <v>5800</v>
+        <v>5650</v>
       </c>
       <c r="J839" t="n">
         <v>5813.2</v>
       </c>
       <c r="K839" t="n">
-        <v>-13.2</v>
+        <v>-163.2</v>
       </c>
       <c r="L839" t="inlineStr">
         <is>
@@ -44081,7 +44081,7 @@
         </is>
       </c>
       <c r="N839" t="n">
-        <v>5.15</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="840">
@@ -44096,31 +44096,31 @@
         </is>
       </c>
       <c r="C840" t="n">
-        <v>2195</v>
+        <v>2165.3</v>
       </c>
       <c r="D840" t="n">
         <v>2293.76</v>
       </c>
       <c r="E840" t="n">
-        <v>-98.76000000000001</v>
+        <v>-128.46</v>
       </c>
       <c r="F840" t="n">
-        <v>2239</v>
+        <v>2219</v>
       </c>
       <c r="G840" t="n">
         <v>2293.76</v>
       </c>
       <c r="H840" t="n">
-        <v>-54.76</v>
+        <v>-74.76000000000001</v>
       </c>
       <c r="I840" t="n">
-        <v>2158.9</v>
+        <v>2156.3</v>
       </c>
       <c r="J840" t="n">
         <v>2152.56</v>
       </c>
       <c r="K840" t="n">
-        <v>6.34</v>
+        <v>3.74</v>
       </c>
       <c r="L840" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         </is>
       </c>
       <c r="N840" t="n">
-        <v>4.31</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="841">
@@ -44148,31 +44148,31 @@
         </is>
       </c>
       <c r="C841" t="n">
-        <v>2561.3</v>
+        <v>2518</v>
       </c>
       <c r="D841" t="n">
         <v>2443.07</v>
       </c>
       <c r="E841" t="n">
-        <v>118.23</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="F841" t="n">
-        <v>2562</v>
+        <v>2563.9</v>
       </c>
       <c r="G841" t="n">
         <v>2443.07</v>
       </c>
       <c r="H841" t="n">
-        <v>118.93</v>
+        <v>120.83</v>
       </c>
       <c r="I841" t="n">
-        <v>2501.7</v>
+        <v>2455.2</v>
       </c>
       <c r="J841" t="n">
         <v>2478.79</v>
       </c>
       <c r="K841" t="n">
-        <v>22.91</v>
+        <v>-23.59</v>
       </c>
       <c r="L841" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         </is>
       </c>
       <c r="N841" t="n">
-        <v>4.84</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="842">
@@ -44200,31 +44200,31 @@
         </is>
       </c>
       <c r="C842" t="n">
-        <v>2478</v>
+        <v>2460</v>
       </c>
       <c r="D842" t="n">
         <v>2445.12</v>
       </c>
       <c r="E842" t="n">
-        <v>32.88</v>
+        <v>14.88</v>
       </c>
       <c r="F842" t="n">
-        <v>2509.5</v>
+        <v>2461.3</v>
       </c>
       <c r="G842" t="n">
         <v>2445.12</v>
       </c>
       <c r="H842" t="n">
-        <v>64.38</v>
+        <v>16.18</v>
       </c>
       <c r="I842" t="n">
-        <v>2464</v>
+        <v>2408.2</v>
       </c>
       <c r="J842" t="n">
         <v>2402.59</v>
       </c>
       <c r="K842" t="n">
-        <v>61.41</v>
+        <v>5.61</v>
       </c>
       <c r="L842" t="inlineStr">
         <is>
@@ -44237,7 +44237,7 @@
         </is>
       </c>
       <c r="N842" t="n">
-        <v>1.34</v>
+        <v>0.61</v>
       </c>
     </row>
   </sheetData>
@@ -52826,31 +52826,31 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1962</v>
+        <v>1961.9</v>
       </c>
       <c r="D22" t="n">
         <v>1877.73</v>
       </c>
       <c r="E22" t="n">
-        <v>84.27</v>
+        <v>84.17</v>
       </c>
       <c r="F22" t="n">
-        <v>1978.5</v>
+        <v>1977.8</v>
       </c>
       <c r="G22" t="n">
         <v>1924.25</v>
       </c>
       <c r="H22" t="n">
-        <v>54.25</v>
+        <v>53.55</v>
       </c>
       <c r="I22" t="n">
-        <v>1939</v>
+        <v>1903.8</v>
       </c>
       <c r="J22" t="n">
         <v>1945.66</v>
       </c>
       <c r="K22" t="n">
-        <v>-6.66</v>
+        <v>-41.86</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -52863,7 +52863,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4.49</v>
+        <v>4.48</v>
       </c>
     </row>
   </sheetData>
@@ -54576,31 +54576,31 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5880</v>
+        <v>5848</v>
       </c>
       <c r="D33" t="n">
         <v>5591.81</v>
       </c>
       <c r="E33" t="n">
-        <v>288.19</v>
+        <v>256.19</v>
       </c>
       <c r="F33" t="n">
-        <v>5905.5</v>
+        <v>5872.5</v>
       </c>
       <c r="G33" t="n">
         <v>5749.84</v>
       </c>
       <c r="H33" t="n">
-        <v>155.66</v>
+        <v>122.66</v>
       </c>
       <c r="I33" t="n">
-        <v>5800</v>
+        <v>5650</v>
       </c>
       <c r="J33" t="n">
         <v>5813.2</v>
       </c>
       <c r="K33" t="n">
-        <v>-13.2</v>
+        <v>-163.2</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -54613,7 +54613,7 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>5.15</v>
+        <v>4.58</v>
       </c>
     </row>
   </sheetData>
@@ -56950,31 +56950,31 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>123.9</v>
+        <v>120.31</v>
       </c>
       <c r="D45" t="n">
         <v>119.72</v>
       </c>
       <c r="E45" t="n">
-        <v>4.18</v>
+        <v>0.59</v>
       </c>
       <c r="F45" t="n">
-        <v>123.9</v>
+        <v>121.5</v>
       </c>
       <c r="G45" t="n">
         <v>123.39</v>
       </c>
       <c r="H45" t="n">
-        <v>0.51</v>
+        <v>-1.89</v>
       </c>
       <c r="I45" t="n">
-        <v>119.62</v>
+        <v>119.42</v>
       </c>
       <c r="J45" t="n">
         <v>123.9</v>
       </c>
       <c r="K45" t="n">
-        <v>-4.28</v>
+        <v>-4.48</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -56983,11 +56983,11 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>3.49</v>
+        <v>0.49</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N842"/>
+  <dimension ref="A1:N851"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44238,6 +44238,474 @@
       </c>
       <c r="N842" t="n">
         <v>0.61</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="C843" t="n">
+        <v>1352</v>
+      </c>
+      <c r="D843" t="n">
+        <v>1495.56</v>
+      </c>
+      <c r="E843" t="n">
+        <v>-143.56</v>
+      </c>
+      <c r="F843" t="n">
+        <v>1363.7</v>
+      </c>
+      <c r="G843" t="n">
+        <v>1495.56</v>
+      </c>
+      <c r="H843" t="n">
+        <v>-131.86</v>
+      </c>
+      <c r="I843" t="n">
+        <v>1345</v>
+      </c>
+      <c r="J843" t="n">
+        <v>1294.83</v>
+      </c>
+      <c r="K843" t="n">
+        <v>50.17</v>
+      </c>
+      <c r="L843" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="M843" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N843" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C844" t="n">
+        <v>186</v>
+      </c>
+      <c r="D844" t="n">
+        <v>188.55</v>
+      </c>
+      <c r="E844" t="n">
+        <v>-2.55</v>
+      </c>
+      <c r="F844" t="n">
+        <v>187.74</v>
+      </c>
+      <c r="G844" t="n">
+        <v>189.84</v>
+      </c>
+      <c r="H844" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="I844" t="n">
+        <v>184.82</v>
+      </c>
+      <c r="J844" t="n">
+        <v>181.02</v>
+      </c>
+      <c r="K844" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L844" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M844" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N844" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="C845" t="n">
+        <v>1428.1</v>
+      </c>
+      <c r="D845" t="n">
+        <v>1431.04</v>
+      </c>
+      <c r="E845" t="n">
+        <v>-2.94</v>
+      </c>
+      <c r="F845" t="n">
+        <v>1452</v>
+      </c>
+      <c r="G845" t="n">
+        <v>1431.04</v>
+      </c>
+      <c r="H845" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="I845" t="n">
+        <v>1410</v>
+      </c>
+      <c r="J845" t="n">
+        <v>1355.96</v>
+      </c>
+      <c r="K845" t="n">
+        <v>54.04</v>
+      </c>
+      <c r="L845" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M845" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N845" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C846" t="n">
+        <v>691.55</v>
+      </c>
+      <c r="D846" t="n">
+        <v>692.4400000000001</v>
+      </c>
+      <c r="E846" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="F846" t="n">
+        <v>699.6</v>
+      </c>
+      <c r="G846" t="n">
+        <v>692.4400000000001</v>
+      </c>
+      <c r="H846" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="I846" t="n">
+        <v>686.5</v>
+      </c>
+      <c r="J846" t="n">
+        <v>662.24</v>
+      </c>
+      <c r="K846" t="n">
+        <v>24.26</v>
+      </c>
+      <c r="L846" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M846" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N846" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C847" t="n">
+        <v>122.85</v>
+      </c>
+      <c r="D847" t="n">
+        <v>124.44</v>
+      </c>
+      <c r="E847" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="F847" t="n">
+        <v>125.09</v>
+      </c>
+      <c r="G847" t="n">
+        <v>124.88</v>
+      </c>
+      <c r="H847" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I847" t="n">
+        <v>122.48</v>
+      </c>
+      <c r="J847" t="n">
+        <v>119.06</v>
+      </c>
+      <c r="K847" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="L847" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M847" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N847" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C848" t="n">
+        <v>6048</v>
+      </c>
+      <c r="D848" t="n">
+        <v>6375.72</v>
+      </c>
+      <c r="E848" t="n">
+        <v>-327.72</v>
+      </c>
+      <c r="F848" t="n">
+        <v>6048.5</v>
+      </c>
+      <c r="G848" t="n">
+        <v>6375.72</v>
+      </c>
+      <c r="H848" t="n">
+        <v>-327.22</v>
+      </c>
+      <c r="I848" t="n">
+        <v>5884</v>
+      </c>
+      <c r="J848" t="n">
+        <v>5900.42</v>
+      </c>
+      <c r="K848" t="n">
+        <v>-16.42</v>
+      </c>
+      <c r="L848" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M848" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N848" t="n">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="C849" t="n">
+        <v>2502.6</v>
+      </c>
+      <c r="D849" t="n">
+        <v>2537.98</v>
+      </c>
+      <c r="E849" t="n">
+        <v>-35.38</v>
+      </c>
+      <c r="F849" t="n">
+        <v>2527.7</v>
+      </c>
+      <c r="G849" t="n">
+        <v>2537.98</v>
+      </c>
+      <c r="H849" t="n">
+        <v>-10.28</v>
+      </c>
+      <c r="I849" t="n">
+        <v>2494.2</v>
+      </c>
+      <c r="J849" t="n">
+        <v>2365.36</v>
+      </c>
+      <c r="K849" t="n">
+        <v>128.84</v>
+      </c>
+      <c r="L849" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M849" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N849" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C850" t="n">
+        <v>2525.6</v>
+      </c>
+      <c r="D850" t="n">
+        <v>2623.88</v>
+      </c>
+      <c r="E850" t="n">
+        <v>-98.28</v>
+      </c>
+      <c r="F850" t="n">
+        <v>2591.3</v>
+      </c>
+      <c r="G850" t="n">
+        <v>2623.88</v>
+      </c>
+      <c r="H850" t="n">
+        <v>-32.58</v>
+      </c>
+      <c r="I850" t="n">
+        <v>2516.6</v>
+      </c>
+      <c r="J850" t="n">
+        <v>2378.75</v>
+      </c>
+      <c r="K850" t="n">
+        <v>137.85</v>
+      </c>
+      <c r="L850" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M850" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N850" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C851" t="n">
+        <v>2165.1</v>
+      </c>
+      <c r="D851" t="n">
+        <v>2060.2</v>
+      </c>
+      <c r="E851" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="F851" t="n">
+        <v>2215.8</v>
+      </c>
+      <c r="G851" t="n">
+        <v>2197.59</v>
+      </c>
+      <c r="H851" t="n">
+        <v>18.21</v>
+      </c>
+      <c r="I851" t="n">
+        <v>2165.1</v>
+      </c>
+      <c r="J851" t="n">
+        <v>2095.04</v>
+      </c>
+      <c r="K851" t="n">
+        <v>70.06</v>
+      </c>
+      <c r="L851" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M851" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N851" t="n">
+        <v>5.09</v>
       </c>
     </row>
   </sheetData>
@@ -52877,7 +53345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54614,6 +55082,58 @@
       </c>
       <c r="N33" t="n">
         <v>4.58</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>6048</v>
+      </c>
+      <c r="D34" t="n">
+        <v>6375.72</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-327.72</v>
+      </c>
+      <c r="F34" t="n">
+        <v>6048.5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>6375.72</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-327.22</v>
+      </c>
+      <c r="I34" t="n">
+        <v>5884</v>
+      </c>
+      <c r="J34" t="n">
+        <v>5900.42</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-16.42</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>5.14</v>
       </c>
     </row>
   </sheetData>
@@ -54627,7 +55147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56988,6 +57508,58 @@
       </c>
       <c r="N45" t="n">
         <v>0.49</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>122.85</v>
+      </c>
+      <c r="D46" t="n">
+        <v>124.44</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="F46" t="n">
+        <v>125.09</v>
+      </c>
+      <c r="G46" t="n">
+        <v>124.88</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I46" t="n">
+        <v>122.48</v>
+      </c>
+      <c r="J46" t="n">
+        <v>119.06</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -44252,31 +44252,31 @@
         </is>
       </c>
       <c r="C843" t="n">
-        <v>1352</v>
+        <v>1345</v>
       </c>
       <c r="D843" t="n">
         <v>1495.56</v>
       </c>
       <c r="E843" t="n">
-        <v>-143.56</v>
+        <v>-150.56</v>
       </c>
       <c r="F843" t="n">
-        <v>1363.7</v>
+        <v>1352.8</v>
       </c>
       <c r="G843" t="n">
         <v>1495.56</v>
       </c>
       <c r="H843" t="n">
-        <v>-131.86</v>
+        <v>-142.76</v>
       </c>
       <c r="I843" t="n">
-        <v>1345</v>
+        <v>1336.1</v>
       </c>
       <c r="J843" t="n">
         <v>1294.83</v>
       </c>
       <c r="K843" t="n">
-        <v>50.17</v>
+        <v>41.27</v>
       </c>
       <c r="L843" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         </is>
       </c>
       <c r="N843" t="n">
-        <v>9.6</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="844">
@@ -44304,31 +44304,31 @@
         </is>
       </c>
       <c r="C844" t="n">
-        <v>186</v>
+        <v>186.5</v>
       </c>
       <c r="D844" t="n">
         <v>188.55</v>
       </c>
       <c r="E844" t="n">
-        <v>-2.55</v>
+        <v>-2.05</v>
       </c>
       <c r="F844" t="n">
-        <v>187.74</v>
+        <v>187.5</v>
       </c>
       <c r="G844" t="n">
         <v>189.84</v>
       </c>
       <c r="H844" t="n">
-        <v>-2.1</v>
+        <v>-2.34</v>
       </c>
       <c r="I844" t="n">
-        <v>184.82</v>
+        <v>182.55</v>
       </c>
       <c r="J844" t="n">
         <v>181.02</v>
       </c>
       <c r="K844" t="n">
-        <v>3.8</v>
+        <v>1.53</v>
       </c>
       <c r="L844" t="inlineStr">
         <is>
@@ -44341,7 +44341,7 @@
         </is>
       </c>
       <c r="N844" t="n">
-        <v>1.35</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="845">
@@ -44356,31 +44356,31 @@
         </is>
       </c>
       <c r="C845" t="n">
-        <v>1428.1</v>
+        <v>1403.9</v>
       </c>
       <c r="D845" t="n">
         <v>1431.04</v>
       </c>
       <c r="E845" t="n">
-        <v>-2.94</v>
+        <v>-27.14</v>
       </c>
       <c r="F845" t="n">
-        <v>1452</v>
+        <v>1421.9</v>
       </c>
       <c r="G845" t="n">
         <v>1431.04</v>
       </c>
       <c r="H845" t="n">
-        <v>20.96</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="I845" t="n">
-        <v>1410</v>
+        <v>1391.1</v>
       </c>
       <c r="J845" t="n">
         <v>1355.96</v>
       </c>
       <c r="K845" t="n">
-        <v>54.04</v>
+        <v>35.14</v>
       </c>
       <c r="L845" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         </is>
       </c>
       <c r="N845" t="n">
-        <v>0.21</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="846">
@@ -44408,31 +44408,31 @@
         </is>
       </c>
       <c r="C846" t="n">
-        <v>691.55</v>
+        <v>694.35</v>
       </c>
       <c r="D846" t="n">
         <v>692.4400000000001</v>
       </c>
       <c r="E846" t="n">
-        <v>-0.89</v>
+        <v>1.91</v>
       </c>
       <c r="F846" t="n">
-        <v>699.6</v>
+        <v>696</v>
       </c>
       <c r="G846" t="n">
         <v>692.4400000000001</v>
       </c>
       <c r="H846" t="n">
-        <v>7.16</v>
+        <v>3.56</v>
       </c>
       <c r="I846" t="n">
-        <v>686.5</v>
+        <v>665</v>
       </c>
       <c r="J846" t="n">
         <v>662.24</v>
       </c>
       <c r="K846" t="n">
-        <v>24.26</v>
+        <v>2.76</v>
       </c>
       <c r="L846" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         </is>
       </c>
       <c r="N846" t="n">
-        <v>0.13</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="847">
@@ -44460,31 +44460,31 @@
         </is>
       </c>
       <c r="C847" t="n">
-        <v>122.85</v>
+        <v>123.9</v>
       </c>
       <c r="D847" t="n">
         <v>124.44</v>
       </c>
       <c r="E847" t="n">
-        <v>-1.59</v>
+        <v>-0.54</v>
       </c>
       <c r="F847" t="n">
-        <v>125.09</v>
+        <v>123.9</v>
       </c>
       <c r="G847" t="n">
         <v>124.88</v>
       </c>
       <c r="H847" t="n">
-        <v>0.21</v>
+        <v>-0.98</v>
       </c>
       <c r="I847" t="n">
-        <v>122.48</v>
+        <v>119.62</v>
       </c>
       <c r="J847" t="n">
         <v>119.06</v>
       </c>
       <c r="K847" t="n">
-        <v>3.42</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L847" t="inlineStr">
         <is>
@@ -44497,7 +44497,7 @@
         </is>
       </c>
       <c r="N847" t="n">
-        <v>1.28</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="848">
@@ -44512,31 +44512,31 @@
         </is>
       </c>
       <c r="C848" t="n">
-        <v>6048</v>
+        <v>5880</v>
       </c>
       <c r="D848" t="n">
         <v>6375.72</v>
       </c>
       <c r="E848" t="n">
-        <v>-327.72</v>
+        <v>-495.72</v>
       </c>
       <c r="F848" t="n">
-        <v>6048.5</v>
+        <v>5905.5</v>
       </c>
       <c r="G848" t="n">
         <v>6375.72</v>
       </c>
       <c r="H848" t="n">
-        <v>-327.22</v>
+        <v>-470.22</v>
       </c>
       <c r="I848" t="n">
-        <v>5884</v>
+        <v>5800</v>
       </c>
       <c r="J848" t="n">
         <v>5900.42</v>
       </c>
       <c r="K848" t="n">
-        <v>-16.42</v>
+        <v>-100.42</v>
       </c>
       <c r="L848" t="inlineStr">
         <is>
@@ -44545,11 +44545,11 @@
       </c>
       <c r="M848" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N848" t="n">
-        <v>5.14</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="849">
@@ -44564,31 +44564,31 @@
         </is>
       </c>
       <c r="C849" t="n">
-        <v>2502.6</v>
+        <v>2478</v>
       </c>
       <c r="D849" t="n">
         <v>2537.98</v>
       </c>
       <c r="E849" t="n">
-        <v>-35.38</v>
+        <v>-59.98</v>
       </c>
       <c r="F849" t="n">
-        <v>2527.7</v>
+        <v>2509.5</v>
       </c>
       <c r="G849" t="n">
         <v>2537.98</v>
       </c>
       <c r="H849" t="n">
-        <v>-10.28</v>
+        <v>-28.48</v>
       </c>
       <c r="I849" t="n">
-        <v>2494.2</v>
+        <v>2464</v>
       </c>
       <c r="J849" t="n">
         <v>2365.36</v>
       </c>
       <c r="K849" t="n">
-        <v>128.84</v>
+        <v>98.64</v>
       </c>
       <c r="L849" t="inlineStr">
         <is>
@@ -44601,7 +44601,7 @@
         </is>
       </c>
       <c r="N849" t="n">
-        <v>1.39</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="850">
@@ -44616,31 +44616,31 @@
         </is>
       </c>
       <c r="C850" t="n">
-        <v>2525.6</v>
+        <v>2561.3</v>
       </c>
       <c r="D850" t="n">
         <v>2623.88</v>
       </c>
       <c r="E850" t="n">
-        <v>-98.28</v>
+        <v>-62.58</v>
       </c>
       <c r="F850" t="n">
-        <v>2591.3</v>
+        <v>2562</v>
       </c>
       <c r="G850" t="n">
         <v>2623.88</v>
       </c>
       <c r="H850" t="n">
-        <v>-32.58</v>
+        <v>-61.88</v>
       </c>
       <c r="I850" t="n">
-        <v>2516.6</v>
+        <v>2501.7</v>
       </c>
       <c r="J850" t="n">
         <v>2378.75</v>
       </c>
       <c r="K850" t="n">
-        <v>137.85</v>
+        <v>122.95</v>
       </c>
       <c r="L850" t="inlineStr">
         <is>
@@ -44653,7 +44653,7 @@
         </is>
       </c>
       <c r="N850" t="n">
-        <v>3.75</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="851">
@@ -44668,31 +44668,31 @@
         </is>
       </c>
       <c r="C851" t="n">
-        <v>2165.1</v>
+        <v>2195</v>
       </c>
       <c r="D851" t="n">
         <v>2060.2</v>
       </c>
       <c r="E851" t="n">
-        <v>104.9</v>
+        <v>134.8</v>
       </c>
       <c r="F851" t="n">
-        <v>2215.8</v>
+        <v>2239</v>
       </c>
       <c r="G851" t="n">
         <v>2197.59</v>
       </c>
       <c r="H851" t="n">
-        <v>18.21</v>
+        <v>41.41</v>
       </c>
       <c r="I851" t="n">
-        <v>2165.1</v>
+        <v>2158.9</v>
       </c>
       <c r="J851" t="n">
         <v>2095.04</v>
       </c>
       <c r="K851" t="n">
-        <v>70.06</v>
+        <v>63.86</v>
       </c>
       <c r="L851" t="inlineStr">
         <is>
@@ -44705,7 +44705,7 @@
         </is>
       </c>
       <c r="N851" t="n">
-        <v>5.09</v>
+        <v>6.54</v>
       </c>
     </row>
   </sheetData>
@@ -55096,31 +55096,31 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>6048</v>
+        <v>5880</v>
       </c>
       <c r="D34" t="n">
         <v>6375.72</v>
       </c>
       <c r="E34" t="n">
-        <v>-327.72</v>
+        <v>-495.72</v>
       </c>
       <c r="F34" t="n">
-        <v>6048.5</v>
+        <v>5905.5</v>
       </c>
       <c r="G34" t="n">
         <v>6375.72</v>
       </c>
       <c r="H34" t="n">
-        <v>-327.22</v>
+        <v>-470.22</v>
       </c>
       <c r="I34" t="n">
-        <v>5884</v>
+        <v>5800</v>
       </c>
       <c r="J34" t="n">
         <v>5900.42</v>
       </c>
       <c r="K34" t="n">
-        <v>-16.42</v>
+        <v>-100.42</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -55129,11 +55129,11 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>5.14</v>
+        <v>7.78</v>
       </c>
     </row>
   </sheetData>
@@ -57522,31 +57522,31 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>122.85</v>
+        <v>123.9</v>
       </c>
       <c r="D46" t="n">
         <v>124.44</v>
       </c>
       <c r="E46" t="n">
-        <v>-1.59</v>
+        <v>-0.54</v>
       </c>
       <c r="F46" t="n">
-        <v>125.09</v>
+        <v>123.9</v>
       </c>
       <c r="G46" t="n">
         <v>124.88</v>
       </c>
       <c r="H46" t="n">
-        <v>0.21</v>
+        <v>-0.98</v>
       </c>
       <c r="I46" t="n">
-        <v>122.48</v>
+        <v>119.62</v>
       </c>
       <c r="J46" t="n">
         <v>119.06</v>
       </c>
       <c r="K46" t="n">
-        <v>3.42</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -57559,7 +57559,7 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.28</v>
+        <v>0.43</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Stocks_Validation.xlsx
+++ b/Post_Market_Stocks_Validation.xlsx
@@ -44252,31 +44252,31 @@
         </is>
       </c>
       <c r="C843" t="n">
+        <v>1352</v>
+      </c>
+      <c r="D843" t="n">
+        <v>1225.62</v>
+      </c>
+      <c r="E843" t="n">
+        <v>126.38</v>
+      </c>
+      <c r="F843" t="n">
+        <v>1363.7</v>
+      </c>
+      <c r="G843" t="n">
+        <v>1328.8</v>
+      </c>
+      <c r="H843" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="I843" t="n">
         <v>1345</v>
       </c>
-      <c r="D843" t="n">
-        <v>1495.56</v>
-      </c>
-      <c r="E843" t="n">
-        <v>-150.56</v>
-      </c>
-      <c r="F843" t="n">
-        <v>1352.8</v>
-      </c>
-      <c r="G843" t="n">
-        <v>1495.56</v>
-      </c>
-      <c r="H843" t="n">
-        <v>-142.76</v>
-      </c>
-      <c r="I843" t="n">
-        <v>1336.1</v>
-      </c>
       <c r="J843" t="n">
-        <v>1294.83</v>
+        <v>1334.32</v>
       </c>
       <c r="K843" t="n">
-        <v>41.27</v>
+        <v>10.68</v>
       </c>
       <c r="L843" t="inlineStr">
         <is>
@@ -44285,11 +44285,11 @@
       </c>
       <c r="M843" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N843" t="n">
-        <v>10.07</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="844">
@@ -44304,31 +44304,31 @@
         </is>
       </c>
       <c r="C844" t="n">
-        <v>186.5</v>
+        <v>186</v>
       </c>
       <c r="D844" t="n">
-        <v>188.55</v>
+        <v>185.45</v>
       </c>
       <c r="E844" t="n">
-        <v>-2.05</v>
+        <v>0.55</v>
       </c>
       <c r="F844" t="n">
-        <v>187.5</v>
+        <v>187.74</v>
       </c>
       <c r="G844" t="n">
-        <v>189.84</v>
+        <v>186.74</v>
       </c>
       <c r="H844" t="n">
-        <v>-2.34</v>
+        <v>1</v>
       </c>
       <c r="I844" t="n">
-        <v>182.55</v>
+        <v>184.82</v>
       </c>
       <c r="J844" t="n">
-        <v>181.02</v>
+        <v>186</v>
       </c>
       <c r="K844" t="n">
-        <v>1.53</v>
+        <v>-1.18</v>
       </c>
       <c r="L844" t="inlineStr">
         <is>
@@ -44341,7 +44341,7 @@
         </is>
       </c>
       <c r="N844" t="n">
-        <v>1.09</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="845">
@@ -44352,35 +44352,35 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C845" t="n">
-        <v>1403.9</v>
+        <v>122.85</v>
       </c>
       <c r="D845" t="n">
-        <v>1431.04</v>
+        <v>123.29</v>
       </c>
       <c r="E845" t="n">
-        <v>-27.14</v>
+        <v>-0.44</v>
       </c>
       <c r="F845" t="n">
-        <v>1421.9</v>
+        <v>125.09</v>
       </c>
       <c r="G845" t="n">
-        <v>1431.04</v>
+        <v>123.29</v>
       </c>
       <c r="H845" t="n">
-        <v>-9.140000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="I845" t="n">
-        <v>1391.1</v>
+        <v>122.48</v>
       </c>
       <c r="J845" t="n">
-        <v>1355.96</v>
+        <v>122.7</v>
       </c>
       <c r="K845" t="n">
-        <v>35.14</v>
+        <v>-0.22</v>
       </c>
       <c r="L845" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         </is>
       </c>
       <c r="N845" t="n">
-        <v>1.9</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="846">
@@ -44408,31 +44408,31 @@
         </is>
       </c>
       <c r="C846" t="n">
-        <v>694.35</v>
+        <v>691.55</v>
       </c>
       <c r="D846" t="n">
-        <v>692.4400000000001</v>
+        <v>699</v>
       </c>
       <c r="E846" t="n">
-        <v>1.91</v>
+        <v>-7.45</v>
       </c>
       <c r="F846" t="n">
-        <v>696</v>
+        <v>699.6</v>
       </c>
       <c r="G846" t="n">
-        <v>692.4400000000001</v>
+        <v>699</v>
       </c>
       <c r="H846" t="n">
-        <v>3.56</v>
+        <v>0.6</v>
       </c>
       <c r="I846" t="n">
-        <v>665</v>
+        <v>686.5</v>
       </c>
       <c r="J846" t="n">
-        <v>662.24</v>
+        <v>682.4400000000001</v>
       </c>
       <c r="K846" t="n">
-        <v>2.76</v>
+        <v>4.06</v>
       </c>
       <c r="L846" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         </is>
       </c>
       <c r="N846" t="n">
-        <v>0.28</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="847">
@@ -44456,35 +44456,35 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="C847" t="n">
-        <v>123.9</v>
+        <v>1428.1</v>
       </c>
       <c r="D847" t="n">
-        <v>124.44</v>
+        <v>1412.21</v>
       </c>
       <c r="E847" t="n">
-        <v>-0.54</v>
+        <v>15.89</v>
       </c>
       <c r="F847" t="n">
-        <v>123.9</v>
+        <v>1452</v>
       </c>
       <c r="G847" t="n">
-        <v>124.88</v>
+        <v>1412.21</v>
       </c>
       <c r="H847" t="n">
-        <v>-0.98</v>
+        <v>39.79</v>
       </c>
       <c r="I847" t="n">
-        <v>119.62</v>
+        <v>1410</v>
       </c>
       <c r="J847" t="n">
-        <v>119.06</v>
+        <v>1397.31</v>
       </c>
       <c r="K847" t="n">
-        <v>0.5600000000000001</v>
+        <v>12.69</v>
       </c>
       <c r="L847" t="inlineStr">
         <is>
@@ -44497,7 +44497,7 @@
         </is>
       </c>
       <c r="N847" t="n">
-        <v>0.43</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="848">
@@ -44512,31 +44512,31 @@
         </is>
       </c>
       <c r="C848" t="n">
-        <v>5880</v>
+        <v>6048</v>
       </c>
       <c r="D848" t="n">
-        <v>6375.72</v>
+        <v>5622.39</v>
       </c>
       <c r="E848" t="n">
-        <v>-495.72</v>
+        <v>425.61</v>
       </c>
       <c r="F848" t="n">
-        <v>5905.5</v>
+        <v>6048.5</v>
       </c>
       <c r="G848" t="n">
-        <v>6375.72</v>
+        <v>6086.5</v>
       </c>
       <c r="H848" t="n">
-        <v>-470.22</v>
+        <v>-38</v>
       </c>
       <c r="I848" t="n">
-        <v>5800</v>
+        <v>5884</v>
       </c>
       <c r="J848" t="n">
-        <v>5900.42</v>
+        <v>6048</v>
       </c>
       <c r="K848" t="n">
-        <v>-100.42</v>
+        <v>-164</v>
       </c>
       <c r="L848" t="inlineStr">
         <is>
@@ -44549,7 +44549,7 @@
         </is>
       </c>
       <c r="N848" t="n">
-        <v>7.78</v>
+        <v>7.57</v>
       </c>
     </row>
     <row r="849">
@@ -44564,31 +44564,31 @@
         </is>
       </c>
       <c r="C849" t="n">
-        <v>2478</v>
+        <v>2502.6</v>
       </c>
       <c r="D849" t="n">
-        <v>2537.98</v>
+        <v>2463.01</v>
       </c>
       <c r="E849" t="n">
-        <v>-59.98</v>
+        <v>39.59</v>
       </c>
       <c r="F849" t="n">
-        <v>2509.5</v>
+        <v>2527.7</v>
       </c>
       <c r="G849" t="n">
-        <v>2537.98</v>
+        <v>2463.01</v>
       </c>
       <c r="H849" t="n">
-        <v>-28.48</v>
+        <v>64.69</v>
       </c>
       <c r="I849" t="n">
-        <v>2464</v>
+        <v>2494.2</v>
       </c>
       <c r="J849" t="n">
-        <v>2365.36</v>
+        <v>2437.51</v>
       </c>
       <c r="K849" t="n">
-        <v>98.64</v>
+        <v>56.69</v>
       </c>
       <c r="L849" t="inlineStr">
         <is>
@@ -44601,7 +44601,7 @@
         </is>
       </c>
       <c r="N849" t="n">
-        <v>2.36</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="850">
@@ -44616,31 +44616,31 @@
         </is>
       </c>
       <c r="C850" t="n">
-        <v>2561.3</v>
+        <v>2525.6</v>
       </c>
       <c r="D850" t="n">
-        <v>2623.88</v>
+        <v>2485.08</v>
       </c>
       <c r="E850" t="n">
-        <v>-62.58</v>
+        <v>40.52</v>
       </c>
       <c r="F850" t="n">
-        <v>2562</v>
+        <v>2591.3</v>
       </c>
       <c r="G850" t="n">
-        <v>2623.88</v>
+        <v>2485.08</v>
       </c>
       <c r="H850" t="n">
-        <v>-61.88</v>
+        <v>106.22</v>
       </c>
       <c r="I850" t="n">
-        <v>2501.7</v>
+        <v>2516.6</v>
       </c>
       <c r="J850" t="n">
-        <v>2378.75</v>
+        <v>2451.31</v>
       </c>
       <c r="K850" t="n">
-        <v>122.95</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="L850" t="inlineStr">
         <is>
@@ -44653,7 +44653,7 @@
         </is>
       </c>
       <c r="N850" t="n">
-        <v>2.39</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="851">
@@ -44668,31 +44668,31 @@
         </is>
       </c>
       <c r="C851" t="n">
-        <v>2195</v>
+        <v>2165.1</v>
       </c>
       <c r="D851" t="n">
-        <v>2060.2</v>
+        <v>2325.22</v>
       </c>
       <c r="E851" t="n">
-        <v>134.8</v>
+        <v>-160.12</v>
       </c>
       <c r="F851" t="n">
-        <v>2239</v>
+        <v>2215.8</v>
       </c>
       <c r="G851" t="n">
-        <v>2197.59</v>
+        <v>2325.22</v>
       </c>
       <c r="H851" t="n">
-        <v>41.41</v>
+        <v>-109.42</v>
       </c>
       <c r="I851" t="n">
-        <v>2158.9</v>
+        <v>2165.1</v>
       </c>
       <c r="J851" t="n">
-        <v>2095.04</v>
+        <v>2158.94</v>
       </c>
       <c r="K851" t="n">
-        <v>63.86</v>
+        <v>6.16</v>
       </c>
       <c r="L851" t="inlineStr">
         <is>
@@ -44705,7 +44705,7 @@
         </is>
       </c>
       <c r="N851" t="n">
-        <v>6.54</v>
+        <v>6.89</v>
       </c>
     </row>
   </sheetData>
@@ -55096,31 +55096,31 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5880</v>
+        <v>6048</v>
       </c>
       <c r="D34" t="n">
-        <v>6375.72</v>
+        <v>5622.39</v>
       </c>
       <c r="E34" t="n">
-        <v>-495.72</v>
+        <v>425.61</v>
       </c>
       <c r="F34" t="n">
-        <v>5905.5</v>
+        <v>6048.5</v>
       </c>
       <c r="G34" t="n">
-        <v>6375.72</v>
+        <v>6086.5</v>
       </c>
       <c r="H34" t="n">
-        <v>-470.22</v>
+        <v>-38</v>
       </c>
       <c r="I34" t="n">
-        <v>5800</v>
+        <v>5884</v>
       </c>
       <c r="J34" t="n">
-        <v>5900.42</v>
+        <v>6048</v>
       </c>
       <c r="K34" t="n">
-        <v>-100.42</v>
+        <v>-164</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -55133,7 +55133,7 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>7.78</v>
+        <v>7.57</v>
       </c>
     </row>
   </sheetData>
@@ -57522,31 +57522,31 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>123.9</v>
+        <v>122.85</v>
       </c>
       <c r="D46" t="n">
-        <v>124.44</v>
+        <v>123.29</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.54</v>
+        <v>-0.44</v>
       </c>
       <c r="F46" t="n">
-        <v>123.9</v>
+        <v>125.09</v>
       </c>
       <c r="G46" t="n">
-        <v>124.88</v>
+        <v>123.29</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.98</v>
+        <v>1.8</v>
       </c>
       <c r="I46" t="n">
-        <v>119.62</v>
+        <v>122.48</v>
       </c>
       <c r="J46" t="n">
-        <v>119.06</v>
+        <v>122.7</v>
       </c>
       <c r="K46" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.22</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -57559,7 +57559,7 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0.43</v>
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>
